--- a/Main_project/master_qualified_leads.xlsx
+++ b/Main_project/master_qualified_leads.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$AR$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$AW$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR47"/>
+  <dimension ref="A1:AW96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -444,7 +444,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="37" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
@@ -476,6 +476,11 @@
     <col width="14" customWidth="1" min="42" max="42"/>
     <col width="34" customWidth="1" min="43" max="43"/>
     <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="7" customWidth="1" min="48" max="48"/>
+    <col width="16" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -699,6 +704,31 @@
           <t>last_seen_at</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>phone_e164</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pincode</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>contacted_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -881,6 +911,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1059,6 +1094,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1233,6 +1273,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1415,6 +1460,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1597,6 +1647,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1771,6 +1826,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1949,6 +2009,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2123,6 +2188,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2301,6 +2371,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2479,6 +2554,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2661,6 +2741,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2835,6 +2920,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3009,6 +3099,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3191,6 +3286,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3369,6 +3469,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3543,6 +3648,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3725,6 +3835,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3903,6 +4018,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4089,6 +4209,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4267,6 +4392,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4441,6 +4571,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4619,6 +4754,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4797,6 +4937,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4975,6 +5120,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5161,6 +5311,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5343,6 +5498,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5525,6 +5685,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5707,6 +5872,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5885,6 +6055,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -6059,6 +6234,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -6241,6 +6421,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -6419,6 +6604,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -6593,6 +6783,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -6771,6 +6966,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6945,6 +7145,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -7119,6 +7324,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -7297,6 +7507,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -7475,6 +7690,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -7653,6 +7873,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -7827,6 +8052,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -8001,6 +8231,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -8179,6 +8414,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -8349,6 +8589,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -8527,6 +8772,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -8701,6 +8951,11 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8875,9 +9130,8673 @@
           <t>2026-10-07T14:58:22.068016+00:00</t>
         </is>
       </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/SLAM+Nolambur/data=!4m7!3m6!1s0x3a52632b4b679da1:0x85f381547317f78b!8m2!3d13.0836824!4d80.1702226!16s%2Fg%2F11gxxsyh_4!19sChIJoZ1nSytjUjoRi_cXc1SB84U</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SLAM Nolambur</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2nd Floor, Plot no 2/4, Kambar St, opp. Reliance Digital, Nolambur, Chennai, Tamil Nadu 600037</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–11 pm"],"Monday":["5:30 am–11 pm"],"Saturday":["5:30 am–11 pm"],"Sunday":["5:30 am–11 pm"],"Thursday":["5:30 am–11 pm"],"Tuesday":["5:30 am–11 pm"],"Wednesday":["5:30 am–11 pm"]}</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>097906 66616</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>35MC+F3 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1686</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>{"1":32,"2":1,"3":13,"4":88,"5":1552}</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>13.083682</v>
+      </c>
+      <c r="R48" t="n">
+        <v>80.17022299999999</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>9652200626093291403</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeeoOYkeHnY2jf27WAg4zSTPbLScBcu1QtnMcq7ltZiO6Og3wtgBcSG-qPBLXnCuObFALRptug8iPS4Y9P0fbTiIBFgmXw4n0pVW-axfyeKAe9C4zGh6N3zwvQUMPIi-s1vb-0BOw=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>0x3a52632b4b679da1:0x85f381547317f78b</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>ChIJoZ1nSytjUjoRi_cXc1SB84U</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[{"link":"https://shop.zuyyu.com/a124398b-8809-4e04-a12c-bbee3ca10916/menu?rwg_token=AE37R_jvJ0KKHN3YzOFaonQbD2Z3ldjvF68Lq6TZo_ztAPbsQMcQEf5r7k4vRbVmFUUiYE8hJH1J7HXMcWYeNSFxWc7rbRilYvB2prfC-CfXv0EgB4_pgYA%3D","source":"zuyyu.com"}]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>{"id":"111361832002855286726","name":"SLAM Nolambur (Owner)","link":"https://www.google.com/maps/contrib/111361832002855286726"}</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>{"borough":"Nolambur","street":"2nd Floor, Plot no 2/4, Kambar St, opp. Reliance Digital","city":"Chennai","postal_code":"600037","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>[{"Name":"dhamu J","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX_uIe9aFmpaEUBCoV2QvAJAjyjLtyD38z-Ki8vUwg_eM8Y4QCofQ=s120-c-rp-mo-br100","Rating":4,"Description":"I had a good experience at slam gym.The gym is well maintained and has a wide range of modern equipment for strength training and cardio.\nPT trainer kishore is an excellent trainer who trained me. He explains every exercise clearly,pays close attention to proper form and creates workout plans based on the individual fitness goal.His guidance has made my workouts more effective and enjoyable.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21aeldWQk1XWFJZYkVGRFR5MHdOMWREZGw5TFNtYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/113415454601396340564/reviews?hl=en-GB","posted_at_unix_micros":1784442384401760,"updated_at_unix_micros":1784442384401760,"language":"en","translated_lang":"","text_original":"I had a good experience at slam gym.The gym is well maintained and has a wide range of modern equipment for strength training and cardio.\nPT trainer kishore is an excellent trainer who trained me. He explains every exercise clearly,pays close attention to proper form and creates workout plans based on the individual fitness goal.His guidance has made my workouts more effective and enjoyable.","text_translated":"","reply_text_original":"Hi Dhamu sir. Thanks for a great review. We are truly grateful for your support and motivation. Feedback like yours boosts our confidence and helps us improve ourselves. Please keep coming regularly and keep sharing your suggestions with us.\n","reply_language":"en","reply_posted_at_unix_micros":1785511004000000,"reply_updated_at_unix_micros":1785511004000000,"published_at":"2026-07-19T06:26:24.40176Z"},{"Name":"Sathiesh Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIKdDD_TO1XoA6qqtelnGBQu3WBp5j33hMMiPuYUO8SWA4kCw=s120-c-rp-mo-br100","Rating":5,"Description":"The ambiance is very good, gym coaches are very patient and compassionate. Equipments are very well maintained. Very much recommended","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcRgm3eHhe9AnHlWcBN48NNtBChwGHWCTUwroMbWLaXD4anpvB0AnFMs1R1JKNaHWZn9Nm5GWRPepw3Yld3Wb5XBKJ6ejhmJjTwXLbVNvGWVaBZB8-HgJc40X_3BMr4gKUmLhAizufyeRv1=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfsNecz2zJj-NwskgVaP4sGnPVsyxBMXqU-E2ZYOH81MEcBQQE702-S37t7BGKmSyf-XQLZjYWd7yv8ARawCT2mMLBoeszaZ_UijM5eOOjaSX9mLZ8kST84kqI2laHlOSu5znOzM6lSK9A=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25KVk5IcGhVR0pIZWpOblZXOVNOV2R4VTJkYVNFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117900099227190945875/reviews?hl=en-GB","posted_at_unix_micros":1782219655449879,"updated_at_unix_micros":1782219655449879,"language":"en","translated_lang":"","text_original":"The ambiance is very good, gym coaches are very patient and compassionate. Equipments are very well maintained. Very much recommended","text_translated":"","reply_text_original":"Hi Sathiesh. Thanks for a great review. We are truly grateful for your support and motivation. Feedback like yours boosts our confidence and helps us improve ourselves. Please keep coming regularly and keep sharing your suggestions with us.","reply_language":"en","reply_posted_at_unix_micros":1785667021000000,"reply_updated_at_unix_micros":1785667021000000,"published_at":"2026-06-23T13:00:55.449879Z"},{"Name":"sathya sugumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXR2_XRwDUmd4MRsMkQgjFwJqlPbb8LVr2GV1vQ3jMaeI2I43_Dcg=s120-c-rp-mo-br100","Rating":5,"Description":"Joining this gym has been one of the best decisions for my fitness journey. The environment is very positive, clean, and motivating.\nSpecial thanks to trainer Elavarasan for his constant support, guidance, and encouragement throughout the workouts. His training style is professional, friendly, and really helps build confidence and discipline.\nHighly recommended for anyone looking to stay fit and motivated💪✨.....","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25Kdk9EWTJZbTE0ZFhkZk5FeG9ka3hFT0ZSWVFrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114891383813495482299/reviews?hl=en-GB","posted_at_unix_micros":1779631457177711,"updated_at_unix_micros":1779631457177711,"language":"en","translated_lang":"","text_original":"Joining this gym has been one of the best decisions for my fitness journey. The environment is very positive, clean, and motivating.\nSpecial thanks to trainer Elavarasan for his constant support, guidance, and encouragement throughout the workouts. His training style is professional, friendly, and really helps build confidence and discipline.\nHighly recommended for anyone looking to stay fit and motivated💪✨.....","text_translated":"","reply_text_original":"Hi Sathya. Thanks for a great review. We are truly grateful for your support and motivation. Feedback like yours boosts our confidence and helps us improve ourselves. Please keep coming regularly and keep sharing your suggestions with us.","reply_language":"en","reply_posted_at_unix_micros":1785667545000000,"reply_updated_at_unix_micros":1785667545000000,"published_at":"2026-05-24T14:04:17.177711Z"},{"Name":"J.P. Rajeswari","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVZHktgB9Xktmt_51y0wG0OKOsDBcG3N23C7NEztyE8h-x8FrQ4jA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I've had a great experience training with Mr. Clinton. He is knowledgeable, patient, and always motivates me to push my limits while ensuring I maintain the correct form during every exercise. His personalized workout plans and guidance have helped me stay consistent and make steady progress toward my fitness goals.\n\nHe's friendly, approachable, and genuinely cares about his clients' improvement. I highly recommend Mr. Clinton to anyone looking for a dedicated and professional personal trainer.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25JeVQwSm1lVFpNUzE5TmExQXplVTVSUjNReE9VRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115743565174473589277/reviews?hl=en-GB","posted_at_unix_micros":1784944043822006,"updated_at_unix_micros":1784944043822006,"language":"en","translated_lang":"","text_original":"I've had a great experience training with Mr. Clinton. He is knowledgeable, patient, and always motivates me to push my limits while ensuring I maintain the correct form during every exercise. His personalized workout plans and guidance have helped me stay consistent and make steady progress toward my fitness goals.\n\nHe's friendly, approachable, and genuinely cares about his clients' improvement. I highly recommend Mr. Clinton to anyone looking for a dedicated and professional personal trainer.","text_translated":"","reply_text_original":"Hi Rajeswari mam. Thanks for a great review. We are truly grateful for your support and motivation. Feedback like yours boosts our confidence and helps us improve ourselves. Please keep coming regularly and keep sharing your suggestions with us.\n","reply_language":"en","reply_posted_at_unix_micros":1785510040000000,"reply_updated_at_unix_micros":1785510040000000,"published_at":"2026-07-25T01:47:23.822006Z"},{"Name":"Gokula Mithran","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX4GeLA7EHkbfrHTdLYDrI7Xp0GCjIxne8UAoOTextCSAzjWl4=s120-c-rp-mo-br100","Rating":5,"Description":"“I’ve had a great experience at this gym. The equipment is well maintained, the environment is clean, and the trainers provide proper guidance with attention to form and technique. Highly recommended for anyone serious about fitness.”“Training under R. Mani has been a game changer for me! His dedication, discipline, and encouragement push me to give my best every day. Truly grateful to have such an inspiring trainer 💪🔥”","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tONlJ5MVlPRWR0YXpkSVVHa3hkR0ZMUTA5RlkzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118347309128717067241/reviews?hl=en-GB","posted_at_unix_micros":1772286745849391,"updated_at_unix_micros":1772286745849391,"language":"en","translated_lang":"","text_original":"“I’ve had a great experience at this gym. The equipment is well maintained, the environment is clean, and the trainers provide proper guidance with attention to form and technique. Highly recommended for anyone serious about fitness.”“Training under R. Mani has been a game changer for me! His dedication, discipline, and encouragement push me to give my best every day. Truly grateful to have such an inspiring trainer 💪🔥”","text_translated":"","reply_text_original":"Hi Gokula. Thanks for a great review. We are truly grateful for your support and motivation. Feedback like yours boosts our confidence and helps us improve ourselves. Please keep coming regularly and keep sharing your suggestions with us.","reply_language":"en","reply_posted_at_unix_micros":1773656605000000,"reply_updated_at_unix_micros":1773656605000000,"published_at":"2026-02-28T13:52:25.849391Z"}]</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Transform+365+CrossFit+%26+Fitness+Studio/data=!4m7!3m6!1s0x3a526fda6f559d37:0xa9bd78485de02166!8m2!3d13.118269!4d80.284706!16s%2Fg%2F11rx1gl3fb!19sChIJN51Vb9pvUjoRZiHgXUh4vak</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Transform 365 CrossFit &amp; Fitness Studio</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>744, Thiruvottiyur High Rd, Korukkupet, Old Washermanpet, Chennai, Tamil Nadu 600021</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–1 am"],"Monday":["5:30 am–1 am"],"Saturday":["5:30 am–1 am"],"Sunday":["7 am–1 am"],"Thursday":["5:30 am–1 am"],"Tuesday":["5:30 am–1 am"],"Wednesday":["5:30 am–1 am"]}</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>093602 21055</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>479M+8V Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1162</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>{"1":20,"2":6,"3":3,"4":48,"5":1085}</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>13.118269</v>
+      </c>
+      <c r="R49" t="n">
+        <v>80.284706</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>12231064415216083302</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLduIRI5wlQk-l_IxIeorEDWu7oRM6x6NdQJmqtlMoSrAL3dk4z_ysLX-M4DNhIBZd-eDFkV4sKIs2GQZQDQq2a7KYyt4Bca81E27BzJERSK8mVOK3PnANLb0Yi2PTW1vPYLTWyq=w408-h398-k-no</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>0x3a526fda6f559d37:0xa9bd78485de02166</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>ChIJN51Vb9pvUjoRZiHgXUh4vak</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>{"id":"116135102080763264965","name":"Transform 365 CrossFit \u0026 Fitness Studio (Owner)","link":"https://www.google.com/maps/contrib/116135102080763264965"}</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>{"borough":"Korukkupet, Old Washermanpet","street":"744, Thiruvottiyur High Rd","city":"Chennai","postal_code":"600021","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>[{"Name":"pranav k","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVfjHcbjz6sgQHu5Haox8bxlXEu0A5EPoWCGyWbfyZ1trypotki=s120-c-rp-mo-br100","Rating":5,"Description":"I've been training at this gym for the past 3 years, and my experience has been excellent. The gym is always clean, well-maintained, and hygienic, which creates a comfortable workout environment. The equipment is regularly cleaned and organized, and the overall atmosphere is motivating. Highly recommended for anyone looking for a clean and professional gym to train in.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25CVmQyTTVWamRLZVdneWIxTnhUWFZVZDAxS1FVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118167290596311058826/reviews?hl=en-GB","posted_at_unix_micros":1780291555492144,"updated_at_unix_micros":1780291555492144,"language":"en","translated_lang":"","text_original":"I've been training at this gym for the past 3 years, and my experience has been excellent. The gym is always clean, well-maintained, and hygienic, which creates a comfortable workout environment. The equipment is regularly cleaned and organized, and the overall atmosphere is motivating. Highly recommended for anyone looking for a clean and professional gym to train in.","text_translated":"","published_at":"2026-06-01T05:25:55.492144Z"},{"Name":"Cathis Mata","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIyGD-xaG27kfto0wVLVEtTzuf7BbjpWDGZ-E3lJFo64nfSCw=s120-c-rp-mo-br100","Rating":1,"Description":"This is one of the finest and most affordable gyms in North Chennai. The infrastructure, equipment, cleanliness, and overall setup are truly impressive considering the pricing.\n\n🏋️‍♂️ Three floors, including a dedicated leg workout floor\n❄️ Air conditioning consistently maintained\n💪 Wide variety of workout machines and exercise options\n🔥 Dedicated CrossFit area\n❤️ Extensive cardio equipment\n🚺 Separate women’s workout area\n🚻 Well-maintained restrooms\n🏍️ Ample parking space\n🌙 Open until nearly midnight, including Sundays\n\nFor experienced fitness enthusiasts, this gym is undoubtedly among the best options in Chennai within this budget range.\n\nHowever, one major issue negatively impacts the overall experience — the lack of trainer involvement on the workout floor.\n\nEven though the gym employs several trainers, they are frequently seen sitting near the reception area talking among themselves instead of actively monitoring members on the workout floors. Especially during peak hours, trainers should remain present on the floor at all times to guide members, assist with spotting, correct improper exercise form, and maintain safety standards.\n\nThe responsibility of a trainer should not be restricted only to personal training clients. Trainers must be approachable and willing to help all members, particularly beginners who may unknowingly perform exercises incorrectly and increase the risk of serious injury.\n\nOn many occasions, members are forced to help each other because trainers are unavailable when needed. Furthermore, during crowded hours, trainers should avoid using gym equipment for their own workouts while members are waiting.\n\nThis gym has the potential to become one of the top fitness centers in Chennai. The infrastructure already deserves a perfect 5/5 rating — only the trainer engagement and floor supervision need serious improvement.\n\nHopefully, the management will take this as constructive criticism and ensure that trainers remain actively involved on the workout floor while properly supporting members. This single change would greatly improve the overall gym experience.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25CTFIwUmllREpJVldGU2FpMVVlSEZGYkc0NVYyYxAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/103130367600158210762/reviews?hl=en-GB","posted_at_unix_micros":1780041148732481,"updated_at_unix_micros":1780041563183546,"language":"en","translated_lang":"","text_original":"This is one of the finest and most affordable gyms in North Chennai. The infrastructure, equipment, cleanliness, and overall setup are truly impressive considering the pricing.\n\n🏋️‍♂️ Three floors, including a dedicated leg workout floor\n❄️ Air conditioning consistently maintained\n💪 Wide variety of workout machines and exercise options\n🔥 Dedicated CrossFit area\n❤️ Extensive cardio equipment\n🚺 Separate women’s workout area\n🚻 Well-maintained restrooms\n🏍️ Ample parking space\n🌙 Open until nearly midnight, including Sundays\n\nFor experienced fitness enthusiasts, this gym is undoubtedly among the best options in Chennai within this budget range.\n\nHowever, one major issue negatively impacts the overall experience — the lack of trainer involvement on the workout floor.\n\nEven though the gym employs several trainers, they are frequently seen sitting near the reception area talking among themselves instead of actively monitoring members on the workout floors. Especially during peak hours, trainers should remain present on the floor at all times to guide members, assist with spotting, correct improper exercise form, and maintain safety standards.\n\nThe responsibility of a trainer should not be restricted only to personal training clients. Trainers must be approachable and willing to help all members, particularly beginners who may unknowingly perform exercises incorrectly and increase the risk of serious injury.\n\nOn many occasions, members are forced to help each other because trainers are unavailable when needed. Furthermore, during crowded hours, trainers should avoid using gym equipment for their own workouts while members are waiting.\n\nThis gym has the potential to become one of the top fitness centers in Chennai. The infrastructure already deserves a perfect 5/5 rating — only the trainer engagement and floor supervision need serious improvement.\n\nHopefully, the management will take this as constructive criticism and ensure that trainers remain actively involved on the workout floor while properly supporting members. This single change would greatly improve the overall gym experience.","text_translated":"","reply_text_original":"Dear sir,\n\nTrainers are available in the floor. General trainers are always instructed to teach the clients who ask for doubts. Any thanks for your feedback. Will take it up seriously. ","reply_language":"en","reply_posted_at_unix_micros":1780404473000000,"reply_updated_at_unix_micros":1780404473000000,"published_at":"2026-05-29T07:52:28.732481Z"},{"Name":"Swathi Lakshmi","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKUKapKlmAfqZMbsQh9KeaWoOZDFV2MZjcyDuOFytJAfX5Bew=s120-c-rp-mo-br100","Rating":5,"Description":"As someone who recently joined, I felt comfortable from day one. The staff is very supportive, and the trainers explain exercises patiently. The equipment is excellent, and the overall atmosphere keeps me motivated to stay consistent. Definitely worth joining!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s1clNHTnBXRVp3WDBwR1FteERVa1ZuYXpRdFFrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104665549278494539437/reviews?hl=en-GB","posted_at_unix_micros":1782873718479461,"updated_at_unix_micros":1782873718479461,"language":"en","translated_lang":"","text_original":"As someone who recently joined, I felt comfortable from day one. The staff is very supportive, and the trainers explain exercises patiently. The equipment is excellent, and the overall atmosphere keeps me motivated to stay consistent. Definitely worth joining!","text_translated":"","published_at":"2026-07-01T02:41:58.479461Z"},{"Name":"Aarthi Arun Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWLN-_kNneOxVbhHbbxhUaFBR-HiTgzEsURYq0ViOaNqqoZZbU=s120-c-rp-mo-br100","Rating":4,"Description":"I've been working out here for the last five months, and the thing I love most is the atmosphere. The gym is spacious, well-equipped, and has friendly trainers. It also provides a dedicated area for women to ensure privacy, along with a well-organized floor layout that caters to different fitness needs.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xNMFExOVlYMVJ0V0hkMU1GYzJNbkJZTFUxNlFYYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/106177367753461761860/reviews?hl=en-GB","posted_at_unix_micros":1780289017286082,"updated_at_unix_micros":1780289017286082,"language":"en","translated_lang":"","text_original":"I've been working out here for the last five months, and the thing I love most is the atmosphere. The gym is spacious, well-equipped, and has friendly trainers. It also provides a dedicated area for women to ensure privacy, along with a well-organized floor layout that caters to different fitness needs.","text_translated":"","published_at":"2026-06-01T04:43:37.286082Z"},{"Name":"Premika Dhanasekaran","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV-jOK1FtuK37zybFUNrzGS6td55zAzMvudLxc5CpKHp8dqV64=s120-c-rp-mo-br100","Rating":5,"Description":"Joined this gym recently and I’m really happy with my decision. The atmosphere is motivating, the equipment is well maintained, and the trainers are friendly and supportive. It’s a great place for anyone looking to start or continue their fitness journey. Highly recommended!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25JM1pFTnRUVzlVTUZKS1VreHpVelV6Y1dsUVoxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116239331365557016842/reviews?hl=en-GB","posted_at_unix_micros":1782873616639531,"updated_at_unix_micros":1782873616639531,"language":"en","translated_lang":"","text_original":"Joined this gym recently and I’m really happy with my decision. The atmosphere is motivating, the equipment is well maintained, and the trainers are friendly and supportive. It’s a great place for anyone looking to start or continue their fitness journey. Highly recommended!","text_translated":"","published_at":"2026-07-01T02:40:16.639531Z"}]</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>(1★) Cathis Mata: This is one of the finest and most affordable gyms in North Chennai. The infrastructure, equipment, cleanliness, and overall setup are truly impressive considering the pricing. 🏋️‍♂️ Three floors, including a dedicated leg workout floor ❄️ Air conditioning consistently maintained 💪 Wide variety of workout machines and exercise options 🔥 Dedicated CrossFit area ❤️ Extensive cardio equipment 🚺 Separate women’s workout area 🚻 Well-maintained restrooms 🏍️ Ample parking space 🌙 Open until nearly midnight, including Sundays For experienced fitness enthusiasts, this gym is undoubtedly among the best options in Chennai within this budget range. However, one major issue negatively impacts the overall experience — the lack of trainer involvement on the workout floor. Even though the gym employs several trainers, they are frequently seen sitting near the reception area talking among themselves instead of actively monitoring members on the workout floors. Especially during peak hours, trainers should remain present on the floor at all times to guide members, assist with spotting, correct improper exercise form, and maintain safety standards. The responsibility of a trainer should not be restricted only to personal training clients. Trainers must be approachable and willing to help all members, particularly beginners who may unknowingly perform exercises incorrectly and increase the risk of serious injury. On many occasions, members are forced to help each other because trainers are unavailable when needed. Furthermore, during crowded hours, trainers should avoid using gym equipment for their own workouts while members are waiting. This gym has the potential to become one of the top fitness centers in Chennai. The infrastructure already deserves a perfect 5/5 rating — only the trainer engagement and floor supervision need serious improvement. Hopefully, the management will take this as constructive criticism and ensure that trainers remain actively involved on the workout floor while properly supporting members. This single change would greatly improve the overall gym experience.</t>
+        </is>
+      </c>
+      <c r="AO49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Slam+Lifestyle+and+Fitness+Studio+-+Saligramam/data=!4m7!3m6!1s0x3a52676ef35580db:0x62f61b6002d1cf7a!8m2!3d13.0552821!4d80.2040429!16s%2Fg%2F11r41b92kr!19sChIJ24BV825nUjoRes_RAmAb9mI</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Slam Lifestyle and Fitness Studio - Saligramam</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1st &amp; 2nd Floor, Slam Lifestyle and Fitness Studio - Saligramam, 47, Arunachalam Rd, Mathiazhagan Nagar, Shanthi Nagar, Saligramam, Chennai, Tamil Nadu 600093</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–10:30 pm"],"Monday":["5 am–10:30 pm"],"Saturday":["5 am–10 pm"],"Sunday":["5 am–10 pm"],"Thursday":["5 am–10:30 pm"],"Tuesday":["5 am–10:30 pm"],"Wednesday":["5 am–10:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>096000 23834</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>3643+4J Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>674</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>{"1":34,"2":3,"3":6,"4":57,"5":574}</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>13.055282</v>
+      </c>
+      <c r="R50" t="n">
+        <v>80.204043</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>7130917159165874042</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfPtg_z90r716ohv3amTTkEhWKcGM145TCHAjmn-glfMMWwqyz7Qlvmm1o2gunWzXnrjctuKUh1LNcEXMmzfURC5dP48D0mlKQw6WP4UETXCneXM8GQqHe9a1Fb2RyIsKs5UmPc=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>0x3a52676ef35580db:0x62f61b6002d1cf7a</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>ChIJ24BV825nUjoRes_RAmAb9mI</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[{"link":"https://shop.zuyyu.com/6eadfa01-f983-4584-bf0c-926e1abfe1b4/menu?rwg_token=AE37R_go2hN9ifCqC1BMt_amSfaTn3v_jGb3BhuJtsINmRwuIbcAttTiX4v0ppBqNmtT9QSEx_uTS6wOXH1l1qMGB5lfvJv5ayVqIshvD6gSN9ngICd2wlc%3D","source":"zuyyu.com"}]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>{"id":"114803246856530192590","name":"Slam Lifestyle and Fitness Studio - Saligramam (Owner)","link":"https://www.google.com/maps/contrib/114803246856530192590"}</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>{"borough":"Mathiazhagan Nagar, Shanthi Nagar, Saligramam","street":"1st \u0026 2nd Floor, 47, Arunachalam Rd","city":"Chennai","postal_code":"600093","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>[{"Name":"J Kishore senthil raj","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVdfx9nz6T98m38_uicHdufmTClqXeAvmyox5IX4R6AiftmUjNV=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"My starting weight was 102.6 reduced to 85.1. Losing 17.5 kg has been one of the most rewarding journeys of my life, and I owe a big part of it to my gym, SLAM Lifestyle and Fitness Studio.\nA special thanks to my trainer, Muni Master, whose guidance and dedication made all the difference. From day one, he was supportive, knowledgeable, and genuinely invested in my progress. The workout plans were well-structured, progressive, and tailored to my goals. His constant motivation and accountability kept me going even on the toughest days.\nThe environment at SLAM Saligramam is energetic and positive, making it easier to stay consistent. Clean facilities, quality equipment, and a great fitness community made every session something to look forward to.\nThis transformation wasn’t just physical—it improved my confidence, discipline, and overall lifestyle.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLe0VP_oH-0SqmRJiRW-2zmGTyAN_tJpLbWqA6SVguSugvjBDSbcFdEk9Q11-se7S8Ro9b1AOFYABHHVPxzmCRddn5a8SIfu1DAOmY3z7o03nICsJRpwqvl1SCsrk891fonKUXfgbVbWeFY=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tKa2RGQkpSR05wVVVGSFpteHVMVFl4ZWtGVE1HYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114103318063428132596/reviews?hl=en-GB","posted_at_unix_micros":1777990793448562,"updated_at_unix_micros":1777991484097345,"language":"en","translated_lang":"","text_original":"My starting weight was 102.6 reduced to 85.1. Losing 17.5 kg has been one of the most rewarding journeys of my life, and I owe a big part of it to my gym, SLAM Lifestyle and Fitness Studio.\nA special thanks to my trainer, Muni Master, whose guidance and dedication made all the difference. From day one, he was supportive, knowledgeable, and genuinely invested in my progress. The workout plans were well-structured, progressive, and tailored to my goals. His constant motivation and accountability kept me going even on the toughest days.\nThe environment at SLAM Saligramam is energetic and positive, making it easier to stay consistent. Clean facilities, quality equipment, and a great fitness community made every session something to look forward to.\nThis transformation wasn’t just physical—it improved my confidence, discipline, and overall lifestyle.","text_translated":"","published_at":"2026-05-05T14:19:53.448562Z"},{"Name":"Fenia Thomas","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXI6uX2oaoWizHTaizsi2IzPEtcEs1536Txq7qBM2rv_h7NMINm=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I had an excellent experience with personal training at SLAM Fitness, Saligrammam, with Master Srinivasan. I joined with the goal of improving my fitness and body composition, and I’m extremely happy with the transformation I’ve been able to achieve in just 4 months.\n\nWhat I really appreciated about Srinivasan was the personalised attention he gave throughout my training. He understood my fitness level and goals, planned the workouts accordingly, and constantly monitored my form to make sure I was doing each exercise correctly. He was very patient when I struggled with certain exercises, but also knew exactly when to push me beyond my comfort zone.\n\nThe biggest motivation for me was being able to actually see a noticeable transformation in my body within 4 months. Along with the physical changes, I could also feel a difference in my strength, stamina, energy levels, and overall confidence.\n\nI never felt like I was just following a generic workout plan, the personal attention and guidance made a big difference to my progress.\n\nI’m genuinely very happy that I chose to take personal training with Master Srinivasan. If you’re looking for a dedicated and supportive personal trainer who genuinely focuses on your progress, I would highly recommend him.\n\nThank you, Master Srinivasan, for all the guidance, motivation, and support over these 4 months! 💪🏻❤️","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pZNWNtSjNYM0YzTW05Q1JISktXbVJXUjBOQk4yYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106556887208311916223/reviews?hl=en-GB","posted_at_unix_micros":1787892355482371,"updated_at_unix_micros":1787892355482371,"language":"en","translated_lang":"","text_original":"I had an excellent experience with personal training at SLAM Fitness, Saligrammam, with Master Srinivasan. I joined with the goal of improving my fitness and body composition, and I’m extremely happy with the transformation I’ve been able to achieve in just 4 months.\n\nWhat I really appreciated about Srinivasan was the personalised attention he gave throughout my training. He understood my fitness level and goals, planned the workouts accordingly, and constantly monitored my form to make sure I was doing each exercise correctly. He was very patient when I struggled with certain exercises, but also knew exactly when to push me beyond my comfort zone.\n\nThe biggest motivation for me was being able to actually see a noticeable transformation in my body within 4 months. Along with the physical changes, I could also feel a difference in my strength, stamina, energy levels, and overall confidence.\n\nI never felt like I was just following a generic workout plan, the personal attention and guidance made a big difference to my progress.\n\nI’m genuinely very happy that I chose to take personal training with Master Srinivasan. If you’re looking for a dedicated and supportive personal trainer who genuinely focuses on your progress, I would highly recommend him.\n\nThank you, Master Srinivasan, for all the guidance, motivation, and support over these 4 months! 💪🏻❤️","text_translated":"","published_at":"2026-08-28T04:45:55.482371Z"},{"Name":"Meghana Atmakuri","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUAuU0D4g7VUnj6X2v_dCNfmMHSWOrBKmkH_V_l3QnC6f2tBtaw=s120-c-rp-mo-br100","Rating":5,"Description":"I’m very happy with the training and guidance provided by Srinu. He is a dedicated, knowledgeable, and supportive trainer who always motivates me to push myself and stay consistent. He pays attention to proper form, explains the exercises clearly, and makes sure the workouts are suitable and effective. His positive attitude and encouragement have made my fitness journey more enjoyable and motivating. Highly recommended Srinu as a great gym trainer! 💪🏋️‍♀️","Images":null,"When":"Edited a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21rMlQwZHhNR1pJWkU1eGRGQkVla2sxVVhkSFFYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112656423594320456138/reviews?hl=en-GB","posted_at_unix_micros":1787651312144559,"updated_at_unix_micros":1788419479007814,"language":"en","translated_lang":"","text_original":"I’m very happy with the training and guidance provided by Srinu. He is a dedicated, knowledgeable, and supportive trainer who always motivates me to push myself and stay consistent. He pays attention to proper form, explains the exercises clearly, and makes sure the workouts are suitable and effective. His positive attitude and encouragement have made my fitness journey more enjoyable and motivating. Highly recommended Srinu as a great gym trainer! 💪🏋️‍♀️","text_translated":"","published_at":"2026-08-25T09:48:32.144559Z"},{"Name":"SIVA","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU410TR_8IE9efZBZNuyZWToxTFqfvrZn1YKV0GQPl9uUaC7Ib_=s120-c-rp-mo-br100","Rating":5,"Description":"The gym has a great ambiance with a clean, spacious, and energetic environment that makes every workout enjoyable. The equipment is well-maintained, and the overall atmosphere is positive and motivating. The surrounding area is pleasant and adds to the comfortable experience of coming here regularly.\n\nA special mention to Master Muni, who is incredibly motivating and supportive. His guidance, encouragement, and positive attitude inspire me to stay consistent and push my limits. He creates a welcoming environment that makes me look forward to coming to the gym every day. Highly recommended for anyone looking for a great fitness experience!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25OT2JsZHNMWHBhUXpoNFdVUmpWMlJaTW01NWJGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109723313757606638074/reviews?hl=en-GB","posted_at_unix_micros":1781747226760760,"updated_at_unix_micros":1781747226760760,"language":"en","translated_lang":"","text_original":"The gym has a great ambiance with a clean, spacious, and energetic environment that makes every workout enjoyable. The equipment is well-maintained, and the overall atmosphere is positive and motivating. The surrounding area is pleasant and adds to the comfortable experience of coming here regularly.\n\nA special mention to Master Muni, who is incredibly motivating and supportive. His guidance, encouragement, and positive attitude inspire me to stay consistent and push my limits. He creates a welcoming environment that makes me look forward to coming to the gym every day. Highly recommended for anyone looking for a great fitness experience!","text_translated":"","published_at":"2026-06-18T01:47:06.76076Z"},{"Name":"Priya Suresh","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWiljaCrCq6gkDjYEswz1R_iMDWPPtyYWdSK7TGBHejk2BGbs4crQ=s120-c-rp-mo-br100","Rating":4,"Description":"Amazing gym atmosphere with a great ambient and positive surrounding that makes every workout enjoyable. The environment is clean, energetic, and keeps me motivated to push harder every day. Special thanks to Muni Master for the constant motivation, support, and guidance. Your encouragement really makes a difference and helps bring out the best in us. Grateful to be training here 💪🔥","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2w4NUxUQXpRVTFFTVZoQk4zTTFURk5rV1Y4eWVIYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/103549905354724439441/reviews?hl=en-GB","posted_at_unix_micros":1782309470045584,"updated_at_unix_micros":1782309470045584,"language":"en","translated_lang":"","text_original":"Amazing gym atmosphere with a great ambient and positive surrounding that makes every workout enjoyable. The environment is clean, energetic, and keeps me motivated to push harder every day. Special thanks to Muni Master for the constant motivation, support, and guidance. Your encouragement really makes a difference and helps bring out the best in us. Grateful to be training here 💪🔥","text_translated":"","published_at":"2026-06-24T13:57:50.045584Z"}]</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/V4+FITNESS+HUB/data=!4m7!3m6!1s0x3a5265c889655b6b:0xbe14a49a913e6e37!8m2!3d13.1314353!4d80.2538928!16s%2Fg%2F11hn7xw8dy!19sChIJa1tlichlUjoRN24-kZqkFL4</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>V4 FITNESS HUB</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>no:37,sidco main road,vasuki nagar, Kaviarasu Kannadhasan Nagar, Kodungaiyur, Tamil Nadu 600118</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["6 am–12 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>090802 31838</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>47J3+HH Kodungaiyur, Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>482</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>{"1":3,"2":0,"3":0,"4":32,"5":447}</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>13.131435</v>
+      </c>
+      <c r="R51" t="n">
+        <v>80.25389300000001</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>13696753350509227575</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdIsw1_Km0y8LVHYSShycd3ykZCgEqVV0tWM58vtbQdpcMwLT0L0oDm_7Ny4DM0ugevXP9CKQriVmhD8zcup0reli5s5P4hrOZuLkhmwON2ynN1EUkZGGdWQAVJHGOOWUiP8cfM=w408-h724-k-no</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>0x3a5265c889655b6b:0xbe14a49a913e6e37</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>ChIJa1tlichlUjoRN24-kZqkFL4</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>{"id":"110836505754783168789","name":"V4 FITNESS HUB (Owner)","link":"https://www.google.com/maps/contrib/110836505754783168789"}</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>{"borough":"Kodungaiyur (East), Kaviarasu Kannadhasan Nagar, Kodungaiyur","street":"no:37,sidco main road,vasuki nagar","city":"Chennai","postal_code":"600118","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>[{"Name":"Papudeshu Rohitha","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX9ulErdgyH0_-g0_KcNtXQ1TrwEMVQY22T7Efh0meQF5Xia0Fu=s120-c-rp-mo-br100","Rating":5,"Description":"I have been a member of V4 Gym for the past 2 months, and my experience has been excellent. The gym has a great atmosphere, good equipment, and a motivating environment for fitness enthusiasts.💪🏻\nA special thanks to Trainer Dinesh 💗 for his outstanding support and guidance. He pays attention to every client, ensures proper workout techniques, and always motivates us to do our best. Even when I work out quietly, he keeps an eye on my progress and provides valuable advice whenever needed. His professionalism, patience, and dedication make a real difference. I highly recommend V4 Gym and Trainer Dinesh to anyone looking to achieve their fitness goals.\n⭐️⭐️⭐️⭐️⭐️ \"Great gym, great trainer, and a great fitness experience!\"","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pWVlZGSndXVU50YWtocFZrc3RhRlIwU0hkeGJtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100411365211557129415/reviews?hl=en-GB","posted_at_unix_micros":1782226338816906,"updated_at_unix_micros":1782226338816906,"language":"en","translated_lang":"","text_original":"I have been a member of V4 Gym for the past 2 months, and my experience has been excellent. The gym has a great atmosphere, good equipment, and a motivating environment for fitness enthusiasts.💪🏻\nA special thanks to Trainer Dinesh 💗 for his outstanding support and guidance. He pays attention to every client, ensures proper workout techniques, and always motivates us to do our best. Even when I work out quietly, he keeps an eye on my progress and provides valuable advice whenever needed. His professionalism, patience, and dedication make a real difference. I highly recommend V4 Gym and Trainer Dinesh to anyone looking to achieve their fitness goals.\n⭐️⭐️⭐️⭐️⭐️ \"Great gym, great trainer, and a great fitness experience!\"","text_translated":"","published_at":"2026-06-23T14:52:18.816906Z"},{"Name":"Aparna T","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU_P1acVy-F0uLX-NwWcEQpXbBX5A1bNgWsZowgM-OBJxkQNRiS=s120-c-rp-mo-br100","Rating":5,"Description":"Joining this gym has been one of the best decisions I've made. The trainers are friendly, supportive, and genuinely care about helping everyone achieve their fitness goals. The gym is always clean, the equipment is well maintained, and the positive atmosphere keeps me motivated to stay consistent. Every workout leaves me feeling stronger and more confident. I'm truly happy with my experience here and would highly recommend this gym to anyone looking for a welcoming and motivating place to start or continue their fitness journey.","Images":null,"When":"Edited 2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25sTlgweGZVR294V1Znd1EzUkVORkZUTnpOaWNXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113737465840998707583/reviews?hl=en-GB","posted_at_unix_micros":1784973381591216,"updated_at_unix_micros":1785818915160120,"language":"en","translated_lang":"","text_original":"Joining this gym has been one of the best decisions I've made. The trainers are friendly, supportive, and genuinely care about helping everyone achieve their fitness goals. The gym is always clean, the equipment is well maintained, and the positive atmosphere keeps me motivated to stay consistent. Every workout leaves me feeling stronger and more confident. I'm truly happy with my experience here and would highly recommend this gym to anyone looking for a welcoming and motivating place to start or continue their fitness journey.","text_translated":"","published_at":"2026-07-25T09:56:21.591216Z"},{"Name":"Sneha Thirukumaran","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVrDhR7qfL2a6MHt_-hAmlNc8mScKtXeBhg4xi2PRELNIPco0lGRw=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training at V4 Fitness with Vinitha as my PT, and my experience has been amazing so far. I’m someone who was completely new to the gym and not really into workouts or dieting, but Vinitha made sure I felt comfortable from day one. She explains everything in detail, is very knowledgeable, and always brings such positive energy.\n\nShe constantly motivates and pushes me to do better, which genuinely makes me look forward to coming to the gym. Having a trainer like her has made my fitness journey much easier and more enjoyable.\n\nApart from that, V4 Fitness has a really great atmosphere and ambience. The gym is always clean, neat, and all the equipment is very well maintained. Overall, this is definitely an A1 gym, and I’d highly recommend it to anyone looking to start their fitness journey!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s5V1VIQTFlbXMzWTBWdE9HWXhhV0ozTlRWek1sRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114132664868400809680/reviews?hl=en-GB","posted_at_unix_micros":1778518059994030,"updated_at_unix_micros":1778518059994030,"language":"en","translated_lang":"","text_original":"I’ve been training at V4 Fitness with Vinitha as my PT, and my experience has been amazing so far. I’m someone who was completely new to the gym and not really into workouts or dieting, but Vinitha made sure I felt comfortable from day one. She explains everything in detail, is very knowledgeable, and always brings such positive energy.\n\nShe constantly motivates and pushes me to do better, which genuinely makes me look forward to coming to the gym. Having a trainer like her has made my fitness journey much easier and more enjoyable.\n\nApart from that, V4 Fitness has a really great atmosphere and ambience. The gym is always clean, neat, and all the equipment is very well maintained. Overall, this is definitely an A1 gym, and I’d highly recommend it to anyone looking to start their fitness journey!","text_translated":"","published_at":"2026-05-11T16:47:39.99403Z"},{"Name":"Rajitha Sasidharan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKdGIAwDJU4PNAz-PKiEuCH0zmGePnYy6_0nyDrT1LlLYTypQ=s120-c-rp-mo-br100","Rating":5,"Description":"My first gym experience at V4 Fitness Hub has been amazing! As a beginner, I was a bit nervous, but the trainers made me feel comfortable from day one. They are very professional, patient, and dedicated, guiding me step by step and correcting my form.\nNow I’m about to complete one year here, and I can confidently say it has been a life-changing journey. I’ve seen great improvements in my strength, confidence, and overall fitness. Huge thanks to the dedicated trainers for their constant support and motivation throughout!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xKcllXRlRhaTEyWWxsNmJITjNkekpMTm1OdVYwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101140303473058534884/reviews?hl=en-GB","posted_at_unix_micros":1777707617209208,"updated_at_unix_micros":1777707617209208,"language":"en","translated_lang":"","text_original":"My first gym experience at V4 Fitness Hub has been amazing! As a beginner, I was a bit nervous, but the trainers made me feel comfortable from day one. They are very professional, patient, and dedicated, guiding me step by step and correcting my form.\nNow I’m about to complete one year here, and I can confidently say it has been a life-changing journey. I’ve seen great improvements in my strength, confidence, and overall fitness. Huge thanks to the dedicated trainers for their constant support and motivation throughout!","text_translated":"","published_at":"2026-05-02T07:40:17.209208Z"},{"Name":"Kishore Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUtkC3EyO-ho_UNY1dFnhwrrq9tw2fSF4ozw8NZ6iok3shrXEZn=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been using this fitness centre for the past four months. The trainers here are highly qualified and certified, and during my time, I’ve noticed that they maintain a great relationship with their clients. My trainer, in particular, has been very supportive and consistently guides me positively throughout my fitness journey. They are always willing to help me out and address all my queries.\nAnother highlight is the quality of the equipment. The centre has all the essential fitness equipment, with separate floors for cardio and strength training. It is a well-equipped, air-conditioned gym that meets all the basic fitness needs.\nOne of the features I appreciate the most is the flexible timing. The gym opens at 5:30 AM and closes at 10:00 PM, which I consider one of its biggest advantages.\nIf you are looking for a training centre with experienced and knowledgeable trainers, I would highly recommend joining this fitness centre and starting your fitness journey.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2t0WlpEbEJabmRSU2xKdGIzaHJZVkZaTTJzNFdIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114574398304630391850/reviews?hl=en-GB","posted_at_unix_micros":1775217385853936,"updated_at_unix_micros":1775217385853936,"language":"en","translated_lang":"","text_original":"I’ve been using this fitness centre for the past four months. The trainers here are highly qualified and certified, and during my time, I’ve noticed that they maintain a great relationship with their clients. My trainer, in particular, has been very supportive and consistently guides me positively throughout my fitness journey. They are always willing to help me out and address all my queries.\nAnother highlight is the quality of the equipment. The centre has all the essential fitness equipment, with separate floors for cardio and strength training. It is a well-equipped, air-conditioned gym that meets all the basic fitness needs.\nOne of the features I appreciate the most is the flexible timing. The gym opens at 5:30 AM and closes at 10:00 PM, which I consider one of its biggest advantages.\nIf you are looking for a training centre with experienced and knowledgeable trainers, I would highly recommend joining this fitness centre and starting your fitness journey.","text_translated":"","published_at":"2026-04-03T11:56:25.853936Z"}]</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>43</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Life+Fitness+Studio/data=!4m7!3m6!1s0x3a526127c1c3c13f:0x835ff3674de19a63!8m2!3d13.0751402!4d80.1815278!16s%2Fg%2F11c2k2s8v5!19sChIJP8HDwSdhUjoRY5rhTWfzX4M</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Life Fitness Studio</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>157, Srinivasan St, Golden George Nagar, Mogappair East, Chennai, Tamil Nadu 600107</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10:30 pm"],"Monday":["5:30 am–10:30 pm"],"Saturday":["5:30 am–10:30 pm"],"Sunday":["5:30 am–10:30 pm"],"Thursday":["5:30 am–10:30 pm"],"Tuesday":["5:30 am–10:30 pm"],"Wednesday":["5:30 am–10:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>072999 90507</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>35GJ+3J Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>451</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>{"1":18,"2":6,"3":14,"4":69,"5":344}</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>13.07514</v>
+      </c>
+      <c r="R52" t="n">
+        <v>80.181528</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>9466552566769883747</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLedczs0b0wpCo9yggok7CVQfc97vRXL3NUKNwXQjGSB1bGQLAVD6MVridsAHNQcYIMQVv99WaXsn8OvqiLP9HmvrSCFH5RixAVsTp2uTwZ_FT-9-vTz7Lw5HyI6nuf_sNbkQDcw=w408-h408-k-no</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>0x3a526127c1c3c13f:0x835ff3674de19a63</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>ChIJP8HDwSdhUjoRY5rhTWfzX4M</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[{"link":"https://shop.zuyyu.com/28f37364-28df-4357-a43f-f35d3228db22/menu?rwg_token=AE37R_ho7OGZrU0VDVtAFg_PuobTb0CVBkBqe_A7onOdYdQuqXAxIXdMPxmS4CFTIqP3WfoYHfWkxcbPWSFZNmbJsljilpl85uWJS1bCbOQRdsLQIjg76Pg%3D","source":"zuyyu.com"}]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>{"id":"107453402372117188203","name":"Life Fitness Studio (Owner)","link":"https://www.google.com/maps/contrib/107453402372117188203"}</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>{"borough":"Golden George Nagar, Mogappair East","street":"157, Srinivasan St","city":"Chennai","postal_code":"600107","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>[{"Name":"Ravindra Rao","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUmqI52_ybIo5fWvUqgtIZZmOmQhmsBOs8U-wibOVrBRn3tpLZH=s120-c-rp-mo-br100","Rating":5,"Description":"Since joining this gym, I’ve seen a significant shift in both my lifestyle and fitness levels. My days now start with high energy, thanks to my coach, Mr. SUDHARSHAN. He possesses extensive knowledge of workout techniques and, more importantly, explains the scientific reasoning behind every movement. His deep understanding of anatomy and body mechanics ensures that every session is effective and safe. Mr. Sudharsan’s constant smile and positive energy are infectious, making even the toughest workouts enjoyable. Beyond physical fitness, I’ve gained immense discipline and confidence. Highly recommended for anyone looking for expert-led personal growth!\n\nI also want to mention that all the coaches in this gym are highly knowledgeable and helpful. The equipment is excellent and well-maintained. I truly give a 5-star rating to the gym, the coaches, and the equipment. If you want to get fit the right way, I highly recommend this place!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfrvVhTppQBR7Cye9aMxd8SJiymWX91K-jXEH0xj3t3JIHTW02SKc4OG7jdWPZOQ78Kw4-3zSMU1V3udUvc7hAm7DLFGgkg5SjpgH_5kBbZhRSnQxXPjaiLETc66PKqZsxaAKgYcM5bzigz=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xaQmVHRlZUblpFZW14ZmRGRXpSMkZ3Y204elMwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118129312575425151013/reviews?hl=en-GB","posted_at_unix_micros":1776967547540166,"updated_at_unix_micros":1776967547540166,"language":"en","translated_lang":"","text_original":"Since joining this gym, I’ve seen a significant shift in both my lifestyle and fitness levels. My days now start with high energy, thanks to my coach, Mr. SUDHARSHAN. He possesses extensive knowledge of workout techniques and, more importantly, explains the scientific reasoning behind every movement. His deep understanding of anatomy and body mechanics ensures that every session is effective and safe. Mr. Sudharsan’s constant smile and positive energy are infectious, making even the toughest workouts enjoyable. Beyond physical fitness, I’ve gained immense discipline and confidence. Highly recommended for anyone looking for expert-led personal growth!\n\nI also want to mention that all the coaches in this gym are highly knowledgeable and helpful. The equipment is excellent and well-maintained. I truly give a 5-star rating to the gym, the coaches, and the equipment. If you want to get fit the right way, I highly recommend this place!","text_translated":"","reply_text_original":"Dear Mr.Ravindra Rao,Thank you so much for your 5-star rating! ⭐⭐⭐⭐⭐ We truly appreciate your support and trust in Life Fitness Studio. Your feedback motivates our entire team to keep providing the best fitness experience. Stay fit, stay healthy, and keep training with us! Team-LFS","reply_language":"en","reply_posted_at_unix_micros":1789618010000000,"reply_updated_at_unix_micros":1789618010000000,"published_at":"2026-04-23T18:05:47.540166Z"},{"Name":"Pavithra","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJMtmYGT8ru7dRHAfb7M5WiHrnQfAfn7bAm1aNLwykJzb3WvA=s120-c-rp-mo-br100","Rating":5,"Description":"Well maintained machines in strength training section. Spacious gym","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdh6gy56ILXOi4HfdH98RDqsoP63ru0HjtdwV_UpMFKr0KE2vTfWga9PR6hRyACx0qIkdwZv5MQY7L6x32cxrhkPSk_nO5b-e8waJ0OV2OUXWdsk4ZK5x3Sah1cNiw6Xf4uRdGNF8-APHix=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfbMwycC2nRCSMOUDztT3_-xxEugOQmmPUBLAQIbZJTtsAjrLFwrD8st1mvZ0SWIi4JzWYvOTz4j5IVBNAxDAqbO5BA7tdIOZYp8zhuKF_PKEY1El2llaLccbOuRi5fbKDiTUs6CwQST7va=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfIxQON0L6P7sfQRHMOBuoVzDB5sKaJFmJ2D22XaguRiS5ePhUlL7ZZ_WAhEzOXQslizuNcbaR-HtfkTmo7gmTYn-2RzmW7tpe5ofFXrNNnYoL_Asa4kUNGQ01zsK4ZEBCVuadUjfToE9Ti=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeC_dKBWSqTcLED-eSFn-NsjUD4dOZThyioLJ83DBHPsA-odXRYEXhlWsLTEDPiD4ozi7j9jTxrVm7j7jEB9Iloxi2syhBam30mYh3muLyq0DGLK4sVlaJEhfD9Ik0SbaXc8LB0VhjDudeG=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLe3y8HCI74PnO6UDrv8KQZeHSgPs63zQrlWzp7R0CDD2LA9XxXJUNOd-tySd_60slestuyvakoxnYLQPQIK_aJGybqk7OhdatPVnaMztJrTn4qZmk9_obW_Zp6x0OGnkZ4C4VTkEyfuwPzs=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeepgz70ed9uGAYWztIR_VQuPMPfFRuuGWv26RSzMGrnijTmm6CzXKUhFnBNkdL4p7ZoW5VMoM-9EER-OTdM91dx-MJERRkfCsghSnV8_k7NSCTWyOba4bV8w0OyleyUgkMFQ8qGH9Vf8M=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLczRyYrd9mWKY7Tnyv7mAFHtqvw74HR0hnPtIwxlOQzFtMBN4GBbE6xHn8mbOJ6GvpIkcz6vxObqGGsCMWFpELF8iHgdJFdFGRs7u4fbRpuPXmYX18Xl213u7BPB6bS5WNqqm-NQmiCS5o=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeAHwaeEM3BRbdUoK2wGzC8POuZhE5HiEm-v-0jPp6mbMJ89MAwbqEJD3rkRmyt40_-BYQIkjEBwDIbeHX6-RA5zu7f9aE5LmaXpWWR5rLcVCUbLkO1i3PblayK3kys0fEpvf7xJ8D9xXQ=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLe-kYVbjbyRBxvwNRtZpaVt1QBgI_A_S72fIBoDzlmlnuxXsFPgxrKtPi4NXIxASntXUsSOhV0jxR9_tx8_zYSAkAFD2Zq4TuhRdMlgGbGjzA9AMDsoirZFhLJIEBtKB7VYicSsrCh9xj3M=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcLEACcwvSIa8d8Mv1uLV0iomRzkYDg2y4Qzj7KgV4ae_jdRrXgk2WYbu3TPl3-PgcM4vQM-PlYtslrVbaFegrrmGBIovFfKXRb4aewnb5N1vjgfkfPekoOOWeRe_mcZkA-GTlCy2IeTs87=k-no"],"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT201Qk1HcEVOMWRzY1MxWFlURjNNa2hCWVdkcmEzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116120373794404117909/reviews?hl=en-GB","posted_at_unix_micros":1787656519996117,"updated_at_unix_micros":1787678612133087,"language":"en","translated_lang":"","text_original":"Well maintained machines in strength training section. Spacious gym","text_translated":"","reply_text_original":"Hi Pavitra,Thank you so much for your wonderful feedback! 🙏 We truly appreciate your kind words and are happy to know that you’re enjoying your experience at Life Fitness Studio. Your support and motivation mean a lot to our entire team. 💪\nWe look forward to helping you achieve your fitness goals and stay healthy. Keep training, keep progressing! 🔥\n— Team LFS","reply_language":"en","reply_posted_at_unix_micros":1789617661000000,"reply_updated_at_unix_micros":1789617661000000,"published_at":"2026-08-25T11:15:19.996117Z"},{"Name":"Srinivas Rao","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW8Kw91BHaLCIIkISQbCy44NAL9I8AW4246D6Ais0zsL-AVzGrV=s120-c-rp-mo-br100","Rating":5,"Description":"I first was really nervous about joining the gym but it's been 3 and half weeks almost a month I feel confident and pushing myself hard as I started to see the results from their motivation and customised workout plans.Thank you For Guiding me entirely from workouts to diet.🙏If your a beginner or experienced this gym you should give it a try atleast once!\nMy experience in these few days itself was great and awesome.All the trainers will teach you the workouts and exercises in a daily basis.They will motivate and push us it will kick start our gym life just like that!💪.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2w5WFJrOURSbFJJVTNCTVpUQkpkMHh1U3paelZWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103654850918734910941/reviews?hl=en-GB","posted_at_unix_micros":1775665795516626,"updated_at_unix_micros":1775665795516626,"language":"en","translated_lang":"","text_original":"I first was really nervous about joining the gym but it's been 3 and half weeks almost a month I feel confident and pushing myself hard as I started to see the results from their motivation and customised workout plans.Thank you For Guiding me entirely from workouts to diet.🙏If your a beginner or experienced this gym you should give it a try atleast once!\nMy experience in these few days itself was great and awesome.All the trainers will teach you the workouts and exercises in a daily basis.They will motivate and push us it will kick start our gym life just like that!💪.","text_translated":"","reply_text_original":"Dear Mr.Srinivasan Rao,Thank you for the awesome review! 🔥 We’re proud to have you as part of our LFS family. Let’s keep pushing limits and achieving new goals together 💪”Team LFS ","reply_language":"en","reply_posted_at_unix_micros":1775721982000000,"reply_updated_at_unix_micros":1775721982000000,"published_at":"2026-04-08T16:29:55.516626Z"},{"Name":"keziah kenny","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL25NxfwCiAkhLkIqKy32ahLpPZvbOKbruaM-7PjgUznKr2S1yy=s120-c-rp-mo-br100","Rating":5,"Description":"I had a great experience at Life Fitness Studio. The workout plans are well-structured and effective, and the diet guidance has helped me adopt a much healthier lifestyle. A special thanks to trainer Srinivasan for his dedication, motivation, and personalized support. His guidance has made a noticeable difference in my fitness journey.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwM1kxTkZhamwyTUVwWlpEY3RkV3gwUlU5bGJsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105672042334774581075/reviews?hl=en-GB","posted_at_unix_micros":1782222879245819,"updated_at_unix_micros":1782222879245819,"language":"en","translated_lang":"","text_original":"I had a great experience at Life Fitness Studio. The workout plans are well-structured and effective, and the diet guidance has helped me adopt a much healthier lifestyle. A special thanks to trainer Srinivasan for his dedication, motivation, and personalized support. His guidance has made a noticeable difference in my fitness journey.","text_translated":"","reply_text_original":"Hii Keziah Kenny,Thank you so much for your 5-star rating! ⭐⭐⭐⭐⭐ We truly appreciate your support and trust in Life Fitness Studio. Your feedback motivates our entire team to keep providing the best fitness experience. Stay fit, stay healthy, and keep training with us! 💪 Team LFS ","reply_language":"en","reply_posted_at_unix_micros":1789617919000000,"reply_updated_at_unix_micros":1789617919000000,"published_at":"2026-06-23T13:54:39.245819Z"},{"Name":"Rajamanickam Ramesh","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIJt279JO5iokxR_uDIdYfKKE9vpYHeJQOT4HEZNHP0xcliahfZ=s120-c-rp-mo-br100","Rating":5,"Description":"I had been to many gyms earlier (almost 30 years). However, this gym transformed not only my body shape but also my confidence level. Thank you, LFS. I remember when I joined here 9 years ago; only the second floor had a gym with minimum equipment. However, over the period, the owner expanded the gym to the first floor too, exclusively for cardio, which is very convenient for the clients. Also, the management had added many new hydraulic machines on the second floor and replaced old machines with new ones; I think all the machines had been replaced, which I used once. I really do appreciate the owner for his effort and his relentless service 24x7. Besides, this gym has got special privileges: \"freedom and no intervention.\" Once again thanks!","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pCMFVsTnRaVzlqWlhwNmVHZGxNSEJzYkdObmNrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106617633856456483195/reviews?hl=en-GB","posted_at_unix_micros":1773307091440886,"updated_at_unix_micros":1773307091440886,"language":"en","translated_lang":"","text_original":"I had been to many gyms earlier (almost 30 years). However, this gym transformed not only my body shape but also my confidence level. Thank you, LFS. I remember when I joined here 9 years ago; only the second floor had a gym with minimum equipment. However, over the period, the owner expanded the gym to the first floor too, exclusively for cardio, which is very convenient for the clients. Also, the management had added many new hydraulic machines on the second floor and replaced old machines with new ones; I think all the machines had been replaced, which I used once. I really do appreciate the owner for his effort and his relentless service 24x7. Besides, this gym has got special privileges: \"freedom and no intervention.\" Once again thanks!","text_translated":"","reply_text_original":"Dear Mr.Rajamanickam Ramesh,Thank you so much for your wonderful review and for being a valued member of Life Fitness Studio for such a long time. Your trust, support, and dedication truly mean a lot to us. Members like you are the strength of our gym family. We are grateful to be part of your fitness journey and will continue to provide the best environment for your health and fitness goals.Once again thank you for your valuable feedback and support.. Team LFS","reply_language":"en","reply_posted_at_unix_micros":1773327282000000,"reply_updated_at_unix_micros":1773327282000000,"published_at":"2026-03-12T09:18:11.440886Z"}]</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>43</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/GYM+BEAN+Fitness+Studio/data=!4m7!3m6!1s0x3a526503fa04fed7:0xaca7f3187baacef2!8m2!3d13.1107699!4d80.2418756!16s%2Fg%2F11kqgmz_db!19sChIJ1_4E-gNlUjoR8s6qexjzp6w</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>GYM BEAN Fitness Studio</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>19 Bunder garden at, opp. LOURDES GIRLS HIGHER SECONDARY SCHOOL, Perambur, Chennai, Tamil Nadu 600011</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{"Friday":["Open 24 hours"],"Monday":["Open 24 hours"],"Saturday":["Open 24 hours"],"Sunday":["Open 24 hours"],"Thursday":["Open 24 hours"],"Tuesday":["Open 24 hours"],"Wednesday":["Open 24 hours"]}</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>063851 61607</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>466R+8Q Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>426</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>{"1":8,"2":0,"3":0,"4":13,"5":405}</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>13.11077</v>
+      </c>
+      <c r="R53" t="n">
+        <v>80.241876</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>12441179782113840882</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLejdspYO0ogJvB0OCJVUII5SaIltZe_f84VGpDPJv6ZFzhy349mA5C_et-TsIaTrRg-rc4SmpG9oxvLYx7ZfgcTJuxkobqGj_p129SaeZ9VUHHFEALqZDG018EKbcHhi-GGTJoRUg=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>0x3a526503fa04fed7:0xaca7f3187baacef2</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>ChIJ1_4E-gNlUjoR8s6qexjzp6w</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>{"id":"117221839513582766419","name":"GYM BEAN Fitness Studio (Owner)","link":"https://www.google.com/maps/contrib/117221839513582766419"}</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>{"borough":"Bunder Garden, Perambur","street":"19 Bunder garden at, opp. LOURDES GIRLS HIGHER SECONDARY SCHOOL","city":"Chennai","postal_code":"600011","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Assistive hearing loop","enabled":false},{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false},{"name":"Wheelchair-accessible seating","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>[{"Name":"Ratish Shiva","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXT9vzb9KHaT-pZwoM0N-voza126wepL4krVI0bvY9HJcY7IkA8iw=s120-c-rp-mo-br100","Rating":5,"Description":"I highly recommend Andrew as a personal trainer at Gym Bean Fitness Studio. I have been training with him for the past 5 months, and the transformation has been incredible. I've lost 12 kg, gained muscle, become much stronger, and now have better stamina, flexibility, and discipline. I also feel much more energetic than before and have gained proper knowledge about fitness and nutrition.\n\nWhat makes Andrew stand out is his professional approach and genuine dedication to his clients. He provides personalized workout plans based on each person's body type, age, and fitness level. His guidance during workouts, motivation, nutrition advice, and regular progress tracking have helped me stay consistent and achieve my goals.\n\nAndrew is always respectful, patient, and encouraging. He gives equal attention to every client, answers questions clearly, and creates a positive and motivating environment in the gym. His experience and knowledge, including injury rehabilitation, make him an outstanding trainer who truly cares about his clients' long-term health and fitness.\n\nIf you're looking for a knowledgeable, disciplined, and supportive personal trainer, I strongly recommend Andrew. Thank you, Andrew, for helping me become a healthier, stronger, and more confident version of myself!....","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25GR1UyMURNMmh5ZFRaUFIyVnJlSGgwVmtjM09HYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104031598281868333789/reviews?hl=en-GB","posted_at_unix_micros":1783594408457051,"updated_at_unix_micros":1783594408457051,"language":"en","translated_lang":"","text_original":"I highly recommend Andrew as a personal trainer at Gym Bean Fitness Studio. I have been training with him for the past 5 months, and the transformation has been incredible. I've lost 12 kg, gained muscle, become much stronger, and now have better stamina, flexibility, and discipline. I also feel much more energetic than before and have gained proper knowledge about fitness and nutrition.\n\nWhat makes Andrew stand out is his professional approach and genuine dedication to his clients. He provides personalized workout plans based on each person's body type, age, and fitness level. His guidance during workouts, motivation, nutrition advice, and regular progress tracking have helped me stay consistent and achieve my goals.\n\nAndrew is always respectful, patient, and encouraging. He gives equal attention to every client, answers questions clearly, and creates a positive and motivating environment in the gym. His experience and knowledge, including injury rehabilitation, make him an outstanding trainer who truly cares about his clients' long-term health and fitness.\n\nIf you're looking for a knowledgeable, disciplined, and supportive personal trainer, I strongly recommend Andrew. Thank you, Andrew, for helping me become a healthier, stronger, and more confident version of myself!....","text_translated":"","published_at":"2026-07-09T10:53:28.457051Z"},{"Name":"Alameen M","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVKkwuQTyzDmdpVh8g40x7gdWUHNHzSg_r3enuZ9CWVL7RwyRxiBQ=s120-c-rp-mo-ba12-br100","Rating":1,"Description":"Visited this gym to enquire about a body transformation plan with a personal trainer. They took my contact number and said they would call me the next day with an update. It’s been a week, and I still haven’t received any call or follow-up. The gym and trainers seemed good, but the lack of communication and customer follow-up was disappointing. Hope they improve this aspect in the future.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT200eVl6bFVSMUUwYVZkUlZreGhjVE5wVldwak5IYxAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/106525378025953812395/reviews?hl=en-GB","posted_at_unix_micros":1785441405331955,"updated_at_unix_micros":1785441405331955,"language":"en","translated_lang":"","text_original":"Visited this gym to enquire about a body transformation plan with a personal trainer. They took my contact number and said they would call me the next day with an update. It’s been a week, and I still haven’t received any call or follow-up. The gym and trainers seemed good, but the lack of communication and customer follow-up was disappointing. Hope they improve this aspect in the future.","text_translated":"","published_at":"2026-07-30T19:56:45.331955Z"},{"Name":"Shubash R","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKyHBVdw8xKovS0r8lSUIbgIHBJNcksh2qnqkyzm0Zk4MlTCg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Gym is very good for beginners and those who look out for a comfortable and motivating place to start their fitness journey...people are friendly it's well maintained ....ac alone needs regular checkups....\nI owe my thanks to all the trainers who help me whenever I ask ....special mention to Mr.Andrews who is very motivating and shows best professionalism...","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25admEzRnVPR2xJWTJwdk5tdE9TVzF0VUZkU09WRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110723549530608792634/reviews?hl=en-GB","posted_at_unix_micros":1779871538652714,"updated_at_unix_micros":1779871538652714,"language":"en","translated_lang":"","text_original":"Gym is very good for beginners and those who look out for a comfortable and motivating place to start their fitness journey...people are friendly it's well maintained ....ac alone needs regular checkups....\nI owe my thanks to all the trainers who help me whenever I ask ....special mention to Mr.Andrews who is very motivating and shows best professionalism...","text_translated":"","published_at":"2026-05-27T08:45:38.652714Z"},{"Name":"147 Muthu Rubhan M","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVi_2NrVHwu3eWaelbwS1QEBzdvx5H1EyX7LE64M5CcalGCypRA=s120-c-rp-mo-br100","Rating":5,"Description":"Great gym in Chennai. Took their 3-day workout pass, very convenient. Wide range of equipment, clean and well-maintained space, nice ambience. Staff and trainers were friendly and helpful. Highly recommended.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2sxM2RHdzVWMFUwZERWa1pVbExiMEZLZFZaRk0zYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104204918602430890069/reviews?hl=en-GB","posted_at_unix_micros":1774538081282754,"updated_at_unix_micros":1774538081282754,"language":"en","translated_lang":"","text_original":"Great gym in Chennai. Took their 3-day workout pass, very convenient. Wide range of equipment, clean and well-maintained space, nice ambience. Staff and trainers were friendly and helpful. Highly recommended.","text_translated":"","published_at":"2026-03-26T15:14:41.282754Z"},{"Name":"Nancy Crocker","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWptQn3U8zdmgy6GjFzcwxxtZXCTsEJe_SC90_GJbj0A6zKg0LS=s120-c-rp-mo-br100","Rating":5,"Description":"It’s a safe space for everyone to work out comfortably, with a friendly and respectful atmosphere. The trainers are incredibly dedicated, offering personalised guidance and support. I have been working out here for sometime and the staff is always present , attentive and supportive. I highly recommend this gym!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfnB8QPo5hmMILdIeK0g0aYLpmPHI8ht_bZ-8wGBRw2KexRJtCJEAdiJfzFNSMvvXiSANu16jRwltDMi9DBdSosL2QB1xx1aDez5_GUIgWnaMH0kWKtub-7o14PzVmOLrTXiRX7=k-no"],"When":"2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURMbk0tZTR3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109415851076867960164/reviews?hl=en-GB","posted_at_unix_micros":1719379652443781,"updated_at_unix_micros":1719380800875725,"language":"en","translated_lang":"","text_original":"It’s a safe space for everyone to work out comfortably, with a friendly and respectful atmosphere. The trainers are incredibly dedicated, offering personalised guidance and support. I have been working out here for sometime and the staff is always present , attentive and supportive. I highly recommend this gym!","text_translated":"","published_at":"2024-06-26T05:27:32.443781Z"}]</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>(1★) Alameen M: Visited this gym to enquire about a body transformation plan with a personal trainer. They took my contact number and said they would call me the next day with an update. It’s been a week, and I still haven’t received any call or follow-up. The gym and trainers seemed good, but the lack of communication and customer follow-up was disappointing. Hope they improve this aspect in the future.</t>
+        </is>
+      </c>
+      <c r="AO53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>43</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/ThorFitness+_Vanagaram/data=!4m7!3m6!1s0x3a5261f3a03f43c1:0x7ab7888052fc6052!8m2!3d13.0618405!4d80.1441559!16s%2Fg%2F11ld41dxxl!19sChIJwUM_oPNhUjoRUmD8UoCIt3o</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ThorFitness _Vanagaram</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>No 245, opposite to Prestige and RWD apartments, Vanagaram, Thiruverkadu, Tamil Nadu 600077</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["9 am–8 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>090031 16775</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>346V+PM Thiruverkadu, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>396</v>
+      </c>
+      <c r="O54" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>{"1":5,"2":0,"3":3,"4":11,"5":377}</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>13.06184</v>
+      </c>
+      <c r="R54" t="n">
+        <v>80.144156</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8842686478094721106</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcyokFtjmCAO4Xur07H8RJjCbN9mgiVex0S4UmtXSVA7P96KeK9rZuDsn5ucFLMKrV3J56TEqdgB71yGVFLbRlaTC0r--pIwW2hWJ4Nes76doRe5Pl0IADlgnrp1Fil04ock5pPdQyEHsrg=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>0x3a5261f3a03f43c1:0x7ab7888052fc6052</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>ChIJwUM_oPNhUjoRUmD8UoCIt3o</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>{"id":"108364221374738347767","name":"ThorFitness _Vanagaram (Owner)","link":"https://www.google.com/maps/contrib/108364221374738347767"}</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>{"borough":"Ganga Nagar, Vanagaram","street":"No 245, opposite to Prestige and RWD apartments","city":"Thiruverkadu","postal_code":"600077","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Assistive hearing loop","enabled":true},{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>[{"Name":"bharath","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ5_jODSCcAoTUcFterRjWX8vFFD9fsQ0929jD3IJ6DCVKwqg=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve had a great experience at this gym so far. The  SHAH master is highly knowledgeable and supportive, always making sure exercises are done with proper form and motivating everyone to push their limits safely. Their personalized guidance really makes a difference, especially for beginners.\n\nThe equipment is well-maintained and modern, with a good variety for strength training, cardio, and functional workouts. I never had to wait too long for machines, even during peak hours.\n\nOne thing I really appreciate is the positive and energetic vibe of the place. The environment is friendly, clean, and encouraging, which keeps me motivated to stay consistent.\n\nOverall, it’s a great place to work on fitness goals, whether you’re just starting out or already experienced.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLe2mKGPI0uuuGdkdbPEjt4ASITYX6Ix1Ajmho3EgP_ErLYHEeGmJMFCccElP7Bm4Pd2Sev_peSFhVt6I1dr6M_fLYflpnJztPfXlZR8TdA1qSShwEGn3PSgwG8fG6fZmA7WrF20rYg5sAOp=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21aSFZWSkVlR3QwY1ZCUFNGcHVVV2RrU0RKbU1GRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116465756320814759366/reviews?hl=en-GB","posted_at_unix_micros":1781005768842675,"updated_at_unix_micros":1781005768842675,"language":"en","translated_lang":"","text_original":"I’ve had a great experience at this gym so far. The  SHAH master is highly knowledgeable and supportive, always making sure exercises are done with proper form and motivating everyone to push their limits safely. Their personalized guidance really makes a difference, especially for beginners.\n\nThe equipment is well-maintained and modern, with a good variety for strength training, cardio, and functional workouts. I never had to wait too long for machines, even during peak hours.\n\nOne thing I really appreciate is the positive and energetic vibe of the place. The environment is friendly, clean, and encouraging, which keeps me motivated to stay consistent.\n\nOverall, it’s a great place to work on fitness goals, whether you’re just starting out or already experienced.","text_translated":"","published_at":"2026-06-09T11:49:28.842675Z"},{"Name":"Vishal S","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVs0hNc_hqITBpHSf4FJDb4Po4PuBGq7-MvLCUyYiT7f3F2kBzu=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been working out at Thor Gym for the past month, and it has been a great experience. The gym is always clean, well-equipped, and has an energetic atmosphere that keeps me motivated. The trainers are knowledgeable, approachable, and genuinely care about helping members improve.\n\nA special thanks to Mr. Shahjahan for his excellent guidance and support. He patiently explains every exercise, corrects my form whenever needed, and constantly motivates me to push my limits safely. His dedication has made my fitness journey much more enjoyable and effective.\n\nI would definitely recommend Thor Gym to anyone looking for a friendly, professional, and motivating place to achieve their fitness goals.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25SUlpEWkhSVzlITVZCcFQzWmtka3RXUmtOTFluYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108932819228477550347/reviews?hl=en-GB","posted_at_unix_micros":1782980343119861,"updated_at_unix_micros":1782980343119861,"language":"en","translated_lang":"","text_original":"I’ve been working out at Thor Gym for the past month, and it has been a great experience. The gym is always clean, well-equipped, and has an energetic atmosphere that keeps me motivated. The trainers are knowledgeable, approachable, and genuinely care about helping members improve.\n\nA special thanks to Mr. Shahjahan for his excellent guidance and support. He patiently explains every exercise, corrects my form whenever needed, and constantly motivates me to push my limits safely. His dedication has made my fitness journey much more enjoyable and effective.\n\nI would definitely recommend Thor Gym to anyone looking for a friendly, professional, and motivating place to achieve their fitness goals.","text_translated":"","published_at":"2026-07-02T08:19:03.119861Z"},{"Name":"Hemalatha Karthik","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJUJn83l1bJyUfFt1Bdp4ISE_NAcHUPZzewXAurFgk_tujx8g=s120-c-rp-mo-br100","Rating":5,"Description":"Thor gym is great in Ambience and full of energy to workout in great vibe. The trainers here are so motivating and energetic. Trainer Nasurudeen and Trainer Mukesh will always feel free to answer all our doubts and train us according to our need and gives us the best. Really happy with this gym and it’s well cleaned all the time and good maintenance  give try without having a second thought","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLePWv6s0YicF5wkx43EU1TJKhkD10dqIgAudwo1kBgmVs8WH8jkyEHawa6D3IZ9Rc9VGHvRDqNWkCQN1pWgRnGlywaEzBcwMLxEwVxaDkZ7u8lALErSP1Pw_FnvJZiWomBmb7vYzthRiQ4=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21SeFdrUjZWV0ZSVmxKbFJFNW1Za1IyVERRMFdIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115909770663025365248/reviews?hl=en-GB","posted_at_unix_micros":1774334905543895,"updated_at_unix_micros":1774334905543895,"language":"en","translated_lang":"","text_original":"Thor gym is great in Ambience and full of energy to workout in great vibe. The trainers here are so motivating and energetic. Trainer Nasurudeen and Trainer Mukesh will always feel free to answer all our doubts and train us according to our need and gives us the best. Really happy with this gym and it’s well cleaned all the time and good maintenance  give try without having a second thought","text_translated":"","published_at":"2026-03-24T06:48:25.543895Z"},{"Name":"Deena Dharshan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVWZFzvlGWvjetRq9ejttrDtmCRiZX8TxL9wfBD5Eoune_Xs4yC=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’ve had a wonderful experience at Thor Gym. The facility is extremely spacious, well-maintained, and properly ventilated, creating a comfortable environment for workouts even during peak hours. The gym is equipped with a wide range of modern, high-quality equipment that caters to beginners as well as advanced fitness enthusiasts.\nOne of the standout features is the personalized attention given to members. The trainers provide BMI assessment and personal training guidance, helping individuals understand their fitness levels and set realistic goals. They take special care to monitor progress and customize workout plans according to each person’s needs, which makes a significant difference in achieving results safely and effectively. The staff and trainers are friendly, supportive, and always available to assist with exercise techniques and fitness-related queries. The cleanliness, organization, and overall atmosphere of the gym reflect a strong commitment to member satisfaction.A great place to build strength and improve health.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s5d2FFZERaa2hDUW01cmRYQXlOMEprV1ZOT1JFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113509583116899022388/reviews?hl=en-GB","posted_at_unix_micros":1780751485961209,"updated_at_unix_micros":1780751485961209,"language":"en","translated_lang":"","text_original":"I’ve had a wonderful experience at Thor Gym. The facility is extremely spacious, well-maintained, and properly ventilated, creating a comfortable environment for workouts even during peak hours. The gym is equipped with a wide range of modern, high-quality equipment that caters to beginners as well as advanced fitness enthusiasts.\nOne of the standout features is the personalized attention given to members. The trainers provide BMI assessment and personal training guidance, helping individuals understand their fitness levels and set realistic goals. They take special care to monitor progress and customize workout plans according to each person’s needs, which makes a significant difference in achieving results safely and effectively. The staff and trainers are friendly, supportive, and always available to assist with exercise techniques and fitness-related queries. The cleanliness, organization, and overall atmosphere of the gym reflect a strong commitment to member satisfaction.A great place to build strength and improve health.","text_translated":"","published_at":"2026-06-06T13:11:25.961209Z"},{"Name":"Aishwarya Baskaran","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJmXP9ASas9dgxBETcZ-9wFIzfhuK6nDFYToyJnMWNVg1R3bA=s120-c-rp-mo-br100","Rating":5,"Description":"I joined Thor Gym a month ago, and my experience has been excellent so far. The gym is clean, well-maintained, and has a positive and motivating atmosphere. The trainers are highly professional, friendly, and always willing to help members achieve their fitness goals. A special thanks to Mr. Mani, who has been guiding me throughout every workout session. He is patient, supportive, and always ensures that I perform exercises with the correct form. His constant motivation and encouragement have helped me stay consistent and confident. I highly recommend Thor Gym to anyone looking for a supportive and professional fitness environment.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xsMVZEWmhPREU0Y2xSdmFGTmtWbUp2ZDBOWFlrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116491396458697968705/reviews?hl=en-GB","posted_at_unix_micros":1781056329210132,"updated_at_unix_micros":1781056329210132,"language":"en","translated_lang":"","text_original":"I joined Thor Gym a month ago, and my experience has been excellent so far. The gym is clean, well-maintained, and has a positive and motivating atmosphere. The trainers are highly professional, friendly, and always willing to help members achieve their fitness goals. A special thanks to Mr. Mani, who has been guiding me throughout every workout session. He is patient, supportive, and always ensures that I perform exercises with the correct form. His constant motivation and encouragement have helped me stay consistent and confident. I highly recommend Thor Gym to anyone looking for a supportive and professional fitness environment.","text_translated":"","published_at":"2026-06-10T01:52:09.210132Z"}]</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>43</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Muscle+Factory+Gym/data=!4m7!3m6!1s0x3a52671b48ffffe3:0x97a3ecd19e485523!8m2!3d13.0242052!4d80.2145936!16s%2Fg%2F11fz9j7qs6!19sChIJ4___SBtnUjoRI1VIntHso5c</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Muscle Factory Gym</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1st floor, Muscle Factory Gym, 29/1, W Jones Rd, West Saidapet, Saidapet, Chennai, Tamil Nadu 600015</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–11 pm"],"Monday":["5:30 am–11 pm"],"Saturday":["5:30 am–11 pm"],"Sunday":["6 am–9 pm"],"Thursday":["5:30 am–11 pm"],"Tuesday":["5:30 am–11 pm"],"Wednesday":["5:30 am–11 pm"]}</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>091761 54882</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>26F7+MR Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>393</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>{"1":10,"2":5,"3":6,"4":32,"5":340}</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>13.024205</v>
+      </c>
+      <c r="R55" t="n">
+        <v>80.21459400000001</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>10926837505978815779</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLd6zXkBZIHUaRTeFgpkt5HXRU260TMMNtWuGCW9qPu4PvmlNeVnk1eDhQdyk0t-Bc-7_ZD_ybzrgy1_ztNm76SIvxwXv1SYSb5gGAAP8usBd-ptdio0_WTgdZ4eHXR5sXZFZ7FzdrqdYbbL=w408-h271-k-no</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>0x3a52671b48ffffe3:0x97a3ecd19e485523</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>ChIJ4___SBtnUjoRI1VIntHso5c</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>{"id":"103106497366196883672","name":"Muscle Factory Gym (Owner)","link":"https://www.google.com/maps/contrib/103106497366196883672"}</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>{"borough":"West Saidapet, Saidapet","street":"1st floor, 29/1, W Jones Rd","city":"Chennai","postal_code":"600015","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>[{"Name":"Manimozhi sivaraj","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIOekqDtrqUQJOQEoQRbwiW4u0eWr85JNSWjjT0GOciNEHf29Y=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Personally very Good and hygiene in place.. we can take a help from the trainers my personal trainer is Mr.Jai he is very professional and friendly person.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfgxgBQ8dJ3YT2Xyr9STev7UQCHYZ7_DoDeb4_MWaXwXly_f6KTZ526JEup281hfoLneySW53ujOF3uoSfeOfQalm-XqNe-ZsPy7u4Ll62y3xwl78EZ0SJ8lPzXyNx3kLXhA2dwlAu1Mbs=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLctd1gm82fhU2ZtTCkE_uu-KbtlTuOudFv2OoNTw309VU0aF_U9L_oxn9wJvsEzTNsycLllP355Nt5z3hemVncxsh7zhsAMazE7cVA8B6DLvVjf-W6mooehVjGbqadR9OJSka6YQ97YjtrR=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd7Vs-vWbeiMrH8disEvgtCmtLppnNEuldag6gICSraGpZh3u3nrX_ESKW7I7hGyEQx3jCxyrS-eRkzXues0sMg464dXsuaoJ3IS-rogGKnUZ3WuXUsT6IsExVitX-01G6PUNvmNZksA4my=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfWEqq9VALE3jRHQLviRq7z1_AKl-3M9ns-EysEkzHoV5VFUXGUU33xUzJjzGbV05tZ-G1g3j2OeApKRj1fUxnEq3IplnhYP6crZLLRtoIxQWeTvbsSlzB_-AWVqlXK5eiGB59-_tUqetuz=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfwEKiaIj2_QzymppcHubS24OLJfv-NmiI9HxunlOCrarrpRseFKYjVmAUlK00HvrwFUk2Prf5tsUrjSYFv2U4hJIHxC0A7FYWFwB3NllTD_0bGBNCGcbz3NSnBxH1bmxA99mQqNQwIPSPy=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeBRVHJBjbz1rneAY7CuXPDfi1iIPq6-EOeqyP8Kd8ekoULZ3IyDBfVanu6QGqn7bDQZ8Cn7Y3ENzXL4Qx75SJ1eAk1p1zZlf8Ckghw1GUmsJXGtKurVq4acfziS4sHqxHunf872dmcTLiq=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21WbmRIVmlOMU5XUWpCNFprRkJTVlpJYVU1SmFXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115360074612444990923/reviews?hl=en-GB","posted_at_unix_micros":1777827048854797,"updated_at_unix_micros":1777827048854797,"language":"en","translated_lang":"","text_original":"Personally very Good and hygiene in place.. we can take a help from the trainers my personal trainer is Mr.Jai he is very professional and friendly person.","text_translated":"","published_at":"2026-05-03T16:50:48.854797Z"},{"Name":"Swetha Suresh","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJILu6gx9RawdcuMy131JQ0yWTJFHzReciAC9-W8uAZ_iwCjkP8=s120-c-rp-mo-br100","Rating":5,"Description":"Great gym with a clean environment and well maintained equipment. Absolutely loving this gym. The trainers are friendly, very special thanks to trainer Jeyawarman always ready to help and motivating and he always makes sure I do exercise with the correct form. Definitely recommend it","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tGZldVZHFSazU2YjJ0Vlkwa3pRekZWYzJGWGNVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108077755111597276200/reviews?hl=en-GB","posted_at_unix_micros":1783609790822608,"updated_at_unix_micros":1783610209490226,"language":"en","translated_lang":"","text_original":"Great gym with a clean environment and well maintained equipment. Absolutely loving this gym. The trainers are friendly, very special thanks to trainer Jeyawarman always ready to help and motivating and he always makes sure I do exercise with the correct form. Definitely recommend it","text_translated":"","published_at":"2026-07-09T15:09:50.822608Z"},{"Name":"Gokulnath D","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVWTn7cw_xeLgH4gwFrLXhqRSKuI2jOsYR_jycgSdavA9z5uR5S=s120-c-rp-mo-br100","Rating":5,"Description":"Feeling truly grateful for both my gym and my incredible coach Ibrahim 💪\n\nThis gym isn’t just a place to work out—it’s a space full of energy, motivation, and positivity. Every session pushes me to go beyond my limits and become stronger, both physically and mentally. The environment here makes you want to show up every single day and give your best.\n\nCoach Ibrahim, your dedication, knowledge, and constant support mean everything. You don’t just train us—you inspire us, guide us, and bring out the best in each one of us. Your belief in me has helped me stay consistent and confident on this journey.\n\nProud to be part of this fitness journey with the best guidance and the best atmosphere.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2t0WlgwRTNVVkYwV25sVFRWRmZSMjVWY1ZaSmNHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109766583061726553041/reviews?hl=en-GB","posted_at_unix_micros":1776522259720429,"updated_at_unix_micros":1776522259720429,"language":"en","translated_lang":"","text_original":"Feeling truly grateful for both my gym and my incredible coach Ibrahim 💪\n\nThis gym isn’t just a place to work out—it’s a space full of energy, motivation, and positivity. Every session pushes me to go beyond my limits and become stronger, both physically and mentally. The environment here makes you want to show up every single day and give your best.\n\nCoach Ibrahim, your dedication, knowledge, and constant support mean everything. You don’t just train us—you inspire us, guide us, and bring out the best in each one of us. Your belief in me has helped me stay consistent and confident on this journey.\n\nProud to be part of this fitness journey with the best guidance and the best atmosphere.","text_translated":"","published_at":"2026-04-18T14:24:19.720429Z"},{"Name":"Sai Adhvik G","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocI6M6me_oQ204lYjkkAFJSXPiTY-44B_PleNvivtdqBv6lhhA=s120-c-rp-mo-br100","Rating":5,"Description":"I’m incredibly grateful to have such an amazing coach like Ibrahim. Your dedication, guidance, and constant encouragement have truly made a difference in my growth. You don’t just teach skills—you inspire confidence, discipline, and a winning mindset.\n\nThank you for always pushing me to be better and believing in me even when I doubt myself. I’m lucky to learn from you.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21SWGNtRnVaa1p5T0daQ05FdG1Wa2RrU2t0dFQxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115276758048535223313/reviews?hl=en-GB","posted_at_unix_micros":1776522167365291,"updated_at_unix_micros":1776522167365291,"language":"en","translated_lang":"","text_original":"I’m incredibly grateful to have such an amazing coach like Ibrahim. Your dedication, guidance, and constant encouragement have truly made a difference in my growth. You don’t just teach skills—you inspire confidence, discipline, and a winning mindset.\n\nThank you for always pushing me to be better and believing in me even when I doubt myself. I’m lucky to learn from you.","text_translated":"","published_at":"2026-04-18T14:22:47.365291Z"},{"Name":"Dhamodharan S","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWPZjaGhOGYStMt6FUJ57b-jvDine07o-d4nFO4Fw4UtfZ2R3Hy=s120-c-rp-mo-br100","Rating":5,"Description":"The space is super clean, well-maintained, and equipped with everything you need - from beginner-friendly machines to advanced workout gear. The trainers are knowledgeable and friendly, which makes it perfect for anyone just starting their fitness journey.\n\nLove the vibe and their motto: “Commit to Fit” - it truly reflects the atmosphere here! 💪🔥","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLc-4uYgSIQgl6Pq0TG1KnnnM5nWUIcCPaxfW9HCjg9tN46o-IYv2zPPl9yFJXZPH8IKue4MZ1I97BipP7PIocCU0ZYZJ3gkPMl9Li6Z25LdpeVEOJVxppJm8aW5DNXm8sSWIohBpOTX0W04=k-no"],"When":"Edited 6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2w5WU5sVlhkMjlPVlhOZlMyTjFibUYwVGxReFNsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108336593531625807295/reviews?hl=en-GB","posted_at_unix_micros":1753711155035226,"updated_at_unix_micros":1774153228883863,"language":"en","translated_lang":"","text_original":"The space is super clean, well-maintained, and equipped with everything you need - from beginner-friendly machines to advanced workout gear. The trainers are knowledgeable and friendly, which makes it perfect for anyone just starting their fitness journey.\n\nLove the vibe and their motto: “Commit to Fit” - it truly reflects the atmosphere here! 💪🔥","text_translated":"","published_at":"2025-07-28T13:59:15.035226Z"}]</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>43</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Pro+Fitness/data=!4m7!3m6!1s0x3a52613d27bb170d:0x8a7f59861725cf3f!8m2!3d13.0303646!4d80.1837911!16s%2Fg%2F11b8yz00lx!19sChIJDRe7Jz1hUjoRP88lF4ZZf4o</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Pro Fitness</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>4, Pro Fitness, 24, Valluvar Salai, Rayala Nagar, Ramapuram, Chennai, Tamil Nadu 600089</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–10 pm"],"Monday":["5 am–10 pm"],"Saturday":["5 am–10 pm"],"Sunday":["5 am–12 pm"],"Thursday":["5 am–10 pm"],"Tuesday":["5 am–10 pm"],"Wednesday":["5 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>096922 88444</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>25JM+4G Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>337</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>{"1":16,"2":2,"3":3,"4":24,"5":292}</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>13.030365</v>
+      </c>
+      <c r="R56" t="n">
+        <v>80.183791</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>9979793731725152063</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLexzsVvvHDdHT1bvOJ_bmGo8Fz69LCaRsEjrX2iXbH3gaL010kS2_BnYpJPs8tDe-J77wL7MeXyw0dA2M1nSglpL3D31cP4Wb-npSoHfyOM9uHC3oVj3p6jp5hR915j-pTgJGM=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>0x3a52613d27bb170d:0x8a7f59861725cf3f</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>ChIJDRe7Jz1hUjoRP88lF4ZZf4o</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>{"id":"115463494573226962958","name":"Pro Fitness (Owner)","link":"https://www.google.com/maps/contrib/115463494573226962958"}</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>{"borough":"Rayala Nagar, Ramapuram","street":"4, 24, Valluvar Salai","city":"Chennai","postal_code":"600089","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>[{"Name":"HARISH MURUGAN","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUWBaWdFLJnoea_nyL-oFm6gDrLW70biQdiGGdkV5AkRWz9PV8=s120-c-rp-mo-br100","Rating":5,"Description":"The gym atmosphere is very fine and clean. Trainers are very supportive and friendly. All equipment are maintained properly and workout experience is super. I am coming daily and feeling motivated and energetic. Overall very good gym for fitness and body transformation Gym is clean and hygienic and the trainers are very friendly to ask help and teach us. Good gym under good budget in Ramapuram. Good for  as well.\nprofitness gym 🤍","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pKNFptZFNlRkJDV1RWUVVHeFNibTl2VkhGV2FHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104083310771825241885/reviews?hl=en-GB","posted_at_unix_micros":1788623516499093,"updated_at_unix_micros":1788623516499093,"language":"en","translated_lang":"","text_original":"The gym atmosphere is very fine and clean. Trainers are very supportive and friendly. All equipment are maintained properly and workout experience is super. I am coming daily and feeling motivated and energetic. Overall very good gym for fitness and body transformation Gym is clean and hygienic and the trainers are very friendly to ask help and teach us. Good gym under good budget in Ramapuram. Good for  as well.\nprofitness gym 🤍","text_translated":"","published_at":"2026-09-05T15:51:56.499093Z"},{"Name":"Dharshini Vaiyapuri","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ-C6TByOQHc_wR7hgShG2IcF0dxa3O9f0Z5bO--qYvvdG0UwU=s120-c-rp-mo-br100","Rating":5,"Description":"Sridhar master Thank you, for your excellent training and constant support. As a sports player, I truly appreciate your dedication, patience, and motivation. Your training methods have helped me improve my strength, fitness, discipline, and confidence. You always encourage me to push my limits and become a better player every day. I am grateful for everything you do. Thank you for being such an inspiring coach.....Sridhar master!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tkc2JuQnFVRzVPZWpOZk1tMXZXSEJQZGw4MFVGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106962704716938458042/reviews?hl=en-GB","posted_at_unix_micros":1785944428235884,"updated_at_unix_micros":1785944428235884,"language":"en","translated_lang":"","text_original":"Sridhar master Thank you, for your excellent training and constant support. As a sports player, I truly appreciate your dedication, patience, and motivation. Your training methods have helped me improve my strength, fitness, discipline, and confidence. You always encourage me to push my limits and become a better player every day. I am grateful for everything you do. Thank you for being such an inspiring coach.....Sridhar master!","text_translated":"","published_at":"2026-08-05T15:40:28.235884Z"},{"Name":"krishnan balakrishnan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJZ40A1UYbwattvoOzsNueGCSKQ4sJnCzzFmBlGo9UM6T_uZLk=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This is Krishnan i joined the gym one month ago..team pro fitness Mr.Tamilnadu \"Sridhar\" Brother is an excellent fitness trainer. His effort for making me fit is awesome. His knowledge about maintaining good health and sharing \u0026 communication is really helping out a lot to stay fit. In addition to fitness he also knows and shares a nutrition diet plan for having good health. The workouts are fun, the fellow members are inspiring, the workouts are led by personal trainers Mr Ajith Brother and Mr Karthik Brother who give hands on instant feedback and adjustments during the workouts and just the right amount of encouragement. The atmosphere is awesome with fully high end fitness equipment. It’s a life changing gym experience and I recommend it highly to all my friends and family.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcou6NGb9djxdPz2lfusoWTMFfj9TLE2no54WswUjw-C4hCGU6Uqwa31RLyR-di6zolZUbTHa-dMsSU5cwVkGG8De-gr6Zq_MyFoVJgYHdqa9AjciuCqDaQUsbD9MXZe8CquvcU=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfanFkMGJh3GAintbW1rxKnw-93wX0EXjqOSPJWVwydee-u7g0F8o5YMk1gf-JU9mZzsNWqHrT8z6NFEtZ_b0UU3nvZ3EGZzr2EtDHOmvABh8kSPk15yYLM-I4KwI2By11aKBDqFA=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdjqAv9R7r6-Ee3y8CSGqaZTtHSbq83YZyOlqmwLSL2BY7LLuI0hRuxjEJTt5YqfC8T4BmqkPp_l5lZ8Y2R-0taZACLjXS4woSpyJ48UrhWro802Jc7XwQUigLUV7cPCFYkTooU=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcT9UyRVnNJ2WuAHSAUUrrfggW1cmo1OqqvvQHnyJSqGoqVFdPUXuqkaS5HI_EGvZzs3yq3HSYAka0Tju6v44wMCJIAYNVfOcdcnBg2V3qBPwmpX1ODoymKthzzWcdjaCSy3T2U=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcV0j2mX4FOmfKvmk7UQfE47u1CebE86czuKGnXRAuDOGaXOOuufzdH6vYpNZto09lyZ_0lWu2t1Z3glu9iHEzJIgCRvdHvRka_3b826Ukm-fTsUi591zZcz287O0SnKXOUStvI=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfH_MPp8C1gr-6Dm9S7V6EyfLC5rZoPxgZzDeqH3JsEAej6ruXrkX1OQRGIBNGsAL255mgAzeta8Vf-5NG-kpnB5gGwPQIbuoCiph8vmMsHhj9tpwQzxwUHNQiBofyIoo8ZirTA0g=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcEiVZ3WokMlFAgUvOwxOLdYjw-AkHAciSPQt7Ht2ysbR00KIf2e40t14lTPr1Urd_iPsJE0Yah5OnKK1DtThStQ6ZIYCOTw_Xen65P8zA39CsR5dEzssc-ISx3XnOL6gpA0B8e=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeVk8kUCWkkvgddXEIcafxR_xRrkXra8pI4oyCpkbTpKEgkRiOcBibarTs3BuWerRr_re2TUmEwPwK4sRuR4BvcbhYOpWI1t6MgSBBgKlRzjGtxRHNzCsaqK-5nleiWQzojxT897Q=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd0G_8ohq6pS3_PkPVR6PIEw1hn9RWu_p2MdknAHYM7MvXEFmSmoojab10Fl_rXCiMEUIL4KeWF-0QKUDMPAiPFcWFnSUCCkGcbqtRQJsfPxwyW3sYq_GA5DviiHzIWz-Dwn0LP=k-no"],"When":"3 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURKNVo2eW1RRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111582959380218769216/reviews?hl=en-GB","posted_at_unix_micros":1689901840026038,"updated_at_unix_micros":1689901840026038,"language":"en","translated_lang":"","text_original":"This is Krishnan i joined the gym one month ago..team pro fitness Mr.Tamilnadu \"Sridhar\" Brother is an excellent fitness trainer. His effort for making me fit is awesome. His knowledge about maintaining good health and sharing \u0026 communication is really helping out a lot to stay fit. In addition to fitness he also knows and shares a nutrition diet plan for having good health. The workouts are fun, the fellow members are inspiring, the workouts are led by personal trainers Mr Ajith Brother and Mr Karthik Brother who give hands on instant feedback and adjustments during the workouts and just the right amount of encouragement. The atmosphere is awesome with fully high end fitness equipment. It’s a life changing gym experience and I recommend it highly to all my friends and family.","text_translated":"","reply_text_original":"Thank you so much sir 🙏🏻💯💪😍\nThank you for sharing your experience with us!  We are so grateful for your kind words and 5-star rating! ..We appreciate your feedback and are delighted to know you enjoyed our service. Thank you for taking the time to leave us a review.","reply_language":"en","reply_posted_at_unix_micros":1690441647000000,"reply_updated_at_unix_micros":1691423037000000,"published_at":"2023-07-21T01:10:40.026038Z"},{"Name":"sathish kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVETHtRkMrJqkyifks-vL3cTBTSvlZk7p9Aclcoy484Bg0jtlKl=s120-c-rp-mo-br100","Rating":5,"Description":"A great place for both beginners and experienced fitness enthusiasts. The trainers are friendly and always ready to guide you through your workouts. I highly recommend joining to turn your fitness goals into reality.","Images":null,"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tKNWRVSmpOM2gzU0Vkd1MzRklSRGhpWXpCV2FXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101568656467645784077/reviews?hl=en-GB","posted_at_unix_micros":1768051580719512,"updated_at_unix_micros":1768051580719512,"language":"en","translated_lang":"","text_original":"A great place for both beginners and experienced fitness enthusiasts. The trainers are friendly and always ready to guide you through your workouts. I highly recommend joining to turn your fitness goals into reality.","text_translated":"","published_at":"2026-01-10T13:26:20.719512Z"},{"Name":"KIT_4_7879 KOTHANDA SARMA M.M","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX_WLWg0acKSqAJh5fgxvZQ7kr-BbPA5-C1mF8SI8Lq8H7XU6jXsg=s120-c-rp-mo-br100","Rating":5,"Description":"Really this gym has high quality imported equipment’s and the space provided is well enough for doing workout .\nMost important thing cleanness is extremely good .\nLast but not least training and trainers are extremely good and experienced.\n.\n.\n.\nIf any body wants to achieve your dream physic . I’ll personally suggest this gym ..!!!!!!!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLellJCwWwP4n7KWuB2cvo4MpW6OmpkAR60lZZ8lwpXQSdGvxG2TMNLYeEFKKCtMQ3xrhJ4Yd-EKe56RYrn2sBk5geyjlXFHNtYQBgmzCCFJ-xS4AhfM_pK3GJrj-XDuU7ZZvt87=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeRSj0RcLjjrp6_olekXyuJqXzwzRG5o4TKotpmlT2RpLwrN0sBKfl6ZmJqJMACN2ip2I-c5BFtySA069iwL6OvnbqwbFy_hPhkRIhsIR9_Cd7KEV_IK55VyEKVfocUSAmcfc2J=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfQ8afDnaphg9gsfPYbSx-ZiMLEOiyG14p-ZkQwd3qOK03XyBozXqueTpe2SxCNOlv2aQHZXPgdNC_AU3fftU8PFVKX-tZrbePbepT-9kJETn9K3-EhsVrLEyOnrEWHMNnk6Xfh4A=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfFrYutRgedg_BTcsyHzN7qUXSQqhzpnCTtcgRHmcRrAyDoo9hDEjKdphK_W_3-1ZE5yD3E8z052IhbeTLtbY-RHD7WP1t_eiSeFk47V5jddcvJeZTMNOJ8YAWgejWN2v-B91w=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfOckLgFwvrslA3e_AKbSqkC7kQkYglceG8yJptI6Z1NFoLUxha-UZv1vgLlS3Q0MsdK-JZvC-Nq4cnLlvwxbVs_9FOJYqlymXF8NnuUPt0jJp1L2R6cOTIuUI1cRJPRBxXllHG=k-no"],"When":"4 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURtOGFtWEtnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112513375540522263002/reviews?hl=en-GB","posted_at_unix_micros":1643695246918769,"updated_at_unix_micros":1643695246918769,"language":"en","translated_lang":"","text_original":"Really this gym has high quality imported equipment’s and the space provided is well enough for doing workout .\nMost important thing cleanness is extremely good .\nLast but not least training and trainers are extremely good and experienced.\n.\n.\n.\nIf any body wants to achieve your dream physic . I’ll personally suggest this gym ..!!!!!!!","text_translated":"","published_at":"2022-02-01T06:00:46.918769Z"}]</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>43</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Elite+Fitness+KK+nagar/data=!4m7!3m6!1s0x3a526765efc91955:0xfeb18e264a1c41ab!8m2!3d13.0365238!4d80.1988748!16s%2Fg%2F11yqp3y2h2!19sChIJVRnJ72VnUjoRq0EcSiaOsf4</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Elite Fitness KK nagar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>NO:12,37, Elite Fitness KK nagar, Anna Main Rd, MGR Nagar, K. K. Nagar, Chennai, Tamil Nadu 600078</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10:30 pm"],"Monday":["5:30 am–10:30 pm"],"Saturday":["5:30 am–10:30 pm"],"Sunday":["7 am–7 pm"],"Thursday":["5:30 am–10:30 pm"],"Tuesday":["5:30 am–10:30 pm"],"Wednesday":["5:30 am–10:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>087788 68611</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>25PX+JG Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>303</v>
+      </c>
+      <c r="O57" t="n">
+        <v>5</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":6,"5":297}</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>13.036524</v>
+      </c>
+      <c r="R57" t="n">
+        <v>80.198875</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>18352606251614749099</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeWMqCA0nq65zOYPr6fiCmk8GHUztckAPtGp6nDX45ityzl5r4D_2njJaO8OWhUjdfdlIlgnXFkVOfP3KcpRPdoL7ucmhNmTZj76P4RV66RpObLs_9vRQcUbncOqNQ5bp9QQ0BfJXzQB1Pb=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>0x3a526765efc91955:0xfeb18e264a1c41ab</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>ChIJVRnJ72VnUjoRq0EcSiaOsf4</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>{"id":"110941879183994897120","name":"Elite Fitness KK nagar (Owner)","link":"https://www.google.com/maps/contrib/110941879183994897120"}</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>{"borough":"MGR Nagar, K. K. Nagar","street":"NO:12,37, Anna Main Rd","city":"Chennai","postal_code":"600078","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>[{"Name":"Poorani Mohan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJSe-PYtBJNMF7bFtjSfMao_XHHe2cnPs7N8N-SUUdtFw0LZA=s120-c-rp-mo-br100","Rating":5,"Description":"I really love my experience at Elite Fitness! The trainers( Sanjay ,ajay and ameen)are very supportive, motivating, and always encourage me to push myself and complete my workouts instead of giving up. I especially love the consistency and positive atmosphere here. As a female, I also feel very comfortable and safe working out here, which makes a big difference. Overall, it’s a great place to stay motivated, build consistency, and enjoy working out. Highly recommended!🫶🏻❤️‍🔥","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLc-DXX0qwuuiwdFRihK1Ty8ShcIAB6rcs6-Ap3DctV7CbPExnPZKOhBVnGO0OvxvlwDmK87d1G9pWrnGScXlKG1-LMp4YLxL7BigIj1wf_7zHG1huWCxwLv13F1Ap9mXdhwkJFjDwhRmDga=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcskErFSqHTbUpXIu1l9hvuKzEYBmhCAutr1kurXDmnzjsoXI-KKwglgWSl_cPTQVwgFinSAsdBYzptzhsX7cmdYNkduPS7HNZsprwU04g3ds81v165xS5tMWA6zOGKWRdtzcOxHnacQ9fq=k-no"],"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25OTmFGRnNia3B2UVhSWGJ6RlFNM0ZLYmpsMk9VRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102106785782959133615/reviews?hl=en-GB","posted_at_unix_micros":1787927337387235,"updated_at_unix_micros":1787927337387235,"language":"en","translated_lang":"","text_original":"I really love my experience at Elite Fitness! The trainers( Sanjay ,ajay and ameen)are very supportive, motivating, and always encourage me to push myself and complete my workouts instead of giving up. I especially love the consistency and positive atmosphere here. As a female, I also feel very comfortable and safe working out here, which makes a big difference. Overall, it’s a great place to stay motivated, build consistency, and enjoy working out. Highly recommended!🫶🏻❤️‍🔥","text_translated":"","reply_text_original":"Thank you so much for this amazing review! 🫶🏻❤️‍🔥 We’re truly happy to know that you’re enjoying your fitness journey at Elite Fitness. A special shoutout to Sanjay, Ajay \u0026 Ameen for always supporting, motivating, and pushing you to give your best! 💪🔥\n\nWe’re especially glad that you feel comfortable, safe, and confident training with us. Your consistency and dedication inspire us too! Keep showing up, keep pushing, and keep getting stronger. ❤️‍🔥\n\nThank you for recommending Elite Fitness! 🏆💙","reply_language":"en","reply_posted_at_unix_micros":1788145579000000,"reply_updated_at_unix_micros":1788145579000000,"published_at":"2026-08-28T14:28:57.387235Z"},{"Name":"kishore kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW5EYZuG8VtV2_H0u9RiaZUj5gOO5YOzcpAP-z24g98LArNkhZhpQ=s120-c-rp-mo-br100","Rating":5,"Description":"Great place to workout 🏋️‍♂️ more space to relax our body 🙌 great atmosphere . Coaches, trainers are friendly and helpful minded persons .","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLeHdpNuC_AEnjNunG2CPHwaHtIZxBK9eVQbG52QP8qMN8HKwdIKa7p-AT9fK0UOLIENT-6RyKM86xP9kELpIn8uxVpFcQcc5wOePHhbBIoSR--FW-ECCd4_QMgVWVLvN3Lf92e_hOquOQ-6=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd0WBMPfI53YHMbn81Bn88MfJwL77iHgec3D2qwoyXwgVDmzsIAEpup9kkiePXciSDZCZ2j3ubTFyXR3rZnXZaDhySz5PQWanBukVL8MU4fRzysFoidCtHjPmb4tA3jO6_2Cxk8XXS4tnjS=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLe5a0G5_ExkNCjzd6fSvXDZ3QWGmFwjyEl2DaZzoKsxEfMEezX-9wV5C99jcvv9zQl4pBfOYoaJYpToM5r1i8cJVMa98SUnI2vqJmMTUTwwNNj-4rXMEG8Loq60agxXG8vLed3l3sNBB5j3=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25WQlkzRnJUbEJqT1hFeWRIaFJlblJuUjJ0c2NtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115665298536241537850/reviews?hl=en-GB","posted_at_unix_micros":1773972863856228,"updated_at_unix_micros":1773972863856228,"language":"en","translated_lang":"","text_original":"Great place to workout 🏋️‍♂️ more space to relax our body 🙌 great atmosphere . Coaches, trainers are friendly and helpful minded persons .","text_translated":"","reply_text_original":"Thank you so much for your wonderful feedback! 😊 We’re really glad to hear that you’re enjoying the space, atmosphere, and overall workout experience at Elite Fitness.\n\nIt’s great to know that our coaches and trainers are making a positive impact with their friendly and supportive approach—that’s exactly what we strive for! 💪\n\nWe truly appreciate your support and look forward to being a part of your fitness journey. Keep pushing! 🙌","reply_language":"en","reply_posted_at_unix_micros":1774357031000000,"reply_updated_at_unix_micros":1774357031000000,"published_at":"2026-03-20T02:14:23.856228Z"},{"Name":"Gunaseelan Annamalai","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIv1ah9M-28LpQceHKO8XqkG5Py7WJBzzqeFem5gsUhBumA9w=s120-c-rp-mo-br100","Rating":5,"Description":"Fantastic gym with a great community vibe. A huge shoutout to the trainers—they are highly motivating, give spot-on form corrections, and actually care about your progress!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdzCZ53UUo5kD92XLBjhejYc9bHFvgmJsoPBRxGurlsyUtt9dmWAHgCZeIHnhINRWWzJVUJcvs8yQJA77gyTSrtPdkkWjCsUM2V8WpRDoZh1ZBLBH1mp5XYchRw7NPAovwi8UOfH85N4D1j=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21oMVZHdFpRMmROUm1sS1pHTlFVMnMyYVVKT1oxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109068662067797389235/reviews?hl=en-GB","posted_at_unix_micros":1782567145735587,"updated_at_unix_micros":1782567145735587,"language":"en","translated_lang":"","text_original":"Fantastic gym with a great community vibe. A huge shoutout to the trainers—they are highly motivating, give spot-on form corrections, and actually care about your progress!","text_translated":"","reply_text_original":"Thank you for the amazing review! ❤️ We're thrilled that you're enjoying the community atmosphere and finding value in our trainers' guidance. Your recognition of their dedication, motivation, and attention to proper form means a lot to us. We're committed to helping every member progress safely and confidently toward their fitness goals. Thank you for being part of our fitness family! 💪🔥\n","reply_language":"en","reply_posted_at_unix_micros":1782569964000000,"reply_updated_at_unix_micros":1782569964000000,"published_at":"2026-06-27T13:32:25.735587Z"},{"Name":"Dinesh Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocICRkN-PoX-wuYMKwEwdttJm4PKaKraYKog8aTncj5NcN_tQQ=s120-c-rp-mo-br100","Rating":5,"Description":"Excellent, good equipments over all good experience, once visit this gym in your life time get motivated by trainers 💪 nice interiors over all I give 100 to the experience","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwTE9FWXpkMWcwUWxOalZVMUhZMjFDZFdsTFVWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102831758500094053120/reviews?hl=en-GB","posted_at_unix_micros":1788605533709555,"updated_at_unix_micros":1788605533709555,"language":"en","translated_lang":"","text_original":"Excellent, good equipments over all good experience, once visit this gym in your life time get motivated by trainers 💪 nice interiors over all I give 100 to the experience","text_translated":"","reply_text_original":"Thank you so much for the fantastic review! 🙌💙 We’re thrilled that you loved our equipment, interiors, and overall experience. Your 100/100 rating truly means a lot to our entire team! 💪🔥 We look forward to keeping you motivated and helping you achieve your fitness goals at Elite Fitness. 🏆","reply_language":"en","reply_posted_at_unix_micros":1788922768000000,"reply_updated_at_unix_micros":1788922768000000,"published_at":"2026-09-05T10:52:13.709555Z"},{"Name":"Kavipriya Mathivanan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIV5roA0S-joO-GCAvEydDH68ojxQFsZKTI8AXTOT4zoxZkWg=s120-c-rp-mo-br100","Rating":5,"Description":"Great gym with good equipment and a clean environment.Trainers are friendly and supportive. Perfect place for anyone who wants to stay fit and build a good physique.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwT1QwVXdZWGN3VWt4TmEzbFlkalJvZDAxVFdtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118351760299438399982/reviews?hl=en-GB","posted_at_unix_micros":1788618237259047,"updated_at_unix_micros":1788618237259047,"language":"en","translated_lang":"","text_original":"Great gym with good equipment and a clean environment.Trainers are friendly and supportive. Perfect place for anyone who wants to stay fit and build a good physique.","text_translated":"","reply_text_original":"Thank you so much for the wonderful review! 🙌💙 We’re glad you’re enjoying our equipment, clean environment, and the support from our trainers. Your words motivate our entire team to keep delivering the best fitness experience. 💪🔥 Looking forward to seeing you achieve your fitness goals with Elite Fitness! 🏋️‍♂️","reply_language":"en","reply_posted_at_unix_micros":1788922677000000,"reply_updated_at_unix_micros":1788922677000000,"published_at":"2026-09-05T14:23:57.259047Z"}]</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>43</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/C3+Fitness+Science+Elite/data=!4m7!3m6!1s0x3a5265995cb65057:0xe8194690eecc1690!8m2!3d13.1190387!4d80.2595392!16s%2Fg%2F11f_kmwnbw!19sChIJV1C2XJllUjoRkBbM7pBGGeg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>C3 Fitness Science Elite</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>No.311, MKB Nagar West Ave, Above Nilgiris, Mahakavi Bharathi Nagar, Vyasarpadi, Chennai, Tamil Nadu 600039</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["6 am–2 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>097909 50309</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>4795+JR Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>297</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>{"1":20,"2":3,"3":9,"4":24,"5":241}</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>13.119039</v>
+      </c>
+      <c r="R58" t="n">
+        <v>80.259539</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>16724476279512635024</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfNct8rcgeBvtzspvmBrhrr8xbffoEcslmX6dShaFo1UtKz9YvSh0KAIM3t-b9LbviXlype2ZDum1FnraGu758wDhGCqYor_qwO-F7HSc2bnyXqZFZCBjLTOxgAvf1SBfXYZ8nb5VNvH7XW=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>0x3a5265995cb65057:0xe8194690eecc1690</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>ChIJV1C2XJllUjoRkBbM7pBGGeg</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>{"id":"106889155407793195360","name":"C3 Fitness Science Elite (Owner)","link":"https://www.google.com/maps/contrib/106889155407793195360"}</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>{"borough":"Mahakavi Bharathi Nagar, Vyasarpadi","street":"No.311, MKB Nagar West Ave, Above Nilgiris","city":"Chennai","postal_code":"600039","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>[{"Name":"padma Priya","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWSuh0y-ArJGdVv-VwM-WSL4iq2Q_Vv49xPpAJ9lK_jtEeEP1fx=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Excellent gym with modern equipment and a clean, spacious setup. The trainer Mr.vinoth  are friendly, professional, and always ready to guide properly. The atmosphere is very motivating and suitable for both beginners and regular gym-goers.”","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pRNFpqRm1TMnBtWlhOR1NrNVdkV3hmZFhocGVYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102247809758421555774/reviews?hl=en-GB","posted_at_unix_micros":1770350586372623,"updated_at_unix_micros":1770350586372623,"language":"en","translated_lang":"","text_original":"Excellent gym with modern equipment and a clean, spacious setup. The trainer Mr.vinoth  are friendly, professional, and always ready to guide properly. The atmosphere is very motivating and suitable for both beginners and regular gym-goers.”","text_translated":"","published_at":"2026-02-06T04:03:06.372623Z"},{"Name":"ABDUL Hameed","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXpBfd_2EClw0QphIKVRa1QHsE0wiLedNFZE2UAZtdkyzCDdaU=s120-c-rp-mo-br100","Rating":5,"Description":"I was training here from past 1year, well maintained and good trainer person especially my trainer Mr.Naveen very much helpful and coordinate person. Highly recommend to this gym","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcy9q1xP4Dkeip0FjIZxKkR1hEBcXPyVK1I8C_QlJw0yjWi3NRkE-yCTbOBaUq-4pAT8Mx8iyejD5Vt5rXa7AAUzUx2OJosdZiZg93Yti0WEz1YbIUXPJ9RlsxVzz2h8vmlDK-D8Ldw2TA=k-no"],"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xKYVZFMU1kMU41UVV0NWVHcHlUelowWHpWaE4xRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107723484334663993417/reviews?hl=en-GB","posted_at_unix_micros":1769147513265889,"updated_at_unix_micros":1769147513265889,"language":"en","translated_lang":"","text_original":"I was training here from past 1year, well maintained and good trainer person especially my trainer Mr.Naveen very much helpful and coordinate person. Highly recommend to this gym","text_translated":"","published_at":"2026-01-23T05:51:53.265889Z"},{"Name":"Kalaivani Ellappan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIU7gRQIcTc94yFSLaHR-IrasTQ6biWnic2Up9p5lNHwWCjNQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’ve been training with RAHUL(Trainer) for the past Few weeks, and I can confidently say he is the best trainer I’ve come across. Whether it’s strength training, weight loss, or building endurance, he tailors each session to my specific goals.\nWhat makes him stand out is the constant motivation, attention to form and posture, and the ability to push me just the right amount. I’ve lost weight and improved my overall fitness under his guidance.\nif you’re looking for results, this is the best place.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfNct8rcgeBvtzspvmBrhrr8xbffoEcslmX6dShaFo1UtKz9YvSh0KAIM3t-b9LbviXlype2ZDum1FnraGu758wDhGCqYor_qwO-F7HSc2bnyXqZFZCBjLTOxgAvf1SBfXYZ8nb5VNvH7XW=k-no"],"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tOWWJqWm5UMnhWYVhwaVFXZGxZbWxYYzJsMGRIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104211709983609276192/reviews?hl=en-GB","posted_at_unix_micros":1752043226340511,"updated_at_unix_micros":1752043226340511,"language":"en","translated_lang":"","text_original":"I’ve been training with RAHUL(Trainer) for the past Few weeks, and I can confidently say he is the best trainer I’ve come across. Whether it’s strength training, weight loss, or building endurance, he tailors each session to my specific goals.\nWhat makes him stand out is the constant motivation, attention to form and posture, and the ability to push me just the right amount. I’ve lost weight and improved my overall fitness under his guidance.\nif you’re looking for results, this is the best place.","text_translated":"","published_at":"2025-07-09T06:40:26.340511Z"},{"Name":"Sanjai .V","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK1Sb4LRzYAA6wenuc1aJ8JAKIHm3dRARZ9U8fIDtzoR0uD7A=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training in this gym for the past three years and its been a wonderful experience. Great atmosphere and good trainers and trainer Dhanush was my personal trainer and he did an excellent work and still does ..💪🏽","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwYWJVRTRUVW8wTWpRNWJsbGxjRGRpV2tKcWJGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112494943485813497861/reviews?hl=en-GB","posted_at_unix_micros":1770218650767352,"updated_at_unix_micros":1770218650767352,"language":"en","translated_lang":"","text_original":"I’ve been training in this gym for the past three years and its been a wonderful experience. Great atmosphere and good trainers and trainer Dhanush was my personal trainer and he did an excellent work and still does ..💪🏽","text_translated":"","published_at":"2026-02-04T15:24:10.767352Z"},{"Name":"M.sakthi Pandiyan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKslXav0moMitR_TGJen8sx2U7pjdnuscjXriRtDacHfxNTJg=s120-c-rp-mo-br100","Rating":4,"Description":"Trainer Dhanush is a very supportive and motivating trainer. He explains  trainer dhanush workouts clearly and makes sure exercises are done safely and correctly. He encourages consistency and helps improve strength and fitness step by step. His friendly nature makes training comfortable and enjoyable. Highly recommended for anyone who wants to stay fit and healthy.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdmcpcV732lRPXN24GCxefnph0zh3P9gcRSQjdSJISGE8fSrcAu1ZvyHkG2Q1NPj_-Bs6yQ4k9t0YmxeHHiNPfMokPhmlo9gUD-ueptdZTqCL3G9ZNhtYu1rizgAKD5ZVw8fTl5iemIO_E=k-no"],"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT201dlkwc3habWN0VUZaNk16WlFSRzVQYkRORVRIYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/111001499370688614294/reviews?hl=en-GB","posted_at_unix_micros":1770227902330070,"updated_at_unix_micros":1770227902330070,"language":"en","translated_lang":"","text_original":"Trainer Dhanush is a very supportive and motivating trainer. He explains  trainer dhanush workouts clearly and makes sure exercises are done safely and correctly. He encourages consistency and helps improve strength and fitness step by step. His friendly nature makes training comfortable and enjoyable. Highly recommended for anyone who wants to stay fit and healthy.","text_translated":"","published_at":"2026-02-04T17:58:22.33007Z"}]</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>43</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Club+%23360+Fitness+Studio+Mogappair+West/data=!4m7!3m6!1s0x3a5263827885aabb:0x24b630312e6db8d7!8m2!3d13.0831432!4d80.1715234!16s%2Fg%2F11sgmzznqh!19sChIJu6qFeIJjUjoR17htLjEwtiQ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Club #360 Fitness Studio Mogappair West</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>PC03/19A JPC Main Road, Mogappair West Main Rd, Chennai, Tamil Nadu 600037</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["7 am–1 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>070923 47777</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>35MC+7J Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>264</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>{"1":4,"2":1,"3":1,"4":8,"5":250}</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>13.083143</v>
+      </c>
+      <c r="R59" t="n">
+        <v>80.17152299999999</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>2645354818917218519</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdpEgp-DSpnUBkJP8n_7IYX4L547q6EbIt7koDeke0Nait1K3y-Xe7L0TbtarnyOuhZ9Z30Ro1ZC99k_skIE0UzY_xN9H7rcQ0Q1f2KbSB5bwiqEWr94xWkn7TZvY3KsHj8R-U=w428-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>0x3a5263827885aabb:0x24b630312e6db8d7</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>ChIJu6qFeIJjUjoR17htLjEwtiQ</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[{"link":"https://shop.zuyyu.com/d658460a-5f0d-4327-a36f-af8e3782e18c/menu?rwg_token=AE37R_iu2hqi8GfekckQSNjrJKVF16OjBNM3-WlkMc2-rNyZTtqld_y1XtDOtcPq53lqWzkVe6IM2vSBjB-41i6G0x4n8fTOUp4_4m6sAtjBAGsE9M7LkQY%3D","source":"zuyyu.com"}]</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>{"id":"112521345557875430608","name":"Club #360 Fitness Studio Mogappair West (Owner)","link":"https://www.google.com/maps/contrib/112521345557875430608"}</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>{"borough":"Mogappair West, Mohanram Nagar, Mogappair","street":"PC03/19A JPC Main Road, Mogappair West Main Rd","city":"Chennai","postal_code":"600037","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>[{"Name":"gango gangsta","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJDmepO4RKdlFgi-G7jrmD523-IWSylA_oHWihjM0UOiHnFPQ=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been a part of Club 360 since 2018 and it has played a major role in my body transformation and overall fitness journey. The gym is equipped with the best strength machines, advanced cardio setup and even a dedicated floor for functional workouts – everything you need under one roof.\n\nA huge part of my transformation goes to my trainer “PANDIYARAJAN” who has been the biggest pillar of support throughout my journey. From being an oversized 110 kg guy at 6 feet tall, he helped me transform into someone confident enough to walk the ramp. He pushed my limits and believed in me more than I ever did. He gave me the strength and motivation to reach my goals. I can never thank him enough, he’s not just my coach but also a true friend.\n\nBig thanks to Club 360 for giving me not just a gym, but a family-like vibe. Special thanks as well to Coach Dhaya, Vasu and all the trainers for their constant support. Truly grateful for this amazing journey!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdsAEwKXeDoDkAgHk0XkV2TlqV0a-ikHF1QiqrXVj9Y_XVe8GmKbiiuhBxK3d5frftvic1cumvlHnHTJOOzrxirBUjpfE3NKZJ6ultqPAizC7BPzuvgfZVhS5QMEEpPF_moP0ghArrt9f6K=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfQLQFUD4YJUJK2XpJiJVmzoNcrp_1xIq9ZaX-rvJXLpYNiNq7caMx_4lEadErQDxh5kLXN3ET27l_4mWOKyihBOpvO76-mwQX2T13tKwN_It69p_6xghKLKU3NONrZXsg2YwH-3wxqpsMR=k-no"],"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21sQmNtWTNRa3BGVTNJeVpWQjBPVU10T0hKelJuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110112166496382891870/reviews?hl=en-GB","posted_at_unix_micros":1755947823054415,"updated_at_unix_micros":1755947823054415,"language":"en","translated_lang":"","text_original":"I’ve been a part of Club 360 since 2018 and it has played a major role in my body transformation and overall fitness journey. The gym is equipped with the best strength machines, advanced cardio setup and even a dedicated floor for functional workouts – everything you need under one roof.\n\nA huge part of my transformation goes to my trainer “PANDIYARAJAN” who has been the biggest pillar of support throughout my journey. From being an oversized 110 kg guy at 6 feet tall, he helped me transform into someone confident enough to walk the ramp. He pushed my limits and believed in me more than I ever did. He gave me the strength and motivation to reach my goals. I can never thank him enough, he’s not just my coach but also a true friend.\n\nBig thanks to Club 360 for giving me not just a gym, but a family-like vibe. Special thanks as well to Coach Dhaya, Vasu and all the trainers for their constant support. Truly grateful for this amazing journey!","text_translated":"","reply_text_original":"Dear Gango Gangsta,\nMr Pandian one of the well experienced Senior Trainer in our studio. We glad you happy with our service. your words will definitely motivate our staff to give the best. Thanks for recommending us,\nGood luck for your fitness journey .Warm regards!!\n","reply_language":"en","reply_posted_at_unix_micros":1767150143000000,"reply_updated_at_unix_micros":1767150143000000,"published_at":"2025-08-23T11:17:03.054415Z"},{"Name":"Anton Dayanithi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUw__Rw_o5Co6KMSW0H8i_7GjHn44Dh1v_wNoctSNUBFd3_YSl3LQ=s120-c-rp-mo-br100","Rating":5,"Description":"An amazing place for fitness training… the trainers are amazing who are very friendly and they make sure they bring the results.\nMy coach Venkat has put a great effort to bring transformation for me, where I was able to reduce from 98kg to 78kg is 6months which was a tough process as I also has some surgery on legs. My coach trained me in such a way where I was able to strengthen my weakness.\nThe place has helped me to follow some disciplines.\nThey have a very good place for functional workouts as well","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLd2tJuLUmYZ9ucuoS9pMkPayYvevqgVYRjC-YfhJv0nXKg24gF8qdK8wnU4vR83lnV6HBIEYpxWgq3qvvcR_bweZ2Knsku_eEYChYJ20sbTx6inw0cCV0hch6gknUkxg83lL2It=k-no"],"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNsLWZLaUNnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112540635654599674890/reviews?hl=en-GB","posted_at_unix_micros":1700654548206218,"updated_at_unix_micros":1700654729346379,"language":"en","translated_lang":"","text_original":"An amazing place for fitness training… the trainers are amazing who are very friendly and they make sure they bring the results.\nMy coach Venkat has put a great effort to bring transformation for me, where I was able to reduce from 98kg to 78kg is 6months which was a tough process as I also has some surgery on legs. My coach trained me in such a way where I was able to strengthen my weakness.\nThe place has helped me to follow some disciplines.\nThey have a very good place for functional workouts as well","text_translated":"","reply_text_original":"Dear Anton,\n\nThanks for recommending us, Good luck for your fitness journey, We glad you are happy with our service. your words will definitely motivate our staff Mr.Venkat to give the best service. Warm regard!!!\n","reply_language":"en","reply_posted_at_unix_micros":1701131793000000,"reply_updated_at_unix_micros":1701131793000000,"published_at":"2023-11-22T12:02:28.206218Z"},{"Name":"Kingsly Arun Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXaJ0beiNzvU1zrftMnoJCT_Vkxwn3-cZCmtrN7dnWBqXOWrst6=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I have been training with this gym for the past 3 months. Quality equipments with quality trainers, good ambiance and located in prime area with sufficient parking space. Separate floors for weight training and CrossFit training.   I strongly recommend this gym for the ppl who are looking out for personal training. Also a special mention to my personal trainer Mr. Venkat. He is highly qualified coach in training routine and diet consultation and weight loss and CrossFit training.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLffatmwsdY8j1a_qokrHvSg9vEkicZwmGK8n7-GBAharnDygl3HO_d4w2b-Kh1RT3zzUa5afRePeUSEe1GBUve9MkZHJPx_WJcBso9WSYygN45imXZ_iHnzFJAbQeUQlBuU-RU=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcVL-DSO_kvtPROiWnogjGrMO6CEx78X5A7o7w3hBtqUbF3psbUIeaRHo1B73aa1LiJehvLdHhH9oG5qCdkoFFOGpVjxdgbWWFbjJT5ZVW5sTk0sPrW2u7g2p_OYjwACGaRxUVG5Q=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLft02EjAG4_-C-mQ174FEAOQadAifWQPb99YvRFlVe7aXEeiwYOQMLdNtdiSWwIQOGeRUMDb_nUCwZy2EzUwLU-LJ0_X6zUnh18vSOHBuZ6OV_4gISEmYhF1hcv6NOFyMo9TPIb=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLf-Oy5Dfy8RbejnNYqI1NP93Fabxk-ZfTfTx1AjKcfh0FkXcjhtDshCkZYOFT4ypb38J7pM3vusgcOAU1RBbxnz7Tq7tvgyqiBWFYsqkcwAUsNyA6aTVUIWei_UHnnmB448f9YtjA=k-no"],"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNtMDkzTzdBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115384754450850098465/reviews?hl=en-GB","posted_at_unix_micros":1641657679811571,"updated_at_unix_micros":1641657679811571,"language":"en","translated_lang":"","text_original":"I have been training with this gym for the past 3 months. Quality equipments with quality trainers, good ambiance and located in prime area with sufficient parking space. Separate floors for weight training and CrossFit training.   I strongly recommend this gym for the ppl who are looking out for personal training. Also a special mention to my personal trainer Mr. Venkat. He is highly qualified coach in training routine and diet consultation and weight loss and CrossFit training.","text_translated":"","reply_text_original":"Hello Kingsly. Thanks for the review. Mr venkat will be inspired to even better from your kind words. We will strive for the best always. Regards","reply_language":"en","reply_posted_at_unix_micros":1643592149000000,"reply_updated_at_unix_micros":1643592149000000,"published_at":"2022-01-08T16:01:19.811571Z"},{"Name":"Chithran R","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU5W3rY5omjzJeXza2GVwfJQygtmZoA7_cg8QkoZno_K-lBYP_m=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"One of the best gyms in mogapair. The coaches guide us based on our goals. They help you maintain fitness as a part of our lifestyle.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcBXg5JdAk4DiCLN5689D91wUazUAwdu8pYNAj0ORToDFKkuV6d1PVOAsc6LPRLXPVuAKi5Ylr6e9AIfGD8JfNjiCA8Tk0jVfAflEBfdJ0wPnmlzrDrmaC4WvVOFX_hN-TlaPoPiDV68oUk=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeV1PAisVkju5X7adGsBlpk43ooZlUuV7tU5-gjUClFIIOwWbp9Gy6ikcbqxFNtfq_vu8Df0ruFSwxJjQ3hFcHrSYS9vzqhn9hVlnYdp-DnwXQmrqQtQlf8uCo5ryd5MQAZbt6Z3aIqVY2K=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLehdvgPbSO6mdMFoK8y-FP700VRmx75pHdW6yx1XTEjsxaZ-WF87xOzMgWSvpKnl2yYmg6yBQxrPw4qLZ5yhPyyAVLzSuu97MKB-CYPQwRtI1IT6pCakc3Cx-0r9vkICG-2S4yvFslLpKE4=k-no"],"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xnNFZHeHFhbk5aUWpGeGFXTTBPRFl3U0ZCeVgyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101277198624055078046/reviews?hl=en-GB","posted_at_unix_micros":1768685807646958,"updated_at_unix_micros":1768685807646958,"language":"en","translated_lang":"","text_original":"One of the best gyms in mogapair. The coaches guide us based on our goals. They help you maintain fitness as a part of our lifestyle.","text_translated":"","reply_text_original":"Dear Chithran\nGood luck for your fitness journey, We are glad that you are happy with our service, your words will definitely motivate our coach to give best service. Thanks for recommending us, Warm regard!!!\n","reply_language":"en","reply_posted_at_unix_micros":1781061676000000,"reply_updated_at_unix_micros":1781061676000000,"published_at":"2026-01-17T21:36:47.646958Z"},{"Name":"Nirmal kumar NK","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVSXG_DvG0xVcmY4CFNHyn9b8ArO4bKohzaAnevA7p7b4WAddA=s120-c-rp-mo-br100","Rating":5,"Description":"I had a great experience at Club 360, Mogappair and achieved very good results here. The gym has a positive environment, and all the coaches are very friendly, supportive, and train you properly with the right techniques.\n\nA special mention to my coach Mr. Pandiya Rajan, who guided me consistently, monitored my progress closely, and motivated me throughout my fitness journey. His coaching and dedication made a big difference in my results.\n\nI highly recommend Club 360 Mogappair to anyone looking for serious training with professional and supportive trainers.","Images":null,"When":"10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pObkxXRjFaa0o2WmpVNWMzcHhNbmxqZVZRNGVYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101089496966639827708/reviews?hl=en-GB","posted_at_unix_micros":1765770209020948,"updated_at_unix_micros":1765770209020948,"language":"en","translated_lang":"","text_original":"I had a great experience at Club 360, Mogappair and achieved very good results here. The gym has a positive environment, and all the coaches are very friendly, supportive, and train you properly with the right techniques.\n\nA special mention to my coach Mr. Pandiya Rajan, who guided me consistently, monitored my progress closely, and motivated me throughout my fitness journey. His coaching and dedication made a big difference in my results.\n\nI highly recommend Club 360 Mogappair to anyone looking for serious training with professional and supportive trainers.","text_translated":"","reply_text_original":"Dear Nirmal Kumar\nGood luck for your fitness journey, We glad you are happy with our service, your words will definitely motivate our staff Mr.Pandian to give the best service. Thanks for recommending us, Warm regard!!!\n","reply_language":"en","reply_posted_at_unix_micros":1767150283000000,"reply_updated_at_unix_micros":1767150283000000,"published_at":"2025-12-15T03:43:29.020948Z"}]</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>43</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/WESIX+LIFESTYLE+%26+FITNESS+HUB/data=!4m7!3m6!1s0x3a5267e1074be893:0x637766b3e4c98e44!8m2!3d13.0430145!4d80.1936356!16s%2Fg%2F11y29nzb0s!19sChIJk-hLB-FnUjoRRI7J5LNmd2M</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>WESIX LIFESTYLE &amp; FITNESS HUB</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>No:774/154, WESIX LIFESTYLE &amp; FITNESS HUB, Wesix Fitness Hub, Munusamy Salai, Bangaru Colony, K. K. Nagar, Chennai, Tamil Nadu 600078</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–10 pm"],"Monday":["5 am–10 pm"],"Saturday":["5 am–10 pm"],"Sunday":["7 am–7 pm"],"Thursday":["5 am–10 pm"],"Tuesday":["5 am–10 pm"],"Wednesday":["5 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>093440 71571</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>25VV+6F Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>243</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>{"1":8,"2":0,"3":2,"4":10,"5":223}</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>13.043014</v>
+      </c>
+      <c r="R60" t="n">
+        <v>80.193636</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>7167310254807027268</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLecX-kKsKFK4PsMdf79LnlASctJaVOmcruHPV2XUT0PWAa9ozWG95iOeYLThUbSl-KyT5ttec02DaCBrT8zLCvg8T2OM5GHQ84u3MOdc1swL6U1En4QSyQ2gtxhtAUCBLfWcNgMCG03SIr_=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>0x3a5267e1074be893:0x637766b3e4c98e44</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>ChIJk-hLB-FnUjoRRI7J5LNmd2M</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>{"id":"104420497542804114400","name":"WESIX LIFESTYLE \u0026 FITNESS HUB (Owner)","link":"https://www.google.com/maps/contrib/104420497542804114400"}</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>{"borough":"Bangaru Colony, K. K. Nagar","street":"No:774/154, Wesix Fitness Hub, Munusamy Salai","city":"Chennai","postal_code":"600078","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Assistive hearing loop","enabled":false},{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false},{"name":"Wheelchair-accessible seating","enabled":false},{"name":"Wheelchair-accessible toilet","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>[{"Name":"PRANAV.K","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX_HaDJpBMQbXJAyPyNAVU2Rd17n3H2x9O4bLDyMzWrzWZ9OBnX=s120-c-rp-mo-br100","Rating":5,"Description":"Joined Wesix Fitness as a complete beginner and felt comfortable from day one. The trainers are supportive, patient, and always ready to help with proper form and technique. The gym is clean, well-maintained, and has a great atmosphere. Highly recommended for anyone starting their fitness journey.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfaQkuDdGKTGQJiKLfq0mlJpp1DflYaj3eqGTPlIoRQvCWtrivxEaG5XOKQWG0E-51FZzqFWYwVcEAUK4a6nRKz2m8XPts_gYwS8uOoxOJkJ2ggTp2M_WA9ALPVqoLtrZhxc6i7ydZgFkJC=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLflAMQa754Rnk_prYImb3NKMcOhgAU7UqDorywS9k8R9tWsulC82DOibgM11vcARw2yqmwc_JabE7Lr_aFXAkgR7Abtc36ohHyWaM95nrdHO1BSCKgOVhaXYR3r6QwKlMcVspJZtwFtS28=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21WYU0zRjBNa0ZXUjJ0WFRqaHZUUzF6VVVKTmFVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111149483134172264763/reviews?hl=en-GB","posted_at_unix_micros":1781360649445125,"updated_at_unix_micros":1781360649445125,"language":"en","translated_lang":"","text_original":"Joined Wesix Fitness as a complete beginner and felt comfortable from day one. The trainers are supportive, patient, and always ready to help with proper form and technique. The gym is clean, well-maintained, and has a great atmosphere. Highly recommended for anyone starting their fitness journey.","text_translated":"","published_at":"2026-06-13T14:24:09.445125Z"},{"Name":"Lakshmi","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLvQfxDWhAyxLhGxdLbFa4Z0zGVsjUZfAAPbA4Srvr8x3Qf_g=s120-c-rp-mo-br100","Rating":5,"Description":"Me and my friend joined Wesix Fitness as complete beginners, and we already feel more confident and active. The trainers explain workouts clearly, correct our form properly, and never make beginners feel judged. Great atmosphere and positive vibe throughout the gym.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLd3iVF0upjQBwNcxCsPHfA49rHpMSaGs_HglpNNYThm9xNP4vA5giuB4UZZsQRbfntb4kjbfWpSZaRPgawCjpU7Kfe3LlP_tK4M9lqo16k27r9tE0IfgyAUhmri5l-VdWHTwt6mrY7Y-CqN=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLc1satFXhG68qwh5WG_cxd8SpnNkujmPl0-T9Iesl0O1FMP4RS93CR846k695nb3955kD0Jlbu4hLF7fCzuVMFECmxcRq_RLU05Cb7OH6xJBcQAXk9LOBT-s2Wwecpsi_7NeMHgQ5QFLA8=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psSE9VRjZZM1l0VnpsbU5WQktTRGxTZW5sSFQyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106318455138097646661/reviews?hl=en-GB","posted_at_unix_micros":1780756688766619,"updated_at_unix_micros":1780757176498292,"language":"en","translated_lang":"","text_original":"Me and my friend joined Wesix Fitness as complete beginners, and we already feel more confident and active. The trainers explain workouts clearly, correct our form properly, and never make beginners feel judged. Great atmosphere and positive vibe throughout the gym.","text_translated":"","published_at":"2026-06-06T14:38:08.766619Z"},{"Name":"Sangeetha M","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVBwsuwpQRZT8rs61pLlUuuNrGkfTTbSa5DePoz9EFJ686lZ-Tr=s120-c-rp-mo-br100","Rating":5,"Description":"I've been training at this gym for the past three months, and it has been one of the best decisions I've made for my fitness journey. As a woman who values both fitness and overall well-being, I truly appreciate the positive ambience and motivating atmosphere here.\n\nThe trainers are highly professional, knowledgeable, and always ready to guide and encourage you with the right techniques. The gym is well-organized with three dedicated floors for cardio, strength training, and Zumba, making every workout comfortable and focused.\n\nWhat I love the most is the friendly and welcoming environment. Whether you're a beginner or someone experienced, you'll feel supported throughout your journey. If you're looking for a place that combines professionalism, great facilities, and a positive fitness community, I highly recommend this gym. It's a place where you don't just work out you build a healthier, stronger version of yourself.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pFd2RXbHlWRTVyV21ReVprUnROVXBWZFVOMllsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112067826721298886440/reviews?hl=en-GB","posted_at_unix_micros":1785940907079467,"updated_at_unix_micros":1785940907079467,"language":"en","translated_lang":"","text_original":"I've been training at this gym for the past three months, and it has been one of the best decisions I've made for my fitness journey. As a woman who values both fitness and overall well-being, I truly appreciate the positive ambience and motivating atmosphere here.\n\nThe trainers are highly professional, knowledgeable, and always ready to guide and encourage you with the right techniques. The gym is well-organized with three dedicated floors for cardio, strength training, and Zumba, making every workout comfortable and focused.\n\nWhat I love the most is the friendly and welcoming environment. Whether you're a beginner or someone experienced, you'll feel supported throughout your journey. If you're looking for a place that combines professionalism, great facilities, and a positive fitness community, I highly recommend this gym. It's a place where you don't just work out you build a healthier, stronger version of yourself.","text_translated":"","published_at":"2026-08-05T14:41:47.079467Z"},{"Name":"Bark Bork","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKsbWkZd82sGd7WyRLn4Oap-rR7Ve7mn0IoUdCFKznKXB4CaQ=s120-c-rp-mo-br100","Rating":5,"Description":"As a beginner, I was honestly nervous to join a gym, but Wesix Fitness made the experience super comfortable. The trainers are very supportive, guide us patiently, and the environment feels friendly and motivating. Perfect place to start a fitness journey.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLenn5kFCHhf8_s1HaG9-2m7xjQkOANWSx2XBZemBpNFMI5cwq20Gyr6PEFkEK4MnCDykQplkJxAjvC9-6mreudP_gwddJK0tX5OlwbkERKhMXLVxjrCvVznSZrT7lLerwAb6MSPdqUSs1v4=k-no"],"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pkTWFFTnFTekpWVWpkbllXNWpNSHBJY2tZMlVHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108151227834632461571/reviews?hl=en-GB","posted_at_unix_micros":1780756669168842,"updated_at_unix_micros":1780756669168842,"language":"en","translated_lang":"","text_original":"As a beginner, I was honestly nervous to join a gym, but Wesix Fitness made the experience super comfortable. The trainers are very supportive, guide us patiently, and the environment feels friendly and motivating. Perfect place to start a fitness journey.","text_translated":"","published_at":"2026-06-06T14:37:49.168842Z"},{"Name":"Sulaiman A","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocITpwYdwZ9z8SDcmKodBID0aa5nLM-hdTTARPGtFT2f4JO8-g=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve had a great experience at Wesix Gym. The trainers are knowledgeable, friendly, and genuinely care about helping members achieve their fitness goals. The gym is clean, well-equipped, and has a motivating atmosphere that makes every workout enjoyable.\n\nWhether you’re a beginner or experienced, Wesix Gym provides the right guidance and support. Highly recommended for anyone looking to start or level up their fitness journey!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21ad1VtWnBMV1J6VTJSTlF6QkNiME5sUTNCQ2FVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115873048562053714366/reviews?hl=en-GB","posted_at_unix_micros":1785321233133226,"updated_at_unix_micros":1785321233133226,"language":"en","translated_lang":"","text_original":"I’ve had a great experience at Wesix Gym. The trainers are knowledgeable, friendly, and genuinely care about helping members achieve their fitness goals. The gym is clean, well-equipped, and has a motivating atmosphere that makes every workout enjoyable.\n\nWhether you’re a beginner or experienced, Wesix Gym provides the right guidance and support. Highly recommended for anyone looking to start or level up their fitness journey!","text_translated":"","published_at":"2026-07-29T10:33:53.133226Z"}]</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>43</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/C3+Fitness+Science+%28Kilpauk%29/data=!4m7!3m6!1s0x3a52667fb08bc5af:0xe22429d185021ed5!8m2!3d13.0785658!4d80.2339787!16s%2Fg%2F11f0_dqtr1!19sChIJr8WLsH9mUjoR1R4ChdEpJOI</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>C3 Fitness Science (Kilpauk)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>17 Lakshmi Street, New Avadi Rd, Kilpauk, Chennai, Tamil Nadu 600010</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9:45 pm"],"Monday":["6 am–9:45 pm"],"Saturday":["6 am–9:45 pm"],"Sunday":["6 am–12 am"],"Thursday":["6 am–9:45 pm"],"Tuesday":["6 am–9:45 pm"],"Wednesday":["6 am–9:45 pm"]}</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>091768 99333</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>36HM+CH Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>221</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>{"1":30,"2":3,"3":5,"4":31,"5":152}</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>13.078566</v>
+      </c>
+      <c r="R61" t="n">
+        <v>80.23397900000001</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>16295195331589709525</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfdlzF7sFM20L3CJSK7voePCXcVr-5FTPcsgbhYdchBLUrbAy3xNbbjaaWBrW3xzBnP2W9hq44YZPigDETRz0Z9jeE86CTohnpLPw27UjQUKcbaFl6cP2Xuh2nWbuarNaN8rUgS=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>0x3a52667fb08bc5af:0xe22429d185021ed5</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>ChIJr8WLsH9mUjoR1R4ChdEpJOI</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>{"id":"114524548016669018832","name":"C3 Fitness Science (Kilpauk) (Owner)","link":"https://www.google.com/maps/contrib/114524548016669018832"}</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>{"borough":"Alagappa Nagar, Kilpauk","street":"17 Lakshmi Street, New Avadi Rd","city":"Chennai","postal_code":"600010","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>[{"Name":"Deena","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIgzFEB_37Xi86BBrLHE81vTUSkdgiRHjD6EA9Uy53u0P459Q=s120-c-rp-mo-br100","Rating":5,"Description":"One of the best gym in Kilpauk area  im happy with their service .compare to other gym this gym as more space and more mechines they have mainly nice and friendly crowd there I will sure recommend this place worth for money","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLf8hAlfPNXnplaVMATitDLSn18PUjpvF3TrG_koU4XwoB4QBdF0sAf-GcZiE3gC5679fxy-rIOpci7_LplDJxJ6IzePa6cbbeDaw2dNWV1ruhLT0jUpXzNVwFHLC2wrrXASA32DbPS8CHZ1=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLf4m0zAeJQQg1KgXVacaUfKQYCM6FjRkgPGuXPnviePmH7pXWlZ8b3SAkxMRh9DIgdsWvwF-XKoYXASN-t7EKSM94kJDdijtfzxhX-BtdrC0UcIEuqdSOt8anDD35ogO4UCt6Ae3YI5orrh=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd4msCLr7lf3Xve-b5RzoO2-WMR_sVCpx9mEaOm2EHZvmr8XFo0xqSbM4LiB0FHDIvRfNk7JiDk6I7ie4SaFMMFYfd-KNzh1gpro4oIkalkXFand_MZREfyaG-9nvq-cT3PzNQgzmCRhV8B=k-no"],"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xKWFJVZFJVVXhQTFZvNGFrVkNMV05aWWtRMFIwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113465094465222564405/reviews?hl=en-GB","posted_at_unix_micros":1759408042503815,"updated_at_unix_micros":1759408042503815,"language":"en","translated_lang":"","text_original":"One of the best gym in Kilpauk area  im happy with their service .compare to other gym this gym as more space and more mechines they have mainly nice and friendly crowd there I will sure recommend this place worth for money","text_translated":"","published_at":"2025-10-02T12:27:22.503815Z"},{"Name":"dharani b","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUTPdaQ26oCRFzprdLKcf1iwKN_fAEAuc1SwOWTZxEtFiWFHnQcbA=s120-c-rp-mo-br100","Rating":5,"Description":"The gym is clean, comfortable, and well-maintained. The equipment is in great condition, and the environment is motivating. My trainer ganesh is very supportive and knowledgeable, which makes workouts even more effective. Overall, it’s a great place to stay fit.","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2taeVFuTkJVR05QTkRCNU1ITmxOM05JUm14R2VXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107539144543194426274/reviews?hl=en-GB","posted_at_unix_micros":1757681286783175,"updated_at_unix_micros":1757681286783175,"language":"en","translated_lang":"","text_original":"The gym is clean, comfortable, and well-maintained. The equipment is in great condition, and the environment is motivating. My trainer ganesh is very supportive and knowledgeable, which makes workouts even more effective. Overall, it’s a great place to stay fit.","text_translated":"","published_at":"2025-09-12T12:48:06.783175Z"},{"Name":"alagappan arunachalam","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLJytee1XmVo5kpHmlg5nfo0BYz3-BA-HaHVZgT0F4-_1yW4Yw2=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Nice gym.  All the facilities inside. Good crowd and reasonable charges.  Located next to new avadi road kilpak. Good trainers and royal infrastructure like five star level","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfN5O7kXpRwTlR8qUo-oBdeRVxT_NXj3PDWJraZb1E-3msGE8XqTSKJO0OD4r8hWcFWwfy8MQQ_Gdq55mGr-MIAcce9laibjsrSyeZEo1KHqbj1_mxmb_0ryaINsUd7AGYz8__RaQ=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcusaJVSG8B0-9m3bH0CrUdSXvq1qfOm7WUrOaNFQSm9NtxdSgnaW9rm6bCjr37PLqQvpK0QeGUhAZB3ZfpFIrU4ueM0rWvjwZVIN4naoqzkj8KCAwQfo8jASJ6FwaleCdR6J7TWg=k-no"],"When":"7 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURVNXVhWWl3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111669462809346258992/reviews?hl=en-GB","posted_at_unix_micros":1566455546254227,"updated_at_unix_micros":1566455546254227,"language":"en","translated_lang":"","text_original":"Nice gym.  All the facilities inside. Good crowd and reasonable charges.  Located next to new avadi road kilpak. Good trainers and royal infrastructure like five star level","text_translated":"","published_at":"2019-08-22T06:32:26.254227Z"},{"Name":"Balakrishnan C.N","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKZVuaM4rWHNm9M3ljrdyDzOM6i4AACZqajuBmSLL8QFOCEmQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This is by far one of the better gyms I have worked out in several years. Well maintained, clean, with lots of emphasis on Time Management. The space in the gym has been well utilised. The machines, weights are of good quality. The trainers are dedicated, helpful and know their jobs and are respectful. A gym's popularity can be assessed by the homogenity of the crowd that comes here. There is a healthy ratio of women who work out because of the above factors and hygiene. Altogether my experience is good. I joined in January 2024. My trainer Ganesh is really a great guy who has supported me like a friend and well wisher in my path to attain a healthy and toned physique!","Images":null,"When":"Edited 10 months ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURINXBQWlBnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108871989456048605413/reviews?hl=en-GB","posted_at_unix_micros":1726408668906118,"updated_at_unix_micros":1763810911290284,"language":"en","translated_lang":"","text_original":"This is by far one of the better gyms I have worked out in several years. Well maintained, clean, with lots of emphasis on Time Management. The space in the gym has been well utilised. The machines, weights are of good quality. The trainers are dedicated, helpful and know their jobs and are respectful. A gym's popularity can be assessed by the homogenity of the crowd that comes here. There is a healthy ratio of women who work out because of the above factors and hygiene. Altogether my experience is good. I joined in January 2024. My trainer Ganesh is really a great guy who has supported me like a friend and well wisher in my path to attain a healthy and toned physique!","text_translated":"","published_at":"2024-09-15T13:57:48.906118Z"},{"Name":"Colorfull Cosmic","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJoAiSpeqkckc542nXhLHU4dWGIIW07hec8fr8W1HX5PDbOZw=s120-c-rp-mo-br100","Rating":1,"Description":"**Disappointed with Unfair Pricing \u0026 Misleading Policies**\n\nI’m extremely unhappy with C3 Gym Kilpauk’s recent changes. They increased fees by ₹2,000 compared to last year, claiming it was because *all Sundays would be operational*. However, now they’ve backtracked—only *2 Sundays a month* are open while the other 2 remain closed. Will they refund the extra money we paid for those Sundays? **Doubt it.**\n\nOn top of that, their gym timings are inconvenient compared to other gyms. They have *long breaks** (closed from 1 PM to 4 PM), while many top gyms operate full-day or even 24/7. Why pay more for worse service?\n\n**False promises + unfair pricing + outdated timings = Poor value for money.** Would not recommend unless they fix these issues.","Images":null,"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnTUNvbksyZ0RREAE","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/106088567229518398446/reviews?hl=en-GB","posted_at_unix_micros":1744709983522659,"updated_at_unix_micros":1744726565450062,"language":"en","translated_lang":"","text_original":"**Disappointed with Unfair Pricing \u0026 Misleading Policies**\n\nI’m extremely unhappy with C3 Gym Kilpauk’s recent changes. They increased fees by ₹2,000 compared to last year, claiming it was because *all Sundays would be operational*. However, now they’ve backtracked—only *2 Sundays a month* are open while the other 2 remain closed. Will they refund the extra money we paid for those Sundays? **Doubt it.**\n\nOn top of that, their gym timings are inconvenient compared to other gyms. They have *long breaks** (closed from 1 PM to 4 PM), while many top gyms operate full-day or even 24/7. Why pay more for worse service?\n\n**False promises + unfair pricing + outdated timings = Poor value for money.** Would not recommend unless they fix these issues.","text_translated":"","published_at":"2025-04-15T09:39:43.522659Z"}]</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>(1★) Colorfull Cosmic: **Disappointed with Unfair Pricing &amp; Misleading Policies** I’m extremely unhappy with C3 Gym Kilpauk’s recent changes. They increased fees by ₹2,000 compared to last year, claiming it was because *all Sundays would be operational*. However, now they’ve backtracked—only *2 Sundays a month* are open while the other 2 remain closed. Will they refund the extra money we paid for those Sundays? **Doubt it.** On top of that, their gym timings are inconvenient compared to other gyms. They have *long breaks** (closed from 1 PM to 4 PM), while many top gyms operate full-day or even 24/7. Why pay more for worse service? **False promises + unfair pricing + outdated timings = Poor value for money.** Would not recommend unless they fix these issues.</t>
+        </is>
+      </c>
+      <c r="AO61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>43</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Marvel+Fitness+Zone+-+Alwarthirunagar/data=!4m7!3m6!1s0x3a5261329c7d6adb:0xca0709348bfc366e!8m2!3d13.0454118!4d80.1858108!16s%2Fg%2F11bxfwnp4v!19sChIJ22p9nDJhUjoRbjb8izQJB8o</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Marvel Fitness Zone - Alwarthirunagar</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>No-4, 2nd floor, Marvel Fitness Zone - Alwarthirunagar, Gandhi St, opposite to Mega Mart, near Domino’s, Alwartirunagar, Valasaravakkam, Chennai, Tamil Nadu 600087</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["6–10 am"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>095148 45454</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>25WP+58 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>207</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":1,"3":1,"4":11,"5":193}</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>13.045412</v>
+      </c>
+      <c r="R62" t="n">
+        <v>80.185811</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>14557614441789929070</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdjybvzHr3frqBWRjTztuIaEXJhZiOrUEcam1zhU0fDzbTwFlFVLbvb48pkxbNY1K8BE9Bt24d5qimo6Mn2nor4BDKzb-MKlkH20h95DJ0-yh8q1iANfGObPSQc7eAvC3_yjbg=w408-h271-k-no</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>0x3a5261329c7d6adb:0xca0709348bfc366e</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>ChIJ22p9nDJhUjoRbjb8izQJB8o</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>{"id":"108416338702010960751","name":"Marvel Fitness Zone - Alwarthirunagar (Owner)","link":"https://www.google.com/maps/contrib/108416338702010960751"}</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>{"borough":"Alwartirunagar, Valasaravakkam","street":"No-4, 2nd floor, Gandhi St, opposite to Mega Mart, near Domino’s","city":"Chennai","postal_code":"600087","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>[{"Name":"Nitheesh M","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIf2Xh7c8oBvyYnNHJRUJdSjLOlcImpcaJj0Xh1luCi0PDjOQ=s120-c-rp-mo-br100","Rating":5,"Description":"Great gym for beginners! The environment is friendly and not intimidating, which really helps when you're just starting out. The equipment is well-maintained, and there’s enough variety for a full workout. Trainer is supportive and guide’s  you when needed. Overall, I’ve started noticing real gains and improved strength. Definitely a good place to begin your fitness journey.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21OR1NsVlphMHhSTTJoc2J6SnZiVVUzY0ZCTFgwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107765484695224527499/reviews?hl=en-GB","posted_at_unix_micros":1774282934770854,"updated_at_unix_micros":1774282934770854,"language":"en","translated_lang":"","text_original":"Great gym for beginners! The environment is friendly and not intimidating, which really helps when you're just starting out. The equipment is well-maintained, and there’s enough variety for a full workout. Trainer is supportive and guide’s  you when needed. Overall, I’ve started noticing real gains and improved strength. Definitely a good place to begin your fitness journey.","text_translated":"","reply_text_original":"Thank you so much for your valuable review and support 🙏🏻\nWe are happy to be a part of your fitness journey.\n\nYour motivation and dedication inspire us to do even better everyday 💪🏻.","reply_language":"en","reply_posted_at_unix_micros":1778682585000000,"reply_updated_at_unix_micros":1778682585000000,"published_at":"2026-03-23T16:22:14.770854Z"},{"Name":"Manjusha Nair","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLq3WnQRpOfvFtmd38cygCEpRhKXbBFgjGahQB7qkZ9thm4ig=s120-c-rp-mo-br100","Rating":5,"Description":"I have been taking personal training with Kannan sir since almost 4 months and he has helped me with my biggest problem - consistency. He plans the workout in such a way that it’s not repetitive or boring or extremely difficult. He has slowly helped me progress and I can feel the difference in my strength and stamina. He never misses to track the workout days and is super flexible. On days when it’s very tiring, he reduces the intensity to not break the consistency. Sir guides well on the form and motivates to try a little extra each time. I totally recommend sir’s coaching. Thank you Sir 😊","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s5dk5FTlBWMVJ3YVVGR1JYVjNUalp4ZEVWMFZrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111839779378508276200/reviews?hl=en-GB","posted_at_unix_micros":1781276699058913,"updated_at_unix_micros":1781276699058913,"language":"en","translated_lang":"","text_original":"I have been taking personal training with Kannan sir since almost 4 months and he has helped me with my biggest problem - consistency. He plans the workout in such a way that it’s not repetitive or boring or extremely difficult. He has slowly helped me progress and I can feel the difference in my strength and stamina. He never misses to track the workout days and is super flexible. On days when it’s very tiring, he reduces the intensity to not break the consistency. Sir guides well on the form and motivates to try a little extra each time. I totally recommend sir’s coaching. Thank you Sir 😊","text_translated":"","reply_text_original":"Thank you so much maam☺️\nYour support motivates our entire marvel fitness team to give the best every day 💪🏻","reply_language":"en","reply_posted_at_unix_micros":1782696071000000,"reply_updated_at_unix_micros":1782696071000000,"published_at":"2026-06-12T15:04:59.058913Z"},{"Name":"Ananth Narayanan P","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVii8eOZwbXXPRlQ26h-U6k-PV5pNU5AlZBNkTY_2s6kxK4UBE=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Been hitting the gym for the past couple of months.\nGot to say felt the most comfortable here over other gyms tried in the past. Kannan master is friendly and always supportive. He always makes sure to keep an eye over everyone, in their form and also keeping track of their exercises.\nGym is equipped with all the required machines and is well maintained. Also the cheapest in the locality\n\nHighly recommend to others and bang-for-the-buck.","Images":null,"When":"Edited 7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21GRWFIWkVWMnRRYlUwNE9UazFMVUZRWDI5bGVHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118346489064373521920/reviews?hl=en-GB","posted_at_unix_micros":1772773848674805,"updated_at_unix_micros":1772973208572300,"language":"en","translated_lang":"","text_original":"Been hitting the gym for the past couple of months.\nGot to say felt the most comfortable here over other gyms tried in the past. Kannan master is friendly and always supportive. He always makes sure to keep an eye over everyone, in their form and also keeping track of their exercises.\nGym is equipped with all the required machines and is well maintained. Also the cheapest in the locality\n\nHighly recommend to others and bang-for-the-buck.","text_translated":"","reply_text_original":"We truly appreciate your kind words and support 🔥\nSeeing your progress and happiness gives us great motivation.💪🏻\nThank you for being a valuable member of the marvel fitness family ❤️","reply_language":"en","reply_posted_at_unix_micros":1778683049000000,"reply_updated_at_unix_micros":1778683049000000,"published_at":"2026-03-06T05:10:48.674805Z"},{"Name":"arun kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXI-hhzqI7dSc7kjDIBP0XpPF9AQ7GeYqI7ufHmV2M9wm8uiVfVmg=s120-c-rp-mo-br100","Rating":5,"Description":"Excellent gym with well-maintained equipment and clean environment The atmosphere is very positive and perfect for daily workouts.Highly recommended for anyone looking to improve fitness and stay healthy\nThank you master Kannan","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pWeWRsQjVaMGhzTkhobmIzTndZbGRXZEV4NWIxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106287198805199563207/reviews?hl=en-GB","posted_at_unix_micros":1778592896438908,"updated_at_unix_micros":1778592990046270,"language":"en","translated_lang":"","text_original":"Excellent gym with well-maintained equipment and clean environment The atmosphere is very positive and perfect for daily workouts.Highly recommended for anyone looking to improve fitness and stay healthy\nThank you master Kannan","text_translated":"","reply_text_original":"Thank you for taking the time to share your experience with marvel fitness 🥳\n\nWe truly appreciate your support in your transformation journey 🔥","reply_language":"en","reply_posted_at_unix_micros":1778682440000000,"reply_updated_at_unix_micros":1778682440000000,"published_at":"2026-05-12T13:34:56.438908Z"},{"Name":"Akshay Malachiyil","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV5gXoogLww-bTFlT6Ck6f28PJTfw0Y6lt7zJSI-_LFyFkM-qQ=s120-c-rp-mo-br100","Rating":5,"Description":"“I’ve been training here with my personal coach, and it’s been an incredible journey. The gym is well-equipped, clean, and has a great fitness atmosphere. My coach customizes every workout to suit my goals, corrects my form, and constantly motivates me to push past my limits. The guidance on both training and nutrition has given me real results. If you’re looking for a gym with the right environment and a dedicated personal trainer, this is the place to be!”","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfRX_RGZIpgwAsdQsqjKgyFEg7dw4rrguy_n2nLrddLKEpYEIQ0xAvxkdaTVW_f0RwFWBLeXJV3rv1e6JGy1eeSTDc5WQbEOHvAHJb0SUJNnptTmrWiXP6syRUefP_VLuseZ4sKLbz494Mb=k-no"],"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tSRmRVMXBabHBOUzA1dFJqQktOM1JUTTA4MkxWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109475855185282597931/reviews?hl=en-GB","posted_at_unix_micros":1755317957960905,"updated_at_unix_micros":1755317957960905,"language":"en","translated_lang":"","text_original":"“I’ve been training here with my personal coach, and it’s been an incredible journey. The gym is well-equipped, clean, and has a great fitness atmosphere. My coach customizes every workout to suit my goals, corrects my form, and constantly motivates me to push past my limits. The guidance on both training and nutrition has given me real results. If you’re looking for a gym with the right environment and a dedicated personal trainer, this is the place to be!”","text_translated":"","reply_text_original":"Thankyou for your support ","reply_language":"en","reply_posted_at_unix_micros":1755318128000000,"reply_updated_at_unix_micros":1755318128000000,"published_at":"2025-08-16T04:19:17.960905Z"}]</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>43</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Power+Zone+Gym/data=!4m7!3m6!1s0x3a52611558384aad:0x49940afe9e23341a!8m2!3d13.0172242!4d80.1775385!16s%2Fg%2F11pvb3nywx!19sChIJrUo4WBVhUjoRGjQjnv4KlEk</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Power Zone Gym</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>:19/20, Manapakkam Main Rd, above Tea Time, Velavan Nagar, Lalithamba Nagar, Manapakkam, Chennai, Tamil Nadu 600125</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["7 am–12:30 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>086808 80109</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>258H+V2 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>206</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>{"1":4,"2":1,"3":3,"4":11,"5":187}</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>13.017224</v>
+      </c>
+      <c r="R63" t="n">
+        <v>80.177538</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>5301874750012994586</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe7xRwg1Sj1sbE2PXRDYxXDET5qTMB8d0rYLSEkSQwo_g6CKjzTCpQxBJxqbOGT92ygKynxL0wXfPpobAum0DUXGN0IAEzmNbDx3Yy2jWceKe0ymGV6guCxo8QyqR19g-1k1K9N=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>0x3a52611558384aad:0x49940afe9e23341a</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>ChIJrUo4WBVhUjoRGjQjnv4KlEk</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>{"id":"114779599207756995983","name":"Power Zone Gym (Owner)","link":"https://www.google.com/maps/contrib/114779599207756995983"}</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>{"borough":"Velavan Nagar, Lalithamba Nagar, Manapakkam","street":":19/20, Manapakkam Main Rd, above Tea Time","city":"Chennai","postal_code":"600125","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>[{"Name":"POWER COOLING SYSTEMS","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVaTrLd0ziUE3_sGxxEpHUX_ocZlPZdQGRIBHWEbUUExvII5F8=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This gym truly stands out for anyone serious about fitness and a healthy lifestyle. From the moment you walk in, the environment feels clean, energetic, and motivating.\n💪 Equipment \u0026 Facilities\nThe gym is fully equipped with modern machines for cardio, strength training, and functional workouts. All equipment is well-maintained, allowing smooth and safe workouts without waiting.\n👨‍🏫 Trainers \u0026 Guidance\nCertified and friendly trainers provide excellent guidance, whether you are a beginner or an advanced fitness enthusiast. Personal attention, correct form correction, and workout planning make a big difference here.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLc7L6zbARksLU6gPQ3bPqGGF9KVJv2cnxwfb7vrcBS6l0bm6_sck5mU8zWXeTBRLlnsf6FPE20dREv_77WqrpbWJrrWMB0lc1O06yDLQ8ZvbLG3ghVE2LWEZQnK9YYvR83JDb3Pg5BXCnw=k-no"],"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21KNVZrVTRPVXhCVmtRMWVtcFRSazVMWlhBMFVHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101877215213881997889/reviews?hl=en-GB","posted_at_unix_micros":1771066010408593,"updated_at_unix_micros":1771066010408593,"language":"en","translated_lang":"","text_original":"This gym truly stands out for anyone serious about fitness and a healthy lifestyle. From the moment you walk in, the environment feels clean, energetic, and motivating.\n💪 Equipment \u0026 Facilities\nThe gym is fully equipped with modern machines for cardio, strength training, and functional workouts. All equipment is well-maintained, allowing smooth and safe workouts without waiting.\n👨‍🏫 Trainers \u0026 Guidance\nCertified and friendly trainers provide excellent guidance, whether you are a beginner or an advanced fitness enthusiast. Personal attention, correct form correction, and workout planning make a big difference here.","text_translated":"","published_at":"2026-02-14T10:46:50.408593Z"},{"Name":"manju R Nair","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLYwgsvVjxcFo8OmJv3PBO6urGVvK-kc43zbMyQQeueDZpeUA=s120-c-rp-mo-br100","Rating":5,"Description":"The gym is well-maintained, clean, and equipped with modern machines.\nTrainers are knowledgeable, supportive, and motivate members effectively.\nThe atmosphere is positive and encourages a healthy lifestyle.\nEquipment is arranged neatly, making workouts comfortable and efficient.\nThe gym provides excellent facilities for both beginners and advanced fitness enthusiasts.\nThe staff are friendly, professional, and always ready to help.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xGR2NWcDFiaTFSVURaWVlrY3dXakI1YWtObGIzYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113676432620149462665/reviews?hl=en-GB","posted_at_unix_micros":1780326922696585,"updated_at_unix_micros":1780326922696585,"language":"en","translated_lang":"","text_original":"The gym is well-maintained, clean, and equipped with modern machines.\nTrainers are knowledgeable, supportive, and motivate members effectively.\nThe atmosphere is positive and encourages a healthy lifestyle.\nEquipment is arranged neatly, making workouts comfortable and efficient.\nThe gym provides excellent facilities for both beginners and advanced fitness enthusiasts.\nThe staff are friendly, professional, and always ready to help.","text_translated":"","reply_text_original":"Thanks for your valuable feedback ","reply_language":"en","reply_posted_at_unix_micros":1780328879000000,"reply_updated_at_unix_micros":1780328879000000,"published_at":"2026-06-01T15:15:22.696585Z"},{"Name":"Ravi Raghunandan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU93GMUjLZQeURUPsZsbXwQ2HK_C5DRogdUYhSWxMNLVOmAqN8F=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great gym with an excellent team. Prashanth bro is a fantastic trainer — attentive, knowledgeable, and genuinely tracks your progress. Mani bro has built a clean, well-maintained space with a great culture. If you’re in Manapakkam, this is the place. Highly recommend!","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25ablFVRkdUM1J1UmxwbGJWZ3RTMHQwY0RJMlQxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106897389281060033245/reviews?hl=en-GB","posted_at_unix_micros":1780658626707367,"updated_at_unix_micros":1780658626707367,"language":"en","translated_lang":"","text_original":"Great gym with an excellent team. Prashanth bro is a fantastic trainer — attentive, knowledgeable, and genuinely tracks your progress. Mani bro has built a clean, well-maintained space with a great culture. If you’re in Manapakkam, this is the place. Highly recommend!","text_translated":"","reply_text_original":"Thanks for your valuable feedback sir","reply_language":"en","reply_posted_at_unix_micros":1781536723000000,"reply_updated_at_unix_micros":1781536723000000,"published_at":"2026-06-05T11:23:46.707367Z"},{"Name":"Balamurugan S","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXLBWCEDj5UIsgu089XG_ZGNybFGbK9ntEu9jPNwvbfD19VB4lqDA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I juggled across lots of gym during the course my lifting life. But, to be honest, Its already been a year as a powerzone community member 🎊. I feel grateful for Mani Anna, Harish and Gokul Anna for constantly improvising the gym based on the customer's need.Thank you for your supports Anna (s).\n\nHumble and approachable trainers with well grounded knowledge in Fitness and Cross sport. One example about the advancement in gym is recently they have also unlocked a newly imported multi functional training machine, which feels smooth as cheese to perform actions and trainings.\n\nComing to next phase, they also perform group activity sessions for women and men, like a community energetic, enthusiastic and enjoyable way of performing chained - workout for weightloss (especially for womens)\n\n3rd floor is specially structured for cross fits and other dynamic workouts like boxing and snatches.\n\nThe most unique, authentic attribute about the gym is the internal community they build. They strengthen the relationship with the customer, at time provide support and motivation to them.\n\nOverall, I will definitely recommend you to give it a shot and try being a part of powerzone community.\n\nThank you for reading until the end😊","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfE-5J1abI3f7Dj0odY9fTNLuMbvgXd0cEpD8e9QCJ1-91t5KML1Pp5eVQfqXpm9x272wIN8tXH6RLccPWAaKt4F53lM9drXHI350hJ3xb9LJ3tz6lGT8qAUwyEo0NJgpz2P05kGA=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLds1X2rppCjMxCI1u7UTSrxXkU6cIGtKmVhlEMUBszmT1cMKpjU19ic5kXJM73t3RpGyj9yJOI5w0rNxgN9blJfdt35Ky8ATPbjSZwRtFW9KjV3UhVSe8Y05-XurF0074Vchzz0=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdvz29MDRWPDSla8nEUHluUp_QK8LpRca4YvO1mtsqkkSxaPtpVnGol5fXpAfqw8kGElK2kh1u14DwWvtjB2wWcU21aUvODtakVkmNmyeTdaiQWqI34cbSzhe0d9maA1hKMiZuGhw=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLf4jz78HGsgbYwymro3MBeEFpREiYiJrEtzxWR6Vb5zJB0XCoqIed0CDkUEhOy7HIfSNBT4WXty2d_XWbvwx9o-3D_Im194n6GW-QZiLq8ixdi09AEKUU8LaNRiIeWe5TdCCoFp=k-no"],"When":"2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUQ5aG96RnN3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117174433934518826521/reviews?hl=en-GB","posted_at_unix_micros":1710548368575193,"updated_at_unix_micros":1710548368575193,"language":"en","translated_lang":"","text_original":"I juggled across lots of gym during the course my lifting life. But, to be honest, Its already been a year as a powerzone community member 🎊. I feel grateful for Mani Anna, Harish and Gokul Anna for constantly improvising the gym based on the customer's need.Thank you for your supports Anna (s).\n\nHumble and approachable trainers with well grounded knowledge in Fitness and Cross sport. One example about the advancement in gym is recently they have also unlocked a newly imported multi functional training machine, which feels smooth as cheese to perform actions and trainings.\n\nComing to next phase, they also perform group activity sessions for women and men, like a community energetic, enthusiastic and enjoyable way of performing chained - workout for weightloss (especially for womens)\n\n3rd floor is specially structured for cross fits and other dynamic workouts like boxing and snatches.\n\nThe most unique, authentic attribute about the gym is the internal community they build. They strengthen the relationship with the customer, at time provide support and motivation to them.\n\nOverall, I will definitely recommend you to give it a shot and try being a part of powerzone community.\n\nThank you for reading until the end😊","text_translated":"","reply_text_original":"Thanks for your valuable feedback.","reply_language":"en","reply_posted_at_unix_micros":1710555133000000,"reply_updated_at_unix_micros":1710555133000000,"published_at":"2024-03-16T00:19:28.575193Z"},{"Name":"Vignesh Pugalenthi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXHmlSrr8LQDhZFDoxNdrlby7nK7_h0PB7VdCOGSxV0gH_krBAR4Q=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This gym is amazing. Amazing trainer, top equipment and great environment. Good service with friendly master and super clean and comfortable gym for everyone from beginners to professional athletes.\nThe master was extremely welcoming and we were able to do all our routines while on holiday for a reasonable cost. I intend to use their gym every time🤩","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdoDxolKDtUOq9zU0G0z4Lbu7UjC63teTiN1ngbcwofAxHV69MRqmdYcqhzle7obPXLNPk_cxSDmK1W5LRsaZRO1cy0dPRd8JPrgW2rGlXrdX0amGEn0bKtpvHaze9O-N58RuAO=k-no"],"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUR4MDR1Nk9nEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106665864904233162711/reviews?hl=en-GB","posted_at_unix_micros":1686747007614438,"updated_at_unix_micros":1686747033766402,"language":"en","translated_lang":"","text_original":"This gym is amazing. Amazing trainer, top equipment and great environment. Good service with friendly master and super clean and comfortable gym for everyone from beginners to professional athletes.\nThe master was extremely welcoming and we were able to do all our routines while on holiday for a reasonable cost. I intend to use their gym every time🤩","text_translated":"","reply_text_original":"Thanks for the valuable feedback sir ☺️🙂🙂","reply_language":"en","reply_posted_at_unix_micros":1686747941000000,"reply_updated_at_unix_micros":1686747941000000,"published_at":"2023-06-14T12:50:07.614438Z"}]</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>43</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/The+Yard+Fitness+Studio/data=!4m7!3m6!1s0x3a526100635adfed:0x58b1d4611e22ca29!8m2!3d13.0755511!4d80.1775139!16s%2Fg%2F11vxzfffqc!19sChIJ7d9aYwBhUjoRKcoiHmHUsVg</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>The Yard Fitness Studio</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>No.1052, 6th Main Rd, Mogappair West, Mogappair, Chennai, Tamil Nadu 600037</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10:30 pm"],"Monday":["5:30 am–10:30 pm"],"Saturday":["5:30 am–10:30 pm"],"Sunday":["6 am–1 pm"],"Thursday":["5:30 am–10:30 pm"],"Tuesday":["5:30 am–10:30 pm"],"Wednesday":["5:30 am–10:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>073959 51526</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>35GH+62 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>200</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>{"1":4,"2":0,"3":0,"4":2,"5":194}</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>13.075551</v>
+      </c>
+      <c r="R64" t="n">
+        <v>80.177514</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>6391122859797957161</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfV38jaV9sb0eguNlSbHkuofmqbYsqxkmYy3i_yiEnBuvCvk0Z50CGu224StAWLgpg3nIjMDlG4oI-wMJQKvvBZcYBcbStks6EphxcTJDSS8aCKQjsHjWs7u96PsrePa5ZhXGxa=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>0x3a526100635adfed:0x58b1d4611e22ca29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>ChIJ7d9aYwBhUjoRKcoiHmHUsVg</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[{"link":"https://wa.me/917395951526","source":"wa.me"},{"link":"https://shop.zuyyu.com/bfe7f173-d314-44d0-aab8-8cabe63e15b5/menu?rwg_token=AE37R_gLzdxUa-v8WUKAybwxn9DR0d6y0ammVD3Z0M6lokD5rsHLPN0Vut2Diinpyq-o-HPMa8HAl9wQSt-bTfBzzD4azr-81MfOYRvV0IRi4K26kW-_QM8%3D","source":"zuyyu.com"}]</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>{"id":"108390408828854651150","name":"The Yard Fitness Studio (Owner)","link":"https://www.google.com/maps/contrib/108390408828854651150"}</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>{"borough":"Mogappair West, Mogappair","street":"No.1052, 6th Main Rd","city":"Chennai","postal_code":"600037","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>[{"Name":"PARAMASIVAM R","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXcxJm5LZvIRPQi6ify7OqfzpMnTy-UFPT3qlz2Jrw-laMkel81=s120-c-rp-mo-br100","Rating":5,"Description":"Finally found the perfect fit! ⭐⭐⭐⭐⭐\n​After searching for the right gym for nearly a year, I am so glad I found this place. It has been an absolute game-changer for my fitness goals.\n​What makes this gym stand out:\n​Supportive Trainers: The coaching staff is incredibly friendly, welcoming, and genuinely invested in your success. Their daily guidance has been invaluable.\n​Data-Driven Progress: The individual profile monitoring and regular BMI tracking are fantastic. It keeps me accountable and focused.\n​Realistic Routines: The workout plans are practical, easy to follow, and—most importantly—they yield real results.\n​Thanks to the team here, I’ve gained so much confidence in my weight loss journey. The facility is clean, decent, and has a great environment. Highly recommended! Value for Money!!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psME5uZG9ObGt4WTJSUlZsUkNSSFJ3YTFSNlUwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105255608334300301795/reviews?hl=en-GB","posted_at_unix_micros":1784265680402521,"updated_at_unix_micros":1784265680402521,"language":"en","translated_lang":"","text_original":"Finally found the perfect fit! ⭐⭐⭐⭐⭐\n​After searching for the right gym for nearly a year, I am so glad I found this place. It has been an absolute game-changer for my fitness goals.\n​What makes this gym stand out:\n​Supportive Trainers: The coaching staff is incredibly friendly, welcoming, and genuinely invested in your success. Their daily guidance has been invaluable.\n​Data-Driven Progress: The individual profile monitoring and regular BMI tracking are fantastic. It keeps me accountable and focused.\n​Realistic Routines: The workout plans are practical, easy to follow, and—most importantly—they yield real results.\n​Thanks to the team here, I’ve gained so much confidence in my weight loss journey. The facility is clean, decent, and has a great environment. Highly recommended! Value for Money!!","text_translated":"","published_at":"2026-07-17T05:21:20.402521Z"},{"Name":"Kavi Nilavu","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocImNcmvR7HXLAfmxKf3VOIPctIlHDn5L7hsF-CL0M2yImCQHw=s120-c-rp-mo-br100","Rating":5,"Description":"As a complete beginner to fitness, walking into a gym can feel incredibly intimidating, but this place completely changed that for me! From day one, the energy here has been nothing but beautiful, positive, and incredibly welcoming. A huge shoutout to my trainers (Prem, Fredrick), who treats me with so much patience, kindness, and genuine care, making every workout feel encouraging rather than overwhelming. The gym itself is an absolute dream—the atmosphere is always neat, clean, and beautifully maintained, and they have top-tier equipment that is kept in perfect condition. I absolutely love coming here; it truly feels like a space built on motivation and care. If you are looking for a place to start your fitness journey with zero judgment and 100% support, this is absolutely it.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21jd2IzQjBhMUZyY1ZCV1RXTlpTSFIwU0Y5WmJHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116805754483314359145/reviews?hl=en-GB","posted_at_unix_micros":1780947299601852,"updated_at_unix_micros":1780947299601852,"language":"en","translated_lang":"","text_original":"As a complete beginner to fitness, walking into a gym can feel incredibly intimidating, but this place completely changed that for me! From day one, the energy here has been nothing but beautiful, positive, and incredibly welcoming. A huge shoutout to my trainers (Prem, Fredrick), who treats me with so much patience, kindness, and genuine care, making every workout feel encouraging rather than overwhelming. The gym itself is an absolute dream—the atmosphere is always neat, clean, and beautifully maintained, and they have top-tier equipment that is kept in perfect condition. I absolutely love coming here; it truly feels like a space built on motivation and care. If you are looking for a place to start your fitness journey with zero judgment and 100% support, this is absolutely it.","text_translated":"","published_at":"2026-06-08T19:34:59.601852Z"},{"Name":"Mangaiyarkarasi Vasu","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV3dz_clJNYUmKALNJf84iZMWXAv5xra5-_968NC5TA0VDAayIb=s120-c-rp-mo-br100","Rating":5,"Description":"⭐⭐⭐⭐⭐\n\nA very well-equipped gym with a clean and pleasant atmosphere. The trainers are friendly, knowledgeable, and provide excellent guidance according to individual fitness goals. As a woman, I especially appreciate how decent, respectful, and well-mannered all the trainers are, which makes me feel comfortable and confident while working out. Overall, it's a great place for anyone looking to start or continue their fitness journey. Highly recommended!","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tSTE1VOUZXR05SZW5SUFRXMUNkRXhrWnpCeVpWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103205381354166105037/reviews?hl=en-GB","posted_at_unix_micros":1784111353374953,"updated_at_unix_micros":1784111353374953,"language":"en","translated_lang":"","text_original":"⭐⭐⭐⭐⭐\n\nA very well-equipped gym with a clean and pleasant atmosphere. The trainers are friendly, knowledgeable, and provide excellent guidance according to individual fitness goals. As a woman, I especially appreciate how decent, respectful, and well-mannered all the trainers are, which makes me feel comfortable and confident while working out. Overall, it's a great place for anyone looking to start or continue their fitness journey. Highly recommended!","text_translated":"","published_at":"2026-07-15T10:29:13.374953Z"},{"Name":"Bhavna","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIsApmWek5TcuCiZfmNAfIB_tWUttxYpjNF2CnRKhFmcNQBUSw=s120-c-rp-mo-br100","Rating":5,"Description":"It's only been a month since I joined this gym, and it's been a great place for beginners. The trainers are supportive and guide you throughout your workouts, and the gym is also well-maintained. Although all the trainers are helpful and provide excellent guidance, Chris has helped me the most by offering hands-on guidance on how to perform the exercises correctly and explaining the benefits of each one. His support has made my fitness journey much more effective and enjoyable.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pSdVowRmFSalpyY3pGNk5HMTRXbGMzV1dSZmVuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103622710671849198754/reviews?hl=en-GB","posted_at_unix_micros":1784186498380531,"updated_at_unix_micros":1784186498380531,"language":"en","translated_lang":"","text_original":"It's only been a month since I joined this gym, and it's been a great place for beginners. The trainers are supportive and guide you throughout your workouts, and the gym is also well-maintained. Although all the trainers are helpful and provide excellent guidance, Chris has helped me the most by offering hands-on guidance on how to perform the exercises correctly and explaining the benefits of each one. His support has made my fitness journey much more effective and enjoyable.","text_translated":"","published_at":"2026-07-16T07:21:38.380531Z"},{"Name":"Avaneesh S.S","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVuQOePuNXcV4DEy-UaJ6YKKr5NvbHfchGy1VFsjiDvxcZme38D=s120-c-rp-mo-br100","Rating":5,"Description":"Highly recommend this gym for anyone who wants a striking transformation in their lives. Out of the many gyms I visited in mogappair I found this gym to be the best due to several pros\n1) Hygiene- this gym has been around for 2+ years but they keep hygeine as their maximum priority. When u enter the gym you don't get any sweat ordor or anything that ruins ur mood while working out.\n\n2) Friendly coaches- coaches that actually show up in time and teach u side by side as if u have actually hired a private trainer. They are extremely friendly and pushy when it comes to your transformation.\n\n3) Equipment- this gym features highly sophisticated machinery and advanced tools to finish ur gym excercise in ease and provide various amenities too in this 3 floor building.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xabFFtOTRNRTFSVTFSMlptWlRXVTFxTFdWSlZuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104930909095606404045/reviews?hl=en-GB","posted_at_unix_micros":1784075822594593,"updated_at_unix_micros":1784075822594593,"language":"en","translated_lang":"","text_original":"Highly recommend this gym for anyone who wants a striking transformation in their lives. Out of the many gyms I visited in mogappair I found this gym to be the best due to several pros\n1) Hygiene- this gym has been around for 2+ years but they keep hygeine as their maximum priority. When u enter the gym you don't get any sweat ordor or anything that ruins ur mood while working out.\n\n2) Friendly coaches- coaches that actually show up in time and teach u side by side as if u have actually hired a private trainer. They are extremely friendly and pushy when it comes to your transformation.\n\n3) Equipment- this gym features highly sophisticated machinery and advanced tools to finish ur gym excercise in ease and provide various amenities too in this 3 floor building.","text_translated":"","published_at":"2026-07-15T00:37:02.594593Z"}]</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>43</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/TUFF+FITNESS+CENTRE/data=!4m7!3m6!1s0x3a52637ada2b601d:0x20985985ebc0f092!8m2!3d13.0821477!4d80.1700332!16s%2Fg%2F11pgypl2lq!19sChIJHWAr2npjUjoRkvDA64VZmCA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>TUFF FITNESS CENTRE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>PC -3 , 8th Block ,1st FLOOR, Bharathi Salai, Mogappair West, Chennai, Tamil Nadu 600037</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>099444 64145</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>35JC+V2 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>181</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>{"1":13,"2":3,"3":6,"4":16,"5":143}</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>13.082148</v>
+      </c>
+      <c r="R65" t="n">
+        <v>80.170033</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>2348725637394526354</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf_sd1yzqb23hghB6qGo4CbAM7aGUMWTEvf63oQ_F6BZbwdd0btHo-7AGBNwEdnDhWkb7soScFqxeyaLmfW-XAxuyJoJ9clqQe2H_T--2cbkQtgNYb9Xt97svgvG9gZiqO34coZOg=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>0x3a52637ada2b601d:0x20985985ebc0f092</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>ChIJHWAr2npjUjoRkvDA64VZmCA</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>{"id":"","name":"TUFF FITNESS CENTRE (Owner)","link":""}</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>{"borough":"Mogappair West, Ambattur Industrial Estate","street":"PC -3 , 8th Block ,1st FLOOR, Bharathi Salai","city":"Chennai","postal_code":"600037","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>[{"Name":"Anirudh Raguram","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWcUcXvbHetvWWQvfqyJ2lerCJP7ZKZfHp3gbydL8xAHeDGnfmNNA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Joined this gym about a month ago, any my experience has been great. The equipments are well maintained and trainers are helpful too. There are always a minimum of 2 trainers on the floor to help you out and guide you. The equipments and gym is clean and we'll maintained and feels premium in nature.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfAaCysGjikpG2aJ0-X69c4vrZPuDLPtP2BYtb5fEriua4UnZvJJeUeTCTtMZhNmNkKqsS6V5BgvPJn9_InErjzWAXQw5Qgn2MWP1O3LKcnMDCbQU8vWFW2s2s2617_zjps8y4l=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfttC8A-tFeGdk0inXvfjgkLRyTT476yvn_tS2XxOcKndhZHJaMonntVnFFyEz23IloP70XQLIJB9eP_2FNk6iyS74Ap7AdgNTc6j_JL5okG6hlFb3vABVD0l5M8hTzZCn9mXuP=k-no"],"When":"5 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNhNEk3S1NnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116201801239157208747/reviews?hl=en-GB","posted_at_unix_micros":1626847746286745,"updated_at_unix_micros":1626847746286745,"language":"en","translated_lang":"","text_original":"Joined this gym about a month ago, any my experience has been great. The equipments are well maintained and trainers are helpful too. There are always a minimum of 2 trainers on the floor to help you out and guide you. The equipments and gym is clean and we'll maintained and feels premium in nature.","text_translated":"","published_at":"2021-07-21T06:09:06.286745Z"},{"Name":"Pranesh Bobby","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX6IRW1PbcbJFjE60MuvLMcwiefcG_VfYjB8v0ZiZWE4qht5TWl=s120-c-rp-mo-br100","Rating":5,"Description":"It’s is a wonderful gym the interiors are amazing😍 Gym trainers are awesome teaching like friendly especially dinu bro, Dinesh bro and sri cuttler  bro💪..They teach us a wonderful workouts😍❤️\n\n\"… They even motivate me when I feel tired . …\"\n\n\"… They motivates me a lot \u0026 help me out in achieving my goals \u0026 target","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcjA3X6UkQ0yPpo8dh4h6wEfwSilQ73bUA_gOJoFZDYYR7apmMUlSvqHAGqmhILb3aCgb0h70xufm-q64G4LGEPUNWxt0ZiLAYYad0VI3Z1IdFw1GmKet-9tw_JGXryvWuICDxX=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdu_7-8E9Y3q0AReMPG2W124BNq5CcUdA1tWPFbsV9Kbvh8D13M1hKg_W_a0fAnyhDc4YkIJI23Vi6HEpSYrLyEZSAOTFWaY9ccWQsoMp81PQSjbUbjWJLrclOk8C89bSaEAwaE=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd9sVfF7-yczKOct1x4TD_A1C-XjPRfuk-CUpJ7GJhDawPnddumIjSYDcWVLBRUo84Oh75pEowGosanuJ3KFIndGgyJ9rF1dhHRSqOLsPPuHXFYkID_c_hyDDrxXAnspdhIJ6oOsw=k-no"],"When":"5 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURxbS1PTElnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117828693378891319468/reviews?hl=en-GB","posted_at_unix_micros":1626417731702316,"updated_at_unix_micros":1626417878763665,"language":"en","translated_lang":"","text_original":"It’s is a wonderful gym the interiors are amazing😍 Gym trainers are awesome teaching like friendly especially dinu bro, Dinesh bro and sri cuttler  bro💪..They teach us a wonderful workouts😍❤️\n\n\"… They even motivate me when I feel tired . …\"\n\n\"… They motivates me a lot \u0026 help me out in achieving my goals \u0026 target","text_translated":"","published_at":"2021-07-16T06:42:11.702316Z"},{"Name":"Jaspreet Singh","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWZnVwQuSLp9BAx4QFgplPeYysaKtaELbMAkrZm-DhKX3knAH0=s120-c-rp-mo-br100","Rating":5,"Description":"TUFF, brilliant fitness centre.\nI joined this post multiple research and I’m proud of the decision been made is accurate.\n\nSurya (a.k.surya_) manages brilliantly, extremely brilliant lad for fitness discussions and world-class friendly by nature and most importantly the regular feedback’s regarding the facilities to improvise further with a futuristic vision.\n\nDinu Prasanth (dinu_turgut), absolutely down-to earth and friendly by default. Blessed with world-class interpersonal skills.\n“Skills might be achieved by anyone but conveying it accurately is what it matters and not everyone are world-class at it” and that’s the beauty of being Pro at interpersonal.\n\nThanks for Training us.\n\nOverall, the future of this brand is in right hands and direction! 💪🏻","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcrRFPxSGoYYccil-6jRz2eHZkxecxdDhMPKWshUVq_FP0tATcjFXhwgblIs8VvoDTLPVssXYg5fLtUhZl55iHyPsyG-nMxuz4c0IJVfXfCTS3-C0ifVYFGqn5nZR_6XtWX5Im5sw=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLedBddcsUcAtml_Q0G1ImOGG21CuzEmTfs0e_As2wDVMm4fKF2a_M0iIzE4vZ5QL3NeEBw27YeL1dvHIeosv1HmsdHB85bO5jqX_ighbngYfWV5L2aTAy0WopyahFWgL7P1YmJn=k-no"],"When":"5 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNLOFpMZmF3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110322386976174942318/reviews?hl=en-GB","posted_at_unix_micros":1617975119432635,"updated_at_unix_micros":1617975119432635,"language":"en","translated_lang":"","text_original":"TUFF, brilliant fitness centre.\nI joined this post multiple research and I’m proud of the decision been made is accurate.\n\nSurya (a.k.surya_) manages brilliantly, extremely brilliant lad for fitness discussions and world-class friendly by nature and most importantly the regular feedback’s regarding the facilities to improvise further with a futuristic vision.\n\nDinu Prasanth (dinu_turgut), absolutely down-to earth and friendly by default. Blessed with world-class interpersonal skills.\n“Skills might be achieved by anyone but conveying it accurately is what it matters and not everyone are world-class at it” and that’s the beauty of being Pro at interpersonal.\n\nThanks for Training us.\n\nOverall, the future of this brand is in right hands and direction! 💪🏻","text_translated":"","published_at":"2021-04-09T13:31:59.432635Z"},{"Name":"Lloyd McDonald","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXN680MBQNE9tuInU80y9lvfYJMUMPDWoAEKIQYzA6wmDq9Hvokqw=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great gym. Friendly trainers, great equipment and ample space to workout. Since the gym is spread across 4 floors, it is mostly never crowded and this is something that I love about gyms in general. They have janitors cleaning the gym around the clock which is necessary especially in these times(COVID). All in all it is functional, spacious, clean, convenient and friendly!","Images":null,"When":"Edited 4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUN1eEtfV2tRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109813498786116173731/reviews?hl=en-GB","posted_at_unix_micros":1658392320506984,"updated_at_unix_micros":1659000349887456,"language":"en","translated_lang":"","text_original":"Great gym. Friendly trainers, great equipment and ample space to workout. Since the gym is spread across 4 floors, it is mostly never crowded and this is something that I love about gyms in general. They have janitors cleaning the gym around the clock which is necessary especially in these times(COVID). All in all it is functional, spacious, clean, convenient and friendly!","text_translated":"","published_at":"2022-07-21T08:32:00.506984Z"},{"Name":"Karthik Venkateswaran","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVRMowgdD0wfgzrMorXfAjKr6AznyJTmKZTbpj93eXPZ-VxCEY9=s120-c-rp-mo-br100","Rating":5,"Description":"Tuff Fitness gym is a great place for both beginners and experienced gym goers. The place is well maintained and professional.  The trainers are all very friendly and helpful. Being a beginner myself, the trainers were very kind and made sure to help me out and teach me about different things whenever I had any questions.","Images":null,"When":"4 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUQyc2FpdEVREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104041343671122988832/reviews?hl=en-GB","posted_at_unix_micros":1652802274822832,"updated_at_unix_micros":1652802274822832,"language":"en","translated_lang":"","text_original":"Tuff Fitness gym is a great place for both beginners and experienced gym goers. The place is well maintained and professional.  The trainers are all very friendly and helpful. Being a beginner myself, the trainers were very kind and made sure to help me out and teach me about different things whenever I had any questions.","text_translated":"","published_at":"2022-05-17T15:44:34.822832Z"}]</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>43</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3443ec21-504f-4465-9e7d-5470d56e0e66</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Icon+CrossFit+Fitness+studio/data=!4m7!3m6!1s0x3a525f9b46523bc1:0x8b65807cb9020a5d!8m2!3d12.906081!4d80.1053483!16s%2Fg%2F11rsqdpcwm!19sChIJwTtSRptfUjoRXQoCuXyAZYs</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Icon CrossFit Fitness studio</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>No.2a/3,Devanesan Nagar 2nd Main Road, Anna St, New Perungalathur, Arinnar, Chennai, Tamil Nadu 600063</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–9 pm"],"Monday":["5 am–9 pm"],"Saturday":["5 am–9 pm"],"Sunday":["5:30–9 am"],"Thursday":["5 am–9 pm"],"Tuesday":["5 am–9 pm"],"Wednesday":["5 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>080562 87733</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>W444+C4 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>154</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>{"1":3,"2":0,"3":1,"4":2,"5":148}</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>12.906081</v>
+      </c>
+      <c r="R66" t="n">
+        <v>80.10534800000001</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>10044575817087978077</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdiSzqfWrUu2jihNBgSKUgXeYn2NqFdpfOooGwnbgED6e0S5XYf1BzLV1CAZNUbzAQsWvk-SRMUEVNBvU0bK6MEuXia4hOl0jKy6TaGgEL5KUvQ952HSTap2WRlbcxdyBCmxlJz=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>0x3a525f9b46523bc1:0x8b65807cb9020a5d</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>ChIJwTtSRptfUjoRXQoCuXyAZYs</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>{"id":"106717465125035368742","name":"Icon CrossFit Fitness studio (Owner)","link":"https://www.google.com/maps/contrib/106717465125035368742"}</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>{"borough":"Peerkankaranai, New Perungalathur","street":"No.2a/3,Devanesan Nagar 2nd Main Road, Anna St","city":"Arinnar, Chennai","postal_code":"600063","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>[{"Name":"lakshanya lavi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV76dfFzMqqxTFIDj48LAaNINqunozgJygWVEcdpbNKRdvU4c4=s120-c-rp-mo-br100","Rating":5,"Description":"Helps with weight loss and muscle building.\nImproves fitness, strength, and endurance.for myself\nCreates a routine and discipline for me....\nTrainers can guided me with proper exercise technique\nStarted My journey at 74kg now 70kg now so I'm going good progress.....so it's a great place for me ...  Being an introvert they understands me.... overall good gym....","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tkNE0yVTVXVUkwUTBsVFVrMXZhWGhLT0RobFRrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102180896599756047394/reviews?hl=en-GB","posted_at_unix_micros":1783404313736791,"updated_at_unix_micros":1783404313736791,"language":"en","translated_lang":"","text_original":"Helps with weight loss and muscle building.\nImproves fitness, strength, and endurance.for myself\nCreates a routine and discipline for me....\nTrainers can guided me with proper exercise technique\nStarted My journey at 74kg now 70kg now so I'm going good progress.....so it's a great place for me ...  Being an introvert they understands me.... overall good gym....","text_translated":"","published_at":"2026-07-07T06:05:13.736791Z"},{"Name":"Janakiraman V","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVLYo4y5FT269YNdjoJKM6tLl4J7nDIh_XaZn28s-kwiW5F-pyT=s120-c-rp-mo-br100","Rating":5,"Description":"Hi guys….\n\n“Icon CrossFit fitness studio”….#\nBest gym to built your body with excellent trainers. It is a good place to workout best place in around Perungalathur. Their charges also budget friendly.\n\nYour body is a reflection of your LIFESTYLE.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLf57uoGN1Mm5pVSdbGxUIASK7PlUM8ipTm7To5CMCbJi9kiRPem5ay6ulUHclg1cwhz5SVF30z0knxjdK1I-wJLBliIFOZlO8hQjbZV2Wx9EXvY1iQ87LnikBlt28ohWfIkxKTe=k-no"],"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUMzOXNQYXFRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112935439693844472766/reviews?hl=en-GB","posted_at_unix_micros":1730815468823628,"updated_at_unix_micros":1730815468823628,"language":"en","translated_lang":"","text_original":"Hi guys….\n\n“Icon CrossFit fitness studio”….#\nBest gym to built your body with excellent trainers. It is a good place to workout best place in around Perungalathur. Their charges also budget friendly.\n\nYour body is a reflection of your LIFESTYLE.","text_translated":"","published_at":"2024-11-05T14:04:28.823628Z"},{"Name":"༺༒D༒༻","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV5CvVMjxY18deUd4VvcW0GDR7bCgvVuQ6Wk_onW3CsrqTw1Q3K=s120-c-rp-mo-br100","Rating":5,"Description":"Best gym and Great Trainers!\n\nBudget friendly with all equipments and facilities 💯\n\nHaving a fun filled evening everyday with a great motivation to build my physique 💪....","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfTI9eeKqCTlcrPqsoJZX6AzZpA0QeGy8I_xe2wifkx9nmujJANefazQ0TDug00w-Ley3clBwanYf32tN-9SuX2HpvuTzkKzIkKBhcXovPHIpanM53ObZfa63zlbtNfNU1rfmJs=k-no"],"When":"Edited a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURYMDdxWExnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108754296879761062481/reviews?hl=en-GB","posted_at_unix_micros":1730326258436277,"updated_at_unix_micros":1730816464633136,"language":"en","translated_lang":"","text_original":"Best gym and Great Trainers!\n\nBudget friendly with all equipments and facilities 💯\n\nHaving a fun filled evening everyday with a great motivation to build my physique 💪....","text_translated":"","published_at":"2024-10-30T22:10:58.436277Z"},{"Name":"o' lien","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXphwvuCYsck8rxuZh90oebi4IQD8_wpVvkhcxpqEuXzSqrS7g=s120-c-rp-mo-br100","Rating":5,"Description":"I found Icon Fitness  by my friend  and it was my luckiest find ever. This fitness experience is the real deal. A great workout, great crew of people and a great coach’ I am stronger than I have been","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfayN91pjB9c0vaeQe1boIoKT84TTYlU_V3b4KNMQWssOx951SsfA2FLCxNaxFNaJBTT4sOnJhhE8tnldsRAlppKpNTvh6XidsqdAzYFs0Xf99gQtcXLdwpZKJBqSV-xVmz9ys=k-no"],"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNPdC1fUmpBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101636444859576370062/reviews?hl=en-GB","posted_at_unix_micros":1655906719160294,"updated_at_unix_micros":1655906719160294,"language":"en","translated_lang":"","text_original":"I found Icon Fitness  by my friend  and it was my luckiest find ever. This fitness experience is the real deal. A great workout, great crew of people and a great coach’ I am stronger than I have been","text_translated":"","published_at":"2022-06-22T14:05:19.160294Z"},{"Name":"Geethanjali Muthukrishnan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL4uNlhGmj0tTNVvpUcH2zTAAKdC_JSnlx5pbrq-zq6BRiZ_Q=s120-c-rp-mo-br100","Rating":5,"Description":"I came to the Gym to lose weight, but the master made me understand that losing weight is not our goal instead being fit, being healthy is the most important role in our life. I have lost 14kg in a healthy way. Master taught me about self defence as well as boxing. ICON used to conduct marathon and other competitions. It is very exciting to participate and had wonderful moments. This place really changed my life and i have recovered my health problems. I have overcome many challenges as well.\n\nThank you master 🤝🩵","Images":null,"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnTURBOHRYaG5RRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117735903036418959021/reviews?hl=en-GB","posted_at_unix_micros":1738980447073051,"updated_at_unix_micros":1738980447073051,"language":"en","translated_lang":"","text_original":"I came to the Gym to lose weight, but the master made me understand that losing weight is not our goal instead being fit, being healthy is the most important role in our life. I have lost 14kg in a healthy way. Master taught me about self defence as well as boxing. ICON used to conduct marathon and other competitions. It is very exciting to participate and had wonderful moments. This place really changed my life and i have recovered my health problems. I have overcome many challenges as well.\n\nThank you master 🤝🩵","text_translated":"","published_at":"2025-02-08T02:07:27.073051Z"}]</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>43</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Beast+Fitness+Studio+%28Unisex%29/data=!4m7!3m6!1s0x3a5261ca971d262f:0x15eac83381330725!8m2!3d13.0509782!4d80.1127075!16s%2Fg%2F11rzgx79b7!19sChIJLyYdl8phUjoRJQczgTPI6hU</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Beast Fitness Studio (Unisex)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6/54, Church street, Avadi Rd, opp. to Indian Overseas Bank, Senneer Kuppam, Karayanchavadi, Senneerkuppam, Tamil Nadu 600056</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["6–11 am"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>096770 07018</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>3427+93 Senneerkuppam, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>153</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":2,"4":9,"5":142}</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>13.050978</v>
+      </c>
+      <c r="R67" t="n">
+        <v>80.112707</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1579294742883272485</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdSidzondDlZIn2RgI9fjJfNYn3X8W19rqW8UBdxxlbz9LmrlOtEMoK6pEdGi0IYxJWK5l1C96hnzyeK8-Xi9JgtzVXzgRkfXJu0q5BsU8ttEtZIU35sGz5HAX981wKiNeNPqeW=w408-h906-k-no</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>0x3a5261ca971d262f:0x15eac83381330725</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>ChIJLyYdl8phUjoRJQczgTPI6hU</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>{"id":"101778130163029575397","name":"Beast Fitness Studio (Unisex) (Owner)","link":"https://www.google.com/maps/contrib/101778130163029575397"}</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>{"borough":"Senneer Kuppam, Karayanchavadi","street":"6/54, Church street, Avadi Rd, opp. to Indian Overseas Bank","city":"Senneerkuppam","postal_code":"600056","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Assistive hearing loop","enabled":true},{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>[{"Name":"Gopi","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIBhgOS-dnsmFe_S2qWSpRmcRs8_J7p-Rt1YCuCa8cipAPoFw=s120-c-rp-mo-br100","Rating":5,"Description":"Today pain' tomorrow gain one off the best unisex gym in Poonamallee/ karayachavadi low fees and worth gym equipments ( it's my own experience)","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLegMzM5QzzHWP51GqPK_XBfTEbmq6Pzng2vmTPHBobgrtV1G8K7tefmxf29U56A8hvjheqUAbHQQIqwqwB8gqgxSzsjplBndZzmJcWtB924CGmeL4qHn_nHrIelIkSSUZBn-WVcDqVdGRU=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdiEcDZlIrQzr5lwYnEaFDEOzI2F3oNxZWzTaYuIrGazhdGejSALm8mrGI1DaNd5Gwr9NqWhyMC7T8ELpFysyMr6gMFt9A2BikWV7K-_hQiulh1lZnsdWBMa2P9PGbvzH9nlKJbSxMVCEx0=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfZii1S2U3sa76ta4Ngh8Ow7hSoulcPj21_mNQZQZoDxQvmYEq87OUI_17-6OtueUAb8rihs6E6M5tHiYdQxZuUwNCOZzI8IPq7LgT5rQYukOgQF4xgBjI_Q01iUXJ4L9WYPUJtyCr14wMq=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLc3ZdaARvZHe74Rdh5po1qWXJifaP8nR_aKT85NH0dH9AZKsx-M88rN0qFbfo0lMCEaFxqwi-hQBDeMiFN-bSNdQbs-6t2vxib59Sy2-w9esj3M7vgPja7zair0AS-mB9dnENKrgC11bW8a=k-no"],"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psRmVtd3hkVXRhTWpoNWFFRTRVMkpRUlZCMWRXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108210995361427165155/reviews?hl=en-GB","posted_at_unix_micros":1769182104063371,"updated_at_unix_micros":1769182280445481,"language":"en","translated_lang":"","text_original":"Today pain' tomorrow gain one off the best unisex gym in Poonamallee/ karayachavadi low fees and worth gym equipments ( it's my own experience)","text_translated":"","published_at":"2026-01-23T15:28:24.063371Z"},{"Name":"Rohith S","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVyjQicuso9ETxRYDC-eAJYW6O90n2tK6YoVBSsV0IyTH6dbBEg=s120-c-rp-mo-br100","Rating":5,"Description":"The most affordable gym in Karayanchavadi. It is spacious, well-equiped, and a nice atmosphere inside. The Master guides well, and I recommend this place for beginners. I have been working out here for almost two years and have always had a good experience from the first day.","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2poUlNtRkxTMU5RYm5STFJtRm5OMnBzVlhabWJWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115398255593090158295/reviews?hl=en-GB","posted_at_unix_micros":1754496549474293,"updated_at_unix_micros":1754499512065061,"language":"en","translated_lang":"","text_original":"The most affordable gym in Karayanchavadi. It is spacious, well-equiped, and a nice atmosphere inside. The Master guides well, and I recommend this place for beginners. I have been working out here for almost two years and have always had a good experience from the first day.","text_translated":"","published_at":"2025-08-06T16:09:09.474293Z"},{"Name":"Isaac Charles Immanuel","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXv-pGuvZTCdf--9gelTUW0oiRW7dXOivXRWKKDHMhAHJhVDH48Zg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"✅One of the best Unisex Gym in the neighborhood\n✅The trainer will be there to help you if you need anything\n✅AC, water and steam are available\n✅Cardio, CrossFit and lifting\n✅ Moderate Crowd\n✅5:30 am -10:30 pm","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdff3dAq8MW5YFqCXFAdiOW_gilZNLGe1Wc4ZtnfhfLpxlGlCccr1JYa1wdcpaN6sxmpJ9k6-1y0OR7ipW3QO4FqBe3Hn-ZDOigPNVOjq_UNl-eLOdfRzOepviYeba-eOKZTC-xbg=k-no"],"When":"3 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNod2RPaXVBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107573757547114304987/reviews?hl=en-GB","posted_at_unix_micros":1676398464572342,"updated_at_unix_micros":1676398496380992,"language":"en","translated_lang":"","text_original":"✅One of the best Unisex Gym in the neighborhood\n✅The trainer will be there to help you if you need anything\n✅AC, water and steam are available\n✅Cardio, CrossFit and lifting\n✅ Moderate Crowd\n✅5:30 am -10:30 pm","text_translated":"","published_at":"2023-02-14T18:14:24.572342Z"},{"Name":"Vigneshwaran Vicky","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWfZBlHzv33TuvFMWYjt6enzQza10rSZilcAl5M8KK--Vvez8k=s120-c-rp-mo-br100","Rating":5,"Description":"one of the greatest unisex gym of all time i have seen with all experienced trainers with all sort of modern equipments. Very supportive staffs and personal trainings also given to the best. In one word the best place for fitness freaks to forget everything and keep you in shape always!!","Images":null,"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUN1aVlqczNBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110956566325962320305/reviews?hl=en-GB","posted_at_unix_micros":1659257960140304,"updated_at_unix_micros":1659257960140304,"language":"en","translated_lang":"","text_original":"one of the greatest unisex gym of all time i have seen with all experienced trainers with all sort of modern equipments. Very supportive staffs and personal trainings also given to the best. In one word the best place for fitness freaks to forget everything and keep you in shape always!!","text_translated":"","published_at":"2022-07-31T08:59:20.140304Z"},{"Name":"jayakanth parthipan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUz7iSUqUiLjxXXk08CgsXPyiV2SfIoevcx5ayiEj23kNzWHiYh=s120-c-rp-mo-br100","Rating":5,"Description":"nice atmosphere latest gym equipment good experience and friendly coach 🏋🏽","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLf2GRvoW0QXKzZcfP51vhZO5h1B_xv_vR-lAPnIMIrlQrmoa6aTow_9_zCnwchsuPbxqJNxsWNQX9xvIk4V-TwusF7qg5P2XYbG8qp0R9KWM2JyEl9AW9GzXcwaLK7iWTyQC5-X2g=k-no"],"When":"3 years ago","review_id":"ChRDSUhNMG9nS0VJQ0FnSURoN3RaRxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108063135895705811239/reviews?hl=en-GB","posted_at_unix_micros":1678356862160633,"updated_at_unix_micros":1678356932456533,"language":"en","translated_lang":"","text_original":"nice atmosphere latest gym equipment good experience and friendly coach 🏋🏽","text_translated":"","published_at":"2023-03-09T10:14:22.160633Z"}]</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>43</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fitness+Essentials+%28T.Nagar%29/data=!4m7!3m6!1s0x3a526710b8eb6ef3:0x1a637aecc3841131!8m2!3d13.0492533!4d80.2312832!16s%2Fg%2F11vwnb8kb6!19sChIJ827ruBBnUjoRMRGEw-x6Yxo</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Fitness Essentials (T.Nagar)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>7/40, Ramakrishna St, T. Nagar, Chennai, Tamil Nadu 600017</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10:30 pm"],"Monday":["5:30 am–10:30 pm"],"Saturday":["5:30 am–10:30 pm"],"Sunday":["7 am–12 pm"],"Thursday":["5:30 am–10:30 pm"],"Tuesday":["5:30 am–10:30 pm"],"Wednesday":["5:30 am–10:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>086081 11181</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>26XJ+PG Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>136</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>{"1":2,"2":0,"3":0,"4":5,"5":129}</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>13.049253</v>
+      </c>
+      <c r="R68" t="n">
+        <v>80.231283</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1901498624991564081</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLduDQKqpxDSXvAPKOqkKvvsj-SJKfWO-GZz-g_VOMYen_41CI59xrgO9jUTZE1VhaG3tNcSScFdl3TDcqIFm0ugJ0bx5WugN9hgPZgiJL6W9NZ7DaXZcEEqxeHCSY8fTwXmc8_yDg=w408-h272-k-no</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>0x3a526710b8eb6ef3:0x1a637aecc3841131</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>ChIJ827ruBBnUjoRMRGEw-x6Yxo</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>{"id":"102833507741083838176","name":"Fitness Essentials (T.Nagar) (Owner)","link":"https://www.google.com/maps/contrib/102833507741083838176"}</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>{"borough":"T. Nagar","street":"7/40, Ramakrishna St","city":"Chennai","postal_code":"600017","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>[{"Name":"Shivanand Raj","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVhjNdTm3joKzdVw4AVMGeqKYraUDeUFLterMe4IskAhF1Qcgwe=s120-c-rp-mo-br100","Rating":5,"Description":"The Best Gym in Chennai. Period.\n\nI've been working out at Fitness Essentials, T-Nagar for almost two years now, and having trained at multiple gyms across Chennai over the years, I can confidently say this is one of the best gyms in the city right now ❤️💪\n\nSpread across three floors of pure awesomeness, the moment you walk in, you notice how spacious and well-lit the space is. There’s room to breathe, move, and actually focus on your workout without feeling cramped or distracted. No overcrowding, no chaos, just the right environment to focus and show up for yourself.\n\nThe equipment is world-class. It's clear the team behind this gym hasn't cut corners, they've invested thoughtfully in every detail.\n\nWhether you're lifting, doing cardio, or working on mobility, everything you need is available and always in excellent condition.\n\nCleanliness is another big win. From the workout floor to the locker rooms, everything is consistently pristine and well-maintained.\n\nIt's one of those rare gyms where you actually enjoy spending time, not just rushing in and out.\n\nThe management is warm, friendly and approachable. You can feel that this gym was created with genuine intent and passion, not just as a business, but as a space for people who love to train.\n\nI'm genuinely grateful a place like this exists right in the heart of Chennai. Highly recommend 💯","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLf4JMYf_ABfJj33ayOU9hYjMOvXTXHjodm7YTOewOjUAUgeNdwr9tasdVR-hdD5b6f4xZNX1RGWCS8gKoIzErGFZJz61Y5kFPegbLzH73YSzIfd_drQqglIPBp7D5uR4fCAVjyG3q4waPn5=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcMiLfx244fE-w9DZ4KghosFcXgbRjsiSl-WuwsWtnS1c11JcYwFomzclu3briVmFW7jISPu9AE8d1gLXFqbsMpmyu1aWs9dQPvVzKsb6m0Fa8Bi1umQcfEtiQ6rkUhxiwMpUvJ657-JDc0=k-no"],"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pOcVZGRm9ZVmhLU0VoeVkwSnNPVU56TFd3eVRtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105925174868385715848/reviews?hl=en-GB","posted_at_unix_micros":1775288720864918,"updated_at_unix_micros":1775293420670842,"language":"en","translated_lang":"","text_original":"The Best Gym in Chennai. Period.\n\nI've been working out at Fitness Essentials, T-Nagar for almost two years now, and having trained at multiple gyms across Chennai over the years, I can confidently say this is one of the best gyms in the city right now ❤️💪\n\nSpread across three floors of pure awesomeness, the moment you walk in, you notice how spacious and well-lit the space is. There’s room to breathe, move, and actually focus on your workout without feeling cramped or distracted. No overcrowding, no chaos, just the right environment to focus and show up for yourself.\n\nThe equipment is world-class. It's clear the team behind this gym hasn't cut corners, they've invested thoughtfully in every detail.\n\nWhether you're lifting, doing cardio, or working on mobility, everything you need is available and always in excellent condition.\n\nCleanliness is another big win. From the workout floor to the locker rooms, everything is consistently pristine and well-maintained.\n\nIt's one of those rare gyms where you actually enjoy spending time, not just rushing in and out.\n\nThe management is warm, friendly and approachable. You can feel that this gym was created with genuine intent and passion, not just as a business, but as a space for people who love to train.\n\nI'm genuinely grateful a place like this exists right in the heart of Chennai. Highly recommend 💯","text_translated":"","published_at":"2026-04-04T07:45:20.864918Z"},{"Name":"sruthii praveen","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKL6O74yjAbokS-1UwrOL65P2fOA8XUVCf24VT5dySu8HGA=s120-c-rp-mo-br100","Rating":5,"Description":"A very well-maintained gym spread across three floors, with a dedicated cardio area that never feels overcrowded. The cleanliness standards are impressive—sanitizers are available at all stations, and there is always a staff member actively cleaning and sanitizing the equipment throughout the day. The overall environment is neat, hygienic, and comfortable, making it a great place to work out consistently. Highly recommended for anyone looking for a clean and well-organized fitness facility. 💪🏻🏋️‍♀️","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21KNlltZGxRbDkwWlZOek9UZDRNVE5KVjB3dGJYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111834868962919962530/reviews?hl=en-GB","posted_at_unix_micros":1781589268921346,"updated_at_unix_micros":1781589268921346,"language":"en","translated_lang":"","text_original":"A very well-maintained gym spread across three floors, with a dedicated cardio area that never feels overcrowded. The cleanliness standards are impressive—sanitizers are available at all stations, and there is always a staff member actively cleaning and sanitizing the equipment throughout the day. The overall environment is neat, hygienic, and comfortable, making it a great place to work out consistently. Highly recommended for anyone looking for a clean and well-organized fitness facility. 💪🏻🏋️‍♀️","text_translated":"","published_at":"2026-06-16T05:54:28.921346Z"},{"Name":"Ainsely Raj","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUP1vJ40xlvJWy2xkDuY-3GAX9WtCdww37Oi9jxkZS55FJ4EhTL=s120-c-rp-mo-br100","Rating":5,"Description":"Been working out at Fitness Essentials with my dad for a while now, and it’s been a great experience for both of us. The gym is well-equipped with all the essentials, and everything is kept clean and well-maintained.\n\nThe environment is really comfortable and motivating, which makes it easy to stay consistent. The trainers are friendly and helpful whenever needed, without being pushy.\n\nIt’s a place that works well for all age groups and fitness levels, which is something we really appreciate. Definitely recommend it if you’re looking for a good gym in T Nagar.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xWQ05td3djVnAwYVVGU2JqTm5TMmt3VDBsTFVrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103859061561847766200/reviews?hl=en-GB","posted_at_unix_micros":1777365810650017,"updated_at_unix_micros":1777365810650017,"language":"en","translated_lang":"","text_original":"Been working out at Fitness Essentials with my dad for a while now, and it’s been a great experience for both of us. The gym is well-equipped with all the essentials, and everything is kept clean and well-maintained.\n\nThe environment is really comfortable and motivating, which makes it easy to stay consistent. The trainers are friendly and helpful whenever needed, without being pushy.\n\nIt’s a place that works well for all age groups and fitness levels, which is something we really appreciate. Definitely recommend it if you’re looking for a good gym in T Nagar.","text_translated":"","published_at":"2026-04-28T08:43:30.650017Z"},{"Name":"Dharmesh Balraj","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVBVvW7bcpQ1pQ92wIOS_9UMlpDA0F5RBZWNu2VW4Vm2IPPWmg=s120-c-rp-mo-br100","Rating":5,"Description":"Gym stands out with its world-class, state-of-the-art facilities and immaculate hygiene standards. Equipped with international-grade machines from Life Fitness, Star Trac, and Hammer Strength, it truly delivers an elite training experience.\n\nTrainers are so friendly, helpful and make sure safety.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tKdlFWSlhjUzFrTkhaRU1FMDJNWGs0TFhwS1owRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103627628229951509321/reviews?hl=en-GB","posted_at_unix_micros":1781621491146673,"updated_at_unix_micros":1781621491146673,"language":"en","translated_lang":"","text_original":"Gym stands out with its world-class, state-of-the-art facilities and immaculate hygiene standards. Equipped with international-grade machines from Life Fitness, Star Trac, and Hammer Strength, it truly delivers an elite training experience.\n\nTrainers are so friendly, helpful and make sure safety.","text_translated":"","published_at":"2026-06-16T14:51:31.146673Z"},{"Name":"Inkarsal P","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKPPqtUtkVVFWLn2t8KV8QhFlwqXfYWIMS0_dw_9HmS-pStqA=s120-c-rp-mo-br100","Rating":5,"Description":"I had one of the most enjoyable and rewarding fitness experiences at Fitness Essentials, T. Nagar. I lost good amount of weight while struggling with Hypothyroidism and PCOS, all thanks to their structured plan and support. The gym offers a clean, hygienic, and comfortable environment that makes working out a pleasure. Mr. Navraj and his team are highly professional, approachable, and always willing to address any concerns while creating personalized fitness plans. Their guidance and support have been invaluable. Without a doubt, this is one of the best gyms in Chennai, and I would highly recommend it to anyone looking to achieve their fitness goals.\n5/5 for real !","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2poemMwVkZlV3RDYkZSSFUyOTVMVXBtZWpkTlpYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105438473810854814851/reviews?hl=en-GB","posted_at_unix_micros":1781368737943965,"updated_at_unix_micros":1781368737943965,"language":"en","translated_lang":"","text_original":"I had one of the most enjoyable and rewarding fitness experiences at Fitness Essentials, T. Nagar. I lost good amount of weight while struggling with Hypothyroidism and PCOS, all thanks to their structured plan and support. The gym offers a clean, hygienic, and comfortable environment that makes working out a pleasure. Mr. Navraj and his team are highly professional, approachable, and always willing to address any concerns while creating personalized fitness plans. Their guidance and support have been invaluable. Without a doubt, this is one of the best gyms in Chennai, and I would highly recommend it to anyone looking to achieve their fitness goals.\n5/5 for real !","text_translated":"","published_at":"2026-06-13T16:38:57.943965Z"}]</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP68" t="inlineStr"/>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>43</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Target+fitness+center/data=!4m7!3m6!1s0x3a5261ebc2e7a619:0xbc35da2e67f625f6!8m2!3d13.0097437!4d80.1228226!16s%2Fg%2F11spxl0ssg!19sChIJGabnwuthUjoR9iX2Zy7aNbw</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Target fitness center</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>7/116, Target fitness center, Kundrathur Main Rd, Kovur, Dhanalakshmi Nagar, Tharapakkam, Kovur, Tamil Nadu 600128</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–9:30 pm"],"Monday":["5:30 am–9:30 pm"],"Saturday":["5:30 am–9:30 pm"],"Sunday":["7–11 am"],"Thursday":["5:30 am–9:30 pm"],"Tuesday":["5:30 am–9:30 pm"],"Wednesday":["5:30 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>098843 31770</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>245F+V4 Kovur, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>136</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>{"1":4,"2":2,"3":2,"4":20,"5":108}</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>13.009744</v>
+      </c>
+      <c r="R69" t="n">
+        <v>80.122823</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>13561985745743652342</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcWs5YiY0zerqMFvX1qbcBQ87HSHQ2PlIC6hmRCyyKKn9acpIw8LD4a3iSx-PFJ3j4EJyClrBoL08hGkqFVG7CMnU5gEKCBwJKqzmTuZMNLFhTQcgFejV3Ql7Z62Zv6j2I4NVlG=w408-h725-k-no</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>0x3a5261ebc2e7a619:0xbc35da2e67f625f6</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>ChIJGabnwuthUjoR9iX2Zy7aNbw</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>{"id":"108205684965668417084","name":"Target fitness center (Owner)","link":"https://www.google.com/maps/contrib/108205684965668417084"}</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>{"borough":"Kovur, Dhanalakshmi Nagar, Tharapakkam","street":"7/116, Kundrathur Main Rd","city":"Kovur","postal_code":"600128","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>[{"Name":"Fuzail Ahmed","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVXogi-ibt3R5J8mcAobEerm4hi7afLdoxSQolN3AxuENUcJyz1=s120-c-rp-mo-br100","Rating":4,"Description":"This gym is one of the best places to train if you’re serious about fitness. The equipment is modern, well-maintained, and suitable for all types of workouts including strength training, cardio, and functional exercises","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLc_oB2zeEfled8K7Cd9A25uzM8f5ugfIJzXUS-iG5E0Pefaj7QZQwVXq7bhU_w2z2dCKgExLRBtjrrJFvt0-MjaqXMVV7OLonx_4j47oBKXkQ9acCIxG8pDbU6nmHFewPl4zuq5jBWOyk3x=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tsVmFWSlpURFIyU0ZKNVpXNUtXbXB6WkZWWWNtYxAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/114654501895042659350/reviews?hl=en-GB","posted_at_unix_micros":1777686218654013,"updated_at_unix_micros":1777686218654013,"language":"en","translated_lang":"","text_original":"This gym is one of the best places to train if you’re serious about fitness. The equipment is modern, well-maintained, and suitable for all types of workouts including strength training, cardio, and functional exercises","text_translated":"","published_at":"2026-05-02T01:43:38.654013Z"},{"Name":"king sharafath","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUyXJdDT2K7XLWXIORg6uHEoM1WQORqQE72OF8TFGbo66U4qaI=s120-c-rp-mo-br100","Rating":5,"Description":"The trainers are really friendly and helpful in this place. The gym has good facilities and a lot of machines to workout with. There are many numbers of weights available. I've been working out in this gym for some time now and I'm seeing great results. The gym is really spacious with 2 floors, one for lifting and one for cardio. If you live near kovur, I recommend this gym.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT200eU5Va3hUR2R4U1hGTE1YWlhPRFpUVkhKNlNuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107038138275390468243/reviews?hl=en-GB","posted_at_unix_micros":1776697810593159,"updated_at_unix_micros":1776697810593159,"language":"en","translated_lang":"","text_original":"The trainers are really friendly and helpful in this place. The gym has good facilities and a lot of machines to workout with. There are many numbers of weights available. I've been working out in this gym for some time now and I'm seeing great results. The gym is really spacious with 2 floors, one for lifting and one for cardio. If you live near kovur, I recommend this gym.","text_translated":"","reply_text_original":"We really appreciate the recommendation! It’s awesome to have you training with us and seeing such progress. We'll be sure to share your kind words with the training team. See you on the floor!","reply_language":"en","reply_posted_at_unix_micros":1776821098000000,"reply_updated_at_unix_micros":1776821098000000,"published_at":"2026-04-20T15:10:10.593159Z"},{"Name":"DINESH Dinesh3811","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVPKiI_5JOjKlrD5dMXqX30Ytzt04eftnvMdiQbOD2AZJBdPZwk=s120-c-rp-mo-br100","Rating":5,"Description":"Great gym with good equipment and a clean environment. The trainers are friendly and always ready to help. Really motivates me to stay consistent with my workouts.","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xSQ1FrMXZkbGhEV2tzMVNYRnpXa2xTVjFwWFIwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107320780790245998151/reviews?hl=en-GB","posted_at_unix_micros":1776735111475216,"updated_at_unix_micros":1776735111475216,"language":"en","translated_lang":"","text_original":"Great gym with good equipment and a clean environment. The trainers are friendly and always ready to help. Really motivates me to stay consistent with my workouts.","text_translated":"","reply_text_original":"Thank you for the recommendation! We’re glad you’re enjoying the facility and the support from our team. Stay strong!\"","reply_language":"en","reply_posted_at_unix_micros":1776820963000000,"reply_updated_at_unix_micros":1776820963000000,"published_at":"2026-04-21T01:31:51.475216Z"},{"Name":"JIABUR Rahman","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXxSeIiOUfXewFvYDSlkz4OrYAGTaMC6l296eNISg7RQ8pBrW2n=s120-c-rp-mo-br100","Rating":5,"Description":"The gym center here is excellent. The gym trainer is also very good. If you want to maintain your fitness, you should definitely come here 😍💪","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21sUFIwRkJSVk5uTUVsRE0wWm9ZblJoWW1GNVJuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109480084549449467805/reviews?hl=en-GB","posted_at_unix_micros":1776749535719489,"updated_at_unix_micros":1776750148607675,"language":"en","translated_lang":"","text_original":"The gym center here is excellent. The gym trainer is also very good. If you want to maintain your fitness, you should definitely come here 😍💪","text_translated":"","reply_text_original":"We really appreciate the recommendation! It’s great to have you training with us. Our team is dedicated to providing the best guidance possible. See you at your next session.","reply_language":"en","reply_posted_at_unix_micros":1776820840000000,"reply_updated_at_unix_micros":1776820840000000,"published_at":"2026-04-21T05:32:15.719489Z"},{"Name":"Chakravarthi RT","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU6Y63LhSpJPQR-Ud9X8sItlrtJhCwLvPnZvSV0wyUcNwgmAfCq=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Best gym in Chennai\nValue for money\nYearly package is budget friendly\nMaster and Trainers are friendly people\nBig area to workout near to 4k sq ft\nTotal 2 floor, one floor for strength training\nAnd one floor for cardio, zumba and other activities. All equipment are fresh and clean environment.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfDdfNlqmXoSwxVkiWG3uEXjE0IuPDgEAoTSuH-SA0enOUsSZAWGt-m5za4eZBtfiazCUjzlyK2i36DYZx5QJMXswohpJWNT_x5rpkwI9dzADhhFvVCAMdCMzbUuTC_xFDkJNIEKw=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLe0SJcvgZQxBFNu5RZlWnOPVcfmJZ9BXBzj2y0oXjZIFLd5L96gwiPj64fEyAzQjqA9ZkFq-vBYShKH3xdGoGLZh1w8cKnBhacIhhdxYfPivctPiAJAFX7M537utQuiIJAyrOcS=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLc0v3DaUdRk7No46OgR6OmvEjCDWKI6D-HBt3i5UXDxhPQ3X4FrygFwYUgx60DcYdvSL_DFiEsT7a4FDRI5pZOcvJagW_wUxMOax-3exY4jJYEPLWjPsLTQ7bJ2YQrPvH1M_NBe=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeig6bipMJiNuvyRy0YimQR2WqdyzJdNtqVgp9hfWFQPVe4gEBRooyHV-zMOFUNLX4X81MV_1u1Df3wyAH5F6tRu-SIS9TsvdK-cI9--nMW9jNjkkdVRKEzMRMl_mhZClviSOCH=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLco2aOm5SeIqoFroiwpi2rPZyBYKzNaig56dV5lUCACz3oUCFIlhFPU3MXfVJZXwSYMZlJDgkVwmibKRApgaywIWLO8J80-ARgGZMEdm3Dvjn9R69K8mNXVq44aBUWcsX2UroyqIA=k-no"],"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURyeUxmX1ZREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101676168401973913026/reviews?hl=en-GB","posted_at_unix_micros":1720890262252317,"updated_at_unix_micros":1720890262252317,"language":"en","translated_lang":"","text_original":"Best gym in Chennai\nValue for money\nYearly package is budget friendly\nMaster and Trainers are friendly people\nBig area to workout near to 4k sq ft\nTotal 2 floor, one floor for strength training\nAnd one floor for cardio, zumba and other activities. All equipment are fresh and clean environment.","text_translated":"","published_at":"2024-07-13T17:04:22.252317Z"}]</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>43</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Geez+Squad/data=!4m7!3m6!1s0x3a52674b40727a51:0x882a70c8e6d3d946!8m2!3d13.0469388!4d80.1990631!16s%2Fg%2F11qpr67_cr!19sChIJUXpyQEtnUjoRRtnT5shwKog</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Geez Squad</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6, 80 Feet Road, Sathya Garden, Saligramam, Chennai, Tamil Nadu 600093</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–10 pm"],"Monday":["6 am–10 pm"],"Saturday":["6 am–10 pm"],"Sunday":["Closed"],"Thursday":["6 am–10 pm"],"Tuesday":["6 am–10 pm"],"Wednesday":["6 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>096000 64354</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>25WX+QJ Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>130</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>{"1":10,"2":1,"3":1,"4":4,"5":114}</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>13.046939</v>
+      </c>
+      <c r="R70" t="n">
+        <v>80.199063</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>9811778746348460358</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcteiKfRC0BsihjXA5RXftpWHbBn_RXNXZl8rpQQwtFQgswOjc8n1MpoNSYsI0eQ_OK6vZSu7JBlehz2BXf_YbLteZuO7cRgbnfl52Rzse-nTlkgo9EWcql0ICVBD4gqWHFbIQqbQ=w425-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>0x3a52674b40727a51:0x882a70c8e6d3d946</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>ChIJUXpyQEtnUjoRRtnT5shwKog</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>{"id":"115816058297691204317","name":"Geez Squad (Owner)","link":"https://www.google.com/maps/contrib/115816058297691204317"}</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>{"borough":"Sathya Garden, Saligramam","street":"6, 80 Feet Road","city":"Chennai","postal_code":"600093","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>[{"Name":"Karthika Kanagaraj","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK-iuBXnCGvAVYit2ddS7pIB4PBkkASoiU5p9zTB-BeRv0YnQ=s120-c-rp-mo-br100","Rating":5,"Description":"Joining Geez Squad has been one of the best decisions I’ve made for my fitness journey. The entire team is supportive, motivating, and genuinely invested in helping you achieve your goals.\n\nA special thanks to Peter for always encouraging me, pushing me to do better, and being so flexible with schedules—it really helps me stay consistent. Even though I only have one HIIT session a week, Madhu makes it so impactful that it keeps me motivated all week.\n\nFrom workouts and nutrition guidance to regular check-ins and constant encouragement, Geez Squad makes fitness enjoyable. I actually look forward to every session and can’t wait to see how far this journey takes me. Highly recommend! ⭐⭐⭐⭐⭐","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21saU15MHpRV054ZVVWYWFqRXhXWE5hWldrNWJHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118204822659138797971/reviews?hl=en-GB","posted_at_unix_micros":1783526014952984,"updated_at_unix_micros":1783526014952984,"language":"en","translated_lang":"","text_original":"Joining Geez Squad has been one of the best decisions I’ve made for my fitness journey. The entire team is supportive, motivating, and genuinely invested in helping you achieve your goals.\n\nA special thanks to Peter for always encouraging me, pushing me to do better, and being so flexible with schedules—it really helps me stay consistent. Even though I only have one HIIT session a week, Madhu makes it so impactful that it keeps me motivated all week.\n\nFrom workouts and nutrition guidance to regular check-ins and constant encouragement, Geez Squad makes fitness enjoyable. I actually look forward to every session and can’t wait to see how far this journey takes me. Highly recommend! ⭐⭐⭐⭐⭐","text_translated":"","reply_text_original":"Thank you so much for sharing such a wonderful review! ❤️ We’re truly happy to know that your journey with Geez Squad has been enjoyable, motivating, and consistent.\n\nA special shoutout to Peter and Madhu for making such a positive impact! 💪 Your kind words about their support, flexibility, and dedication mean a lot to the entire team.\n\nWe’re proud to be a part of your fitness journey and can’t wait to see you achieve even more. Keep showing up, keep pushing, and keep believing in yourself! 🔥\n\nThank you for trusting Geez Squad and recommending us. Here’s to many more milestones together! ⭐⭐⭐⭐⭐\n","reply_language":"en","reply_posted_at_unix_micros":1788330635000000,"reply_updated_at_unix_micros":1788330635000000,"published_at":"2026-07-08T15:53:34.952984Z"},{"Name":"Sharun Priya","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVzEz7XhwcpkLHzW9QhJIL1K35_35MIrjfUMAIOgVmgdYVpYsU=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I’m incredibly grateful for the online training support I received during my postpartum recovery journey. Recovering from diastasis recti after pregnancy felt challenging at first, but my trainer Deepika made the entire process safe, manageable, and motivating even through virtual sessions.\n\nWhat amazed me most was how effective the online sessions were. With consistent guidance and support, I was able to recover from diastasis recti, regain my strength, and feel confident in my body again — all from home.\n\nHighly recommend Geez Squad to any new mom looking for safe and professional postpartum recovery support online!  Thank you 👍👍","Images":null,"When":"Edited 4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pjNVMyNHhiVk16V2pKVkxWRmZMVTVTYzJSM2IyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118197915358923000210/reviews?hl=en-GB","posted_at_unix_micros":1779877852022438,"updated_at_unix_micros":1779979114849614,"language":"en","translated_lang":"","text_original":"I’m incredibly grateful for the online training support I received during my postpartum recovery journey. Recovering from diastasis recti after pregnancy felt challenging at first, but my trainer Deepika made the entire process safe, manageable, and motivating even through virtual sessions.\n\nWhat amazed me most was how effective the online sessions were. With consistent guidance and support, I was able to recover from diastasis recti, regain my strength, and feel confident in my body again — all from home.\n\nHighly recommend Geez Squad to any new mom looking for safe and professional postpartum recovery support online!  Thank you 👍👍","text_translated":"","reply_text_original":"Thank you so much for your kind words, Sharun Priya! ❤️ \n\nWe're truly grateful to have been a part of your postpartum recovery journey. Your dedication and consistency played a huge role in achieving these amazing results. We're especially happy to hear that our online coaching made you feel supported, safe, and confident throughout the process.\nA special thank you for recognizing Deepika's efforts—she is passionate about helping every client recover and grow stronger with confidence. 💪\n\nWishing you continued strength, health, and happiness ahead. Thank you for trusting Geez Squad and for recommending us to other moms! 🙏✨\n– Team Geez Squad ❤️","reply_language":"en","reply_posted_at_unix_micros":1780408757000000,"reply_updated_at_unix_micros":1780408757000000,"published_at":"2026-05-27T10:30:52.022438Z"},{"Name":"Abinaya Gokul","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJesk7Gw1AooYnaM-VO37f2jaqVRSoqA1k7mTKjQGsYJF03kYU=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"​Enrolling with Geez Squad and training under Nandha’s guidance has been an absolute game-changer. My efforts to shed weight and gain muscle had consistently hit an insurmountable wall. But Nandha actually took the time to figure out exactly what works for my body.\n​He put together the perfect mix of strength and cardio, and the weight and inches are finally dropping!\nBeyond his stellar technical expertise, his unwavering motivation and meticulous dietary oversight were the catalysts I truly needed. This was far from a transient fitness phase; Nandha has fundamentally elevated my lifestyle. GEEZ SQUAD.. Thank u...","Images":null,"When":"Edited 4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xCMU4zZFBUa056Vmw5b1RHVkVNRlpQYmtreFdVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106128113159500491310/reviews?hl=en-GB","posted_at_unix_micros":1780923924940592,"updated_at_unix_micros":1781192329378199,"language":"en","translated_lang":"","text_original":"​Enrolling with Geez Squad and training under Nandha’s guidance has been an absolute game-changer. My efforts to shed weight and gain muscle had consistently hit an insurmountable wall. But Nandha actually took the time to figure out exactly what works for my body.\n​He put together the perfect mix of strength and cardio, and the weight and inches are finally dropping!\nBeyond his stellar technical expertise, his unwavering motivation and meticulous dietary oversight were the catalysts I truly needed. This was far from a transient fitness phase; Nandha has fundamentally elevated my lifestyle. GEEZ SQUAD.. Thank u...","text_translated":"","reply_text_original":"Thank you so much for your wonderful feedback! ❤️ We’re thrilled to know that Nandha’s guidance has made such a positive impact on your fitness journey.\n\nYour trust, consistency, and dedication are truly inspiring. 💪 We’re proud to be part of your transformation and lifestyle change. Keep pushing and achieving new milestones! 🔥\n\nThank you for choosing Geez Squad! ⭐\n","reply_language":"en","reply_posted_at_unix_micros":1788330878000000,"reply_updated_at_unix_micros":1788330878000000,"published_at":"2026-06-08T13:05:24.940592Z"},{"Name":"Shalu Priya","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVxJY-DBwBCmKEf4FRGW5dwbRDo4lWe2tZz60WWqZAImrqZCerN=s120-c-rp-mo-br100","Rating":5,"Description":"In the middle of 3+ hours of daily travel, endless to-do lists, kitchen chaos, family responsibilities, and career hustle, I found me at this gym.\nI've always believed I was strong, but this journey has made me stronger—both physically and mentally. What makes the difference is having a trainer who keeps you consistent, especially on the days when giving up feels easier than showing up.\nI may not have reached all my goals yet, but today I have something even more valuable: the confidence that I will. Every workout, every bit of encouragement, and every push beyond my comfort zone has brought me closer to becoming the best version of myself.\n\nThank you for believing in me, for your patience, and for reminding me to prioritize myself even when life gets overwhelming.\nThis journey wouldn't have been possible without your guidance.\nThank you Geez Squad","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tOVU1WUXhUaTFRT1ZjdExVeFpWREp6ZERGV09XYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108473695356998528967/reviews?hl=en-GB","posted_at_unix_micros":1782301430846718,"updated_at_unix_micros":1782301430846718,"language":"en","translated_lang":"","text_original":"In the middle of 3+ hours of daily travel, endless to-do lists, kitchen chaos, family responsibilities, and career hustle, I found me at this gym.\nI've always believed I was strong, but this journey has made me stronger—both physically and mentally. What makes the difference is having a trainer who keeps you consistent, especially on the days when giving up feels easier than showing up.\nI may not have reached all my goals yet, but today I have something even more valuable: the confidence that I will. Every workout, every bit of encouragement, and every push beyond my comfort zone has brought me closer to becoming the best version of myself.\n\nThank you for believing in me, for your patience, and for reminding me to prioritize myself even when life gets overwhelming.\nThis journey wouldn't have been possible without your guidance.\nThank you Geez Squad","text_translated":"","reply_text_original":"Thank you so much, Shalu Mam ❤️ Your words mean the world to us. We’re so proud of your consistency, strength, and commitment despite your busy schedule. 💪\n\nThank you for trusting Geez Squad and allowing us to be part of your journey. Keep pushing—you’re doing amazing! 🔥\n","reply_language":"en","reply_posted_at_unix_micros":1788330721000000,"reply_updated_at_unix_micros":1788330721000000,"published_at":"2026-06-24T11:43:50.846718Z"},{"Name":"Rani Rajendran","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJvR8dVFVw9jiFWxjXffX7xlnXD8QUTwKQkkPNZl6YSvRfPzA=s120-c-rp-mo-br100","Rating":5,"Description":"After years of neglecting my physical health,I finally mustered the courage to step foot into the intimidating world of the gym.My initial trepidation dissolved as soon as I walked through the doors of Geez Squad ,you are enveloped in a world of motivation,dedication and hard work .A sanctuary where sweat,determination and camaraderie intermingled.The sound of weight’s clanking, bodies pushing themselves to their limits and trainers shouting words of encouragement created a symphony of strength and resilience.Surrounded by machines that promised transformation and individuals who exuded dedication,I felt a sense of belonging that I had never experienced before.Each drop of sweat shed was not in vain but rather a badge of honour in the sanctum dedicated to self improvement.\nAn amazing experience in the geez squad transformed me not only physically but also mentally.Molding me into someone capable of conquering any obstacle that stands in my way","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdX7Vl7ADq7dxZhL334cblWhdJF4Pkz99V0kPc7P9vv23F0iwW4HHuO6_KQH8ivHURAXnNXlY1hny8gLo3ZcyOlTujCDs_4Z0gLGUCIK88_hBgOOnU50hcofKTGCzR6KV3u6xJV=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdHvhcci5pxUFnJMg6yJaXqIeDT2x7D1lZxrACNqkKJH_xCULg74-0NJ3wYtILYZAghRBe2BmELA1q3HBUmpMtLF7LKwpcb2-i5qHf_Pd2N3gEOHXup-x_eE17_2n-TuoIqj10r7A=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLedp5j_WkeuHKH66Cnrx8KsW6VfQewqAlueI12sFEK6K35FL2OMpkukNI1T9C1UbyDDeR3hvdt6-9dBE-TuoAOjgIdpr86pVfWyQMjfWVXpwZgYe8QyxX2EL476orZ4V8lb1HyI=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLezt9MkXs_tg3UAK25vwmM9CEFgaXHfa_Gqq4atcHVJnHs2I6R_UtiPxKvfzKdYM-44b2xr7B8F4WLStNDVxzxU0uvv8A3308Rfn-DFs27HQB0D-uBzjYRDEaIoNycJQgRtYocCTw=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd6u-RtMRFbGRCoWMQchGsHiKC1iLxD_fbrOZyN2L7K-sNqaZk2jCMWwpGfzpmbGkIX9gTh4TNyf011QX2TptD9Fb_50lvhMpf47rbJuxiWstrL6VRLoNYH2aKJUcd0R5qtLVM=k-no"],"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURudzhHaEJnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109596882578025626056/reviews?hl=en-GB","posted_at_unix_micros":1728467130366688,"updated_at_unix_micros":1728474548504882,"language":"en","translated_lang":"","text_original":"After years of neglecting my physical health,I finally mustered the courage to step foot into the intimidating world of the gym.My initial trepidation dissolved as soon as I walked through the doors of Geez Squad ,you are enveloped in a world of motivation,dedication and hard work .A sanctuary where sweat,determination and camaraderie intermingled.The sound of weight’s clanking, bodies pushing themselves to their limits and trainers shouting words of encouragement created a symphony of strength and resilience.Surrounded by machines that promised transformation and individuals who exuded dedication,I felt a sense of belonging that I had never experienced before.Each drop of sweat shed was not in vain but rather a badge of honour in the sanctum dedicated to self improvement.\nAn amazing experience in the geez squad transformed me not only physically but also mentally.Molding me into someone capable of conquering any obstacle that stands in my way","text_translated":"","published_at":"2024-10-09T09:45:30.366688Z"}]</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>43</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Stretch+Fitness+Club/data=!4m7!3m6!1s0x3a526197ae1ae633:0x90eed96c27d73dfa!8m2!3d13.076676!4d80.1259516!16s%2Fg%2F11tp38z78w!19sChIJM-YarpdhUjoR-j3XJ2zZ7pA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Stretch Fitness Club</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>117/1 devi nagar 8th street, salai, Koladi, Thiruverkadu, Tamil Nadu 600077</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–12:30 pm","1:30–10 pm"],"Monday":["5 am–12:30 pm","1:30–10 pm"],"Saturday":["5 am–12:30 pm","1:30–10 pm"],"Sunday":["6:30 am–12 pm"],"Thursday":["5 am–12:30 pm","1:30–10 pm"],"Tuesday":["5 am–12:30 pm","1:30–10 pm"],"Wednesday":["5 am–12:30 pm","1:30–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>090032 08288</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>34GG+M9 Thiruverkadu, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>130</v>
+      </c>
+      <c r="O71" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>{"1":14,"2":0,"3":0,"4":11,"5":105}</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>13.076676</v>
+      </c>
+      <c r="R71" t="n">
+        <v>80.125952</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>10443523644466871802</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLew_dZwXpnuo-H76L7tN6EIxGRRzQchW5E7mj8L2DoN1YI6f5Dy4bkH1dIXFcrjbZn_9NARLtCFE_5s5XX85Z_Qc3jXEMTzOKaJIYP4GX-BS6UXrmOOtd5Slb8GiSrnFLwRp5CZ=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>0x3a526197ae1ae633:0x90eed96c27d73dfa</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>ChIJM-YarpdhUjoR-j3XJ2zZ7pA</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>{"id":"104986551458558692759","name":"Stretch Fitness Club (Owner)","link":"https://www.google.com/maps/contrib/104986551458558692759"}</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>{"borough":"Koladi, Thiruverkadu","street":"117/1 devi nagar 8th street, salai","city":"Thiruverkadu","postal_code":"600077","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Assistive hearing loop","enabled":true},{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>[{"Name":"Lakshmi Prasath","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK-H77L2UopjudYQQ_6er103nBr8ZnNB7VHiaYrWZJNid9pVA=s120-c-rp-mo-br100","Rating":1,"Description":"The gym is spacious and has good infrastructure, but the trainer Manikandan is very rude and unprofessional. Instead of helping members, he mostly focuses on himself—taking videos, doing his own workouts, and spending time talking only with a few clients. Beginners who genuinely need guidance are completely ignored.\n\nA trainer’s job is to support and guide members, but he shows no interest in helping people who pay for the gym. This kind of attitude can ruin the experience even if the gym has good facilities. The management should seriously look into this issue.\n\nSpecial thanks to trainer Harish, who is very supportive and actually helps members improve.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25WdGFqRXpORVF4VlhkT1J6VnZYMUJMZVVScFNrRRAB","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/112037783521447564180/reviews?hl=en-GB","posted_at_unix_micros":1772887605854588,"updated_at_unix_micros":1772887605854588,"language":"en","translated_lang":"","text_original":"The gym is spacious and has good infrastructure, but the trainer Manikandan is very rude and unprofessional. Instead of helping members, he mostly focuses on himself—taking videos, doing his own workouts, and spending time talking only with a few clients. Beginners who genuinely need guidance are completely ignored.\n\nA trainer’s job is to support and guide members, but he shows no interest in helping people who pay for the gym. This kind of attitude can ruin the experience even if the gym has good facilities. The management should seriously look into this issue.\n\nSpecial thanks to trainer Harish, who is very supportive and actually helps members improve.","text_translated":"","published_at":"2026-03-07T12:46:45.854588Z"},{"Name":"Bhaskar Narayanan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVDjLraV4jqHC6zSGGluoPrVcll4TmURaeIdBLtJ4X33j-iDoto=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great place to being fitted.. amazing fecility and amenities.i really appreciate gyms owner and his staffs.really respected peoples.great ambience also change your mind to achive the goals.i reffer to my friends for this ultra class gym.\n\nEquipments-10/10\nStaffs and coach-10/10\nAc-10/10\nAmbience-10/10\nParking-10/10\nRestroom 🚻 10/10\nWater-10/10\n\nReally happy to be a member of SFC\n🙏","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdVRPMzgOzsc1c-tQAfgZ0MXRqZPzX6wa5Fo5pBptzecuhN8NoGIIlBrAnpCd2MgPdFiOIorQE-HwTI51E7TnOM16nrYV7JWmuIj5q-bC2Mtbo6j1NPSNDSS3BGQ6_9U-BZgDi1Ng=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd0z18lSD4V8EYz3Zxa8meGw0F6JiZz0MXgW3-5RU8JiGEi73AENNDb8IrRpzjkGIk_XOsXy7woOIbXK8hnNhDuOx2ExJDeUOPSopgZpg7xIRQ3qOLRRZpijATmAtwh5JA_BXg=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeFOHWz6WgZ7X49wXY8l5zvuS3sKu0s4mKrOCAMdU6jsC6J3M7A9NeEX8OCY9nR3iyh7JrSOikxfuBPUUjbeDfzUIbUZkzn65T7XPRUJNW8dK_BGL8A-JXDS_wKn3t8Y0gs_JLFeg=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLea_JB__y41ZXXkNVlaSsbTHmy3Ar2EJ0APbQkVtxx8Y-nimlxvqQ0XBN9jXFcObYtC1ozGt7dkjJQPoFLa9iyjlfL18StX9mFIfHhHpGUUePqPgHkM-U-MDDrEFicWvybmJFGM=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeqvKiscmH2mn1KDlJsAwJz7mdE-_Ps08MoZvc87oGr6qNxm4HljKckM9LvDrPF7UBmmb4U0RfW01TtWKRfmhPGQRmz7Lc4bKwxdejDUgbMTBdPcLGUA6mcaFeERQhTcwF_UCOK=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcp0LmHTBDTHZH9iPI9SwoGr9r9oxRWe4vY93QEj4TYq6LCUcVfGQYG1boeo8DD5Ux-xG43uP0jlaUT8JYRq0qgxd1yRExQR0_N9upjVXwOMzqa3uEW-E2zAdKxhe9lx4Z-IeFP=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfdfWH2sUUcYYXPNDOFH4uKzPYKYrnE2M60nSuTJFCaM8CyaHD7_Q557Qu07Q5v9BaRSIB-DGlxy2_wjW8xFq5leOB4K-8RnyarwSgIwyovcRxd-iQ3Rs80MKtBB9MNxbcFzG5HDQ=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdGxvsvIkbeJ4KNejWGklP-YsD-HcEbT49R1nutgTF27zvkclEsOhhb_jLMh-Cd7fvrSwM-qd9tVy3mJlYqaK-AX5fTBaqR150HuqbhR7ZcjWnbYwB5ZgMxV38DwTFfqkxVdKJB=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdwBkh4Dtam1t7uihfaDu9rTi22ZSut93TN4LBNkqGDBRtAKRFCsf2Z9kFGoSKlcuX__SsOoLeIYT3ztwd8JzNhyLMtZ_PZ9kAPsos_7fRlwKuYvChIJTrupbged1H8evLhKVip=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfAP6yhH9ucW39ZRDGRnVMxSV3VMG5eE-aPabDsUt_qoqUP9EQwK02gJAOsBQwmY3ryrCZChhkK1uNuhIJQ1jXL4-3nWRh5PpCnGGzrnCvjXgEFAvvDbdPBrVIZlfuiv5DpyQoD=k-no"],"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURobVpTVGN3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105256992578823381411/reviews?hl=en-GB","posted_at_unix_micros":1678625092669178,"updated_at_unix_micros":1678625092669178,"language":"en","translated_lang":"","text_original":"Great place to being fitted.. amazing fecility and amenities.i really appreciate gyms owner and his staffs.really respected peoples.great ambience also change your mind to achive the goals.i reffer to my friends for this ultra class gym.\n\nEquipments-10/10\nStaffs and coach-10/10\nAc-10/10\nAmbience-10/10\nParking-10/10\nRestroom 🚻 10/10\nWater-10/10\n\nReally happy to be a member of SFC\n🙏","text_translated":"","published_at":"2023-03-12T12:44:52.669178Z"},{"Name":"Swetha v","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUQR6a9bsAwQGViKcES_aBO0a_JnIW0DyWa0o2MD1cumgUTs-SEIQ=s120-c-rp-mo-br100","Rating":5,"Description":"Excellent gym with a welcoming atmosphere, spotless facilities, and high-quality equipment and the coaches supportive, and genuinely committed to helping you achieve your fitness goals.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT214bmFUZE5OVGgzUjFkRGNEZHBURW81ZHpkUE1WRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107706160871577042743/reviews?hl=en-GB","posted_at_unix_micros":1785743666788803,"updated_at_unix_micros":1785743666788803,"language":"en","translated_lang":"","text_original":"Excellent gym with a welcoming atmosphere, spotless facilities, and high-quality equipment and the coaches supportive, and genuinely committed to helping you achieve your fitness goals.","text_translated":"","published_at":"2026-08-03T07:54:26.788803Z"},{"Name":"AAKAASH V P","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVeCh0Ab2IioSZaNaxKKIfsYb2e2mOvCVT0P28NF6SqtBaw-EojnA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"One of the best gym in the surrounding neighborhood. Friendly staffs , clean and neat ambience . More number of equipments. They also have separate space for cardio and hiit . Affordable yearly fee .","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdKjY_LytIPVBu9m2jgGSq-gOAv-Eucis_xnu8njL8CDvjMoWTxPqPlBR-9Jg5aZ9Kj22WLK7CQ353jg4A_PQVVm99hVt4hPFlM_8aoAGmcjuipkj3G-AnVfYa67ZFSlEVQ2uj4=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfg2dwfBITrr5FM1PfHz7ESWkj3kIDpFlurBFVfO72-wkx6WG03TquoAwdf1WkmChRVHM8DO5a0rPirivt1DZZWyW8Feh1-ruDc0E4C-KS3542jTbJ-eXg8h1Lu9P3B0meNbrIrAA=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLepdT9kABugMq6VWZThZgoN5cM2swTOxdq1iC1kyzF4zNWfO-OJ25fKedCfdUA12OrC7dfWVPYhcaFSMsUdX34hTQuC81JezANXF6mmIMHkqyYqXxCi3zmSmX9kFJZPZubVTimm=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLf0cmIbc_od8sk_FLzklWoOvuSFzrnfP4emDT6HW7ChBml1MlpQmBE6T9b447vNgktNG6pbdnB3zWTENQ4cBFl4tbkyyhwTXql2dvHwidI0egUSfQdfnullB01Z-nw--go7vQVPuA=k-no"],"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURSb1BfMUlnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106596716155075915742/reviews?hl=en-GB","posted_at_unix_micros":1681553148327261,"updated_at_unix_micros":1681553185245473,"language":"en","translated_lang":"","text_original":"One of the best gym in the surrounding neighborhood. Friendly staffs , clean and neat ambience . More number of equipments. They also have separate space for cardio and hiit . Affordable yearly fee .","text_translated":"","published_at":"2023-04-15T10:05:48.327261Z"},{"Name":"Akash Sreekumar","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLBgRYUcWKs27LRr3aO0EObWRIODZWfnRRPzAWC-waxCwucMw=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"One of the best and aesthetic gym in and around thiruverkadu.The equipments are very unique with high quality and also has ample space around the gym.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLf4EndCgVw2cF0VNKgIM5Cvtv38EACMmvaypSegx-45Bs5tPshJjQLFzJkai3fBvi79a8JGm_0qVBzNH65GT1L9vZ6lrabfgKzu8wRa6eFJZlQP_3rL22peH9LNJ31HYzh3U7yjPQ=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdWb0ZXsB9y4uyMRSbo-w_ImHdfn0XtjL94NLT_DxcvzmmacrJVyVyxsNbiYsT5-riK-EPq9vMfGCxBm1NIWfuelPCI_l47z2lJkGE8tnqaVW18m7Q4t_ataLukWzR6bYCNqsw=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfK-Tb3A9ura0pwtvNp0GxwZKOtKgB9AqDmFWKwQ9gbYS-eUDDSaMAlthlH1Ku1UdRGqOtEb7yZasZllOw252BiVZ3ij-j7p8Mw76Kre-dRdjkUHwJwiKk-7ZXBo5uCryOE7mA0Ag=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfYrrrEx7MgRfrApAd1XZ7jD9Pl4odzhe4Grcs3rckJ0xbMMEDk0SpnBb43hBxhTJeMnAsJ_b9D1YU-lmnIod85gvH-uFF54LW0Dt6kiawFhf0CA9qZ7FBmBXtIs7KSWLB-ZvI=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdDcnIcFceQwtVb9n1oMMXQ-AkyMUH39AWDGvktuKDDEVO1O3Db8Tc6drPh1z9WroLr0XmEiXOQAh-eoKOaNYA0ADA9kEXyRAZWUJI43_ovE4J09E6nKxlFHWZ1Qk2ojt0hXmD2=k-no"],"When":"Edited 3 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNobE9uMy1BRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102859853370987233165/reviews?hl=en-GB","posted_at_unix_micros":1675658630584737,"updated_at_unix_micros":1679247233859550,"language":"en","translated_lang":"","text_original":"One of the best and aesthetic gym in and around thiruverkadu.The equipments are very unique with high quality and also has ample space around the gym.","text_translated":"","published_at":"2023-02-06T04:43:50.584737Z"}]</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>(1★) Lakshmi Prasath: The gym is spacious and has good infrastructure, but the trainer Manikandan is very rude and unprofessional. Instead of helping members, he mostly focuses on himself—taking videos, doing his own workouts, and spending time talking only with a few clients. Beginners who genuinely need guidance are completely ignored. A trainer’s job is to support and guide members, but he shows no interest in helping people who pay for the gym. This kind of attitude can ruin the experience even if the gym has good facilities. The management should seriously look into this issue. Special thanks to trainer Harish, who is very supportive and actually helps members improve.</t>
+        </is>
+      </c>
+      <c r="AO71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>43</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Titan+Fitness+Club/data=!4m7!3m6!1s0x3a5267cba4d95699:0x9e10da4956260a85!8m2!3d13.0431656!4d80.2033033!16s%2Fg%2F11xp66sgh1!19sChIJmVbZpMtnUjoRhQomVknaEJ4</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Titan Fitness Club</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1st floor, Titan Fitness Club, 18, PV Rajamannar Salai, Kamaraj Nagar, Vijayaraghavapuram, K. K. Nagar, Chennai, Tamil Nadu 600093</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–10 pm"],"Monday":["5 am–10 pm"],"Saturday":["5 am–10 pm"],"Sunday":["5 am–10 pm"],"Thursday":["5 am–10 pm"],"Tuesday":["5 am–10 pm"],"Wednesday":["5 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>097106 93303</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>26V3+78 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>121</v>
+      </c>
+      <c r="O72" t="n">
+        <v>5</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":1,"5":120}</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>13.043166</v>
+      </c>
+      <c r="R72" t="n">
+        <v>80.20330300000001</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>11389843466132785797</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfS0SeKmP8nJGVoW0ntvxHsGKFIMnGXfui7zpLr-ucM2ycIOIBSrQo4lmG8XnokN2_7wqgxmffw1L-YWZwpT0Mmcjvzsp0nx-fjd6HcxconTwC3Xc635DoPPRmn9pKlZ3nWvrH_SjNuNBk=w427-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>0x3a5267cba4d95699:0x9e10da4956260a85</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>ChIJmVbZpMtnUjoRhQomVknaEJ4</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>{"id":"110400356808799276691","name":"Titan Fitness Club (Owner)","link":"https://www.google.com/maps/contrib/110400356808799276691"}</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>{"borough":"Kamaraj Nagar, Vijayaraghavapuram, K. K. Nagar","street":"1st floor, 18, PV Rajamannar Salai","city":"Chennai","postal_code":"600093","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>[{"Name":"Akilan Akilan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVPgIRPQE5quXylyKgGlRCEHsUm8GAmM0lnAsxFICU6c2BIomLk=s120-c-rp-mo-br100","Rating":5,"Description":"The facilities are good, equipment is well maintained, and the gym environment is comfortable and motivating. One thing I really appreciate is the way the management responds to any issue or concern. That shows how much importance he gives to the members. Apart from the gym facilities, I also appreciate his friendly and good character. He is approachable and supportive, which makes the overall gym experience even better.\nIt’s been only 2 months for me, but so far, my experience has been very good and satisfying. Looking forward to continuing my fitness journey with Titan Fitness Club. ❤️💪🔥\n\nKeep up the great work, Team Titan! 🏆","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2twcFdFWklkazVaWjFkaGIzTmtZV2x0Y2xST1RXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112001241158633561689/reviews?hl=en-GB","posted_at_unix_micros":1788500583510336,"updated_at_unix_micros":1788500583510336,"language":"en","translated_lang":"","text_original":"The facilities are good, equipment is well maintained, and the gym environment is comfortable and motivating. One thing I really appreciate is the way the management responds to any issue or concern. That shows how much importance he gives to the members. Apart from the gym facilities, I also appreciate his friendly and good character. He is approachable and supportive, which makes the overall gym experience even better.\nIt’s been only 2 months for me, but so far, my experience has been very good and satisfying. Looking forward to continuing my fitness journey with Titan Fitness Club. ❤️💪🔥\n\nKeep up the great work, Team Titan! 🏆","text_translated":"","published_at":"2026-09-04T05:43:03.510336Z"},{"Name":"Kavia Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKVPKwfa9IEjIUp8C-9ttR7f4MlwjDYQlOPjpqy0apGWOyjy44I=s120-c-rp-mo-br100","Rating":5,"Description":"Hi surya\nThis Kavia here!\n\nI’ve had a really good experience at this gym so far. The trainers are friendly, supportive and always willing to guide me whenever I need help with the exercises. The atmosphere is comfortable and motivating. The equipment’s are well maintained.\n\nAs a beginner, I really appreciate the guidance and encouragement from you. Overall, it’s a great place to stay consistent, work on fitness, and enjoy the workout journey. Highly recommended!","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwWFNuVkxkVlpqZGxOUE4yeHFMV1prV0UxRVprRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102336872543591263194/reviews?hl=en-GB","posted_at_unix_micros":1788796487348379,"updated_at_unix_micros":1788796487348379,"language":"en","translated_lang":"","text_original":"Hi surya\nThis Kavia here!\n\nI’ve had a really good experience at this gym so far. The trainers are friendly, supportive and always willing to guide me whenever I need help with the exercises. The atmosphere is comfortable and motivating. The equipment’s are well maintained.\n\nAs a beginner, I really appreciate the guidance and encouragement from you. Overall, it’s a great place to stay consistent, work on fitness, and enjoy the workout journey. Highly recommended!","text_translated":"","published_at":"2026-09-07T15:54:47.348379Z"},{"Name":"Monikaa R","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUfUoCClfvZExo82liHQz8EDZfUr5KGtoLhdpFRJxOqP_WN1fVQ=s120-c-rp-mo-br100","Rating":5,"Description":"This gym is a great place for workouts. The equipment is well maintained and there are enough machines for different types of training. The atmosphere is very motivating and the gym is always clean and organized.\n\nA special mention to trainer Karthi. He is very friendly, supportive, and knowledgeable. He explains the workouts clearly and always motivates everyone to push their limits safely. He also pays attention to each member and corrects our form, which helps avoid injuries and improves results.\n\nOverall, it’s a very good gym for anyone who wants to improve their fitness and stay healthy. Highly recommended!","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25sMVEybHNkeTE2VkU1R1VsVk9iM1YyZUVrNGVtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100232229036349993128/reviews?hl=en-GB","posted_at_unix_micros":1773640597841911,"updated_at_unix_micros":1773710765692307,"language":"en","translated_lang":"","text_original":"This gym is a great place for workouts. The equipment is well maintained and there are enough machines for different types of training. The atmosphere is very motivating and the gym is always clean and organized.\n\nA special mention to trainer Karthi. He is very friendly, supportive, and knowledgeable. He explains the workouts clearly and always motivates everyone to push their limits safely. He also pays attention to each member and corrects our form, which helps avoid injuries and improves results.\n\nOverall, it’s a very good gym for anyone who wants to improve their fitness and stay healthy. Highly recommended!","text_translated":"","published_at":"2026-03-16T05:56:37.841911Z"},{"Name":"Sugumar","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJwERm9FH-f8ohAI0cUEJ1MtgSl0SaedDeaIT16Bvz0FoYhTv8=s120-c-rp-mo-br100","Rating":5,"Description":"Titan Fitness Club is an amazing gym! The equipment is always clean and well-maintained, and there’s everything you could possibly need for a great workout.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLczUT05rzluLUOADsQ2KY6trsRd-cLIcmFLkWtflzP6wOTsW3keQqnqnYRiklNtajr0sW2OZKTZHsVUwWKyo5WEQBUoN6ozhxtZLwxPxlXLPQh1kT5xH1W2ZOF4cGv11BK1dNce1wDE2jsh=k-no"],"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2paME9XUXlWV1JIWlRSNlVpMXNibkZHV25kQ1RuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117325199426835423174/reviews?hl=en-GB","posted_at_unix_micros":1767407373216441,"updated_at_unix_micros":1767407373216441,"language":"en","translated_lang":"","text_original":"Titan Fitness Club is an amazing gym! The equipment is always clean and well-maintained, and there’s everything you could possibly need for a great workout.","text_translated":"","published_at":"2026-01-03T02:29:33.216441Z"},{"Name":"Ajesh kumar K","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXuhOrLgp2u0Rja120gt6sXDDrZlYtS88NjkwXGdS6gm3nQuQkf=s120-c-rp-mo-br100","Rating":5,"Description":"Titan Fitness Club is one of the best gyms with a great workout atmosphere and well-maintained equipment. The trainers are friendly, motivating, and always ready to help. The gym is clean, spacious, and suitable for both beginners and experienced fitness lovers","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21WTE1FNVNabXBPUWtGaU4zUndhSFIyWkhWSVpFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105113643505339975549/reviews?hl=en-GB","posted_at_unix_micros":1780494003642229,"updated_at_unix_micros":1780494003642229,"language":"en","translated_lang":"","text_original":"Titan Fitness Club is one of the best gyms with a great workout atmosphere and well-maintained equipment. The trainers are friendly, motivating, and always ready to help. The gym is clean, spacious, and suitable for both beginners and experienced fitness lovers","text_translated":"","published_at":"2026-06-03T13:40:03.642229Z"}]</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>43</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Smash+Hiit+fitness+studio+%28Unisex%29/data=!4m7!3m6!1s0x3a526171c7d08e01:0x343e4e9c3e1ee69!8m2!3d13.0326571!4d80.1113885!16s%2Fg%2F11t6f_gswk!19sChIJAY7Qx3FhUjoRae7hw-nkQwM</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Smash Hiit fitness studio (Unisex)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>494, Smash Hiit fitness studio (Unisex), thandava naiker, complex, Kundrathur Main Rd, Kamatchiamman Nagar, Mangadu, Tamil Nadu 600122</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–9:45 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–9:45 pm"],"Sunday":["6:30 am–12:30 pm"],"Thursday":["5:30 am–9:45 pm"],"Tuesday":["5:30 am–9:45 pm"],"Wednesday":["5:30 am–9:45 pm"]}</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>096884 28371</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>24M6+3H Mangadu, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>111</v>
+      </c>
+      <c r="O73" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":1,"3":0,"4":6,"5":103}</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>13.032657</v>
+      </c>
+      <c r="R73" t="n">
+        <v>80.11138800000001</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>235283298218274409</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdqEMu4Rh2PZpFz_7aNQ3WHtUs543vl988FAvwIZz6pqzox-WHxsdUEUML3dbwzY_Aei642cfVPI8Mp_EESILvk7phgMLK_347f_hafMZYmYdNeUO8tBQwaImdmkCxnvRtZUlom=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>0x3a526171c7d08e01:0x343e4e9c3e1ee69</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>ChIJAY7Qx3FhUjoRae7hw-nkQwM</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>{"id":"114662625420183730821","name":"Smash Hiit fitness studio (Unisex) (Owner)","link":"https://www.google.com/maps/contrib/114662625420183730821"}</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>{"borough":"Kamatchiamman Nagar, Mangadu","street":"494, thandava naiker, complex, Kundrathur Main Rd","city":"Mangadu","postal_code":"600122","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>[{"Name":"JANA S","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUk9YF4HTuqYuGgxqC2DBWOuTNsM6J-0qLiAMX0HvpLHqCpGtI1=s120-c-rp-mo-br100","Rating":5,"Description":"Amazing place to stay fit and healthy! The atmosphere keeps me motivated. Trainers are supportive and professional. Best gym experience so far! 💥📈","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21JMVVVZFlRbVJIVEZwclIzaFRSMk5GYmtodFZrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114116559376732750440/reviews?hl=en-GB","posted_at_unix_micros":1771943834133010,"updated_at_unix_micros":1771943834133010,"language":"en","translated_lang":"","text_original":"Amazing place to stay fit and healthy! The atmosphere keeps me motivated. Trainers are supportive and professional. Best gym experience so far! 💥📈","text_translated":"","published_at":"2026-02-24T14:37:14.13301Z"},{"Name":"Ashwin Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXzJ6oAjIDJxBUKOq5U0ZY8uFb50RBRnhouowvWr6nozXrPcjaG=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"The gym has new equipments installed recently. They maintain it neat and clean. The trainers are knowledgeable and friendly.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT205SFNFVllVbmQzTlVoUFYxTlJURk50VVVoemJIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106624768196691161484/reviews?hl=en-GB","posted_at_unix_micros":1779277237991899,"updated_at_unix_micros":1779277237991899,"language":"en","translated_lang":"","text_original":"The gym has new equipments installed recently. They maintain it neat and clean. The trainers are knowledgeable and friendly.","text_translated":"","published_at":"2026-05-20T11:40:37.991899Z"},{"Name":"Sneha Parameswaran","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKcJd2_bG0_gpwLfKuPfAnrc_x0gqco_AD6uov3u_Os3l_HXA=s120-c-rp-mo-br100","Rating":5,"Description":"Actually it’s great more than I expected. The trainers keep track, help and guide at every step forward in workouts and plans. Also it’s close to my home which makes it more easier for me to go regularly. Looking forward to lose weight and tone up as per my goal with their help.","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pKV1h6VTBjMmx0VTBSRFdWVmliWFZQT0RSdGJXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107544922084444934917/reviews?hl=en-GB","posted_at_unix_micros":1769088830516053,"updated_at_unix_micros":1769088830516053,"language":"en","translated_lang":"","text_original":"Actually it’s great more than I expected. The trainers keep track, help and guide at every step forward in workouts and plans. Also it’s close to my home which makes it more easier for me to go regularly. Looking forward to lose weight and tone up as per my goal with their help.","text_translated":"","published_at":"2026-01-22T13:33:50.516053Z"},{"Name":"Balaji","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWn_YeBVSv_MC4pjuUAlkvTtmj2SjeU3LIlMIu4hSSpMxiIg2Co=s120-c-rp-mo-br100","Rating":5,"Description":"Great gym with good machines and friendly trainers. Clean atmosphere and positive vibes. Worth joining!Trainers guide properly and motivate every day.📈","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25ZMmNYQkVObGhOYzJKeFlYQkdRM040YnpOUE1rRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102359054167079366275/reviews?hl=en-GB","posted_at_unix_micros":1771943765732358,"updated_at_unix_micros":1771943765732358,"language":"en","translated_lang":"","text_original":"Great gym with good machines and friendly trainers. Clean atmosphere and positive vibes. Worth joining!Trainers guide properly and motivate every day.📈","text_translated":"","published_at":"2026-02-24T14:36:05.732358Z"},{"Name":"pooja u","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV0-EMRjgt3qetsSnE9kuXLyQn7U6RovTssQxsmM2AfGKuV47OM=s120-c-rp-mo-br100","Rating":5,"Description":"Good environment and friendly trainers. They are very supportive and help us with proper workouts.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21KRWIwZzVTVmhVWTJwUE5sOXhPV2RRTlhSeGJWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116896162963025528862/reviews?hl=en-GB","posted_at_unix_micros":1773234899382613,"updated_at_unix_micros":1773234899382613,"language":"en","translated_lang":"","text_original":"Good environment and friendly trainers. They are very supportive and help us with proper workouts.","text_translated":"","published_at":"2026-03-11T13:14:59.382613Z"}]</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>43</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fitness+Religion+Crossfit+%26+Wellness/data=!4m7!3m6!1s0x3a52637e012feb25:0x3d6f0d47bb1a492e!8m2!3d13.1287978!4d80.1504211!16s%2Fg%2F11tcqyrzc6!19sChIJJesvAX5jUjoRLkkau0cNbz0</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Fitness Religion Crossfit &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>8 Erikarai Salai Venkateshwara Nagar, Gandhi Nagar Oragadam, Ambattur, Chennai, Tamil Nadu 600053</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–12 pm","5–9 pm"],"Monday":["5:30 am–12 pm","5–9 pm"],"Saturday":["5:30 am–12 pm","5–9 pm"],"Sunday":["Closed"],"Thursday":["5:30 am–12 pm","5–9 pm"],"Tuesday":["5:30 am–12 pm","5–9 pm"],"Wednesday":["5:30 am–12 pm","5–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>090031 32905</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>45H2+G5 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>109</v>
+      </c>
+      <c r="O74" t="n">
+        <v>5</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":1,"5":108}</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>13.128798</v>
+      </c>
+      <c r="R74" t="n">
+        <v>80.15042099999999</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>4426771560461388078</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeBl_InRQ7mpqyNycLTv69fqzzkz8GJqzcRqLMiY4PqeN4FS-zBSNE-B7u4V5NYwAKqe9IDfCcrm6ie3SepfNSOXrpcx--dcUquy3uMOQy5JwKuopbwb0W81rv-yxTJPAxdMJo=w408-h271-k-no</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>0x3a52637e012feb25:0x3d6f0d47bb1a492e</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>ChIJJesvAX5jUjoRLkkau0cNbz0</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>{"id":"115900637086678209755","name":"Fitness Religion Crossfit \u0026 Wellness (Owner)","link":"https://www.google.com/maps/contrib/115900637086678209755"}</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>{"borough":"Gandhi Nagar, Ambattur","street":"8 Erikarai Salai Venkateshwara Nagar, Gandhi Nagar Oragadam","city":"Chennai","postal_code":"600053","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>[{"Name":"Harshitha Rao","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX4S92Hfn0t7KAKjwnjDTpw4CXe5JOfPtUGeEoiF0OCifcESY37=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"If you're new to working out or feeling hesitant about gym life, visit Fitness Religion and you'll see why it's worth it. The trainers are friendly, patient, motivating, and professional, giving personal attention to each individual. Pavithran Sir and Thamim Master are always around to help, and they customize workouts if you have an injury or struggle with an exercise. The fee is budget friendly, too. The positive atmosphere really motivates you to go to the gym every day.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21kcU1EazVWRXRLYVRNMWIwUjBjMU0wUTBOd1RWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111225716681559332560/reviews?hl=en-GB","posted_at_unix_micros":1785830699352847,"updated_at_unix_micros":1785830752670270,"language":"en","translated_lang":"","text_original":"If you're new to working out or feeling hesitant about gym life, visit Fitness Religion and you'll see why it's worth it. The trainers are friendly, patient, motivating, and professional, giving personal attention to each individual. Pavithran Sir and Thamim Master are always around to help, and they customize workouts if you have an injury or struggle with an exercise. The fee is budget friendly, too. The positive atmosphere really motivates you to go to the gym every day.","text_translated":"","published_at":"2026-08-04T08:04:59.352847Z"},{"Name":"Roshan Maharajan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXGEXpYJm8DL9pEjuJm7GJ-UoBwSVtCiXcUYYUcjUP9kieVdkBOZw=s120-c-rp-mo-br100","Rating":5,"Description":"I’m really satisfied with the outcome after joining this gym because I can clearly see visible changes in my body. The ambience of the gym is clean, and energetic.\nThe trainers are very friendly and professional. Their teaching methods are excellent — they guide properly, correct our form.\nWhat makes this gym different from other gyms is the personal attention, supportive environment, and the way they genuinely care about members progress instead of just workouts.\nWithin a short time, I’ve noticed good improvement in my strength, fitness, and overall physique. I feel more confident and healthy now.\nOverall, it’s one of the best gyms for anyone who wants real results with proper guidance. Highly recommended! 💪🔥⭐","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pNelltaENVRkJ5WkRCSVIzaDJSbEppWlZoSk9IYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111700521868483744045/reviews?hl=en-GB","posted_at_unix_micros":1779546728131831,"updated_at_unix_micros":1779546769434134,"language":"en","translated_lang":"","text_original":"I’m really satisfied with the outcome after joining this gym because I can clearly see visible changes in my body. The ambience of the gym is clean, and energetic.\nThe trainers are very friendly and professional. Their teaching methods are excellent — they guide properly, correct our form.\nWhat makes this gym different from other gyms is the personal attention, supportive environment, and the way they genuinely care about members progress instead of just workouts.\nWithin a short time, I’ve noticed good improvement in my strength, fitness, and overall physique. I feel more confident and healthy now.\nOverall, it’s one of the best gyms for anyone who wants real results with proper guidance. Highly recommended! 💪🔥⭐","text_translated":"","reply_text_original":"Thank you for your valuable feedback brother ","reply_language":"en","reply_posted_at_unix_micros":1779556879000000,"reply_updated_at_unix_micros":1779556879000000,"published_at":"2026-05-23T14:32:08.131831Z"},{"Name":"Srinivasan Sambasivam","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ9E4m4TugGyMEnBeJWgIpf_QQCxBhOWehLVDuSbHHEdKXOlw=s120-c-rp-mo-br100","Rating":5,"Description":"Fitness Religion is a welcoming place. The trainers are knowledgeable and dedicated to helping you reach your goals safely, regardless of your fitness level. I highly recommend it to anyone looking to elevate their health and workout routine.","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT205aVVuWjZTVmxJTmxsZmRXVlVNblpLWW5OZlVrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108050090234454997228/reviews?hl=en-GB","posted_at_unix_micros":1786595936062756,"updated_at_unix_micros":1786595936062756,"language":"en","translated_lang":"","text_original":"Fitness Religion is a welcoming place. The trainers are knowledgeable and dedicated to helping you reach your goals safely, regardless of your fitness level. I highly recommend it to anyone looking to elevate their health and workout routine.","text_translated":"","published_at":"2026-08-13T04:38:56.062756Z"},{"Name":"Brinda P","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXGyFg86cpicvhfOQzTnQ-63lefwOk3xbe2Se999J3x-IUuf_fJ=s120-c-rp-mo-br100","Rating":5,"Description":"I have a great experience at this gym.The ambience is clean, spacious, and motivating with a positive vibe.\nThe trainers are highly professional and very supportive, using teaching methods that are easy to follow yet effective.\nSince joining, I’ve noticed great results in my fitness, strength, and overall energy levels.\nIn my opinion, this is one of the best gyms around for anyone serious about their health and fitness. Highly recommended!","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tSdlYweHpRemxtZUcxVWJHZElWakZPUzA5c2FtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107223766541450438624/reviews?hl=en-GB","posted_at_unix_micros":1757045723227754,"updated_at_unix_micros":1757045723227754,"language":"en","translated_lang":"","text_original":"I have a great experience at this gym.The ambience is clean, spacious, and motivating with a positive vibe.\nThe trainers are highly professional and very supportive, using teaching methods that are easy to follow yet effective.\nSince joining, I’ve noticed great results in my fitness, strength, and overall energy levels.\nIn my opinion, this is one of the best gyms around for anyone serious about their health and fitness. Highly recommended!","text_translated":"","reply_text_original":"Thanks a lot for your valuable feedback mam..! ","reply_language":"en","reply_posted_at_unix_micros":1757046425000000,"reply_updated_at_unix_micros":1757046425000000,"published_at":"2025-09-05T04:15:23.227754Z"},{"Name":"Murugaiyan S","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJBgCdlS_QGZpe1QSBiA6cErBesOcfIfHIwi9mQFgn16FG3YQ=s120-c-rp-mo-br100","Rating":5,"Description":"This gym strikes a great balance between traditional strength training and CrossFit-style workouts. The instructor stands out for being both warm and patient—he takes the time to explain techniques clearly and tailors workouts to different skill levels, which makes the environment welcoming for beginners.  Highly recommended for anyone looking for a supportive and versatile training space. I’m really enjoying my time here, and the affordable pricing makes it even better compared to other gyms.","Images":null,"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tSUVIyeE5jRGxQY2xZM2FYSmllbXMyUlZKcVFuYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100119141826563951173/reviews?hl=en-GB","posted_at_unix_micros":1757153359978022,"updated_at_unix_micros":1757153359978022,"language":"en","translated_lang":"","text_original":"This gym strikes a great balance between traditional strength training and CrossFit-style workouts. The instructor stands out for being both warm and patient—he takes the time to explain techniques clearly and tailors workouts to different skill levels, which makes the environment welcoming for beginners.  Highly recommended for anyone looking for a supportive and versatile training space. I’m really enjoying my time here, and the affordable pricing makes it even better compared to other gyms.","text_translated":"","reply_text_original":"Thanks a lot for your valuable feedback sir..!! ","reply_language":"en","reply_posted_at_unix_micros":1757239688000000,"reply_updated_at_unix_micros":1757239688000000,"published_at":"2025-09-06T10:09:19.978022Z"}]</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP74" t="inlineStr"/>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AU74" t="inlineStr"/>
+      <c r="AV74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>43</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Forever+Fitness/data=!4m7!3m6!1s0x3a5265eb019bae0b:0x2d5c90fc993e8d38!8m2!3d13.1169532!4d80.1983288!16s%2Fg%2F11sgy_qxn1!19sChIJC66bAetlUjoROI0-mfyQXC0</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Forever Fitness</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>No.21, Jawaharlal Nehru Salai, Sri Venkatesa Thiyagaraya Nagar, Villivakkam, Chennai, Tamil Nadu 600049</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["6–11 am"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>073581 67929</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>458X+Q8 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>88</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":7,"5":81}</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>13.116953</v>
+      </c>
+      <c r="R75" t="n">
+        <v>80.198329</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3268646844141309240</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdybEX-EepwHMT_3235rnU53cJxKO7Hw_cPy-SXeNs3fF26ij3Omhd3ZRBrZHEL9W2Uyv1vIvlyvV0ab1g6fcGpt3jqu4SO-H5J1-cFIy4K9lEev9jp-lZJevcSLj6OM6UTMC4a=w531-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>0x3a5265eb019bae0b:0x2d5c90fc993e8d38</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>ChIJC66bAetlUjoROI0-mfyQXC0</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>{"id":"112866400161356354236","name":"Forever Fitness (Owner)","link":"https://www.google.com/maps/contrib/112866400161356354236"}</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>{"borough":"Sri Venkatesa Thiyagaraya Nagar, Villivakkam","street":"No.21, Jawaharlal Nehru Salai","city":"Chennai","postal_code":"600049","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Assistive hearing loop","enabled":true},{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>[{"Name":"Lokeash A","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIyU0LQ5UOIhJJnp09fMpydO3Czmw8hKmtD-EvG_8-rPFZ_tw=s120-c-rp-mo-br100","Rating":5,"Description":"\"I've been a member at Gym  Reshape Fitness Studio for a while now, and I can confidently say it's the best gym experience I've ever had!\n\nThe trainers are knowledgeable, motivating, and always willing to help with customized workout\n\nOverall, I highly recommend Gym  Reshape Fitness Studio to anyone looking for a top-notch gym experience. You won't regret it!\"\n\nFeel free to modify it to fit your personal experience!","Images":null,"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUQ3ODl2WFZnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112077213991933874251/reviews?hl=en-GB","posted_at_unix_micros":1724845754324560,"updated_at_unix_micros":1724845754324560,"language":"en","translated_lang":"","text_original":"\"I've been a member at Gym  Reshape Fitness Studio for a while now, and I can confidently say it's the best gym experience I've ever had!\n\nThe trainers are knowledgeable, motivating, and always willing to help with customized workout\n\nOverall, I highly recommend Gym  Reshape Fitness Studio to anyone looking for a top-notch gym experience. You won't regret it!\"\n\nFeel free to modify it to fit your personal experience!","text_translated":"","published_at":"2024-08-28T11:49:14.32456Z"},{"Name":"nandhini madhu","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJtlOl2ZgdRyuTVIwvL_p6RfRe89-6SoETxveq9K8KUoeBeIA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Well maintained, air conditioned and neat environment makes the place perfect to start your day.The quality of equipments are great and all working in good order. Professional trainers are giving better efforts to see the results of their clients.","Images":null,"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUN2d2VIRS1BRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109204243000535451453/reviews?hl=en-GB","posted_at_unix_micros":1733937702716306,"updated_at_unix_micros":1733937702716306,"language":"en","translated_lang":"","text_original":"Well maintained, air conditioned and neat environment makes the place perfect to start your day.The quality of equipments are great and all working in good order. Professional trainers are giving better efforts to see the results of their clients.","text_translated":"","published_at":"2024-12-11T17:21:42.716306Z"},{"Name":"samrita murugesan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJaGd2GeAKnT88S5qaR0douzSlD1G4R3dB7tKiOdYptU1bNptsw=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been going to reshape for almost 3 months now and I’m thoroughly impressed! The facility is clean, well-maintained, and equipped with all kinds of machines for both cardio and strength training. The trainers are knowledgeable, approachable, and always willing to help with form and workout tips.","Images":null,"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUN2NmFQMWVnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108267678490901062487/reviews?hl=en-GB","posted_at_unix_micros":1734012398959949,"updated_at_unix_micros":1734012398959949,"language":"en","translated_lang":"","text_original":"I’ve been going to reshape for almost 3 months now and I’m thoroughly impressed! The facility is clean, well-maintained, and equipped with all kinds of machines for both cardio and strength training. The trainers are knowledgeable, approachable, and always willing to help with form and workout tips.","text_translated":"","published_at":"2024-12-12T14:06:38.959949Z"},{"Name":"jaya lakshmi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXAzJAONZ-LQFmYNd6e4mRTN0Avv_5BSrb-NmS4bSLTxxVnE1me=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Amazing facility,  and great environment. Good service with friendly staff and super clean and comfortable gym for everyone. I found the  coaching very helpful, encouraging and non-judgemental. I would definitely recommend Trainer Vishal  as a personal trainer because he  is very professional but  friendly. I am learning a lot,He is extremely reliable \u0026 punctual , always set up \u0026 ready to start training ahead of time, with an exercise routine planned.","Images":null,"When":"2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUQ3M2JPbW13RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100810356314822997405/reviews?hl=en-GB","posted_at_unix_micros":1724767172404570,"updated_at_unix_micros":1724767198712242,"language":"en","translated_lang":"","text_original":"Amazing facility,  and great environment. Good service with friendly staff and super clean and comfortable gym for everyone. I found the  coaching very helpful, encouraging and non-judgemental. I would definitely recommend Trainer Vishal  as a personal trainer because he  is very professional but  friendly. I am learning a lot,He is extremely reliable \u0026 punctual , always set up \u0026 ready to start training ahead of time, with an exercise routine planned.","text_translated":"","published_at":"2024-08-27T13:59:32.40457Z"},{"Name":"Sandhya Saravanan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL4MRy4VkglBr_I5re5O34gwHW069PSw9m8OVLnhmkF5XLLzw=s120-c-rp-mo-br100","Rating":5,"Description":"Gym ambience is good.. The trainers are very well trained... They provide us free amino for muscle recovery,bag and shaker. General trainers too teach us good even though they aren't our personal trainer..","Images":null,"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUQ3bW9xemN3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116009790572870330826/reviews?hl=en-GB","posted_at_unix_micros":1724417646333033,"updated_at_unix_micros":1724417646333033,"language":"en","translated_lang":"","text_original":"Gym ambience is good.. The trainers are very well trained... They provide us free amino for muscle recovery,bag and shaker. General trainers too teach us good even though they aren't our personal trainer..","text_translated":"","published_at":"2024-08-23T12:54:06.333033Z"}]</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AU75" t="inlineStr"/>
+      <c r="AV75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>43</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Fit+2+Fight+unisex+gym/data=!4m7!3m6!1s0x3a52618e075cbb39:0xacb33bcb4e195a0c!8m2!3d13.0430823!4d80.1368517!16s%2Fg%2F11rd9877hl!19sChIJObtcB45hUjoRDFoZTss7s6w</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Fit 2 Fight unisex gym</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Oil Mill Road, 2/821, Krishnaveni Ammal Nagar, Iyyappanthangal, Tamil Nadu 600056</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–9:30 pm"],"Monday":["5 am–9:30 pm"],"Saturday":["5 am–9:30 pm"],"Sunday":["7–11 am"],"Thursday":["5 am–9:30 pm"],"Tuesday":["5 am–9:30 pm"],"Wednesday":["5 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>090031 36807</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>24VP+6P Iyyappanthangal, Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>85</v>
+      </c>
+      <c r="O76" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>{"1":2,"2":0,"3":2,"4":3,"5":78}</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>13.043082</v>
+      </c>
+      <c r="R76" t="n">
+        <v>80.136852</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>12444355939729496588</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLegvjt_3HTEYOiIhZWHHuN7tSzsX7-ffzvjbXS-afQFOXUf7SDWlOeya1ZeoHb4pvu3sY7E-zB1yHynBFDMw24VBHCHegZqXbZ49X1D0WNgNo62QnrafjQg8DTx7TMpgLZOCvWBfrUk86w=w408-h905-k-no</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>0x3a52618e075cbb39:0xacb33bcb4e195a0c</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>ChIJObtcB45hUjoRDFoZTss7s6w</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>{"id":"116920604278905821832","name":"Fit 2 Fight unisex gym (Owner)","link":"https://www.google.com/maps/contrib/116920604278905821832"}</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>{"borough":"Krishnaveni Ammal Nagar, Balaji Avenue, Iyyappanthangal","street":"Oil Mill Road, 2/821","city":"Ayyappanthangal","postal_code":"600056","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>[{"Name":"Swapna","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVPS8d3l95iqTiXDRqaLsl6Tw5A1SmgN-CVqEJyjL0SGX8LnJ3B=s120-c-rp-mo-br100","Rating":5,"Description":"Awesome, comfortable \u0026 decent place to work out specially for all women’s\nSupportive and Helpful and Easy going Gym Mates..AND\nThe Best Personal Trainer Ever!!!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcks5YXZvTb9ehUlhUWx-3MTuGt3tu7QDzh2rU82xEApEf6vRR0g8ndUyJ50AJoM8PZ5FvIRslet-pbOu4Buv3yV3L6Dewe0ErkihT87nEXIWE7_2L4wZAgH8NEdwDmwJaXuLRRnQ=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfzv2dF0mP0LhhpnW1BU1d85Zaw9Bhuw65upkx3UfpkmCC0oHjdEHf7tk_HXFTfD8fm3DiaCsaR9amV1Gr3L4g7TSK6Ldwaw3OYnI-3gxqzXxFm-0zTM1ihQWZ5KxrUArH0CXSj=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLc3S3FtW1jDTH0slpYwH087GVMPb6D7D8XXEHd_dHPcQNnvjZefd3hYayEFtIkPgky8crcIQJOKzr5FAEQU8S5ktTKsiFmmzLxz7IL4w_O9mxIWSGWTOHdGmnrZJbCVxuVtp-A=k-no"],"When":"Edited 3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNCbVlMRFVnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112336610693031252910/reviews?hl=en-GB","posted_at_unix_micros":1672330994496430,"updated_at_unix_micros":1682094508400562,"language":"en","translated_lang":"","text_original":"Awesome, comfortable \u0026 decent place to work out specially for all women’s\nSupportive and Helpful and Easy going Gym Mates..AND\nThe Best Personal Trainer Ever!!!","text_translated":"","published_at":"2022-12-29T16:23:14.49643Z"},{"Name":"Selva Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWmUXW8CDE_4F4Rys1g1QIjAgeizNIxvxSTJLvMT7T851iStWWz=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This gym is amazing. Amazing facility, good equipment and great environment. Good service with friendly staff and super clean and comfortable gym for everyone. I especially recommend here their personal training program conducted by Mr. Naveendran. which is very affordable and  you will get a personal trainer for you, who will push you to your limits and and help you to get your dream body early.","Images":null,"When":"2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNubjRYYTNnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118180610684505669628/reviews?hl=en-GB","posted_at_unix_micros":1727792170701410,"updated_at_unix_micros":1727792170701410,"language":"en","translated_lang":"","text_original":"This gym is amazing. Amazing facility, good equipment and great environment. Good service with friendly staff and super clean and comfortable gym for everyone. I especially recommend here their personal training program conducted by Mr. Naveendran. which is very affordable and  you will get a personal trainer for you, who will push you to your limits and and help you to get your dream body early.","text_translated":"","published_at":"2024-10-01T14:16:10.70141Z"},{"Name":"Shankar Ganesh","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVO2S5Ru54aSEQYJ3WRrfQJoc37sNWhQAWQUgA3-sqwiyjVbWVL1g=s120-c-rp-mo-br100","Rating":5,"Description":"For beginners it's a wonderful place to transform yourself, he(master) will motivate you to grow to the next level of an amazing person.\n\nWell maintained gym in oil mill road,i always\nloved the response from Navin(master).he will respond to your questions calmly ,clearly and teaches you as many times...he keeps on eye on your diet...\n\nGood humble and a nice person ....Navin..kudos to you\n\nDedication....I love the most...\nCheers\nWork hard\nStay strong Go strong..🔥✨","Images":null,"When":"3 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURwanRfLWpnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102265982945912325593/reviews?hl=en-GB","posted_at_unix_micros":1692675904019966,"updated_at_unix_micros":1692676580545012,"language":"en","translated_lang":"","text_original":"For beginners it's a wonderful place to transform yourself, he(master) will motivate you to grow to the next level of an amazing person.\n\nWell maintained gym in oil mill road,i always\nloved the response from Navin(master).he will respond to your questions calmly ,clearly and teaches you as many times...he keeps on eye on your diet...\n\nGood humble and a nice person ....Navin..kudos to you\n\nDedication....I love the most...\nCheers\nWork hard\nStay strong Go strong..🔥✨","text_translated":"","published_at":"2023-08-22T03:45:04.019966Z"},{"Name":"Hameed Riswan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXcTyklk7AE-1JV8iOGEqb20IHoZkQoZRneJZWvW3EoYaheDDa6=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Here I joined for a weight loss. Master Naveen guiding well with good schedule. Every day I can feel the changes happening in myself.\n\nIt's a unisex gym ladies also coming in more no to do their fitness workouts.\n\nGood ambience with supporting people.\n\nSpecial green mat area for cardio exercise.\n\nHydraulic and manual equipments are available at here.\n\nMany young people's choice is this gym and they enjoying with their friends at here.","Images":null,"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURXbE9La19nRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111305686634929595555/reviews?hl=en-GB","posted_at_unix_micros":1647402631742102,"updated_at_unix_micros":1647402631742102,"language":"en","translated_lang":"","text_original":"Here I joined for a weight loss. Master Naveen guiding well with good schedule. Every day I can feel the changes happening in myself.\n\nIt's a unisex gym ladies also coming in more no to do their fitness workouts.\n\nGood ambience with supporting people.\n\nSpecial green mat area for cardio exercise.\n\nHydraulic and manual equipments are available at here.\n\nMany young people's choice is this gym and they enjoying with their friends at here.","text_translated":"","published_at":"2022-03-16T03:50:31.742102Z"},{"Name":"S Ravikumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVLmESzXIsUIrqsD08VInpeceyPQdFIVNz-E1NQ7lKOKe7RYuuR=s120-c-rp-mo-br100","Rating":5,"Description":"Good coaching and friendly handling training I have very good improvement...master Naveen very well trained....fees also average","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLeSdp70BP2EczS_FfWrj5NkDEXxuWbMY9kXyK0eJtGvz5nOoZqTTNhmLHb7LC28RQOSOMvnmqMU8JI7sKPURpAmBedmomQWhQ9MCQSEi-XeuXHPdCT82xDErseFlUzKPbfj8bE=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd1dR37F1989doCHVCANqU2TnCYOihx25mcYDdzBx3awpcxfq6HCLIeYzb1-zVihDyuN8XZ5EeK3S2Q_hWVAM5mzlKmvUjT-rw94YWUSv7k-sWc3vFJHYsgwzFDSqgJ33dFTRzZzg=k-no"],"When":"Edited 2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNHd3NlanhRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109545776477489606225/reviews?hl=en-GB","posted_at_unix_micros":1635060756473876,"updated_at_unix_micros":1715876634957938,"language":"en","translated_lang":"","text_original":"Good coaching and friendly handling training I have very good improvement...master Naveen very well trained....fees also average","text_translated":"","published_at":"2021-10-24T07:32:36.473876Z"}]</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AU76" t="inlineStr"/>
+      <c r="AV76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>43</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Life+Health+Fitness/data=!4m7!3m6!1s0x3a52610b60ddd679:0xf141291eb909ad9e!8m2!3d13.0655625!4d80.1921875!16s%2Fg%2F11m80wjh_6!19sChIJedbdYAthUjoRnq0JuR4pQfE</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Life Health Fitness</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>358R+6VC, 5th St, Avvai Tiru Nagar Sri Iyappa Nagar, Koyambedu, Chennai, Tamil Nadu 600092</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–10 pm"],"Monday":["5 am–10 pm"],"Saturday":["5 am–10 pm"],"Sunday":["6–10 am"],"Thursday":["5 am–10 pm"],"Tuesday":["5 am–10 pm"],"Wednesday":["5 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>099413 75840</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>358R+6V Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>78</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>{"1":2,"2":0,"3":1,"4":2,"5":73}</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>13.065562</v>
+      </c>
+      <c r="R77" t="n">
+        <v>80.192188</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>17384221248557002142</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeL-lc83qRuzS45y-8QOw_QqPhwjEs7MSuR6GzttI2Si7I-1ifREbwjTK0IMZrfS4ONJz_JIqg40e8BYgVL_Ueq2tkV_sjFCIBQYo7XtFQbrCGq2LF2Z3CxiMYsd-gK0sXYt5k0Qg=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>0x3a52610b60ddd679:0xf141291eb909ad9e</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>ChIJedbdYAthUjoRnq0JuR4pQfE</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>[{"link":"https://shop.zuyyu.com/e18877bd-dd80-421a-b284-780ef112a8c9/menu?rwg_token=AE37R_gJUkfDPJWmu7tepF2jicvsidIz8qc8M-LsiZ1Tb65o1AtMVnoBfq2w5AtSJYgABS_uZBhB1-G8QjLNSwrFMeN8wtR9hWIBfe8GSvN-fj0pV8-50mk%3D","source":"zuyyu.com"}]</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>{"id":"108059452412251160250","name":"Life Health Fitness (Owner)","link":"https://www.google.com/maps/contrib/108059452412251160250"}</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>{"borough":"Avvai Tiru Nagar, Koyambedu","street":"358R+6VC, 5th St, Avvai Tiru Nagar Sri Iyappa Nagar","city":"Chennai","postal_code":"600092","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>[{"Name":"Poojasahitya Poojasahitya","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIaPHSUSatZTn4xO8WIHxvqkRWVo9QgJJY4jYfBWXRt28Ruhg=s120-c-rp-mo-br100","Rating":5,"Description":"Clean and neat place.. every equipment imported machine..\nFully motivated painting arts   with good atmosphere.\nExcellent super physical trainner.\nDisadvantages.\nSome loose  crack people not obey the trainner instructions and doing excercise himself\n..\nOtherwise super neat clean beautiful gym","Images":null,"When":"Edited 6 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURDOWJ5b3B3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105371424860015568315/reviews?hl=en-GB","posted_at_unix_micros":1601967792517389,"updated_at_unix_micros":1602577570093114,"language":"en","translated_lang":"","text_original":"Clean and neat place.. every equipment imported machine..\nFully motivated painting arts   with good atmosphere.\nExcellent super physical trainner.\nDisadvantages.\nSome loose  crack people not obey the trainner instructions and doing excercise himself\n..\nOtherwise super neat clean beautiful gym","text_translated":"","published_at":"2020-10-06T07:03:12.517389Z"},{"Name":"Ramesh rrr","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV9wIPoAoR-chkn5liVIAhSrEKoPjuz7M7LZGETJC6zFMaWRtnr=s120-c-rp-mo-br100","Rating":5,"Description":"Very very good gym .good master very friendly actually my weight is too high 3month I will join now  i am 6kg loss .so kindly master😍🥰🤩😍🥰","Images":null,"When":"Edited 2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNEc2ZuczVRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107730161566842646111/reviews?hl=en-GB","posted_at_unix_micros":1711724694323945,"updated_at_unix_micros":1712755208919989,"language":"en","translated_lang":"","text_original":"Very very good gym .good master very friendly actually my weight is too high 3month I will join now  i am 6kg loss .so kindly master😍🥰🤩😍🥰","text_translated":"","published_at":"2024-03-29T15:04:54.323945Z"},{"Name":"Prabhakaran P","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW9W6EQ5dAeanXOcCW0OKB83jAc1APJpew-KPe2QMb35Uv03uViNg=s120-c-rp-mo-br100","Rating":5,"Description":"Clean Space, Updated Equipment, Easy Parking, friendly trainer, Nice environment, flexible timing, getting maximum results in minimal time at the gym. Best gym in this locality.","Images":null,"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURtOGFyVXRBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103532525494469821424/reviews?hl=en-GB","posted_at_unix_micros":1643689433628615,"updated_at_unix_micros":1643690193211630,"language":"en","translated_lang":"","text_original":"Clean Space, Updated Equipment, Easy Parking, friendly trainer, Nice environment, flexible timing, getting maximum results in minimal time at the gym. Best gym in this locality.","text_translated":"","published_at":"2022-02-01T04:23:53.628615Z"},{"Name":"Rama Nathan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUlE33zen04uVYuZMb3D9uY0QNLtrCW0YS8WC1gyJkQSMQdMeSn=s120-c-rp-mo-br100","Rating":5,"Description":"Coach is very friendly and supportive even for a biginer and making realise the importance of workouts and the benefits of it.\nWish more \u0026 more branches to open for the benefits of all. Wishing success for a bright future.","Images":null,"When":"6 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURDOWJ5MUlBEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111396578003762937943/reviews?hl=en-GB","posted_at_unix_micros":1601967934387310,"updated_at_unix_micros":1601967934387310,"language":"en","translated_lang":"","text_original":"Coach is very friendly and supportive even for a biginer and making realise the importance of workouts and the benefits of it.\nWish more \u0026 more branches to open for the benefits of all. Wishing success for a bright future.","text_translated":"","published_at":"2020-10-06T07:05:34.38731Z"},{"Name":"Bharath AFC","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVpHkJOp__vd16wSrgkEt83ELmjEHb4gl9KyOYfgHyztDfKHcddnQ=s120-c-rp-mo-br100","Rating":5,"Description":"Nice master 💯👏 and a amazing gym ❤️it's a new theropy to all guys💯🤌this is the place too develope your self ❤️","Images":null,"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURUdjktaGNBEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101402459882593062389/reviews?hl=en-GB","posted_at_unix_micros":1716993639513225,"updated_at_unix_micros":1716993639513225,"language":"en","translated_lang":"","text_original":"Nice master 💯👏 and a amazing gym ❤️it's a new theropy to all guys💯🤌this is the place too develope your self ❤️","text_translated":"","published_at":"2024-05-29T14:40:39.513225Z"}]</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AU77" t="inlineStr"/>
+      <c r="AV77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>43</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Muscle+hacking/data=!4m7!3m6!1s0x3a52678c011e5ee9:0xc21ef746b6ff16ba!8m2!3d13.0522117!4d80.228152!16s%2Fg%2F11spwnt_4g!19sChIJ6V4eAYxnUjoRuhb_tkb3HsI</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Muscle hacking</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>45/2, Akbarabad 2nd St, Akbarabad, Kodambakkam, Chennai, Tamil Nadu 600024</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30–11 am","5–9 pm"],"Monday":["5:30–11 am","5–9 pm"],"Saturday":["5:30–11 am","5–9 pm"],"Sunday":["Closed"],"Thursday":["5:30–11 am","5–9 pm"],"Tuesday":["5:30–11 am","5–9 pm"],"Wednesday":["5:30–11 am","5–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>073388 11307</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>362H+V7 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>74</v>
+      </c>
+      <c r="O78" t="n">
+        <v>5</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":1,"5":73}</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>13.052212</v>
+      </c>
+      <c r="R78" t="n">
+        <v>80.22815199999999</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>13987889375749281466</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeNz3YaBVajrjU_1tvf9sWtLNzg37ZqxTSUSXmciEVDlsDw6YZJ7ikuOA7w0S1WVHGVd4wfFzpKHHz93bA_9g5_aqGnFjAG2NiTlAEFKMU7YDDA1e40d9TCOd765ZKos4O6xr45WHNXVoQ=w408-h408-k-no</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>0x3a52678c011e5ee9:0xc21ef746b6ff16ba</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>ChIJ6V4eAYxnUjoRuhb_tkb3HsI</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>{"id":"111953623249249647957","name":"Muscle hacking (Owner)","link":"https://www.google.com/maps/contrib/111953623249249647957"}</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>{"borough":"Akbarabad, Kodambakkam","street":"45/2, Akbarabad 2nd St","city":"Chennai","postal_code":"600024","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>[{"Name":"Jegatheesh Jegan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVwhygGVMKD0xj5ED7FNTd7XJgfKgI5Kl1EZ7CKkFDcYDscKdv0=s120-c-rp-mo-br100","Rating":5,"Description":"Muscle Hacking is truly one of the best gym. I've experienced in my fitness career. I’m so grateful for the amazing environment at this gym. The gym buddies are friendly and supportive. perfect balance of healthy workouts and a great vibe\n\nPersonally Master Gokul has been an incredibly friendly and supportive trainer throughout my fitness journey. His positive attitude and personalized approach made all the difference in my transformation. Thank you so much, Master Gokul, for helping me achieve my goals and for being such an inspiring and motivating person. ❤️❤️❤️","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcGra11wbjauLHW4i45HvYe9n8CkIaNS0LzTljVusgoqaeI30A-2WcuGdPqNW6LSPQv4DPVZ7DDQ441KYDKw8-PHJINzc4TTdY_yfbs0InfjO50kh9T9VhSu456UR7fpyuJhJM=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdJ3LVbp8VCw0iTTuyHhzVYkzN_tK9_T1gYR4vW7GIq-rSL645j8QjwzaPzcubZVQTYjl5ob3rmnzpLmwzBfi_adKrGlY5VW1ExITgs4G78iSeal6cI2PwlDGpG0SalvlQCe3WGvg=k-no"],"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURQbDQ3WGhBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103046085114952981394/reviews?hl=en-GB","posted_at_unix_micros":1733467142493447,"updated_at_unix_micros":1733467142493447,"language":"en","translated_lang":"","text_original":"Muscle Hacking is truly one of the best gym. I've experienced in my fitness career. I’m so grateful for the amazing environment at this gym. The gym buddies are friendly and supportive. perfect balance of healthy workouts and a great vibe\n\nPersonally Master Gokul has been an incredibly friendly and supportive trainer throughout my fitness journey. His positive attitude and personalized approach made all the difference in my transformation. Thank you so much, Master Gokul, for helping me achieve my goals and for being such an inspiring and motivating person. ❤️❤️❤️","text_translated":"","published_at":"2024-12-06T06:39:02.493447Z"},{"Name":"SUBASH","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXeY1u6ddBZYNy16cVCm-V0ZiJev_MPLQCSlqcPlFS5IES2hCX8=s120-c-rp-mo-br100","Rating":5,"Description":"I've been working out at (MUSCLE HACKING GYM] for [2] months, and I've seen incredible results! The equipment is top-notch, and the STAFF GOKUL MASTER is super supportive. The trainers are knowledgeable and motivating, helping me reach my fitness goals. The atmosphere is energetic and clean. Highly recommend","Images":null,"When":"Edited a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT205T1Yyd3pXa0kwYlVnelEwOXhiMHd5VG5Nd01sRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101716815892597592240/reviews?hl=en-GB","posted_at_unix_micros":1749445117764469,"updated_at_unix_micros":1754630485975204,"language":"en","translated_lang":"","text_original":"I've been working out at (MUSCLE HACKING GYM] for [2] months, and I've seen incredible results! The equipment is top-notch, and the STAFF GOKUL MASTER is super supportive. The trainers are knowledgeable and motivating, helping me reach my fitness goals. The atmosphere is energetic and clean. Highly recommend","text_translated":"","published_at":"2025-06-09T04:58:37.764469Z"},{"Name":"Raghuram","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXxF1DICEB45odipzcaG4uZB4c_8qwvuB8R6dhaO4dwG3fjqJ5b=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been coming to this gym for a while now, and I’m really impressed with the professionalism and friendly attitude of the trainer \u0026 owner (Gokul). He is motivative, well-mannered, patient, genuinely supportive and ensures I’m using the right techniques. The positive environment here makes it easy to stay committed to my fitness goals. Highly recommend this gym if you want expert guidance in a respectful and encouraging atmosphere!!","Images":null,"When":"a year ago","review_id":"ChZDSUhNMG9nS0VQcmVuOG5oaXZ5cUx3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104688325948860240587/reviews?hl=en-GB","posted_at_unix_micros":1749011249920014,"updated_at_unix_micros":1749011249920014,"language":"en","translated_lang":"","text_original":"I’ve been coming to this gym for a while now, and I’m really impressed with the professionalism and friendly attitude of the trainer \u0026 owner (Gokul). He is motivative, well-mannered, patient, genuinely supportive and ensures I’m using the right techniques. The positive environment here makes it easy to stay committed to my fitness goals. Highly recommend this gym if you want expert guidance in a respectful and encouraging atmosphere!!","text_translated":"","published_at":"2025-06-04T04:27:29.920014Z"},{"Name":"Ayyanar Priya","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUbXUbSP_XtqWQmw5I5IHp8Phs2bis-B5dccR5Btlhu5-D868uaPw=s120-c-rp-mo-br100","Rating":5,"Description":"As a female I got a warm , safe and most comfortable atmosphere in this gym. The gym active time is more practical. Master , gives a personalized training for everyone. Based on the client need he gives a various training like somebody needs weight losing, gaining, muscle building,life style modification etc.. he customise the training based on clients need. not only a personalized,costomised training ,the gym also improves the lifestyle qualities which made our mind at peace. Master not only focus on clients physic, but also made a lively real time events in the field.\nI am proud and happy to become a part of the MUSCLE HACKING family.about the equipment,workout space,trainer is all perfect.\n\nAnd everyone mind their own business but a friendly gym mets.","Images":null,"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURmdTViVkdnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102392785871232564743/reviews?hl=en-GB","posted_at_unix_micros":1736518110570057,"updated_at_unix_micros":1736518110570057,"language":"en","translated_lang":"","text_original":"As a female I got a warm , safe and most comfortable atmosphere in this gym. The gym active time is more practical. Master , gives a personalized training for everyone. Based on the client need he gives a various training like somebody needs weight losing, gaining, muscle building,life style modification etc.. he customise the training based on clients need. not only a personalized,costomised training ,the gym also improves the lifestyle qualities which made our mind at peace. Master not only focus on clients physic, but also made a lively real time events in the field.\nI am proud and happy to become a part of the MUSCLE HACKING family.about the equipment,workout space,trainer is all perfect.\n\nAnd everyone mind their own business but a friendly gym mets.","text_translated":"","published_at":"2025-01-10T14:08:30.570057Z"},{"Name":"GOWTHAM VENKATACHALAM","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVD1zNcJOka5VnoX9qkHfhr-4xVoSsAvQb4zBGTvwzQwwcqqgFm=s120-c-rp-mo-br100","Rating":5,"Description":"I’m addicted to this gym, I’m more addicted to the workout style given by Gokul master, such an excellent and experienced trainer.\nNo fee considered for training .. free personal training at. Flexible timings .\nI can see visible results within a month.\nThanks to Gokul master….","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLdX_JGFG7uVsTREc1WypYQDoof5_qHVi3M07bCXXw3KR41JB330Xr2F6m3Tp5DstP9XxZFlSE4HokuSbZMyeG8dpT4KXzxzAgeytaWyDcjwO8gkAMwnzUandwbC1J9od9F0BM3Jr2DY_CFp=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfUFmKBhjdtgkRYmd1cvEZBB9N7mb_QJXzBPEYMWeDUleroli8sW5tB3Zy4lYinkUt6OtiRCCfmTukwKfSRX8ZAwLatbJf1S5u7NisCWQmS1QKpQYF3dgLcAV0kN3t83azTHgvkHKty8AsS=k-no"],"When":"a year ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25wbk9WbEhjamRDZGpaNU9ETklNekpJWDJrNVUwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116510756018748949635/reviews?hl=en-GB","posted_at_unix_micros":1753196754685156,"updated_at_unix_micros":1753196754685156,"language":"en","translated_lang":"","text_original":"I’m addicted to this gym, I’m more addicted to the workout style given by Gokul master, such an excellent and experienced trainer.\nNo fee considered for training .. free personal training at. Flexible timings .\nI can see visible results within a month.\nThanks to Gokul master….","text_translated":"","published_at":"2025-07-22T15:05:54.685156Z"}]</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AU78" t="inlineStr"/>
+      <c r="AV78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>43</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/RF+Gym+%26+Crossfit/data=!4m7!3m6!1s0x3a525e4711318af7:0x7d6834516d8c90d!8m2!3d12.9663329!4d80.1489406!16s%2Fg%2F11f39s9dgj!19sChIJ94oxEUdeUjoRDcnYFkWD1gc</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>RF Gym &amp; Crossfit</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>No 1, SN Building, Dharga Rd, Pallavaram, Pallavaram (Contonment), Tamil Nadu 600043</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–9:30 pm"],"Monday":["5 am–9:30 pm"],"Saturday":["5 am–9:30 pm"],"Sunday":["5 am–12 pm"],"Thursday":["5 am–9:30 pm"],"Tuesday":["5 am–9:30 pm"],"Wednesday":["5 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>099529 50090</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>X48X+GH Pallavaram (Contonment), Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>69</v>
+      </c>
+      <c r="O79" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":1,"3":3,"4":12,"5":53}</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>12.966333</v>
+      </c>
+      <c r="R79" t="n">
+        <v>80.14894099999999</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>564783136040864013</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLezKdNElUCr-kB1SAtg__q0IA3ZwBLOOepyoZuyLu-nXzYdVpVi3BL0m5T4jXD6qBAEm-Yzfu9W-68eqeTX4V24IpCJom94wJ26wg7IS7URV3P4g3uRYwpKqV7vNTj2B0mSyWY7sg=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>0x3a525e4711318af7:0x7d6834516d8c90d</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>ChIJ94oxEUdeUjoRDcnYFkWD1gc</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>{"id":"107651413908423093877","name":"RF Gym \u0026 Crossfit (Owner)","link":"https://www.google.com/maps/contrib/107651413908423093877"}</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>{"borough":"Subramaniya, Pallavaram","street":"No 1, SN Building, Dharga Rd, Pallavaram","city":"Pallavaram (Contonment)","postal_code":"600043","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>[{"Name":"Ravikumar R","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWcxDi5F46hdw3926N99n0N_hoY1MWTvfp8mZb9YL8DRriWP-6cuw=s120-c-rp-mo-ba12-br100","Rating":4,"Description":"RF GYM.\n🥋  💪\nGYM  with good \u0026 complete\nset of  equipments.🏋️🏃⛓️\nExperienced Trainers.\n\nEspecially Mr.Zaheer guided  team members effectively.\n\n✅ Complete guidance\n✅Easy accessibility\n✅Flexible timings slots\n✅Comfortable place for 🆕 Joiners.\n✅Reasonable fees\n\nAnnual payments option available","Images":null,"When":"Edited 2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURXeUlpN3ZRRRAB","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/112175637422207574812/reviews?hl=en-GB","posted_at_unix_micros":1647191905417541,"updated_at_unix_micros":1704981362625697,"language":"en","translated_lang":"","text_original":"RF GYM.\n🥋  💪\nGYM  with good \u0026 complete\nset of  equipments.🏋️🏃⛓️\nExperienced Trainers.\n\nEspecially Mr.Zaheer guided  team members effectively.\n\n✅ Complete guidance\n✅Easy accessibility\n✅Flexible timings slots\n✅Comfortable place for 🆕 Joiners.\n✅Reasonable fees\n\nAnnual payments option available","text_translated":"","reply_text_original":"Thank u Ravi sir","reply_language":"en","reply_posted_at_unix_micros":1704980143000000,"reply_updated_at_unix_micros":1706243195000000,"published_at":"2022-03-13T17:18:25.417541Z"},{"Name":"Mansoor Ahamed Khan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUpJ03WtGDZh5lp_KZKSvgoj9B8NrSH3xKGfSoi5USMnRCIbCnv=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"RF GYM pallavaram is located slightly away from my residence. However, I continue my gym only in RF Gym because of Master Zahir. He is excellent in terms of coaching. Very kind and cool temperament while coaching.\nWith regards to the GYM facilities it is upto the mark and you have seperate hall to do cardio workouts.\nThe fee structure also very nominal and crowd also was decent and friendly atmosphere.\nAll credit goes to Master Zahir.","Images":null,"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUQtMXAzR0JnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103626375506843770622/reviews?hl=en-GB","posted_at_unix_micros":1669711471846347,"updated_at_unix_micros":1669711471846347,"language":"en","translated_lang":"","text_original":"RF GYM pallavaram is located slightly away from my residence. However, I continue my gym only in RF Gym because of Master Zahir. He is excellent in terms of coaching. Very kind and cool temperament while coaching.\nWith regards to the GYM facilities it is upto the mark and you have seperate hall to do cardio workouts.\nThe fee structure also very nominal and crowd also was decent and friendly atmosphere.\nAll credit goes to Master Zahir.","text_translated":"","reply_text_original":"Thanks brother always welcome","reply_language":"en","reply_posted_at_unix_micros":1704979927000000,"reply_updated_at_unix_micros":1704979927000000,"published_at":"2022-11-29T08:44:31.846347Z"},{"Name":"Kripa Leah","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVno1LAxmPoit7osXYQRCyh11tfPS9vog_Y67CJOpPAuU4bIEor1A=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Wonderful working master thre ; he is very helpful and goal oriented : u dnt get that service and training anywhere in the top gyms choose this\n\nI was 78 now i am 68\n\nI am maintaining it\n\nThanks to master","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLd9e2GsOg9rsUGY4WI2TD_hYV6seR5m_FGqUc4zRQzWwopoWbXLdxdjY915xZ4qTYyBss0vY4XeKjk3GMnWlbHwXBncMwVTgML69XCbDphpNFqON2EJIgKKyvkwBGfSzSmUQl4=k-no"],"When":"3 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUQta3I3OGdBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107451906288432602220/reviews?hl=en-GB","posted_at_unix_micros":1669386528867677,"updated_at_unix_micros":1669386528867677,"language":"en","translated_lang":"","text_original":"Wonderful working master thre ; he is very helpful and goal oriented : u dnt get that service and training anywhere in the top gyms choose this\n\nI was 78 now i am 68\n\nI am maintaining it\n\nThanks to master","text_translated":"","reply_text_original":"Thank you ever much 👍","reply_language":"en","reply_posted_at_unix_micros":1669434741000000,"reply_updated_at_unix_micros":1669434741000000,"published_at":"2022-11-25T14:28:48.867677Z"},{"Name":"jhansi gopi","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWAvu1_msXS_2gxkZgonVEXuJxnLNvf4MQKeRQuGOm8HgCodGQ=s120-c-rp-mo-br100","Rating":4,"Description":"A good place to lose weight ... Zakir\u0026 rafi master motivated well ... Excellent coaching given by rafi master \u0026 special care given to every individual... Zakir master is too humble man ... Giving  fabulous abs exercise , plank ... Within 3 month i loses 10 kg ..i glad to reduce more calories ....","Images":null,"When":"7 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURZMWJtYmJ3EAE","source":"Google","rating_scale":5,"rating_float":4,"author_url":"https://www.google.com/maps/contrib/107374908288343108723/reviews?hl=en-GB","posted_at_unix_micros":1558060844407261,"updated_at_unix_micros":1558064581792787,"language":"en","translated_lang":"","text_original":"A good place to lose weight ... Zakir\u0026 rafi master motivated well ... Excellent coaching given by rafi master \u0026 special care given to every individual... Zakir master is too humble man ... Giving  fabulous abs exercise , plank ... Within 3 month i loses 10 kg ..i glad to reduce more calories ....","text_translated":"","reply_text_original":"Thanking you madem","reply_language":"en","reply_posted_at_unix_micros":1558068124000000,"reply_updated_at_unix_micros":1558068124000000,"published_at":"2019-05-17T02:40:44.407261Z"},{"Name":"Manoj Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWq_04okpu3JQKbhqBSB7DWlQaDNKsOPSWiTyJ_7jcJii6nilyL=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Super, high teach equipments, cross fit compuslosry on monday. Good training from master, steching for every exersice increases the load and gets motivated.","Images":null,"When":"7 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNZb0pIWlJBEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107287266209158619497/reviews?hl=en-GB","posted_at_unix_micros":1553840847444202,"updated_at_unix_micros":1553840847444202,"language":"en","translated_lang":"","text_original":"Super, high teach equipments, cross fit compuslosry on monday. Good training from master, steching for every exersice increases the load and gets motivated.","text_translated":"","reply_text_original":"Thanks bro","reply_language":"en","reply_posted_at_unix_micros":1553843149000000,"reply_updated_at_unix_micros":1553843149000000,"published_at":"2019-03-29T06:27:27.444202Z"}]</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AU79" t="inlineStr"/>
+      <c r="AV79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>43</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2145f2ed-c254-4642-a1fc-f6bf5fdca394</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/HUSTLE+HUB+Gym/data=!4m7!3m6!1s0x3a526571659181ad:0xc8face1a593d6b4!8m2!3d13.0913739!4d80.2068971!16s%2Fg%2F11swfk5bzf!19sChIJrYGRZXFlUjoRtNaTpeGsjww</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>HUSTLE HUB Gym</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>18th St, Belly Area, Anna Nagar West, Anna Nagar, Chennai, Tamil Nadu 600040</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–10 pm"],"Monday":["6 am–10 pm"],"Saturday":["6–9 am"],"Sunday":["Closed"],"Thursday":["6 am–10 pm"],"Tuesday":["6 am–10 pm"],"Wednesday":["6 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>099404 34361</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>36R4+GQ Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>46</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":1,"4":1,"5":44}</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>13.091374</v>
+      </c>
+      <c r="R80" t="n">
+        <v>80.206897</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>905132135270307508</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfa0rjHMXCKI5UsDKMzhwspbkpce0gOXkh67gEK2oqsJ5h-cTcGgzcfr-K5qlgvVoshcicP6TDScslO6V_hdJ8bpy3eOfVlWAxxtHhWDqyqVKx_bQ34C4p_-kekDqiCffANBwO0=w408-h530-k-no</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>0x3a526571659181ad:0xc8face1a593d6b4</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>ChIJrYGRZXFlUjoRtNaTpeGsjww</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>{"id":"103021949198376266825","name":"HUSTLE HUB Gym (Owner)","link":"https://www.google.com/maps/contrib/103021949198376266825"}</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>{"borough":"Belly Area, Anna Nagar West, Anna Nagar","street":"18th St","city":"Chennai","postal_code":"600040","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>[{"Name":"Raj M","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJMv3-vEpuxSJZXBKgocvd-_-XJN4bSiOz-EN9NYh2VJ6aEEQ=s120-c-rp-mo-br100","Rating":5,"Description":"Hustle Gym has been an amazing place to train and grow stronger. What truly sets it apart is the personalized approach to fitness. The workouts are thoughtfully designed around individual fitness levels and goals, with a strong focus on strength training, HIIT, and agility. The programs feel balanced, structured, and effective.\n\nCoach Balaji is the heart of Hustle Gym. He has a great ability to connect with trainees where they are and get them on board in a way that feels natural and motivating. He effectively customizes each program so it’s both challenging and sustainable. His knowledge, dedication, and friendly approach make a huge difference in the overall experience.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2toUmMxaFpkazV3WVhoS016Z3pNRU13U3pGV2FsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113523910400040904139/reviews?hl=en-GB","posted_at_unix_micros":1772128741757692,"updated_at_unix_micros":1772128741757692,"language":"en","translated_lang":"","text_original":"Hustle Gym has been an amazing place to train and grow stronger. What truly sets it apart is the personalized approach to fitness. The workouts are thoughtfully designed around individual fitness levels and goals, with a strong focus on strength training, HIIT, and agility. The programs feel balanced, structured, and effective.\n\nCoach Balaji is the heart of Hustle Gym. He has a great ability to connect with trainees where they are and get them on board in a way that feels natural and motivating. He effectively customizes each program so it’s both challenging and sustainable. His knowledge, dedication, and friendly approach make a huge difference in the overall experience.","text_translated":"","reply_text_original":"Thankyou 🙏🏻\n","reply_language":"en","reply_posted_at_unix_micros":1772155721000000,"reply_updated_at_unix_micros":1773223075000000,"published_at":"2026-02-26T17:59:01.757692Z"},{"Name":"Vaisnavi S","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLgvPDMpF0Y4Mv4gdvu9pikLi11LQdd5cHlx4-_Babr0p91sw=s120-c-rp-mo-br100","Rating":5,"Description":"This is an excellent personalized strength and conditioning gym. Coach Balaji is highly knowledgeable, professional, and genuinely invested in his clients’ progress. Every workout is customized based on individual goals, fitness levels, and limitations, which makes a huge difference in results and injury prevention.\n\nThe training environment is motivating, focused, and well-structured. Balaji anna pays close attention to form, technique, and consistency, pushing you just the right amount while keeping sessions safe and effective. Whether your goal is strength, fat loss, mobility, or overall fitness, this gym delivers real results.\n\nHighly recommended for anyone serious about improving their fitness with proper guidance.","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psaU1uWkhNRzVQTURacVdrVXhiV3BVU0U1U1ZWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107210206666224450282/reviews?hl=en-GB","posted_at_unix_micros":1769696801564100,"updated_at_unix_micros":1769696801564100,"language":"en","translated_lang":"","text_original":"This is an excellent personalized strength and conditioning gym. Coach Balaji is highly knowledgeable, professional, and genuinely invested in his clients’ progress. Every workout is customized based on individual goals, fitness levels, and limitations, which makes a huge difference in results and injury prevention.\n\nThe training environment is motivating, focused, and well-structured. Balaji anna pays close attention to form, technique, and consistency, pushing you just the right amount while keeping sessions safe and effective. Whether your goal is strength, fat loss, mobility, or overall fitness, this gym delivers real results.\n\nHighly recommended for anyone serious about improving their fitness with proper guidance.","text_translated":"","reply_text_original":"Thankyou 🙏🏻","reply_language":"en","reply_posted_at_unix_micros":1769698599000000,"reply_updated_at_unix_micros":1769698599000000,"published_at":"2026-01-29T14:26:41.5641Z"},{"Name":"Muthu Sathiamurthy","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU85ea7v6HVStOOz6HmRKxAYlBaNfNpkfcrhjdAo6z1mDjZ3Myn=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Hustle hub is a personalised gym where coach Balaji devises a workout routine for every individual. Routine keeps changing per our goals and what we achieve. When I started with him almost a year ago, it was mostly HIIT and agility to get me back into active fitness mode.  Now he started incorporating a lot of strength training.\n\nCoach accepts new clients based on time slot availability to ensure he is not overcrowding a specific timeslot.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfTxactOD_IJ9W4NrK4h98gtgeb2o1zcn3iOJBAUS8R7Kwu_FcgMR5jD518oE1extd7CKrE_e3a_HoofXyhdi96TPoBmIiEHOT5-5PyjELN6Hckc6Cfc8rOnAJ-BuNLhUWcsnu7KY00-Cr1=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLe3kt1l-zT2XJqzo3pdNREEmth1l2uGAhDg7gBLmku3KWf_KX5kD4tRH1j2SiOhGKgltkciS-B4ZFZUKO2Finvv2RqZ1CBFVgRoWvjF8Ea4Ju5X6VqDQWlIAnVhnoXlGVNyQvF9PsX69Kk=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfp4E9p8yQEuUYg3FzsifWo9AtVS5c999gyj4EIywARVlXhwIlSc1V9tfUcSFs91nTk-s-iZtzKSI6mmf3Ef7T_oI7Dcon_wjuVh74d2cAZwOSN-HLEyOoq7r6o_wmLKSBouwJMpr4OEy4M=k-no"],"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xReFJFUjJTM2xhUzI5WlZGSnBRazB0ZUU5dmVWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116584328673372558449/reviews?hl=en-GB","posted_at_unix_micros":1770456529624157,"updated_at_unix_micros":1770456529624157,"language":"en","translated_lang":"","text_original":"Hustle hub is a personalised gym where coach Balaji devises a workout routine for every individual. Routine keeps changing per our goals and what we achieve. When I started with him almost a year ago, it was mostly HIIT and agility to get me back into active fitness mode.  Now he started incorporating a lot of strength training.\n\nCoach accepts new clients based on time slot availability to ensure he is not overcrowding a specific timeslot.","text_translated":"","reply_text_original":"Thankyou 🙏🏻","reply_language":"en","reply_posted_at_unix_micros":1770463831000000,"reply_updated_at_unix_micros":1770463831000000,"published_at":"2026-02-07T09:28:49.624157Z"},{"Name":"yogesh ravichandran","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJRLCWqOtL6dQT1D--j4WvD8b0hBJC_ojpQtAL_wRxCk5-FxA=s120-c-rp-mo-br100","Rating":5,"Description":"Balaji is an excellent coach who gives personalised workout everyday and definitely makes you sweat it out at the end of the session. It feels like a personalised gym. Do check out!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xkVk9GcEdjM2xpTmpJNFUyZERjSEIwYWpCVlVFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116712870805257055086/reviews?hl=en-GB","posted_at_unix_micros":1777389964339395,"updated_at_unix_micros":1777389964339395,"language":"en","translated_lang":"","text_original":"Balaji is an excellent coach who gives personalised workout everyday and definitely makes you sweat it out at the end of the session. It feels like a personalised gym. Do check out!","text_translated":"","reply_text_original":"Thankyou 👍🏻","reply_language":"en","reply_posted_at_unix_micros":1777392233000000,"reply_updated_at_unix_micros":1777392233000000,"published_at":"2026-04-28T15:26:04.339395Z"},{"Name":"Ranjani Balasubramanian","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWUgCIJ_pvdI_OeD26CpY6nbz1thPtusqcVx7Lh2fB-QCPCuxHH=s120-c-rp-mo-br100","Rating":5,"Description":"One of the best places to workout. you feel your body change here in a short span. Coach Balaji designs the workout according to individual and motivates and pushes you to do it. He focuses on the form of exercise too to avoid any injury .","Images":null,"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2w5V1F6WndkVVJGTkhWb1NFa3pNMWt3TkdnM1QyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114592927259317231046/reviews?hl=en-GB","posted_at_unix_micros":1762693161316520,"updated_at_unix_micros":1762693161316520,"language":"en","translated_lang":"","text_original":"One of the best places to workout. you feel your body change here in a short span. Coach Balaji designs the workout according to individual and motivates and pushes you to do it. He focuses on the form of exercise too to avoid any injury .","text_translated":"","reply_text_original":"Thankyou 👍🏻","reply_language":"en","reply_posted_at_unix_micros":1762704205000000,"reply_updated_at_unix_micros":1762704205000000,"published_at":"2025-11-09T12:59:21.31652Z"}]</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>43</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Spotter+Fitness/data=!4m7!3m6!1s0x3a5267ad6f4b2689:0xcdf46c95f7af1417!8m2!3d13.0609834!4d80.2180661!16s%2Fg%2F11s2lmmvjr!19sChIJiSZLb61nUjoRFxSv95Vs9M0</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spotter Fitness</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>55/, 2nd Floor, Spotter Fitness, Nehru Street, Avvai Nagar, Choolaimedu, Chennai, Tamil Nadu 600094</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>097097 08006</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>3669+96 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>43</v>
+      </c>
+      <c r="O81" t="n">
+        <v>5</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":2,"5":41}</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>13.060983</v>
+      </c>
+      <c r="R81" t="n">
+        <v>80.21806599999999</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>14840606063454000151</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLflDnkRers4JQkMfVGBxXnJtqYpxEXhGkHeqyZU9ez5tYj3z-X5YtBMEOBFDGbENKXWMJFPbS2yLQNnKQ9KWYdinvEsfJTnOMyXae0K73Wnnsak99j5CwCVecAkcTym4mxLPSQ2Qw=w408-h505-k-no</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>0x3a5267ad6f4b2689:0xcdf46c95f7af1417</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>ChIJiSZLb61nUjoRFxSv95Vs9M0</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>{"id":"115307016818722671567","name":"Spotter Fitness (Owner)","link":"https://www.google.com/maps/contrib/115307016818722671567"}</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>{"borough":"Avvai Nagar, Choolaimedu","street":"55/, 2nd Floor, Nehru Street","city":"Chennai","postal_code":"600094","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>[{"Name":"Robbie Johnson","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV0cmhDpoNYB_y92oAlxlb5pSlJdqJWbhActuzbG6M_K3M71uXs=s120-c-rp-mo-br100","Rating":5,"Description":"This is the Gym where I am experiencing wonderful support, guidance and tracking of my improvement towards health goal... Best place to do workout. Easily affordable price with best result on health... Gym Master is one of the best person i have ever met.. Thanks for initiative and support Master. Keep it up.","Images":null,"When":"4 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNPbHVLTDl3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101430416192479754729/reviews?hl=en-GB","posted_at_unix_micros":1654747745956909,"updated_at_unix_micros":1654747861551760,"language":"en","translated_lang":"","text_original":"This is the Gym where I am experiencing wonderful support, guidance and tracking of my improvement towards health goal... Best place to do workout. Easily affordable price with best result on health... Gym Master is one of the best person i have ever met.. Thanks for initiative and support Master. Keep it up.","text_translated":"","published_at":"2022-06-09T04:09:05.956909Z"},{"Name":"John Solomon","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWtivgx4gDWBrEpnEX2ZnATovKXHorWcBJk0qRR0k1MCEPWekxjEg=s120-c-rp-mo-br100","Rating":5,"Description":"(1.)Amazing facility, top equipment and great environment. (2)The trainers are really awesome and helpful\"( 3)Good service with friendly staff and super clean and comfortable gym.....","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLejiW9sjTKrJR-er0gZmwt25wvwVELZolh4RazsOFV4x3YNwovv9SG1NCaI5O2kZ64rIUkwiybx3i_PU3ZY_5sYdlKAYN4pvmHvtSHDAEbc1eSYhCw36qgnyB3rb5imlY6iFOwjMw=k-no"],"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnTUNRNmFtRmJREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112384365444927765847/reviews?hl=en-GB","posted_at_unix_micros":1741190267868156,"updated_at_unix_micros":1741190267868156,"language":"en","translated_lang":"","text_original":"(1.)Amazing facility, top equipment and great environment. (2)The trainers are really awesome and helpful\"( 3)Good service with friendly staff and super clean and comfortable gym.....","text_translated":"","published_at":"2025-03-05T15:57:47.868156Z"},{"Name":"Dinesh T","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV7TSDXso6U-1uU2HWUjBROdWWfNcy5oDu_uDmuDHauKOX5kHqN=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This gym is so personal to me. I was 88 kg when i was joining and reduced to 65kg ....such a peaceful ambiance, a perfect gym makes you to do what you want.","Images":null,"When":"4 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNPZzdmaFlBEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102597384144421971242/reviews?hl=en-GB","posted_at_unix_micros":1655522351052107,"updated_at_unix_micros":1655523218144620,"language":"en","translated_lang":"","text_original":"This gym is so personal to me. I was 88 kg when i was joining and reduced to 65kg ....such a peaceful ambiance, a perfect gym makes you to do what you want.","text_translated":"","published_at":"2022-06-18T03:19:11.052107Z"},{"Name":"Idhaya devan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVerD9H_tKPfYzRD_6MXPSbl_oSrnwwc-ca7wxrIX4NrHsyKkGx=s120-c-rp-mo-br100","Rating":5,"Description":"I have started workout since 2019 ,till now it's good and It is a friendly environment and all are look our friends,You can think as your home","Images":null,"When":"4 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUN1cHQzQUZnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100958867360086599042/reviews?hl=en-GB","posted_at_unix_micros":1658915777786045,"updated_at_unix_micros":1658915777786045,"language":"en","translated_lang":"","text_original":"I have started workout since 2019 ,till now it's good and It is a friendly environment and all are look our friends,You can think as your home","text_translated":"","published_at":"2022-07-27T09:56:17.786045Z"},{"Name":"TIGER_igm_","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUyYqDLbsRSglzhl_T92eyna0kHiCH9prNnEbTNo-LFKf48wTI=s120-c-rp-mo-br100","Rating":5,"Description":"Good Gym💯","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tOd05HNHdORzV1ZW1OQlNWTnZTakZYUTBaR2RHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112098483777991905636/reviews?hl=en-GB","posted_at_unix_micros":1776570770340614,"updated_at_unix_micros":1776570770340614,"language":"en","translated_lang":"","text_original":"Good Gym💯","text_translated":"","published_at":"2026-04-19T03:52:50.340614Z"}]</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>43</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Flex+%26+Flow+Unisex+Fitness/data=!4m7!3m6!1s0x3a526700067dfd81:0x7e2a241364cfbe82!8m2!3d13.015854!4d80.245119!16s%2Fg%2F11n9t6q7ph!19sChIJgf19BgBnUjoRgr7PZBMkKn4</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Flex &amp; Flow Unisex Fitness</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>40/57, Ellaiamman Koil St, Kotturpuram, Chennai, Tamil Nadu 600085</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–11 pm"],"Monday":["5 am–11 pm"],"Saturday":["5 am–11 pm"],"Sunday":["6 am–8 pm"],"Thursday":["5 am–11 pm"],"Tuesday":["5 am–11 pm"],"Wednesday":["5 am–11 pm"]}</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>095144 28411</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>268W+82 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>39</v>
+      </c>
+      <c r="O82" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":1,"4":0,"5":38}</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>13.015854</v>
+      </c>
+      <c r="R82" t="n">
+        <v>80.245119</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>9091118463515082370</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfRUrMDEGkTxA3nW-yqBVBWmQA84vtV2NYUc_bRQwj3w3_Frx2g4Bz3iI7j8c-malV9aOI43kn_Wjg3eFRoAqjqJNb7GSH7wSwHsqfa673ED-HEgxknpvoHaCNqFJtr4o53cORppETt7xOP=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>0x3a526700067dfd81:0x7e2a241364cfbe82</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>ChIJgf19BgBnUjoRgr7PZBMkKn4</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>{"id":"113065609792305675494","name":"Flex \u0026 Flow Unisex Fitness (Owner)","link":"https://www.google.com/maps/contrib/113065609792305675494"}</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>{"borough":"Kotturpuram","street":"40/57, Ellaiamman Koil St","city":"Chennai","postal_code":"600085","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>[{"Name":"C Priyadharshini","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJFRYUdgVYiFUeI06myQy9cmmzzivD5Z-kswC3dcvBCWe5_YA=s120-c-rp-mo-br100","Rating":5,"Description":"“This is my first gym experience, and it has been truly amazing. The gym offers excellent training with highly skilled and supportive trainers who focus on proper techniques and personalized workout plans, especially Trainer Prabhu ❤️ Trainer Arun ❤️ \u0026 Trainer Sathish ❤️. They motivate consistently, helping achieve fitness goals effectively. The trainers are friendly, approachable, and always ready to guide, whether you are a beginner or experienced. The environment is clean, energetic, and well-equipped. Most importantly, it feels very safe and comfortable for women. Special attention is given to each member’s progress, ensuring visible results. Highly recommended for quality training, women’s safety, and dedicated coaching.”","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2s5eFpXOURSVXBVTUVGYVEybEdaVGxoWVVnM01HYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111792601542575576515/reviews?hl=en-GB","posted_at_unix_micros":1779242765131327,"updated_at_unix_micros":1779243808513215,"language":"en","translated_lang":"","text_original":"“This is my first gym experience, and it has been truly amazing. The gym offers excellent training with highly skilled and supportive trainers who focus on proper techniques and personalized workout plans, especially Trainer Prabhu ❤️ Trainer Arun ❤️ \u0026 Trainer Sathish ❤️. They motivate consistently, helping achieve fitness goals effectively. The trainers are friendly, approachable, and always ready to guide, whether you are a beginner or experienced. The environment is clean, energetic, and well-equipped. Most importantly, it feels very safe and comfortable for women. Special attention is given to each member’s progress, ensuring visible results. Highly recommended for quality training, women’s safety, and dedicated coaching.”","text_translated":"","published_at":"2026-05-20T02:06:05.131327Z"},{"Name":"viswapriya t p","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK8UVHQm0cDNk-gAcc-snzEKoLShLJhEKL7xkVgNW6MapXMDw=s120-c-rp-mo-br100","Rating":5,"Description":"Joined this gym recently and having a good time since .The trainers are very professional and always helping with daily workouts.Prabu and satish are very cool and friendly .Very patient and motivating to push ourself better!Gym maintenance is great and neat!Safe for women and comfortable too!💯✨","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xWb1gzcG9lV0owVFdSWFYwbG9UMjl5WTJNMFZYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109937047863544543586/reviews?hl=en-GB","posted_at_unix_micros":1780592687120972,"updated_at_unix_micros":1780592743040139,"language":"en","translated_lang":"","text_original":"Joined this gym recently and having a good time since .The trainers are very professional and always helping with daily workouts.Prabu and satish are very cool and friendly .Very patient and motivating to push ourself better!Gym maintenance is great and neat!Safe for women and comfortable too!💯✨","text_translated":"","published_at":"2026-06-04T17:04:47.120972Z"},{"Name":"Buvan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVH7hjCNi3uwkPIFEpazORqqyENdictxsPJr4cR6F7ljyl4YLzG=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"⭐⭐⭐⭐⭐ \"Had a great experience at Flex and Flow. The trainers are knowledgeable, supportive, and always motivate you to do your best. The environment is clean, friendly, and perfect for improving fitness and overall well-being. Highly recommend Flex and Flow to anyone looking for quality training and excellent service!\"\nExcellent gym","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psV1RuRlRRekJsWlMxdFRWWk1VM3B4T1U4eFNVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116399429720507586880/reviews?hl=en-GB","posted_at_unix_micros":1780053982091713,"updated_at_unix_micros":1780053982091713,"language":"en","translated_lang":"","text_original":"⭐⭐⭐⭐⭐ \"Had a great experience at Flex and Flow. The trainers are knowledgeable, supportive, and always motivate you to do your best. The environment is clean, friendly, and perfect for improving fitness and overall well-being. Highly recommend Flex and Flow to anyone looking for quality training and excellent service!\"\nExcellent gym","text_translated":"","published_at":"2026-05-29T11:26:22.091713Z"},{"Name":"Twinkle","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL4Q9Mkx7RhXarssJ9a84IafwU3N046x0bn8kDgF1QWxeeoSBY=s120-c-rp-mo-br100","Rating":5,"Description":"This is my first time gym experience. As a beginner, the trainers guided me very well. They are maintaining the equipments clean and good and price is also affordable.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xWWFVGTkVaRmMzUVhKdVJHWlNkRzFOV0VSck1VRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101751587930653054662/reviews?hl=en-GB","posted_at_unix_micros":1779797301319170,"updated_at_unix_micros":1779797301319170,"language":"en","translated_lang":"","text_original":"This is my first time gym experience. As a beginner, the trainers guided me very well. They are maintaining the equipments clean and good and price is also affordable.","text_translated":"","published_at":"2026-05-26T12:08:21.31917Z"},{"Name":"Yamini Murugan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUQpvYariXUTxgLLkvl4Y6MwuqFSk_6RegnuG4xfzwePuozxFw=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve really enjoyed my experience at this gym. The staff are welcoming, supportive, and always ready to help when needed. The equipment is clean, modern, and well-maintained, which makes workouts comfortable and enjoyable. I also like the positive atmosphere because people here are friendly and motivating. The trainers Prabhu, Arun and Sathish give useful guidance and encourage everyone to reach their fitness goals safely. Overall, it’s a great place for beginners and regular fitness lovers alike. I would happily recommend flex and flow gym to anyone looking for a healthy and motivating environment.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pCcVltbFBVVWRWWW5jMk5IbFhZelJHZEhBNWIxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101186408731322359724/reviews?hl=en-GB","posted_at_unix_micros":1779280866027830,"updated_at_unix_micros":1779280866027830,"language":"en","translated_lang":"","text_original":"I’ve really enjoyed my experience at this gym. The staff are welcoming, supportive, and always ready to help when needed. The equipment is clean, modern, and well-maintained, which makes workouts comfortable and enjoyable. I also like the positive atmosphere because people here are friendly and motivating. The trainers Prabhu, Arun and Sathish give useful guidance and encourage everyone to reach their fitness goals safely. Overall, it’s a great place for beginners and regular fitness lovers alike. I would happily recommend flex and flow gym to anyone looking for a healthy and motivating environment.","text_translated":"","published_at":"2026-05-20T12:41:06.02783Z"}]</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>43</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Tiger+Fitness+Gym/data=!4m7!3m6!1s0x3a526717ab110f5b:0x56117457ef07805b!8m2!3d13.0450098!4d80.1859175!16s%2Fg%2F11vqhpg4m9!19sChIJWw8RqxdnUjoRW4AH71d0EVY</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tiger Fitness Gym</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2nd Floor, Tiger Fitness Gym, Aavin Junction, 1-A, Arcot Rd, opposite Valasaravakkam, Alwartirunagar, Chennai, Tamil Nadu 600087</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["5:30–11 am"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>072998 74551</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>25WP+29 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>36</v>
+      </c>
+      <c r="O83" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":0,"3":2,"4":0,"5":33}</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>13.04501</v>
+      </c>
+      <c r="R83" t="n">
+        <v>80.185918</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>6201866082887106651</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdPsYKNBjLe8G7kJr9D1sLOb-JXgGhPhgm7CIgK-oYYFchEQ5CrHY6ojodZG4ZfNx3s0xsOMi0wA357eQvCkRJoRFLl-P6-yGVP1XJEwylBwi-RhPQqVNLJ45kS1eJGJyozeN3l=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>0x3a526717ab110f5b:0x56117457ef07805b</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>ChIJWw8RqxdnUjoRW4AH71d0EVY</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>{"id":"101607574853635711974","name":"Tiger Fitness Gym (Owner)","link":"https://www.google.com/maps/contrib/101607574853635711974"}</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>{"borough":"Alwartirunagar","street":"2nd Floor, Aavin Junction, 1-A, Arcot Rd, opposite Valasaravakkam","city":"Chennai","postal_code":"600087","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>[{"Name":"Lokesh","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJpOvyKyfGZP8XUxCA5ISS_WrlFkpJeaatt3MhYjYbNhWAwxPk=s120-c-rp-mo-br100","Rating":5,"Description":"Here you can explore gym and other areas like MMA,Boxing,strength training . Great master who  teaches good practices and discipline. #best","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfTsXkmB049QCRBVWDLip4vpMs1Q7K4MSjAD4MH3EozuGpK3Gjvwwe1yX9AsaYHSMTw57kwdZObwkPJdWRpefafkTPiZNOuBbIbUGBpApIjJ89Rr4BAsxY5jmDqaPhK09RvrUqS=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfwR5T-8rdlJsoyy-dYMVP958PqvEsUX2SeSRkGRhCAFVEoUoGmYHFXqLzFv2iKeTJZJxeyKvNlK4fojcrduar4wKB9PPIrd_Vs6LS34Wcs8I1bHc5hKz8b9nmqW13rzYSAABSV=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLf74MR-Mxl6BkTlddb_fB6jgBtkX6FZolFZdYPWV0qTxddzv0Akh8nk-m93kR7sR9F4wM9SReBg-S2NwhpfM_RTdJi1p_-IHIOb2nf95HHWxeR8XMDhDRCqf0j16lIXpdAhenbfWw=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeduApmqpxBqSdwXwGBemA876mnA5-vPJagm8UJAHotbkaQaMIibZ0KQ3rFL3SrTyJ1J1Sr-QW5cc6ZPORzF5V_kTOVqepQHStqL-GXVh2khvlQuXAU6ddXAEBo4NafAXEOgZy4=k-no"],"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUM5Z09ha2RnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/108514348393131446360/reviews?hl=en-GB","posted_at_unix_micros":1709175164683667,"updated_at_unix_micros":1709175164683667,"language":"en","translated_lang":"","text_original":"Here you can explore gym and other areas like MMA,Boxing,strength training . Great master who  teaches good practices and discipline. #best","text_translated":"","published_at":"2024-02-29T02:52:44.683667Z"},{"Name":"Adhavan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLOUdDS3kPH5ovEWM0_TakBQL4wOxZYgpOU8TV5l1mxhR3h1w=s120-c-rp-mo-br100","Rating":5,"Description":"Excellent gym with an epic old skool ambiance and well organised","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLckHPtHfQkz4EvvI6SJJpWfS2A0UZW4zsE3AYlvEl9313Fi0ArQYdZZ9trair7O61HH41OVFeV3jBxTKFzfgUqJJ12sbA_ZHPEIk0im338vgaHXQpma4K_j_DmZ3YJjGZayr4Q=k-no"],"When":"a year ago","review_id":"ChdDSUhNMG9nS0VPU01wODNjOGUyVnpBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114169115604530433368/reviews?hl=en-GB","posted_at_unix_micros":1747364393124807,"updated_at_unix_micros":1747364393124807,"language":"en","translated_lang":"","text_original":"Excellent gym with an epic old skool ambiance and well organised","text_translated":"","published_at":"2025-05-16T02:59:53.124807Z"},{"Name":"R. Rajesh","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKDzeISei-9F8zpPUu4Kv365G2QkjhN4dKPvcFjfTi7r1OE3A=s120-c-rp-mo-br100","Rating":5,"Description":"Worth the money. I'm doing gym workout in tiger fitness gym. I like the Ambience \u0026 surrounding of the gym with motivational gym mates. Master encourages me to push the limits. Very good place to learn MMA too.","Images":null,"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUQzMUptdk53EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113181293292188953682/reviews?hl=en-GB","posted_at_unix_micros":1731422554731019,"updated_at_unix_micros":1731422554731019,"language":"en","translated_lang":"","text_original":"Worth the money. I'm doing gym workout in tiger fitness gym. I like the Ambience \u0026 surrounding of the gym with motivational gym mates. Master encourages me to push the limits. Very good place to learn MMA too.","text_translated":"","published_at":"2024-11-12T14:42:34.731019Z"},{"Name":"Akshai Dhoni","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU-p1z9d-ZZ5CePXQP8TTOabLTT4CsBGCLJIgU2ygmeeDmaWKCJ=s120-c-rp-mo-br100","Rating":5,"Description":"\"I've been training at Tiger Fitness for a while now, and I must say, it's been a game-changer! The coaches are knowledgeable, supportive, and push you to reach your full potential. The atmosphere is electric, and the community is like a family. I've seen significant improvements in my physical fitness and mental toughness. The programs are well-structured, and the facilities are top-notch. Whether you're a beginner or an experienced athlete, Tiger Fitness has something for everyone. I highly recommend it to anyone looking to take their fitness journey to the next level.","Images":null,"When":"2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNIeDluQnF3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115803092860646168279/reviews?hl=en-GB","posted_at_unix_micros":1725897927425045,"updated_at_unix_micros":1725897944328585,"language":"en","translated_lang":"","text_original":"\"I've been training at Tiger Fitness for a while now, and I must say, it's been a game-changer! The coaches are knowledgeable, supportive, and push you to reach your full potential. The atmosphere is electric, and the community is like a family. I've seen significant improvements in my physical fitness and mental toughness. The programs are well-structured, and the facilities are top-notch. Whether you're a beginner or an experienced athlete, Tiger Fitness has something for everyone. I highly recommend it to anyone looking to take their fitness journey to the next level.","text_translated":"","published_at":"2024-09-09T16:05:27.425045Z"},{"Name":"Lokesh D","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXaEmqgl_hubvK-LwTGGEpoJZlf76joB1Hqrb8wB-ydQqXadYWe=s120-c-rp-mo-br100","Rating":5,"Description":"This is one of the rarest gym in Chennai where you can get real workouts and personal training for a reasonable fees.\nThis is entirely different from all other corporate gyms in Chennai. Worth for money.","Images":null,"When":"a year ago","review_id":"ChZDSUhNMG9nS0VJQ0FnTUR3eHJhYUl3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/112302872165245342198/reviews?hl=en-GB","posted_at_unix_micros":1742913838025597,"updated_at_unix_micros":1742913838025597,"language":"en","translated_lang":"","text_original":"This is one of the rarest gym in Chennai where you can get real workouts and personal training for a reasonable fees.\nThis is entirely different from all other corporate gyms in Chennai. Worth for money.","text_translated":"","published_at":"2025-03-25T14:43:58.025597Z"}]</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP83" t="inlineStr"/>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AU83" t="inlineStr"/>
+      <c r="AV83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>43</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6690eb2b-bd5b-4db9-8027-79b4ce3d869d</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/SALT+Functional+Fitness/data=!4m7!3m6!1s0x3a5267ca61d26f19:0x59034e5123cd4ded!8m2!3d13.073299!4d80.247313!16s%2Fg%2F11wc5vkmgt!19sChIJGW_SYcpnUjoR7U3NI1FOA1k</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SALT Functional Fitness</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>3rd floor, SALT Functional Fitness, 28, Club Rd, M.S. Nagar, Chetpet, Chennai, Tamil Nadu 600031</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>{"Friday":["6–8 am","5:30–8:30 pm"],"Monday":["6–8 am","5:30–8:30 pm"],"Saturday":["6:30–7:30 am","4:30–5:30 pm"],"Sunday":["Closed"],"Thursday":["6–8 am","5:30–8:30 pm"],"Tuesday":["6–8 am","5:30–8:30 pm"],"Wednesday":["6–8 am","5:30–8:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>098432 85808</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>36FW+8W Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>35</v>
+      </c>
+      <c r="O84" t="n">
+        <v>5</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":35}</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>13.073299</v>
+      </c>
+      <c r="R84" t="n">
+        <v>80.24731300000001</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>6414056404705693165</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfXZj3jN3mrP-N4qV2s994MrV65GPtaU65DfWlCYaWRzv3DGrT9W6yIVPu9H7VcF7fEJFD-ZSWnNJP7rSvjClCWFXt3pq_-OzfkoYaWPcPNprDten6eupvz22UArbqTdEGBqb94GNuLhTPR=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>0x3a5267ca61d26f19:0x59034e5123cd4ded</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>ChIJGW_SYcpnUjoR7U3NI1FOA1k</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>{"id":"109844532793319141525","name":"SALT Functional Fitness (Owner)","link":"https://www.google.com/maps/contrib/109844532793319141525"}</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>{"borough":"M.S. Nagar, Chetpet","street":"3rd floor, 28, Club Rd","city":"Chennai","postal_code":"600031","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>[{"Name":"Ra Ra","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUE-AArki1S7Xtyb64S8BrDaXURidqUiPPJy4X-cQJEvYtuNq4=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Highly recommend SALT. Friendly workout space and a good trainer! In six months of going 2-3 times a week, I have seen surprisingly good results in strength and also reduced belly fat. I started with no recent experience and after a 3 year break and was able to get there thanks to the varied workouts (different each day) that target different muscle groups in rotation. No unbelievable promises and unscientific methods, Coach keeps the sessions focused on building strength steadily and consistently with the right exercises above all.  A friendly group that works out here helps build community and every now and again there are social events and nights out. Overall a great place to focus on your fitness.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2poWE1XSnVialJwZERCS1oxQjFjemcwWTBsV2FYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102198954011265431895/reviews?hl=en-GB","posted_at_unix_micros":1780126055055276,"updated_at_unix_micros":1780126102098973,"language":"en","translated_lang":"","text_original":"Highly recommend SALT. Friendly workout space and a good trainer! In six months of going 2-3 times a week, I have seen surprisingly good results in strength and also reduced belly fat. I started with no recent experience and after a 3 year break and was able to get there thanks to the varied workouts (different each day) that target different muscle groups in rotation. No unbelievable promises and unscientific methods, Coach keeps the sessions focused on building strength steadily and consistently with the right exercises above all.  A friendly group that works out here helps build community and every now and again there are social events and nights out. Overall a great place to focus on your fitness.","text_translated":"","published_at":"2026-05-30T07:27:35.055276Z"},{"Name":"Preethi Dugar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXHEI1lQyCXz6-T-HFiCeulXbux-6xNosnisD861JEqN192xoSvDQ=s120-c-rp-mo-br100","Rating":5,"Description":"The best part of my day = workout time at Salt Fitness Community.. Partner workouts, station drills, game workouts,it’s all about group energy..Murgi Sir knows how to make us sweat and smile at the same time.This is the one place where workouts never feel boring.. Every session feels different and exciting. He keeps everyone motivated and makes fitness enjoyable rather than a routine..Thanks to Coach Murgi Sir for making fitness so much fun🔥","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25wcFdXMVZTRGxTZFdWSU9VaFFWa1JTWldsaFlsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118246802737528429175/reviews?hl=en-GB","posted_at_unix_micros":1772726068321852,"updated_at_unix_micros":1772726068321852,"language":"en","translated_lang":"","text_original":"The best part of my day = workout time at Salt Fitness Community.. Partner workouts, station drills, game workouts,it’s all about group energy..Murgi Sir knows how to make us sweat and smile at the same time.This is the one place where workouts never feel boring.. Every session feels different and exciting. He keeps everyone motivated and makes fitness enjoyable rather than a routine..Thanks to Coach Murgi Sir for making fitness so much fun🔥","text_translated":"","published_at":"2026-03-05T15:54:28.321852Z"},{"Name":"Debashree Chandra","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocIGR2qbjHf-xba7F-GXuAePh8SocN8sdtvBTfGajkOH9foAxg=s120-c-rp-mo-br100","Rating":5,"Description":"Joining salt is one of the Best decisions I have made in the recent past. A judgement free, friendly and welcoming zone with wholesome workout sessions which are different everyday so it doesn’t get mundane. Coach Murugappan is an extremely friendly and approachable person who helps you achieve your goals without having to compete with anyone else.\nIt’s a fun group as well to workout with","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pOTVZGWnllRVUzZUV0aVIxWjFhVlpRU3padGJYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115392565436403727121/reviews?hl=en-GB","posted_at_unix_micros":1772798500175933,"updated_at_unix_micros":1772798500175933,"language":"en","translated_lang":"","text_original":"Joining salt is one of the Best decisions I have made in the recent past. A judgement free, friendly and welcoming zone with wholesome workout sessions which are different everyday so it doesn’t get mundane. Coach Murugappan is an extremely friendly and approachable person who helps you achieve your goals without having to compete with anyone else.\nIt’s a fun group as well to workout with","text_translated":"","published_at":"2026-03-06T12:01:40.175933Z"},{"Name":"Salma Seyed","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocILq77qTZvjovxn1z6CvckhW5arEkI_nefVP0Q5iEqNv5Qtweo=s120-c-rp-mo-br100","Rating":5,"Description":"3 years in, and I’m still hooked. This isn’t your typical gym where you just clock in and out. It’s a real community! The programming is fresh every single day, keeping you on your toes. A huge part of that is Murgi. He’s a standout coach who pays actual attention to your progress, pushes you to your potential, and ensures you leave feeling accomplished. The positive vibe here is completely contagious and exactly what you need for a great start to the day❤️","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25oZmF6bEhiSEYzTjIwMVdqSjFWbVZ0U0hwSVptYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102940554267756904478/reviews?hl=en-GB","posted_at_unix_micros":1772721158346932,"updated_at_unix_micros":1772721158346932,"language":"en","translated_lang":"","text_original":"3 years in, and I’m still hooked. This isn’t your typical gym where you just clock in and out. It’s a real community! The programming is fresh every single day, keeping you on your toes. A huge part of that is Murgi. He’s a standout coach who pays actual attention to your progress, pushes you to your potential, and ensures you leave feeling accomplished. The positive vibe here is completely contagious and exactly what you need for a great start to the day❤️","text_translated":"","published_at":"2026-03-05T14:32:38.346932Z"},{"Name":"Meena M","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLhvNz1SPPnSw5S5qoAn4f30WCyXdgav6HmnSdd50h1-fDcsw=s120-c-rp-mo-br100","Rating":5,"Description":"I’ve been training with Murgi @ SALT Fitness for almost four years now. I always look forward to his sessions because they’re never repetitive or boring. I can’t imagine doing the volume of workouts I complete in class on my own—without his guidance, I probably wouldn’t even manage 50% of it. 💪","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21RelkwNXZNMHh5Wm5sRmFXTkJNRGxaV0c5SlIxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116084162368989159008/reviews?hl=en-GB","posted_at_unix_micros":1772798110629400,"updated_at_unix_micros":1772798110629400,"language":"en","translated_lang":"","text_original":"I’ve been training with Murgi @ SALT Fitness for almost four years now. I always look forward to his sessions because they’re never repetitive or boring. I can’t imagine doing the volume of workouts I complete in class on my own—without his guidance, I probably wouldn’t even manage 50% of it. 💪","text_translated":"","published_at":"2026-03-06T11:55:10.6294Z"}]</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AU84" t="inlineStr"/>
+      <c r="AV84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>43</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3443ec21-504f-4465-9e7d-5470d56e0e66</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/XS7+Strength+and+Conditioning/data=!4m7!3m6!1s0x3a525f2b6f408049:0xe7ab21c4fa7223af!8m2!3d13.0750083!4d80.169142!16s%2Fg%2F11kk8d70sw!19sChIJSYBAbytfUjoRryNy-sQhq-c</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>XS7 Strength and Conditioning</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>No 75, SPR Sports Academy, 1st Cross Street, Sriram Nagar Main Rd, Nolambur, Chennai, Tamil Nadu 600095</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30–7:30 am"],"Monday":["5:30–7:30 am"],"Saturday":["Closed"],"Sunday":["Closed"],"Thursday":["5:30–7:30 am"],"Tuesday":["5:30–7:30 am"],"Wednesday":["5:30–7:30 am"]}</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>087782 34435</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>35G9+2M Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>34</v>
+      </c>
+      <c r="O85" t="n">
+        <v>5</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":34}</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>13.075008</v>
+      </c>
+      <c r="R85" t="n">
+        <v>80.16914199999999</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>16693473573677966255</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcUqudGKZ5_X1xV0zC9fS2NSLx34MuX2Fy4ONvvfk6WQs6K2pZL8_ZaEvjE4bliqF8IYumywGFhGhHoP4yepc_z_t7sRFKfUKQCqWuI5qLOuU_P9PVptPaAOM-plMMSWhtv_dWW=w426-h240-k-no</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>0x3a525f2b6f408049:0xe7ab21c4fa7223af</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>ChIJSYBAbytfUjoRryNy-sQhq-c</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>{"id":"110904486644796261169","name":"XS7 Strength and Conditioning (Owner)","link":"https://www.google.com/maps/contrib/110904486644796261169"}</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>{"borough":"Nolambur, Ambattur Industrial Estate","street":"No 75, SPR Sports Academy, 1st Cross Street, Sriram Nagar Main Rd","city":"Chennai","postal_code":"600095","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>[{"Name":"Manas Karkal","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVUtGXyYN-yJ8Ryyd3C9DxsOFGummft0rhAnxP0IrBSipgjPn-q=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This fitness center is a true gem! The coach's expertise is remarkable, making workouts highly effective. The sessions are enjoyable, with the coach's energy and creativity keeping you engaged. It's the perfect place to achieve fitness goals while having a great time!\n\nI have been training under Krishna Sir for around 5 to 6 years, and I have to say, he is one of the best coaches that I have trained under. He is highly qualified and vastly experienced in helping athletes train for various sports like badminton, cricket, football, etc. You should come here!!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfXtJawNEVMYfPOQx-1lldOK8_RJ_4uUeEIyZOwaL72rT-3c_RmRk9EjGgsp8iU-YY2d9SEtZyYL-Buxy6uVqPa1-9G2HLTHFhugWuqYWgUIfmvV-e9_LyILHUcXHPisdQrRwmo=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcWZNVZnUWgemvHV7TbWUp8gMldpmT0WyZqure62gWbopCPkNpdYwawbS3Wa7DbHktGnB-AO1UBKPPmyIHhBnMsP8wo4oTkSzHx7BZWL_jNxQPGoVTyY2gP06M69UZBGc0a8EIE=k-no"],"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUN4NU0yMmJREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115357676536066844267/reviews?hl=en-GB","posted_at_unix_micros":1683782008019128,"updated_at_unix_micros":1683782539435304,"language":"en","translated_lang":"","text_original":"This fitness center is a true gem! The coach's expertise is remarkable, making workouts highly effective. The sessions are enjoyable, with the coach's energy and creativity keeping you engaged. It's the perfect place to achieve fitness goals while having a great time!\n\nI have been training under Krishna Sir for around 5 to 6 years, and I have to say, he is one of the best coaches that I have trained under. He is highly qualified and vastly experienced in helping athletes train for various sports like badminton, cricket, football, etc. You should come here!!","text_translated":"","reply_text_original":"Thank you manas. It's my pleasure to help athletes like you.","reply_language":"en","reply_posted_at_unix_micros":1684487809000000,"reply_updated_at_unix_micros":1684487809000000,"published_at":"2023-05-11T05:13:28.019128Z"},{"Name":"Charles Darwin","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUhnv0n_g3xtCUmWrNLiTRvbZHcO2C3x09MyxRQxG47P5_ki-99=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Coach Krishna’s strength and conditioning sessions for my 10-year-old son and 7-year-old daughter have been outstanding for their badminton fitness goals. The daily 1.5-hour early morning sessions combine engaging physical routines, focusing on fundamental movement, age-appropriate strength training, and agility, as well as core badminton footwork and racket skills. The weekly program is very well-balanced, with gym-based strength training twice a week and three days of dynamic on-ground workouts, ensuring both muscle development and sport-specific conditioning.\n\nCoach Krishna utilizes fun, motivating drills and makes sure the exercises are suited to each child’s age and skill level. My children have shown clear improvements in speed, strength, and confidence on the badminton court, and look forward to each session. Highly recommended for parents seeking a structured, supportive, and professional approach to fitness and sports training for young badminton players.","Images":null,"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xBemNVa3lkWFJqTTI1cmJFUTJVSEozVVZKR01VRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107201470398286602951/reviews?hl=en-GB","posted_at_unix_micros":1761567903391367,"updated_at_unix_micros":1761567903391367,"language":"en","translated_lang":"","text_original":"Coach Krishna’s strength and conditioning sessions for my 10-year-old son and 7-year-old daughter have been outstanding for their badminton fitness goals. The daily 1.5-hour early morning sessions combine engaging physical routines, focusing on fundamental movement, age-appropriate strength training, and agility, as well as core badminton footwork and racket skills. The weekly program is very well-balanced, with gym-based strength training twice a week and three days of dynamic on-ground workouts, ensuring both muscle development and sport-specific conditioning.\n\nCoach Krishna utilizes fun, motivating drills and makes sure the exercises are suited to each child’s age and skill level. My children have shown clear improvements in speed, strength, and confidence on the badminton court, and look forward to each session. Highly recommended for parents seeking a structured, supportive, and professional approach to fitness and sports training for young badminton players.","text_translated":"","reply_text_original":"Thank you so much for sharing this detailed and thoughtful feedback. It means a lot to hear that your children are enjoying the sessions and progressing so well in their badminton fitness journey.\n\nWe design every program with the goal of building strong fundamentals, improving athletic qualities, and most importantly—helping young athletes enjoy the process. Your kids’ enthusiasm, consistency, and positive attitude make coaching them a pleasure.\n\nI’m happy to see their improvements in strength, speed, confidence, and overall movement quality. We’ll continue to support them with structured, age-appropriate training that keeps them motivated and growing in the right direction.\n\nThank you again for trusting me with their development!","reply_language":"en","reply_posted_at_unix_micros":1763966860000000,"reply_updated_at_unix_micros":1763966860000000,"published_at":"2025-10-27T12:25:03.391367Z"},{"Name":"AnjanaShree Mart","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKY_2k3baluejHGZtO0EnKgL-7zAiY4Oh6J02W6QpwfIpybvQ=s120-c-rp-mo-br100","Rating":5,"Description":"I've had an amazing experience working with XS7 Strength and Conditioning coach. His expertise, attention to detail, and personalized workout plans have significantly improved my fitness. Mr Ananda Krishnan is incredibly motivational and creates a positive training environment that pushes you to achieve your goals. They're approachable, supportive, and genuinely care about your progress. I highly recommend Mr Ananda Krishnan to anyone looking for an exceptional coach.\n-Yuvi","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfnJb0m59-IW3kMi5sWwr54AWkAFfV1JHEsx-gAm8BOJgvRtSvt40GLgy-ruI26DyOPX9d7UZLL7-gthV6FZr_uoWz2PSa17fxyo8sy0xBziTfUhzet_i_ZMFl6HQkwMh6VzCWadQ=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLd15IxmzW5QGl6nNWlpmB45UssAvBcYkNUE61U2ep-OLqwSkqTKh5G4mpAji27KOJ4EXtZbownPWTPEivGak4iJ--ZXfq7ZU9oEp3YegDrAN7QoFIvzzkNNpzvwRqmWPKDPGNZ7=k-no"],"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURib3VhdkJREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116263967845365521534/reviews?hl=en-GB","posted_at_unix_micros":1722693010274400,"updated_at_unix_micros":1722693010274400,"language":"en","translated_lang":"","text_original":"I've had an amazing experience working with XS7 Strength and Conditioning coach. His expertise, attention to detail, and personalized workout plans have significantly improved my fitness. Mr Ananda Krishnan is incredibly motivational and creates a positive training environment that pushes you to achieve your goals. They're approachable, supportive, and genuinely care about your progress. I highly recommend Mr Ananda Krishnan to anyone looking for an exceptional coach.\n-Yuvi","text_translated":"","reply_text_original":"Hi Yuvi,\n\nThank you so much for your wonderful feedback! I’m thrilled to hear that you’ve had an amazing experience with XS7 Strength and Conditioning. Your progress and satisfaction are our top priorities, and it’s incredibly rewarding to see the positive impact of our training together.\n\nI appreciate your kind words about my coaching style and the training environment we strive to create. It’s a privilege to work with dedicated athletes like you, and your commitment to your fitness goals is truly inspiring.\n\nThank you for recommending me to others! I’m excited to continue supporting you on your journey and helping you reach even greater achievements.\n\nRegards","reply_language":"en","reply_posted_at_unix_micros":1728981412000000,"reply_updated_at_unix_micros":1728981412000000,"published_at":"2024-08-03T13:50:10.2744Z"},{"Name":"Sundar G","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXxPKQXwdY3LWDwZb9GWFLjV9DDgUCEMfVjHJU6ZiND2SQti3qZrQ=s120-c-rp-mo-br100","Rating":5,"Description":"I have been training with XS7 Strength and Conditioning for the last 4 months from the Netherlands, focusing on improving my performance in cricket. The results have been nothing short of phenomenal. My overall performance and physical conditioning have seen a significant boost, which has translated to better on-field results.\n\nBeing an all-rounder, I previously struggled with fitness and recovery, often finding myself completely drained and immobile after match days. However, under the expert guidance of my trainer Krishna, I've noticed a remarkable improvement in both my fitness levels and recovery rate. Krishna's support, motivation, and tailored training programs have been instrumental in this transformation.\n\nAs proof of my improved performance, I'd like to share my progress in a 3K run. When I started training with XS7 Strength and Conditioning 4 months ago, my 3K run time was considerably slower. Last week, I ran the same distance and saw a significant improvement in my time. This tangible progress is a testament to the effectiveness of the training program and the dedication of my trainer.\n\nThanks to XS7 Strength and Conditioning, I am now able to push myself harder on the field and recover quickly, allowing me to perform at my best consistently. I am incredibly grateful for Krishna's dedication and expertise, and I look forward to continuing my journey with XS7 Strength and Conditioning to keep improving. Highly recommended!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfQPsXzCF9eKl-kcHuK3RWL7S8ISvE8xNUNEC1K9o5zTy9Lv2pwbIf1uxwSt_IR0rxDLMCsve-pq61EsdcYTFCbJb8J_Nd_1LRFtMyD2kmHQ__5qdEZw-lchldVxaTOR4WcJdx1nA=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcF7ZZivSoGqhgSr4jZFb3jYMSfcrymQR7aqGiB9JDoVsQngUg9oDDMbgacR-v7tbBcbN2fihDA_lYJkCW220WxhFftqUyRLKYO0uU5bUxEh3SucUMtGqixfdIqcTGSLjSVoPq1=k-no"],"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURidG9lQkJBEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102642511052365587983/reviews?hl=en-GB","posted_at_unix_micros":1722849475340642,"updated_at_unix_micros":1722850190428298,"language":"en","translated_lang":"","text_original":"I have been training with XS7 Strength and Conditioning for the last 4 months from the Netherlands, focusing on improving my performance in cricket. The results have been nothing short of phenomenal. My overall performance and physical conditioning have seen a significant boost, which has translated to better on-field results.\n\nBeing an all-rounder, I previously struggled with fitness and recovery, often finding myself completely drained and immobile after match days. However, under the expert guidance of my trainer Krishna, I've noticed a remarkable improvement in both my fitness levels and recovery rate. Krishna's support, motivation, and tailored training programs have been instrumental in this transformation.\n\nAs proof of my improved performance, I'd like to share my progress in a 3K run. When I started training with XS7 Strength and Conditioning 4 months ago, my 3K run time was considerably slower. Last week, I ran the same distance and saw a significant improvement in my time. This tangible progress is a testament to the effectiveness of the training program and the dedication of my trainer.\n\nThanks to XS7 Strength and Conditioning, I am now able to push myself harder on the field and recover quickly, allowing me to perform at my best consistently. I am incredibly grateful for Krishna's dedication and expertise, and I look forward to continuing my journey with XS7 Strength and Conditioning to keep improving. Highly recommended!","text_translated":"","reply_text_original":"Dear Sundar,\n\nThank you so much for your kind words and for sharing your journey with XS7 Strength and Conditioning! It’s incredibly rewarding to hear about the significant improvements you’ve made in both your fitness levels and on-field performance.\n\nYour dedication and hard work have been key to this transformation, and I’m thrilled to see the results, especially your impressive progress in the 3K run. It’s always a pleasure to witness athletes like you pushing their limits and achieving new milestones.\n\nI’m looking forward to continuing this journey together and helping you reach even greater heights in your cricket performance. Your success is our success, and I truly appreciate your trust in our training programs.\n\nThanks again for the wonderful feedback!\n\nBest,\nKrishna","reply_language":"en","reply_posted_at_unix_micros":1728981251000000,"reply_updated_at_unix_micros":1728981251000000,"published_at":"2024-08-05T09:17:55.340642Z"},{"Name":"Latha Balasubramaniyam","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVC-oI60Col2FVQOkBwyeFmB4rGwhnEYGMB_aaBPoyCpm6K-AUQ=s120-c-rp-mo-br100","Rating":5,"Description":"XS7 is an excellent place for fitness training, and that Coach Krishna Sir is highly skilled in training athletes for various sports. He provides personal attention to every athlete and has been training my kids for the past 6 years.\nI believe that XS7 and Coach Krishna Sir have played a crucial role in my kids' athletic development and that it's the best place for athletes to achieve their goals.","Images":null,"When":"3 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUR4anV5Nk13EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104073157452930250714/reviews?hl=en-GB","posted_at_unix_micros":1686197840912705,"updated_at_unix_micros":1686197840912705,"language":"en","translated_lang":"","text_original":"XS7 is an excellent place for fitness training, and that Coach Krishna Sir is highly skilled in training athletes for various sports. He provides personal attention to every athlete and has been training my kids for the past 6 years.\nI believe that XS7 and Coach Krishna Sir have played a crucial role in my kids' athletic development and that it's the best place for athletes to achieve their goals.","text_translated":"","reply_text_original":"Thank you madam!!","reply_language":"en","reply_posted_at_unix_micros":1686810918000000,"reply_updated_at_unix_micros":1686810918000000,"published_at":"2023-06-08T04:17:20.912705Z"}]</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr"/>
+      <c r="AO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP85" t="inlineStr"/>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AU85" t="inlineStr"/>
+      <c r="AV85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>43</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Crucible+Barbell/data=!4m7!3m6!1s0x3a5267ceccf85bdd:0x5b4efeb7e1287af0!8m2!3d13.0314243!4d80.2530746!16s%2Fg%2F11xckpvz5v!19sChIJ3Vv4zM5nUjoR8Hoo4bf-Tls</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Crucible Barbell</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Abhiramapuram 4th St, Alwarpet, Chennai, Tamil Nadu 600018</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–8 pm"],"Monday":["6 am–8 pm"],"Saturday":["6 am–8 pm"],"Sunday":["Closed"],"Thursday":["6 am–8 pm"],"Tuesday":["6 am–8 pm"],"Wednesday":["6 am–8 pm"]}</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>098840 69025</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>27J3+H6 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>25</v>
+      </c>
+      <c r="O86" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":3,"5":22}</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>13.031424</v>
+      </c>
+      <c r="R86" t="n">
+        <v>80.253075</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>6579476171344870128</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLczXnSh999w3ZtGYi-_tVHe1FiWl9nCtCVc4PY4FYVfa5LLF-E4LgHHKW5jpvwyOn2C6yk30gbFWNZ42ytV3UvGSotpLNfAAv1bBmGw3tWZq6T2PJ3r6au7gwjp2Q9YzsGWce_t_oJOp8lm=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>0x3a5267ceccf85bdd:0x5b4efeb7e1287af0</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>ChIJ3Vv4zM5nUjoR8Hoo4bf-Tls</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>{"id":"104631463596559828809","name":"Crucible Barbell (Owner)","link":"https://www.google.com/maps/contrib/104631463596559828809"}</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>{"borough":"Alwarpet","street":"Abhiramapuram 4th St","city":"Chennai","postal_code":"600018","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Assistive hearing loop","enabled":false},{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false},{"name":"Wheelchair-accessible seating","enabled":false},{"name":"Wheelchair-accessible toilet","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>[{"Name":"Abishek","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXoR7fbeTk5sKppOlnRV0L9ESmUbJsc2Wx-j_Y5YjRLVdplA2oF_w=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Kid in a candy shop is the feeling you get with crucible\n\nCrucible is an ideal place to train any sort of iron sport be it Powerlifting , Olympic weightlifting , Strong man or general fitness.\n\nHaving around 5 platforms , multiple squat racks , dedicated power rack and 1000 kg+ weights in variety of old-school plates , Competition bumpers , Regular Bumpers , ELEIKO powerlifting plates AND barbells\nand a selection of speciality barbell !! - They have it all\n\nThis place have made me hit several PRs and have had a ton of fun while doing it with my Team\n\nThe place is super clean well maintained and the washroom area is incredible as well\n\nIn Short this place is built with immense passion to serve all\n\nI primarily train for Powerlifting with Team GULCH under Head coach Aaqib and he is phenomenal !!He is the man if you want to unleash the best version of yourself - His nuances and his expertise is unmatched in the field","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcoULHtGeX28bQxIM_UUzWnWkrYkZaGIVTihPAbxUxO-MCBz2K7EdijEOKnTGpsDHgNFTcL85Zaz-bCnY4VdnvUQBRU9vnekdwFUtN4g7lNGylYlSZ-Gr8Uy-StSVLM8VVZrwX-AQU2bWWg=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLc6Xvo_lywV6ywa286q2u0ZAXyWOmtEbti2-Xodlu7ZlMdYR82AdBE6sep2Dy0cIK-jQSaTMxjLTI2g6icMifSl6XzXj7SR1sS8xzRh-UZaLR3vbDPAp5r38X9uYrFgVrUdfnhi16o1HWn0=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfmTDrC9fGmQ4tWx95csAUtNvF-d9Q2FiYqSxpMzhhsaMfT2d1Z98kI4GKcQ7PIYWDlXWNpQkF-bNeoTa6D6nXY-3zIpfJigH5UQWnLgpkQvrhUrCrjFnG4RotaqsVPzshJz6-Li0VX4Zo=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLczXnSh999w3ZtGYi-_tVHe1FiWl9nCtCVc4PY4FYVfa5LLF-E4LgHHKW5jpvwyOn2C6yk30gbFWNZ42ytV3UvGSotpLNfAAv1bBmGw3tWZq6T2PJ3r6au7gwjp2Q9YzsGWce_t_oJOp8lm=k-no"],"When":"Edited 10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT205cU9UbG9XSEpFY3pac1UzVjZla2wxWlRkelVXYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113311668608391108804/reviews?hl=en-GB","posted_at_unix_micros":1752422610353416,"updated_at_unix_micros":1764066402933309,"language":"en","translated_lang":"","text_original":"Kid in a candy shop is the feeling you get with crucible\n\nCrucible is an ideal place to train any sort of iron sport be it Powerlifting , Olympic weightlifting , Strong man or general fitness.\n\nHaving around 5 platforms , multiple squat racks , dedicated power rack and 1000 kg+ weights in variety of old-school plates , Competition bumpers , Regular Bumpers , ELEIKO powerlifting plates AND barbells\nand a selection of speciality barbell !! - They have it all\n\nThis place have made me hit several PRs and have had a ton of fun while doing it with my Team\n\nThe place is super clean well maintained and the washroom area is incredible as well\n\nIn Short this place is built with immense passion to serve all\n\nI primarily train for Powerlifting with Team GULCH under Head coach Aaqib and he is phenomenal !!He is the man if you want to unleash the best version of yourself - His nuances and his expertise is unmatched in the field","text_translated":"","published_at":"2025-07-13T16:03:30.353416Z"},{"Name":"Sharun A","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVVZJYPV4KqDFFjVhOnkFxUy0Qk7FywR-spY8GY3p-1BsGX3ENopg=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"A Lifter’s Haven\n\nThe perfect gym for all kinds of lifters. I primarily train in powerlifting, and this space is absolutely ideal for it. I’ve also had strongman and Olympic weightlifting sessions here, which speaks volumes about how well-equipped the gym is across disciplines. Whether you're into strength sports or just lifting heavy, Crucible has everything you need.\n\nMultiple platforms mean there’s never a bottleneck, even when groups or multiple lifters are training simultaneously. The coaches? Easily some of the best in town. They bring deep, scientific,  practical knowledge of lifting that truly sets the gym apart.\n\nOne of my favorite parts of Crucible is the community, it’s filled with like-minded lifters and athletes who bring a great energy to the space. It’s friendly, motivating, and gives you that MENTAL PUMP to push yourself.\n\nWhile it's a dream setup for advanced lifters, the coaches do a phenomenal job of making it accessible and effective for beginners and general fitness enthusiasts as well.\n\nAlso, a quick shoutout to how well-maintained the facility is. As someone who notices the little things, the washroom facilities are a solid 10/10. And being located in the city center makes it super convenient for just about anyone.\n\nShoutout to Aaqib who's the head coach and a phenomenal lifter.\n\nOverall, Crucible is more than just a gym, \"it’s a LIFTER's HAVEN\"","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLfh4PdBA2wMrvVNwh4DY5wgL4rMVo9ZRGYjltCv0yzMCxJycUmUkQRLcUyYOVkms_M98rpTDhsl9XXl_TyqqC2qXV1FcTHbLURCSO4kYMKg2DBiqJSiZJCnvlnvTxPTdZRRSnip=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfmV33LHIN-sylF5vFJa59j5EqgXeTSEC9FnVgKrd5-x5voQYhZx3Vjf9exfCkpTybaTMGotONM5C3J1xDkM6ou9-_qzWS6VBlhq5HjnYiXmLexPi94KqoTzGcx3qu5J2Anm3nJ=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcQXn5mZSznc_XAErpdsPnuzg9FeiC67f-hWVOefTvOKZKiHT7iotB31FDxHyQcyhycjemMECZhn6T2woStFbWDLKpxv0kOKB6oRMofJU3yRKDkSXcPSh61UuMMgU_8f6aPovV8=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfOhBOzD_9ZAqJSMC9RTjsv0As98eIy_hPRXDzLL0Nc08uF4iQk4DzwBDRi0qydV7ftGZTKfYrE3s3sCejfGd30kpnFeHG9PddPf8_3s7kewKq2fzm37HVsXRu0A5SajuTZgPPY=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeT6vxAsGrMqKervfVNO_WkRQxnTnFmSlWkhv4z324wW4OJwaSdV3xgAtOLyfplBjDJ0PhZaMkQRuea_EuJEPVtpg_-HsbPJQYz0_CVVNuq4d7D65VevQ19hUGsagZM1_E6X5Hs=k-no"],"When":"Edited a year ago","review_id":"ChdDSUhNMG9nS0VOdmwyX0xjamItOHh3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116284978014918175007/reviews?hl=en-GB","posted_at_unix_micros":1747897509246402,"updated_at_unix_micros":1751117162258131,"language":"en","translated_lang":"","text_original":"A Lifter’s Haven\n\nThe perfect gym for all kinds of lifters. I primarily train in powerlifting, and this space is absolutely ideal for it. I’ve also had strongman and Olympic weightlifting sessions here, which speaks volumes about how well-equipped the gym is across disciplines. Whether you're into strength sports or just lifting heavy, Crucible has everything you need.\n\nMultiple platforms mean there’s never a bottleneck, even when groups or multiple lifters are training simultaneously. The coaches? Easily some of the best in town. They bring deep, scientific,  practical knowledge of lifting that truly sets the gym apart.\n\nOne of my favorite parts of Crucible is the community, it’s filled with like-minded lifters and athletes who bring a great energy to the space. It’s friendly, motivating, and gives you that MENTAL PUMP to push yourself.\n\nWhile it's a dream setup for advanced lifters, the coaches do a phenomenal job of making it accessible and effective for beginners and general fitness enthusiasts as well.\n\nAlso, a quick shoutout to how well-maintained the facility is. As someone who notices the little things, the washroom facilities are a solid 10/10. And being located in the city center makes it super convenient for just about anyone.\n\nShoutout to Aaqib who's the head coach and a phenomenal lifter.\n\nOverall, Crucible is more than just a gym, \"it’s a LIFTER's HAVEN\"","text_translated":"","published_at":"2025-05-22T07:05:09.246402Z"},{"Name":"Preeti Mangala Shekar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWwK7QZcPbaxOPP69u7fdmieBiUJUSeEnlWni3L2M4xRIzLg8uF=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great place to get into the fitness groove..supportive community, very patient and effective trainers and good equipment. Highly recommend for people who need gentle hand holding to find their fitness groove. Ask for Usman for personal training and guidance - he is awesome!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2sxS1RGZEhhMHBqYm1KRGRYTmhOblIxWVZGdk1YYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114649298891400173762/reviews?hl=en-GB","posted_at_unix_micros":1777022665361924,"updated_at_unix_micros":1777022665361924,"language":"en","translated_lang":"","text_original":"Great place to get into the fitness groove..supportive community, very patient and effective trainers and good equipment. Highly recommend for people who need gentle hand holding to find their fitness groove. Ask for Usman for personal training and guidance - he is awesome!","text_translated":"","published_at":"2026-04-24T09:24:25.361924Z"},{"Name":"vishnoo","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJD1w0jmCNCB_zBzwXRjroeZ2N4ip2Ms4C687hJ-DGR1XmsTQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Crucible is hands down one of the best gyms I've ever trained at. The facility is incredibly well-equipped, with multiple squat platforms that make it easy to train without waiting around for equipment. Whether you're focused on powerlifting or Olympic lifting, this gym has everything you need.\n\nWhat really sets Crucible Barbell apart is the professionalism and expertise of the coaches. Everyone here clearly knows their stuff, from technical lifts to programming advice, you’re in great hands. Their knowledge of weightlifting and Olympic lifting is top-tier, and they create an environment that’s both welcoming and serious about progress.\n\nIf you're looking for a place where you can truly focus on your lifting, be coached by knowledgeable professionals, and train in a high-quality environment, Crucible is the place to go.","Images":null,"When":"a year ago","review_id":"ChdDSUhNMG9nS0VNT0l4b0xtamFtVDhnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102235659504847016565/reviews?hl=en-GB","posted_at_unix_micros":1746972784346747,"updated_at_unix_micros":1746973135230835,"language":"en","translated_lang":"","text_original":"Crucible is hands down one of the best gyms I've ever trained at. The facility is incredibly well-equipped, with multiple squat platforms that make it easy to train without waiting around for equipment. Whether you're focused on powerlifting or Olympic lifting, this gym has everything you need.\n\nWhat really sets Crucible Barbell apart is the professionalism and expertise of the coaches. Everyone here clearly knows their stuff, from technical lifts to programming advice, you’re in great hands. Their knowledge of weightlifting and Olympic lifting is top-tier, and they create an environment that’s both welcoming and serious about progress.\n\nIf you're looking for a place where you can truly focus on your lifting, be coached by knowledgeable professionals, and train in a high-quality environment, Crucible is the place to go.","text_translated":"","published_at":"2025-05-11T14:13:04.346747Z"},{"Name":"vijay sharma","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXshspooBEc485yvK4FVouB7ObLkpiJ1fShSCCQXu8haMSA-aVMng=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Very good strengthening place. Mr. Manick and team is excellent in their handling of the facility. Their subject knowledge is very good and guidance is impeccable.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21rd2JtSlZlSEZEV0RSalZHeHJTa3QxVGsxbk1XYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116423678686585975373/reviews?hl=en-GB","posted_at_unix_micros":1787052305925956,"updated_at_unix_micros":1787052305925956,"language":"en","translated_lang":"","text_original":"Very good strengthening place. Mr. Manick and team is excellent in their handling of the facility. Their subject knowledge is very good and guidance is impeccable.","text_translated":"","published_at":"2026-08-18T11:25:05.925956Z"}]</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP86" t="inlineStr"/>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AU86" t="inlineStr"/>
+      <c r="AV86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>43</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Inshapez+crossfit/data=!4m7!3m6!1s0x3a52641790930905:0x9e18c09211039546!8m2!3d13.0843851!4d80.1940631!16s%2Fg%2F11fy_47x8q!19sChIJBQmTkBdkUjoRRpUDEZLAGJ4</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Inshapez crossfit</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Inshapez, Tiruvalleeswarar Nagar, Anna Nagar West, Anna Nagar West Extension, Chennai, Tamil Nadu 600040</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>072004 34700</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>35MV+QJ Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>25</v>
+      </c>
+      <c r="O87" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":0,"3":1,"4":2,"5":21}</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>13.084385</v>
+      </c>
+      <c r="R87" t="n">
+        <v>80.194063</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>11392066991016875334</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfEMV4lREMUTm8pzxR607FpLO4Nzdqx_CdBZIOacRBorEIVQP4M6mZ4NZUHkCwUecpKatM6C_ZrYOWj5NraymUqS3Im1xi0GU3VqZx8c4TSEwDmrHCAQZSMsd_-ucq4GipyEd-e=w408-h408-k-no</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>0x3a52641790930905:0x9e18c09211039546</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>ChIJBQmTkBdkUjoRRpUDEZLAGJ4</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>{"id":"116109617729977589346","name":"Inshapez crossfit (Owner)","link":"https://www.google.com/maps/contrib/116109617729977589346"}</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>{"borough":"Tiruvalleeswarar Nagar, Anna Nagar West, Anna Nagar West Extension","street":"Inshapez","city":"Chennai","postal_code":"600040","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>[{"Name":"sharan rajkumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU-HGsmXplL2MlsVjN0D_X5TzlfMpF7sMZvEoUQSf6zRIu4OyqI=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This gym without doubt is the best gym in Anna Nagar! Im gng to this gym for the past 4 months and I have already lost weight and so many changes in me! I highly recommend it. believe me if I say it's true I'm a frequent defaulter but I'm a regular to this gym","Images":null,"When":"8 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURRbnMyODV3RRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/107753296401400729694/reviews?hl=en-GB","posted_at_unix_micros":1535464473991363,"updated_at_unix_micros":1535464914754370,"language":"en","translated_lang":"","text_original":"This gym without doubt is the best gym in Anna Nagar! Im gng to this gym for the past 4 months and I have already lost weight and so many changes in me! I highly recommend it. believe me if I say it's true I'm a frequent defaulter but I'm a regular to this gym","text_translated":"","published_at":"2018-08-28T13:54:33.991363Z"},{"Name":"Manoj Shankar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWibHIqmSG0aKJT9F9UxZ-VhizDhWDOBCUSbrhoGUee2IsW600_mA=s120-c-rp-mo-br100","Rating":5,"Description":"Best gym to get motivation. Thumbs up to Ramesh master who is a qualified personal trainer. I strongly recommend this crossfit center.","Images":null,"When":"8 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUN3NnZfYWtRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114220034678800512601/reviews?hl=en-GB","posted_at_unix_micros":1535522273923277,"updated_at_unix_micros":1535522638434957,"language":"en","translated_lang":"","text_original":"Best gym to get motivation. Thumbs up to Ramesh master who is a qualified personal trainer. I strongly recommend this crossfit center.","text_translated":"","published_at":"2018-08-29T05:57:53.923277Z"},{"Name":"panchayath valapandal","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJOQfHvo496RCjpt9mLCdyYJWCzVtKpdiHYU4W3CitHEB2NuA=s120-c-rp-mo-br100","Rating":5,"Description":"Very useful for me and my kids\nAwesome workouts 🤗\nVery very intelligent trainer and nice person ... Good manner","Images":null,"When":"9 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNRb3ZLQzhRRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111431030915352029243/reviews?hl=en-GB","posted_at_unix_micros":1505914833087000,"updated_at_unix_micros":1505914930239000,"language":"en","translated_lang":"","text_original":"Very useful for me and my kids\nAwesome workouts 🤗\nVery very intelligent trainer and nice person ... Good manner","text_translated":"","published_at":"2017-09-20T13:40:33.087Z"},{"Name":"Lavanya Ranganathan","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJf7HJksmDSWlUIQBZqi9GSMcyyQeogfAUPMpA8PwiBLlKlxA=s120-c-rp-mo-br100","Rating":5,"Description":"It's entirely different from gym.. very useful for all.. customer friendly... So make use of it.. n be fit...","Images":null,"When":"8 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNnc19QMlJREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105972960437998545818/reviews?hl=en-GB","posted_at_unix_micros":1535462806464720,"updated_at_unix_micros":1535463340328483,"language":"en","translated_lang":"","text_original":"It's entirely different from gym.. very useful for all.. customer friendly... So make use of it.. n be fit...","text_translated":"","published_at":"2018-08-28T13:26:46.46472Z"},{"Name":"skm naveen","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW1cPlexsT_rHh_RjfRXc1DJ58AU0tDBC2tRqxZw0su6XxnHEQi=s120-c-rp-mo-br100","Rating":5,"Description":"It's totally different from gym.. Very useful for all.. Men, women, kids\nThank u inshapez...","Images":null,"When":"9 years ago","review_id":"ChRDSUhNMG9nS0VJQ0FnSURRd3RkdhAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/115006068946867528671/reviews?hl=en-GB","posted_at_unix_micros":1505914669467000,"updated_at_unix_micros":1505914739335000,"language":"en","translated_lang":"","text_original":"It's totally different from gym.. Very useful for all.. Men, women, kids\nThank u inshapez...","text_translated":"","published_at":"2017-09-20T13:37:49.467Z"}]</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AU87" t="inlineStr"/>
+      <c r="AV87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>43</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3443ec21-504f-4465-9e7d-5470d56e0e66</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/ELEVATE+CROSSFIT+GYM+%28personal+trainer%29/data=!4m7!3m6!1s0x3a5267ac26fbd87d:0x6610b88dc6190013!8m2!3d13.0231071!4d80.2126015!16s%2Fg%2F11w315xn0p!19sChIJfdj7JqxnUjoREwAZxo24EGY</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ELEVATE CROSSFIT GYM (personal trainer)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Fitness center</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>No.02, Punniyakoti St, West Saidapet, Vinayagapuram, Chennai, Tamil Nadu 600015</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>{"Friday":["5 am–9:30 pm"],"Monday":["5 am–9:30 pm"],"Saturday":["5–7:30 am"],"Sunday":["8 am–9:30 pm"],"Thursday":["5 am–9:30 pm"],"Tuesday":["5 am–9:30 pm"],"Wednesday":["5 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>082487 64622</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>26F7+62 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>24</v>
+      </c>
+      <c r="O88" t="n">
+        <v>5</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":24}</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>13.023107</v>
+      </c>
+      <c r="R88" t="n">
+        <v>80.21260100000001</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>7354581110549446675</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfRh9et8A52AEq2XNy8VfFamTtTDJ6iPS0vCngcEG4pfVd8R5RxPE1KxPRX04YPaN-Sv3VHWDvIWnJfkxl40J6rNVp4csLqFTCDTH9ku0jYSgl4FjYe0Vx-CMxoMrGPpTCMKaxX=w408-h726-k-no</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>0x3a5267ac26fbd87d:0x6610b88dc6190013</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>ChIJfdj7JqxnUjoREwAZxo24EGY</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>{"id":"101234565476177169732","name":"ELEVATE CROSSFIT GYM (personal trainer) (Owner)","link":"https://www.google.com/maps/contrib/101234565476177169732"}</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>{"borough":"West Saidapet, Vinayagapuram","street":"No.02, Punniyakoti St","city":"Chennai","postal_code":"600015","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>[{"Name":"arivazhagan srinivasan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVIqos3t07Z1Re671uDnwyNjzcOUB-2ZqcBC54Yx565RuTSW9IJVA=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"I joined this gym two months ago, and it’s been one of the best fitness experiences I’ve had.\n\nThe gym is owned and trained by Coach Vinayagam and Dr. Chitraselvan (Physiotherapist + Fitness Coach) — both are highly certified, extremely professional, and genuinely passionate about their clients’ progress.\n\nThey pay individual attention to every member, analyze posture and energy levels, and customize workouts based on each person’s capability. I really appreciate how they follow up daily and ensure you stay consistent.\n\nThe ambience is great — clean, well-organized, and filled with positive energy. It’s an excellent place to build strength, lose weight, and improve flexibility. Having a physio on-site is a huge bonus, especially if you have posture issues or body pain.\n\nThey also provide personal fitness and physio sessions at home, which is perfect for those who can’t make it to the gym.\n\nMinor note: parking is only on the roadside, and there’s no AC — but the ventilation and fans are more than enough.\n\nOverall, a fantastic gym with caring, skilled coaches. I’m thankful I found this place through Google — definitely worth joining if you’re serious about fitness and overall wellbeing! 💪","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLerCCUrJFlKWYI_jzqnCSB8dX5F_8ceZkmZZb-E-VuUn60lVbVgtrdDIvQeAlVflqbazsPtPtS0OLaviRJBvHA6l2flhwWw5tr_fok-Ejzcdkklv7j80HxLW6RxUtmKYttCAosijhMXLZQR=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLePF9mRU1s8aoocPSFiJCwuuElxZV7QOpLMAS-bGUSR6HdVcxctAjuKZ44AVZoRrAhzu_9yceVNTOJCVpyUrlfMbnx8BieyRs-A8N_Y-Br5A957UfeLclWdW3xMNN5-eBnuaygQ8kCVwH31=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcisbPO_iURURMMuHgsjWvW9Kfa7fMOVuqJ-ThkbZxiaHCCJMDD_I2Sd7Jb5jcwgYq48jWgKlt4Ajqv4aQKA-WpYNbnPb9r7TWzm1KGybJd-cswgl6LfBWGXNu7-0brrIPlquKi4SXXP5Gm=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfsnxnKti_Hx_tI9ip2L3hONIDhwSJLiU5R6pA0BmcST1SI77Mpdg82rQti_QzzgvquWxCJKEwZJHH00f2fAJHkXWifBRs_40EPGds8gd5AqrWEaQFVc5j2vQEhuR8q5OuzcNK6_qYUJR8=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdpBYxaoxddnP021H-kCO6RdMpDyAH2J1FY0msKqoqFRuElBKnu5UBxAOGgPJHvGPdYGU2saokmFdMNo6iH20fdQVur3WTUfg49Z2qwi0tpag_A3aufpopgymmN5oV9n-sciwBbjwI3Sf4=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLca4dRjjvjFvbY7ZuyTdX9PpaIqxGHiffl_ginOgJ5Q8zHict4VAH5k6DvRJI1KlfOQqs0jbK8AQLY_dwVBFAVozLCY6ZSymIn1nWFa2gBpZHYcIQX6qwXG27_-nNSDnALovyGCQiMVg3PL=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLcSv5sH52T2W9tS9CQoB0k7tmih2Is4suaoBFTTNcZ79C4c4PkaYz2diBnF8smDKTDmtsgJ031Mlqd1hdgZzbrDb9UcJHInXOPBXrUGxTND94uxA63P90y3VM4jbGB7Q39AQN8xivyun3c_=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLeIVajSeCdsvf9-UugOYWLU8Ir6RHOR1uh-OCvU2RgoUBa-PlHhg_lIw54gRmXEMLsuYo60KnUrwZ6_zC84Rwf-qL4wQlbRF4BydongwIl-Y-2uu767BQFE6JocMV4-fajSbe3mzGwMzzuQ=k-no"],"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21WS01tSnBjMGxFVFVNMlN6RXlZek5HTlVGSFJGRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103096840991916826415/reviews?hl=en-GB","posted_at_unix_micros":1761297326675973,"updated_at_unix_micros":1761297459728509,"language":"en","translated_lang":"","text_original":"I joined this gym two months ago, and it’s been one of the best fitness experiences I’ve had.\n\nThe gym is owned and trained by Coach Vinayagam and Dr. Chitraselvan (Physiotherapist + Fitness Coach) — both are highly certified, extremely professional, and genuinely passionate about their clients’ progress.\n\nThey pay individual attention to every member, analyze posture and energy levels, and customize workouts based on each person’s capability. I really appreciate how they follow up daily and ensure you stay consistent.\n\nThe ambience is great — clean, well-organized, and filled with positive energy. It’s an excellent place to build strength, lose weight, and improve flexibility. Having a physio on-site is a huge bonus, especially if you have posture issues or body pain.\n\nThey also provide personal fitness and physio sessions at home, which is perfect for those who can’t make it to the gym.\n\nMinor note: parking is only on the roadside, and there’s no AC — but the ventilation and fans are more than enough.\n\nOverall, a fantastic gym with caring, skilled coaches. I’m thankful I found this place through Google — definitely worth joining if you’re serious about fitness and overall wellbeing! 💪","text_translated":"","reply_text_original":"Thank you for taking the time to leave such a positive review. We’re delighted to hear that our service surpassed your expectations. Providing high-quality service is at the heart of everything we do, and your feedback reassures us that we’re on the right track. We truly appreciate your trust. Your feedback motivates us to continue delivering the best experience possible.💪🔥","reply_language":"en","reply_posted_at_unix_micros":1761306810000000,"reply_updated_at_unix_micros":1761306810000000,"published_at":"2025-10-24T09:15:26.675973Z"},{"Name":"NIVEDITHA R","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJnsrlsoZzF04Z_u4_oHEWYAus7SKqgo2f186eujmyAOA5kmQ=s120-c-rp-mo-br100","Rating":5,"Description":"After a long search i found this gym. One the best gym in this locality. The trainer Mr.Vinay is very knowledgeable and tends to our requirements keenly.  Everyday workouts are tailor made and individual attention is given. The gym environment feels safe and positive. I think i have found the right place for my workouts, really happy about it.","Images":null,"When":"a month ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwSVpYQlJWVFp1UVhnM1dERlJNelZpUlc1cVYwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116979095563668548870/reviews?hl=en-GB","posted_at_unix_micros":1788359764088898,"updated_at_unix_micros":1788359764088898,"language":"en","translated_lang":"","text_original":"After a long search i found this gym. One the best gym in this locality. The trainer Mr.Vinay is very knowledgeable and tends to our requirements keenly.  Everyday workouts are tailor made and individual attention is given. The gym environment feels safe and positive. I think i have found the right place for my workouts, really happy about it.","text_translated":"","reply_text_original":"Thank you so much for your wonderful and thoughtful review! 🙏\n\nWe’re truly happy to know that you found the right place for your fitness journey at Elevate CrossFit. Your kind words about the personalized workouts, individual attention, and positive gym environment mean a lot to us.\n\nAt Elevate CrossFit, we believe every member has different goals and requirements, so we focus on providing personalized training and consistent guidance.\n\nThank you once again for your trust and support. We look forward to helping you achieve your fitness goals! 💪\n\nStay consistent. Stay strong. Keep elevating!\n— Team Elevate CrossFit","reply_language":"en","reply_posted_at_unix_micros":1788362517000000,"reply_updated_at_unix_micros":1788362517000000,"published_at":"2026-09-02T14:36:04.088898Z"},{"Name":"Gopalakrishnan R","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX6NpjQAbT0-wgqM8KUtYf7wB06wjIdL6G-Grm8NTunB_t05I9j-w=s120-c-rp-mo-br100","Rating":5,"Description":"Elevate is an excellent institution . Vinay is a fantastic trainer who understands you and helps you develop your fitness in a periodical Mannar Even if you have half an hour he would make sure that you are making best use of the time","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xwcllVeDJkVk54V0RoRFNsTnZVMEpxTUZCSk5tYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104360873652326339449/reviews?hl=en-GB","posted_at_unix_micros":1784089883396370,"updated_at_unix_micros":1784092524892013,"language":"en","translated_lang":"","text_original":"Elevate is an excellent institution . Vinay is a fantastic trainer who understands you and helps you develop your fitness in a periodical Mannar Even if you have half an hour he would make sure that you are making best use of the time","text_translated":"","reply_text_original":"Thank you so much for your valuable review! We truly appreciate your support and are delighted to hear about your experience at Elevate CrossFit Gym. We look forward to helping you achieve even greater fitness goals!","reply_language":"en","reply_posted_at_unix_micros":1784117798000000,"reply_updated_at_unix_micros":1784117798000000,"published_at":"2026-07-15T04:31:23.39637Z"},{"Name":"Mageshwaran S","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWwnE8751DGi_r2cbuO6_xuFD-d69dUut3zgCPP08xaGNU0HKyDVw=s120-c-rp-mo-br100","Rating":5,"Description":"Joined this CrossFit gym at 79 kg and now I’m down to 72 kg — such a super experience! 💪\nThe master is extremely friendly, calm, and very supportive. He guides you completely and makes sure you do every workout the right way.\nTruly a great place to train, stay motivated, and see real results. Highly recommended! 🔥","Images":null,"When":"9 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT210NGRYVkZNRU16WVVsR2JsZDNTSE42WlZkelNIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109287997770630871498/reviews?hl=en-GB","posted_at_unix_micros":1766117967462934,"updated_at_unix_micros":1766117967462934,"language":"en","translated_lang":"","text_original":"Joined this CrossFit gym at 79 kg and now I’m down to 72 kg — such a super experience! 💪\nThe master is extremely friendly, calm, and very supportive. He guides you completely and makes sure you do every workout the right way.\nTruly a great place to train, stay motivated, and see real results. Highly recommended! 🔥","text_translated":"","published_at":"2025-12-19T04:19:27.462934Z"},{"Name":"Saranya P","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVPxWk3LnGPwjkHJRvzlcgZwPyyZI9oQZNfL4CAYxUNRdo-Rsc=s120-c-rp-mo-br100","Rating":5,"Description":"Joining Elevate CrossFit Gym has been one of the best decisions for my fitness journey. The workouts are perfectly balanced — intense, varied, and thoughtfully designed.\nA special mention to Vinay, who is incredibly encouraging, patient, and always makes sure I train safely while pushing my limits. The gym has such a friendly and motivating vibe that I actually look forward to workouts now!\nTruly a place that helps you grow stronger — both physically and mentally.","Images":null,"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25OMFJHVk1XREZWZEZwVlIzSjBlRjgxY0doWE1uYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113828276568916138785/reviews?hl=en-GB","posted_at_unix_micros":1761581266231309,"updated_at_unix_micros":1761581266231309,"language":"en","translated_lang":"","text_original":"Joining Elevate CrossFit Gym has been one of the best decisions for my fitness journey. The workouts are perfectly balanced — intense, varied, and thoughtfully designed.\nA special mention to Vinay, who is incredibly encouraging, patient, and always makes sure I train safely while pushing my limits. The gym has such a friendly and motivating vibe that I actually look forward to workouts now!\nTruly a place that helps you grow stronger — both physically and mentally.","text_translated":"","reply_text_original":"Thank you so much for your positive review! We're so glad you had a great experience and look forward to welcoming you back soon.\" 💪🔥","reply_language":"en","reply_posted_at_unix_micros":1761656348000000,"reply_updated_at_unix_micros":1761656348000000,"published_at":"2025-10-27T16:07:46.231309Z"}]</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP88" t="inlineStr"/>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AU88" t="inlineStr"/>
+      <c r="AV88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>43</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Devils+Circuiit/data=!4m7!3m6!1s0x3a5267293bea5d13:0x503d4fc2376da871!8m2!3d13.0446267!4d80.2222535!16s%2Fg%2F11yrv2mhy1!19sChIJE13qOylnUjoRcahtN8JPPVA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Devils Circuiit</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2/11, Hastagiri Street, Samiyar Madam, Kodambakkam, Chennai, Tamil Nadu 600033</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["7–11:30 am","5–9 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>084380 12377</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>26VC+VW Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>20</v>
+      </c>
+      <c r="O89" t="n">
+        <v>5</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":20}</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>13.044627</v>
+      </c>
+      <c r="R89" t="n">
+        <v>80.22225299999999</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>5781865192185768049</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcckecPsJJig01jNWnFhoHnnnbIyPHUtDA3zigTqax7HtWuiTEggE1iP_7ywDmPvYzetroIu3US99mmGAVc3BW7udDjI2brXBX4dFAeHye8QVdzCNoSp7AzVtjCcEQL8da2KPdNof0NSs80=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>0x3a5267293bea5d13:0x503d4fc2376da871</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>ChIJE13qOylnUjoRcahtN8JPPVA</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>{"id":"112356954625815857993","name":"Devils Circuiit (Owner)","link":"https://www.google.com/maps/contrib/112356954625815857993"}</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>{"borough":"Samiyar Madam, Kodambakkam","street":"Devils Circuiit, 2/11, Hastagiri Street","city":"Chennai","postal_code":"600033","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true},{"name":"Wheelchair-accessible toilet","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>[{"Name":"balaji 27","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJPBYuH1C-5p8ZqIWeenx7oCJeCpP0oM3mKLRAqrb6U-GT7xeo=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Ajay and Muthu are excellent trainers. They guide you through every exercise with proper form and positioning, paying attention to every single movement. As a newcomer, you don't have to worry because they are patient, supportive, and always ready to help. This isn't just a gym—it's like a fitness family. The atmosphere is welcoming, motivating, and perfect for anyone starting their fitness journey. Highly recommended!","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tWemEyaDRiblZRVnpab1NWazNiRTFyWmtwbVNVRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109401216159189580626/reviews?hl=en-GB","posted_at_unix_micros":1782918770986410,"updated_at_unix_micros":1782918770986410,"language":"en","translated_lang":"","text_original":"Ajay and Muthu are excellent trainers. They guide you through every exercise with proper form and positioning, paying attention to every single movement. As a newcomer, you don't have to worry because they are patient, supportive, and always ready to help. This isn't just a gym—it's like a fitness family. The atmosphere is welcoming, motivating, and perfect for anyone starting their fitness journey. Highly recommended!","text_translated":"","reply_text_original":"Thank you ❤️","reply_language":"en","reply_posted_at_unix_micros":1782919616000000,"reply_updated_at_unix_micros":1782919616000000,"published_at":"2026-07-01T15:12:50.98641Z"},{"Name":"Bavadharini Komagan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVuXseycPdh8uE266pofmF9XiN1OvjCeocuwqxdoekwOiq6_yXK=s120-c-rp-mo-br100","Rating":5,"Description":"Fabulous environment to workout!! Ajay bro is very enthusiastic and full of energy.. keep doing great and I strongly recommend to join over here to shape you up like what you need 💪🏻\nSpecialized on: Strength training, Cross fit","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25kdll6ZEpXamN0VjBsaGMySnRiM0pwWDBwdWExRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109348072607021837978/reviews?hl=en-GB","posted_at_unix_micros":1770119487322000,"updated_at_unix_micros":1770119487322000,"language":"en","translated_lang":"","text_original":"Fabulous environment to workout!! Ajay bro is very enthusiastic and full of energy.. keep doing great and I strongly recommend to join over here to shape you up like what you need 💪🏻\nSpecialized on: Strength training, Cross fit","text_translated":"","published_at":"2026-02-03T11:51:27.322Z"},{"Name":"Mohideen Mohideen","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjV-1_gjX8Pk2Xfcjt52gnvlgtEwBwFu-4uwVH_Xb1SIILwxXg=s120-c-rp-mo-br100","Rating":5,"Description":"One of the best functional training gyms in West Mambalam, Chennai. Professional trainers, well-planned workouts, and a great training environment. Highly recommended for anyone looking to improve fitness, strength, and endurance","Images":null,"When":"10 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21WSlJuaG5ja2xxVjJ4WFUxTnJZMDVDUjI5SVltYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117138828625386790746/reviews?hl=en-GB","posted_at_unix_micros":1765366165849634,"updated_at_unix_micros":1765366165849634,"language":"en","translated_lang":"","text_original":"One of the best functional training gyms in West Mambalam, Chennai. Professional trainers, well-planned workouts, and a great training environment. Highly recommended for anyone looking to improve fitness, strength, and endurance","text_translated":"","published_at":"2025-12-10T11:29:25.849634Z"},{"Name":"deepa aru","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJsWtCew9ruPcVbUjjg7sQwlEJ2d4hE56Xg4FTyCFEVIpCPqtg=s120-c-rp-mo-br100","Rating":5,"Description":"This gym has a good atmosphere, the trainer is very helpful and explains everything clearly whenever we ask, and the price is affordable.","Images":null,"When":"6 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25keVQwRlFNR2REUjJoYVdVNVVURW80V1dsSVlYYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/111001223184892413975/reviews?hl=en-GB","posted_at_unix_micros":1775301863545724,"updated_at_unix_micros":1775301863545724,"language":"en","translated_lang":"","text_original":"This gym has a good atmosphere, the trainer is very helpful and explains everything clearly whenever we ask, and the price is affordable.","text_translated":"","published_at":"2026-04-04T11:24:23.545724Z"},{"Name":"bhuvana s","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLfKeLhrd21dNu9OIPT3ORBEUJCCjeE1hDHB29gQ4OrQM85Nw=s120-c-rp-mo-br100","Rating":5,"Description":"Experience and Masterpiece of trainer very good person worthy for health fitness right choice for devils circuit gym","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2psc1NUTklOamhHTTFaQ1FtNVRjVGhEWW1KRU1HYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109516675414858668202/reviews?hl=en-GB","posted_at_unix_micros":1770119562080405,"updated_at_unix_micros":1770119562080405,"language":"en","translated_lang":"","text_original":"Experience and Masterpiece of trainer very good person worthy for health fitness right choice for devils circuit gym","text_translated":"","published_at":"2026-02-03T11:52:42.080405Z"}]</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP89" t="inlineStr"/>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AU89" t="inlineStr"/>
+      <c r="AV89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>43</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>468f567c-f71c-4eee-841d-828ec746034d</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Glow+fitness/data=!4m7!3m6!1s0x3a5265002ba8dfed:0xfea41fd50d35afe9!8m2!3d13.1211183!4d80.2356849!16s%2Fg%2F11myy2mntb!19sChIJ7d-oKwBlUjoR6a81DdUfpP4</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Glow fitness</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>15 pallavan lane, Thiruvengadam St, anbalagan nagar, Chennai, Tamil Nadu 600011</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>{"Friday":["6 am–9 pm"],"Monday":["6 am–9 pm"],"Saturday":["6 am–9 pm"],"Sunday":["6 am–9 pm"],"Thursday":["6 am–9 pm"],"Tuesday":["6 am–9 pm"],"Wednesday":["6 am–9 pm"]}</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>070941 31131</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>46CP+C7 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>19</v>
+      </c>
+      <c r="O90" t="n">
+        <v>5</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":19}</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>13.121118</v>
+      </c>
+      <c r="R90" t="n">
+        <v>80.235685</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>18348825781724360681</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcAHFbr88jfZGMy9G0W302odnnuQVJpsqXJhrQDGe1whkTASDHQqTMCskNT2cMMZThxWuRsEmYk1rj9Zxp3tLtd6eceyctPdMVkgLN3qd8y32K-Cr9k0TDwU2Yv1jaPKoJlAZAZFWjcU7I5=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>0x3a5265002ba8dfed:0xfea41fd50d35afe9</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>ChIJ7d-oKwBlUjoR6a81DdUfpP4</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>{"id":"102526044459901434734","name":"Glow fitness (Owner)","link":"https://www.google.com/maps/contrib/102526044459901434734"}</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>{"borough":"anbalagan nagar, Kennedy Square, Perambur","street":"15 pallavan lane, Thiruvengadam St","city":"Chennai","postal_code":"600011","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>[{"Name":"Abitha V","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUe-kzKMB9Ev2mvoHODnQVqtxbgOoqO1MQ1sCBu5f5RLSxordc=s120-c-rp-mo-br100","Rating":5,"Description":"I had a great experience at Glow Fitness. The gym trainers are very friendly, supportive, and professional. My trainer, Shilpa Akka, is especially kind and encouraging. She patiently corrects every posture during workouts, stays with us while we exercise, and makes sure we perform each movement safely and correctly. The trainers genuinely care about every member.\n\nThe gym has plenty of equipment, a clean and hygienic environment, and a beautiful gold-themed ambience that I really like. It feels very safe and comfortable for women. I highly recommend Glow Fitness to anyone looking for a supportive and motivating place to achieve their fitness goals","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLe9LsV73RU74XQ5ajQf1BQpdU8o81YoQKEux764IC9G8hy6LWeDRVi-9EfArtSEJu21rijc81hC1zcvWY7sYHCjPE1S2cs0q-XcpNOQiNKHfaKxbcC3eTIF_cpVYIx6RwDU4Rktt0sPF5v0=k-no"],"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25wWmQxYzRXVFpuZDB4allrSXhhRXBRZW1aM1dsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/117666834254032300797/reviews?hl=en-GB","posted_at_unix_micros":1783683118228928,"updated_at_unix_micros":1783683118228928,"language":"en","translated_lang":"","text_original":"I had a great experience at Glow Fitness. The gym trainers are very friendly, supportive, and professional. My trainer, Shilpa Akka, is especially kind and encouraging. She patiently corrects every posture during workouts, stays with us while we exercise, and makes sure we perform each movement safely and correctly. The trainers genuinely care about every member.\n\nThe gym has plenty of equipment, a clean and hygienic environment, and a beautiful gold-themed ambience that I really like. It feels very safe and comfortable for women. I highly recommend Glow Fitness to anyone looking for a supportive and motivating place to achieve their fitness goals","text_translated":"","published_at":"2026-07-10T11:31:58.228928Z"},{"Name":"Pooja Pooja","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJL4ysDxikfVKMQH0ZrpEZth5MWvP3DLq-wkCVxlrJvRXvT6Q=s120-c-rp-mo-br100","Rating":5,"Description":"My experience at GLOW Fitness has been excellent. I joined a month ago .The ambience is attractive, energetic, and motivating. The training is outstanding, and the trainers always give personal attention to every member.\nWhenever I perform an exercise with the wrong posture, they immediately correct me and guide me properly. This has helped me improve my technique, stamina, and overall fitness.\nI can see visible results in my body. My muscles are becoming more toned, my strength has increased significantly, and my stamina has improved a lot. Before joining GLOW Fitness, I didn't know how to do a proper push-up, but now I can perform push-ups correctly with the trainers' guidance.\nI could only hold a plank for 30 seconds before, but now I can do a plank for 2½ minutes. I have also noticed a significant reduction in belly fat since joining GLOW Fitness.\nAnother great advantage is the comfortable training environment. The air conditioning is always maintained properly, unlike many other gyms.\nThe one-on-one training, continuous posture corrections, motivation, and result-oriented workouts make GLOW Fitness truly special.\nThank you, GLOW Fitness, for helping me become stronger, healthier, and more confident!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLddM93qUG3mQb4gkyAM6SdDPR2jlNvBqUEhW-2bvNfCzn-YNU_q4vospG2r_VXBfdWGubJujbuQu1F0qCLbOxL_1sfXvJxgRteL0Q3x14iCVO3BgMArat8DhLdQK7HUcdMZAXl9E8NESflu=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLee2H7QLHDXMuapyVY0i0eea910wl9qJFYbhjFmkoN2Dy0bquGyDlD3j2unGcZfNy456fEhASJLux9DlIY_bT3N40BQPImrvH2X1OYy_r1_9TAER9XRRop3RkBS2kB7yCl8wpz01Nj1tqs=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLdZBKipSKFwM7hhcjhN3_fT_MDcL3UTP6L2KaCpOc8rTsqHjqULAujwKbASOy5WN_QnDsGh8MmLVOLhsDInaSdiwW1jFIMDEbIevFBXqPC0mQVjsIm3YecsblCuv98ZFC2HYnb9ZRM9l_Wl=k-no"],"When":"Edited 3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21WcmJYRklXamR6UWxKd2VqVkZUVmRGU0RORU0wRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110988662804630140372/reviews?hl=en-GB","posted_at_unix_micros":1781523915861625,"updated_at_unix_micros":1781611677420622,"language":"en","translated_lang":"","text_original":"My experience at GLOW Fitness has been excellent. I joined a month ago .The ambience is attractive, energetic, and motivating. The training is outstanding, and the trainers always give personal attention to every member.\nWhenever I perform an exercise with the wrong posture, they immediately correct me and guide me properly. This has helped me improve my technique, stamina, and overall fitness.\nI can see visible results in my body. My muscles are becoming more toned, my strength has increased significantly, and my stamina has improved a lot. Before joining GLOW Fitness, I didn't know how to do a proper push-up, but now I can perform push-ups correctly with the trainers' guidance.\nI could only hold a plank for 30 seconds before, but now I can do a plank for 2½ minutes. I have also noticed a significant reduction in belly fat since joining GLOW Fitness.\nAnother great advantage is the comfortable training environment. The air conditioning is always maintained properly, unlike many other gyms.\nThe one-on-one training, continuous posture corrections, motivation, and result-oriented workouts make GLOW Fitness truly special.\nThank you, GLOW Fitness, for helping me become stronger, healthier, and more confident!","text_translated":"","published_at":"2026-06-15T11:45:15.861625Z"},{"Name":"Jo Krish","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjW12-X9iSuM8f-Qw1m6noITa4xKQ5ZGg7lNUL-CPe9rKxV7hHwM=s120-c-rp-mo-br100","Rating":5,"Description":"I had no prior knowledge about the gym, but after joining, I gained a very good experience. I can visibly see changes in my body — better toning, weight loss, and increased strength.\n\nThe ambience is very friendly and comfortable. The training is excellent and personalized according to our body type and needs. I can clearly see good results through this training.\n\nOverall, it has been an excellent experience. I highly recommend everyone to join Glow Fitness.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcTGuMkX99ONYg2yth04dV3QXvnd9HBzJUqoRmsM_cLI9PVIETiSNaUN8FBuP8Ew0ORRCHjgJ0PiBE2h4Vz0piF1FDRmvYTHDF6zNyVvW5JNtQkUwn3LpuAqoCvVBSG7iPO7OGNeitXBx-q=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfYXfw24WdirhDi3DpFA8UDq69fcdPVm_YDwGxS3vJizHgaejecFAeeadtkiU4mUu3DTbQtydp4JcecAHTTKE3Wl7MsBgdECQyVOtdXGxFYVCUeA_7cs-TtBzFLUAv5hGYR3zEtISiKkxeq=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25wcFh6VXhValYwVDNGa1ExVmFTVWwxZW5Kc2NFRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105807345531800510433/reviews?hl=en-GB","posted_at_unix_micros":1778677616997806,"updated_at_unix_micros":1778677616997806,"language":"en","translated_lang":"","text_original":"I had no prior knowledge about the gym, but after joining, I gained a very good experience. I can visibly see changes in my body — better toning, weight loss, and increased strength.\n\nThe ambience is very friendly and comfortable. The training is excellent and personalized according to our body type and needs. I can clearly see good results through this training.\n\nOverall, it has been an excellent experience. I highly recommend everyone to join Glow Fitness.","text_translated":"","published_at":"2026-05-13T13:06:56.997806Z"},{"Name":"Geetha Prabha","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKSkXy5JJJjIwns8RDXkWaZtQ-eKpfkHBxorF-4mXsT73Y4GQ=s120-c-rp-mo-br100","Rating":5,"Description":"I’m Geetha. I underwent brain surgery, and one of my friends suggested Glow Fitness Women's Gym. I joined to regain my strength and improve my overall health.\n\nFrom day one, the trainers understood my health condition and designed my workouts with great care and patience. The gym atmosphere is always positive, motivating, clean, and well maintained.\nBefore joining, I had many fears and lacked confidence. Today, I feel much stronger, more confident, and I've started taking better care of myself.\n\nA special thanks to Shilpa Mam 🥰 She patiently trains me without ever getting frustrated, even when I ask the same questions repeatedly. She always encourages me to overcome my fears.\n\nEarlier, I was afraid to walk on the treadmill without holding the handles. Now I can walk confidently. While cycling, I used to lean to one side, but now I can ride with much better balance and stability. My overall balance has improved, and I'm also able to perform ab exercises like leg raises and waves much better than before.\n\nI'm truly grateful to Glow Fitness Women's Gym for helping me become stronger, healthier, and more confident. I wholeheartedly recommend every woman to join Glow Fitness 🫶🏻","Images":null,"When":"2 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xCeGJWSk5kVUYyTVd3MGFGWlBSbGRzUmpWUmMxRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113036569506572947200/reviews?hl=en-GB","posted_at_unix_micros":1785847949098399,"updated_at_unix_micros":1785847949098399,"language":"en","translated_lang":"","text_original":"I’m Geetha. I underwent brain surgery, and one of my friends suggested Glow Fitness Women's Gym. I joined to regain my strength and improve my overall health.\n\nFrom day one, the trainers understood my health condition and designed my workouts with great care and patience. The gym atmosphere is always positive, motivating, clean, and well maintained.\nBefore joining, I had many fears and lacked confidence. Today, I feel much stronger, more confident, and I've started taking better care of myself.\n\nA special thanks to Shilpa Mam 🥰 She patiently trains me without ever getting frustrated, even when I ask the same questions repeatedly. She always encourages me to overcome my fears.\n\nEarlier, I was afraid to walk on the treadmill without holding the handles. Now I can walk confidently. While cycling, I used to lean to one side, but now I can ride with much better balance and stability. My overall balance has improved, and I'm also able to perform ab exercises like leg raises and waves much better than before.\n\nI'm truly grateful to Glow Fitness Women's Gym for helping me become stronger, healthier, and more confident. I wholeheartedly recommend every woman to join Glow Fitness 🫶🏻","text_translated":"","published_at":"2026-08-04T12:52:29.098399Z"},{"Name":"BHUVANA BABU","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocL7L13zF3aIEyKAb8sBa_Z_XBhADem2ULb9OtkVWOmYIjhOsQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Ambience is very pleasant and neatly maintained. Trainers are top notch in training and guiding us according to our lifestyles which motivates us and makes us to come regularly automatically","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLesJ02JBkKJX1tf52JHO48e5nsOkKOf2AfXFORSlF-f-D49i_cFSA_DElemYWQJN4OECTEk-Gdk1BqmlvTpRMreLLcS1ctRWaVYkUdAkr1JS_L2e0q-ihAnfhi0OYysqVM4CBHGbC2obFQt=k-no"],"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25CTWMyWlJOVk14VFZoNlZqQXRNRzlITmxkSVUwRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106886832494259856135/reviews?hl=en-GB","posted_at_unix_micros":1777517363767112,"updated_at_unix_micros":1777517363767112,"language":"en","translated_lang":"","text_original":"Ambience is very pleasant and neatly maintained. Trainers are top notch in training and guiding us according to our lifestyles which motivates us and makes us to come regularly automatically","text_translated":"","published_at":"2026-04-30T02:49:23.767112Z"}]</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP90" t="inlineStr"/>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AU90" t="inlineStr"/>
+      <c r="AV90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>43</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3443ec21-504f-4465-9e7d-5470d56e0e66</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hi-Transform+Fitness+Hub/data=!4m7!3m6!1s0x3a526744f821ee3b:0xf33c16b1233ce645!8m2!3d13.0599075!4d80.2486418!16s%2Fg%2F11kqrkvxx8!19sChIJO-4h-ERnUjoRReY8I7EWPPM</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Hi-Transform Fitness Hub</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>BS3, Hi-Transform Fitness Hub, Khader Nawaz Khan Rd, Srirampuram, Thousand Lights West, Nungambakkam, Chennai, Poombukar Nagar, Tamil Nadu 600006</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>097104 44023</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>365X+XF Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>15</v>
+      </c>
+      <c r="O91" t="n">
+        <v>5</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>{"1":0,"2":0,"3":0,"4":0,"5":15}</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>13.059907</v>
+      </c>
+      <c r="R91" t="n">
+        <v>80.248642</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>17526908799875343941</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeARak_nS98NZCfwDcCziHM6QEdQzTcNv2M7LA8qLZ2vGGlZ6Ldap-tY74m5ys3WfJdLXSeofuj3O3WPZD1-0EaXEnFDz2i_cBtoKr23UkstwopNFeD3JC-4q2Eym_6eUj9VU6H=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>0x3a526744f821ee3b:0xf33c16b1233ce645</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>ChIJO-4h-ERnUjoRReY8I7EWPPM</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>{"id":"115333053229440904958","name":"Hi-Transform Fitness Hub (Owner)","link":"https://www.google.com/maps/contrib/115333053229440904958"}</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>{"borough":"Srirampuram, Thousand Lights West, Nungambakkam","street":"BS3, Khader Nawaz Khan Rd","city":"Chennai, Poombukar Nagar","postal_code":"600006","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>[{"Name":"Anandha Raman C K","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVj7Jnrv0E69sqHRFP1ChDjKszFN7EVJXE2zv2SgGWbTF5b7_PrhQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Excellent gym services! The trainers are knowledgeable and friendly, always willing to assist with workout plans and equipment usage. The facilities are clean and well-maintained, providing a comfortable environment for workouts.\n\nOverall, highly recommend this gym for anyone looking to achieve their fitness goals!","Images":null,"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURENE1pUkhnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100345608910315439317/reviews?hl=en-GB","posted_at_unix_micros":1712226208791621,"updated_at_unix_micros":1712226208791621,"language":"en","translated_lang":"","text_original":"Excellent gym services! The trainers are knowledgeable and friendly, always willing to assist with workout plans and equipment usage. The facilities are clean and well-maintained, providing a comfortable environment for workouts.\n\nOverall, highly recommend this gym for anyone looking to achieve their fitness goals!","text_translated":"","published_at":"2024-04-04T10:23:28.791621Z"},{"Name":"Harini Nagaraj","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWv324VtNgOEPNMo9yi5OHANNta6kBLBK1HAUc3Tou8nOmSCZkFRw=s120-c-rp-mo-br100","Rating":5,"Description":"One of the best fitness hub... Very clean and tidy. The ambience is fantastic, creating a motivating atmosphere... The trainers are knowledgeable, supportive, and really push you to achieve your goals..","Images":null,"When":"2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNEbjVqdnhnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114999781390372691935/reviews?hl=en-GB","posted_at_unix_micros":1712163854972601,"updated_at_unix_micros":1712163854972601,"language":"en","translated_lang":"","text_original":"One of the best fitness hub... Very clean and tidy. The ambience is fantastic, creating a motivating atmosphere... The trainers are knowledgeable, supportive, and really push you to achieve your goals..","text_translated":"","published_at":"2024-04-03T17:04:14.972601Z"},{"Name":"keerthana m","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVdqQyquerlcGPJvydut8BxeXwKZ7-YV0Nr-LL3_8K7oNIphYNX=s120-c-rp-mo-br100","Rating":5,"Description":"Such a good ambiance. Would recommand this for all the gym people out there :)","Images":null,"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNENzhUZWZREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100427627776591631453/reviews?hl=en-GB","posted_at_unix_micros":1712156634656231,"updated_at_unix_micros":1712156634656231,"language":"en","translated_lang":"","text_original":"Such a good ambiance. Would recommand this for all the gym people out there :)","text_translated":"","published_at":"2024-04-03T15:03:54.656231Z"},{"Name":"Eas Eas","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVUeMoIXX8fmOIPsly_kzpKAC6VlIjlnmiLNbsbqOd70AI67sRU=s120-c-rp-mo-br100","Rating":5,"Description":"Amazing place to get in shape with lot of Motivation. Best peoples! best master! nd best equipments!✨","Images":null,"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNEbjVpblJ3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114251386676370250801/reviews?hl=en-GB","posted_at_unix_micros":1712163850918108,"updated_at_unix_micros":1712163850918108,"language":"en","translated_lang":"","text_original":"Amazing place to get in shape with lot of Motivation. Best peoples! best master! nd best equipments!✨","text_translated":"","published_at":"2024-04-03T17:04:10.918108Z"},{"Name":"sushil kumar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX0xDWRTatNOL3aCHLNE6nt91_yjgJWWIlnlRUwpwihF5yWq69C=s120-c-rp-mo-br100","Rating":5,"Description":"Good gym and nice place to start 👍🏻","Images":null,"When":"2 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNEbjgyQTJnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106534381434344538172/reviews?hl=en-GB","posted_at_unix_micros":1712168703710883,"updated_at_unix_micros":1712168703710883,"language":"en","translated_lang":"","text_original":"Good gym and nice place to start 👍🏻","text_translated":"","published_at":"2024-04-03T18:25:03.710883Z"}]</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP91" t="inlineStr"/>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:42:46.404576+00:00</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AU91" t="inlineStr"/>
+      <c r="AV91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>43</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1bddc0b1-4038-4472-9efc-8686effcc817</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Storm+Fitness+Gym/data=!4m7!3m6!1s0x3a5263531bc45e05:0x7b8b95582fac7568!8m2!3d13.1117807!4d80.1845566!16s%2Fg%2F11f637tcb7!19sChIJBV7EG1NjUjoRaHWsL1iVi3s</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Storm Fitness Gym</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1155, Venkatraman Nagar, Korattur, Chennai, Tamil Nadu 600050</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–9:30 pm"],"Monday":["5:30 am–9:30 pm"],"Saturday":["5:30 am–9:30 pm"],"Sunday":["7 am–12 pm"],"Thursday":["5:30 am–9:30 pm"],"Tuesday":["5:30 am–9:30 pm"],"Wednesday":["5:30 am–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>097898 59855</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>456M+PR Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>191</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":1,"3":1,"4":8,"5":180}</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>13.111781</v>
+      </c>
+      <c r="R92" t="n">
+        <v>80.184557</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>8902373294417409384</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf6vkoAsMVgqkYWAuubxYc4W0eiQWCELNpr1atRfvyG1efjK-voH4droP5iR2APN91m9gpDoBNDiBKQCypz3Qe4gW4vTWVC7bqX5k4vLPQAt8jA7lHwHsh7hAu3nQBYi8JGtO3L=w408-h493-k-no</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>0x3a5263531bc45e05:0x7b8b95582fac7568</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>ChIJBV7EG1NjUjoRaHWsL1iVi3s</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>{"id":"103158862071532141443","name":"Storm Fitness Gym (Owner)","link":"https://www.google.com/maps/contrib/103158862071532141443"}</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>{"borough":"Venkatraman Nagar, Korattur","street":"1155","city":"Chennai","postal_code":"600050","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>[{"Name":"BAVANI ANNADURAI","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXHEg9elbx6Olk6qFYJ7JkdJbu6QtalNpuQEdHSMR81-gAveJlR=s120-c-rp-mo-br100","Rating":5,"Description":"Excellent gym trainer  Mr. Karthick is very knowledgeable, motivating, and supportive. He is highly professional and always encourages me to achieve my fitness goals. Highly recommended","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2paT05WOUZibWR3U1RGWWRIQnNZV1ZtVjB4RE5YYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110639174492021389063/reviews?hl=en-GB","posted_at_unix_micros":1783575600145198,"updated_at_unix_micros":1783575896562114,"language":"en","translated_lang":"","text_original":"Excellent gym trainer  Mr. Karthick is very knowledgeable, motivating, and supportive. He is highly professional and always encourages me to achieve my fitness goals. Highly recommended","text_translated":"","published_at":"2026-07-09T05:40:00.145198Z"},{"Name":"Udaiyya Shankar","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjX4KyOrhjtagzvwfWJow4xtDFuh6QHm_7KuMuOnvz2zovOTKGBn=s120-c-rp-mo-br100","Rating":5,"Description":"Nice gym with friendly trainer.","Images":null,"When":"3 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tkNWJHVnNOa2Q1ZHpWd2RXVlJlSEIxTVRCQk5FRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/116904729733062200139/reviews?hl=en-GB","posted_at_unix_micros":1783575785735223,"updated_at_unix_micros":1783575785735223,"language":"en","translated_lang":"","text_original":"Nice gym with friendly trainer.","text_translated":"","published_at":"2026-07-09T05:43:05.735223Z"},{"Name":"MAX 2 YT","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLYMNXtxwsxJSJx_ZiTXO7i_9iYGCMmID-63jnTNmSEI9WHjiZr=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Great gym and friendly trainers ... Pretty much empty throughout the whole day ... Best choice for a peaceful gym","Images":null,"When":"8 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tSV2IweFpWM0JtYkhkeFVWTmFSalp5WWxsTE0xRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109958817867500027095/reviews?hl=en-GB","posted_at_unix_micros":1768996690954940,"updated_at_unix_micros":1768996690954940,"language":"en","translated_lang":"","text_original":"Great gym and friendly trainers ... Pretty much empty throughout the whole day ... Best choice for a peaceful gym","text_translated":"","published_at":"2026-01-21T11:58:10.95494Z"},{"Name":"Priyanka Yadav","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJ7jjaUvhWSP3qu32pJypq0GeXLoHybfXfFaHdKUTwPuMui-zY=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"It is the best ever secured gym i have seen. Yogi master is ultimately good, he is the only reason why i supposed to be training here. I noticed within a short span of my training is he upgrades himself everyday that can be evident in the fitness equipments#moldyourfuture. This is absolutely right place to change your profile❤😍😍","Images":null,"When":"7 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSURVMmIyc2dBRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113052338561246957393/reviews?hl=en-GB","posted_at_unix_micros":1567012628654882,"updated_at_unix_micros":1567012628654882,"language":"en","translated_lang":"","text_original":"It is the best ever secured gym i have seen. Yogi master is ultimately good, he is the only reason why i supposed to be training here. I noticed within a short span of my training is he upgrades himself everyday that can be evident in the fitness equipments#moldyourfuture. This is absolutely right place to change your profile❤😍😍","text_translated":"","published_at":"2019-08-28T17:17:08.654882Z"},{"Name":"Nandhini Sampath","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUcxnwpfHELSJIl_80-bn-0umsnYeP8qx18WMeJSuo8zbyR7cTu0w=s120-c-rp-mo-br100","Rating":5,"Description":"Awesome gym!!! Mr.Yogesh is one of the Best trainers you can see. Highly motivating and one of the best gym in and around korattur. The place gives you a positive atmosphere and vibes are really great for working out 👍.","Images":null,"When":"7 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNZbFB2aldREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118028260674021472518/reviews?hl=en-GB","posted_at_unix_micros":1554350998850615,"updated_at_unix_micros":1554352799438542,"language":"en","translated_lang":"","text_original":"Awesome gym!!! Mr.Yogesh is one of the Best trainers you can see. Highly motivating and one of the best gym in and around korattur. The place gives you a positive atmosphere and vibes are really great for working out 👍.","text_translated":"","published_at":"2019-04-04T04:09:58.850615Z"}]</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr"/>
+      <c r="AO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AS92" t="n">
+        <v>919789859855</v>
+      </c>
+      <c r="AT92" t="inlineStr">
+        <is>
+          <t>Korattur</t>
+        </is>
+      </c>
+      <c r="AU92" t="n">
+        <v>600050</v>
+      </c>
+      <c r="AV92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>43</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1bddc0b1-4038-4472-9efc-8686effcc817</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Kisi+fitness+club/data=!4m7!3m6!1s0x3a52617633f37db1:0x350c53c53c6f6d56!8m2!3d13.0409128!4d80.1733347!16s%2Fg%2F11swzmf6f0!19sChIJsX3zM3ZhUjoRVm1vPMVTDDU</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Kisi fitness club</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>No.67, 2nd floor, Arcot Rd, Valasaravakkam, Chennai, Tamil Nadu 600087</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10:30 pm"],"Monday":["5:30 am–10:30 pm"],"Saturday":["5:30 am–10:30 pm"],"Sunday":["6 am–1 pm"],"Thursday":["5:30 am–10:30 pm"],"Tuesday":["5:30 am–10:30 pm"],"Wednesday":["5:30 am–10:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>079049 60039</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>25RF+98 Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>157</v>
+      </c>
+      <c r="O93" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>{"1":4,"2":1,"3":0,"4":0,"5":152}</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>13.040913</v>
+      </c>
+      <c r="R93" t="n">
+        <v>80.17333499999999</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3822522290318306646</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdtYQfi2u3iJ4ymlLc5K3ngULVHnFy8K8vqAov4m2cGd01hm-LGJjBhCMb2NRrph4DcUaGDdWsVjUgDO_fVy2hjtAL5bSYPKozIdpkrJ-ze3L47xd-dR6VzF2FeBsdC8g7ZZkIemQ=w408-h306-k-no</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>0x3a52617633f37db1:0x350c53c53c6f6d56</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>ChIJsX3zM3ZhUjoRVm1vPMVTDDU</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>{"id":"105771117492860439949","name":"Kisi fitness club (Owner)","link":"https://www.google.com/maps/contrib/105771117492860439949"}</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>{"borough":"Subramanya Swamy Nagar, Valasaravakkam","street":"No.67, 2nd floor, Arcot Rd","city":"Chennai","postal_code":"600087","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>[{"Name":"Advocate Faize","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVMKTgH0lguEEndFTzZNzQXCEzvbbJ8rN1cw8lDjmCXj8YPPxnd=s120-c-rp-mo-br100","Rating":5,"Description":"The gym atmosphere is too good, definitely recommended for beginners as the trainers here are super patient and helpful, especially Mr.kishore,mani,prabha,manoj, who’s been mentoring me and I definitely recommend you to start ur classes with him, really friendly and super fun to workout with! The equipments are top class and up to mark! Don’t hesitate to join!🔥","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25CelZqTmplVmg2ZEROR2VrbDNNSEpDYlRNMk1IYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/102123226767408573827/reviews?hl=en-GB","posted_at_unix_micros":1780586981709381,"updated_at_unix_micros":1780586981709381,"language":"en","translated_lang":"","text_original":"The gym atmosphere is too good, definitely recommended for beginners as the trainers here are super patient and helpful, especially Mr.kishore,mani,prabha,manoj, who’s been mentoring me and I definitely recommend you to start ur classes with him, really friendly and super fun to workout with! The equipments are top class and up to mark! Don’t hesitate to join!🔥","text_translated":"","published_at":"2026-06-04T15:29:41.709381Z"},{"Name":"maha Lakshmi","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKAaGcNEwk2UpZ2dHW4HWeuHuOy0Tn95lkaH2GltxrLgZPMjg=s120-c-rp-mo-br100","Rating":5,"Description":"Joining this gym was one of my best decisions. The trainers helped me stay consistent and improve my strength and fitness. The gym is clean, spacious, and has all the equipment needed for effective workouts","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21GWk1IZHRhWGRVZEhGa1N6UnJUVkZMWkU1a2VrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/100323943436328327852/reviews?hl=en-GB","posted_at_unix_micros":1780647050964413,"updated_at_unix_micros":1780647050964413,"language":"en","translated_lang":"","text_original":"Joining this gym was one of my best decisions. The trainers helped me stay consistent and improve my strength and fitness. The gym is clean, spacious, and has all the equipment needed for effective workouts","text_translated":"","published_at":"2026-06-05T08:10:50.964413Z"},{"Name":"premnath palanichamy","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjUYTpJTHM3e3QikP53IYKuV4UmGU4FBoL3G0S7QTRHubgXOIII=s120-c-rp-mo-br100","Rating":5,"Description":"My Honest review, The Best Gym in Valasaravakkam, friendly gym coaches, also budget friendly while comparing with other gym around Valasaravakkam.  I also want to mention one thing, with our request master extend evening closing time upto 10:30 pm.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21wUE4xcGpaa2hSYWxGeFgyVXpXa296UVZCRGEyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106765503876541425282/reviews?hl=en-GB","posted_at_unix_micros":1780505807720748,"updated_at_unix_micros":1780506020453421,"language":"en","translated_lang":"","text_original":"My Honest review, The Best Gym in Valasaravakkam, friendly gym coaches, also budget friendly while comparing with other gym around Valasaravakkam.  I also want to mention one thing, with our request master extend evening closing time upto 10:30 pm.","text_translated":"","published_at":"2026-06-03T16:56:47.720748Z"},{"Name":"Supriya Sundaresan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjU6qnhe3BQ5rGEWVO4JuI4_TxDCh12GtKyTmbZbNj74WVW4uCUG=s120-c-rp-mo-br100","Rating":5,"Description":"Best gym in valasaravakkam.Very safe and secured gym place for women.Friendly and approachable coaches. Very affordable price in chennai.Neat and well maintained.","Images":null,"When":"4 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pRdFJrWXhkbkp0U200eGIxbEZVRUo1TnpaMFNtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114735474598476648280/reviews?hl=en-GB","posted_at_unix_micros":1781074099261140,"updated_at_unix_micros":1781074099261140,"language":"en","translated_lang":"","text_original":"Best gym in valasaravakkam.Very safe and secured gym place for women.Friendly and approachable coaches. Very affordable price in chennai.Neat and well maintained.","text_translated":"","published_at":"2026-06-10T06:48:19.26114Z"},{"Name":"Vijay Kumar","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJL3jEvD8AAKUnk0Q_JiCC1mXmDYn-uaSd33kKy2gHdKwqOnA=s120-c-rp-mo-br100","Rating":5,"Description":"Hi, my name is Vijay. At first, I joined the gym just to stay fit and maintain a normal physique. Later, after seeing the people working out there, I developed an interest in bodybuilding. Then I approached Kishore Master, and he put in a lot of effort to train me. The trainers there are also very friendly and supportive.","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2xReU1tbG9iR1ZsVFhZeVdWUjNTbk5hV2pNdGVrRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/113288310302167358228/reviews?hl=en-GB","posted_at_unix_micros":1771512963369615,"updated_at_unix_micros":1771512963369615,"language":"en","translated_lang":"","text_original":"Hi, my name is Vijay. At first, I joined the gym just to stay fit and maintain a normal physique. Later, after seeing the people working out there, I developed an interest in bodybuilding. Then I approached Kishore Master, and he put in a lot of effort to train me. The trainers there are also very friendly and supportive.","text_translated":"","published_at":"2026-02-19T14:56:03.369615Z"}]</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr"/>
+      <c r="AO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AS93" t="n">
+        <v>917904960039</v>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>Valasaravakkam</t>
+        </is>
+      </c>
+      <c r="AU93" t="n">
+        <v>600087</v>
+      </c>
+      <c r="AV93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>43</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1bddc0b1-4038-4472-9efc-8686effcc817</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Planet+1+Fitness+Studio+-+Kolathur/data=!4m7!3m6!1s0x3a52650023955ff9:0xeb5a7b5b1ab4cd55!8m2!3d13.1188799!4d80.206542!16s%2Fg%2F11lv_0szgs!19sChIJ-V-VIwBlUjoRVc20Glt7Wus</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Planet 1 Fitness Studio - Kolathur</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1st Main Rd, Srinivasa Nagar, Kolathur, Chennai, Tamil Nadu 600099</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["7 am–12 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>099529 29079</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>4694+HJ Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>125</v>
+      </c>
+      <c r="O94" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>{"1":2,"2":1,"3":0,"4":9,"5":113}</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>13.11888</v>
+      </c>
+      <c r="R94" t="n">
+        <v>80.206542</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>16959002978037321045</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc_RZ021uqdyE8ahR3zvNfU0cu9_Pi13sND7dY3ykeqlgrkLpoQLEG6zOAauMQfLkYZcjct-a4Js2GQd1lyIwJNPH4ujAiniWJt6RAAKfOcEgFlt91efjGu6Fg0IKb8Xg4Fld2X=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>0x3a52650023955ff9:0xeb5a7b5b1ab4cd55</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>ChIJ-V-VIwBlUjoRVc20Glt7Wus</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>{"id":"110419623807338967215","name":"Planet 1 Fitness Studio - Kolathur (Owner)","link":"https://www.google.com/maps/contrib/110419623807338967215"}</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>{"borough":"Srinivasa Nagar, Kolathur","street":"1st Main Rd","city":"Chennai","postal_code":"600099","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Assistive hearing loop","enabled":false},{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false},{"name":"Wheelchair-accessible seating","enabled":false},{"name":"Wheelchair-accessible toilet","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>[{"Name":"Chandru G","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJZuTTLYnihwcb_xduo-UBXhmshoK5s5CzNFdh1RKrFmAe_0Q=s120-c-rp-mo-br100","Rating":5,"Description":"This is an excellent gym and it’s fully equipped and functional. It’s not crowded as it has three floors.Trainer , Siddique Master and Praveen bro has been an amazing trainer and guides throughout my fitness journey. Both are always encouraging, patient, and genuinely helping me to reach my goals. His workouts are well planned and they always makes sure I’m doing each exercise with the right form. I’ve seen real progress in my strength and confidence since training with him.Thank you for the encouragement which boosted me to come each day.\nI Highly recommend this gym💪🏻","Images":null,"When":"Edited 5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pkVVdGQnVUeTFsUlZSSVUyNXBUV0ZvTld0NlZsRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106435395989372195111/reviews?hl=en-GB","posted_at_unix_micros":1769517499371398,"updated_at_unix_micros":1777380719682697,"language":"en","translated_lang":"","text_original":"This is an excellent gym and it’s fully equipped and functional. It’s not crowded as it has three floors.Trainer , Siddique Master and Praveen bro has been an amazing trainer and guides throughout my fitness journey. Both are always encouraging, patient, and genuinely helping me to reach my goals. His workouts are well planned and they always makes sure I’m doing each exercise with the right form. I’ve seen real progress in my strength and confidence since training with him.Thank you for the encouragement which boosted me to come each day.\nI Highly recommend this gym💪🏻","text_translated":"","published_at":"2026-01-27T12:38:19.371398Z"},{"Name":"Sheikh Shagufta Naz","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJOBMHtM3sMM3amXQHpc89xSMij9-ModMCusvag24vo7rTjVg=s120-c-rp-mo-br100","Rating":5,"Description":"A well-equipped gym with a great ambiance and highly skilled trainers. The entire team is approachable, patient, and always ready to guide and motivate. They also offer helpful dietary advice and structured weekly workout plans. As a beginner, I’ve already started noticing a real difference—not just in my strength, but in my confidence as well. Special thanks to Siddiq, Shahrukh, and Abishek for their constant support throughout my fitness journey. Truly a 10/10 place!","Images":null,"When":"Edited 5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21wM2J6WnJOMlZFZG0xcFoweHdhRVZ5U1d0V05uYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/101946614060666397569/reviews?hl=en-GB","posted_at_unix_micros":1777381569550916,"updated_at_unix_micros":1777630092357144,"language":"en","translated_lang":"","text_original":"A well-equipped gym with a great ambiance and highly skilled trainers. The entire team is approachable, patient, and always ready to guide and motivate. They also offer helpful dietary advice and structured weekly workout plans. As a beginner, I’ve already started noticing a real difference—not just in my strength, but in my confidence as well. Special thanks to Siddiq, Shahrukh, and Abishek for their constant support throughout my fitness journey. Truly a 10/10 place!","text_translated":"","published_at":"2026-04-28T13:06:09.550916Z"},{"Name":"Godwin Abisher","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocLM_-oTkqbe4nv1jCq_vTGeb3rbgpw1igwgcY2ohGkS-R0ztQ=s120-c-rp-mo-br100","Rating":5,"Description":"Great experience at Planet One Gym! 💪\nThe environment is clean, motivating, and perfect for staying consistent.\nSpecial shoutout to trainers Praveen and Abishek — both are highly supportive, knowledgeable, and always push you to give your best while keeping workouts safe and effective.\nHighly recommend this place for anyone serious about fitness!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pKaWJtNVVjME5WTkZobVZWSmhjM1ZMZUhoYVVtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106381222734480380411/reviews?hl=en-GB","posted_at_unix_micros":1777386354568413,"updated_at_unix_micros":1777386354568413,"language":"en","translated_lang":"","text_original":"Great experience at Planet One Gym! 💪\nThe environment is clean, motivating, and perfect for staying consistent.\nSpecial shoutout to trainers Praveen and Abishek — both are highly supportive, knowledgeable, and always push you to give your best while keeping workouts safe and effective.\nHighly recommend this place for anyone serious about fitness!","text_translated":"","published_at":"2026-04-28T14:25:54.568413Z"},{"Name":"Ganesan B","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVy8U5bAvnXEJleU9-7HCnDdEwZUyRwEH9V9QIR3nn91cEYU5E4=s120-c-rp-mo-br100","Rating":5,"Description":"I had a great experience at Planet Gym!\nThe environment is clean, energetic, and well-maintained.\nSpecial thanks to Abishek and Praveen for their constant support and expert guidance.\nTheir motivation really helped me improve my fitness and stay consistent.\nHighly recommend Planet Gym for anyone serious about training!","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2kxR1FqYzFlV2xzUzFkVU5tWktObXBvZUhSeGNtYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/118077067939238713184/reviews?hl=en-GB","posted_at_unix_micros":1777386146798957,"updated_at_unix_micros":1777386146798957,"language":"en","translated_lang":"","text_original":"I had a great experience at Planet Gym!\nThe environment is clean, energetic, and well-maintained.\nSpecial thanks to Abishek and Praveen for their constant support and expert guidance.\nTheir motivation really helped me improve my fitness and stay consistent.\nHighly recommend Planet Gym for anyone serious about training!","text_translated":"","published_at":"2026-04-28T14:22:26.798957Z"},{"Name":"Gopikrish T","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocKLkCSlfxoysfNjeA7xsD_fIGzfIwo7soPowKDEY_58zeJNYexN=s120-c-rp-mo-br100","Rating":5,"Description":"This an excellent gym with fully equipped facilities and a great ambience.\nThe 2 trainers especially Abishek and Praveen are excellently guiding all the beginners and professionals throughout their whole package. Such a great gym","Images":null,"When":"5 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2tOR2FHWk1ZbVExWmtsWE0wbzVPV2h1Y1ZONFkyYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/103391545174598542422/reviews?hl=en-GB","posted_at_unix_micros":1777384946080145,"updated_at_unix_micros":1777384946080145,"language":"en","translated_lang":"","text_original":"This an excellent gym with fully equipped facilities and a great ambience.\nThe 2 trainers especially Abishek and Praveen are excellently guiding all the beginners and professionals throughout their whole package. Such a great gym","text_translated":"","published_at":"2026-04-28T14:02:26.080145Z"}]</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr"/>
+      <c r="AN94" t="inlineStr"/>
+      <c r="AO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AS94" t="n">
+        <v>919952929079</v>
+      </c>
+      <c r="AT94" t="inlineStr">
+        <is>
+          <t>Kolathur</t>
+        </is>
+      </c>
+      <c r="AU94" t="n">
+        <v>600099</v>
+      </c>
+      <c r="AV94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>43</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1bddc0b1-4038-4472-9efc-8686effcc817</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Stay+Strong+Fitness+Factory+Gym/data=!4m7!3m6!1s0x3a526741810fc307:0xf7eb3058987dcde2!8m2!3d12.9947036!4d80.2044794!16s%2Fg%2F11mvxvj22x!19sChIJB8MPgUFnUjoR4s19mFgw6_c</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Stay Strong Fitness Factory Gym</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1st Floor, Stay Strong Fitness Factory Gym, TVS TYRE Building, Thiruvalluvar Main Rd, opp. Jana Small Financial Bank, Balakrishnapuram, Adambakkam, Chennai, Tamil Nadu 600088</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30–11 am","5–9:30 pm"],"Monday":["5:30–11 am","5–9:30 pm"],"Saturday":["5:30–11 am","5–9:30 pm"],"Sunday":["Closed"],"Thursday":["5:30–11 am","5–9:30 pm"],"Tuesday":["5:30–11 am","5–9:30 pm"],"Wednesday":["5:30–11 am","5–9:30 pm"]}</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>098846 48936</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>X6V3+VQ Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>45</v>
+      </c>
+      <c r="O95" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>{"1":2,"2":0,"3":0,"4":0,"5":43}</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>12.994704</v>
+      </c>
+      <c r="R95" t="n">
+        <v>80.20447900000001</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>17864425503968841186</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfY0KJhClq3pGVU4SV-byrgNloMQ5bCRPTSyzIhHt1ov0V9c7Zt72E9Zo4pIkDPeuoSY-39NSC90sApx6IEPJhlifOYlCixOdEYWfGr7ML-SgKSJ3sSY4s5F0jW2NFEoksciA_I=w408-h333-k-no</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>0x3a526741810fc307:0xf7eb3058987dcde2</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>ChIJB8MPgUFnUjoR4s19mFgw6_c</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>{"id":"105894983275248912804","name":"Stay Strong Fitness Factory Gym (Owner)","link":"https://www.google.com/maps/contrib/105894983275248912804"}</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>{"borough":"Balakrishnapuram, Adambakkam","street":"1st Floor, TVS TYRE Building, Thiruvalluvar Main Rd, opp. Jana Small Financial Bank","city":"Chennai","postal_code":"600088","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":false},{"name":"Wheelchair-accessible entrance","enabled":false}]}]</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>[{"Name":"vincy priya","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXzUN1iGScq22rJjDEOIEbgdYpTPqXv56HCrOGUikpR3YWr0Ix3lQ=s120-c-rp-mo-br100","Rating":1,"Description":"This is not even a gym,this is a place gym master can chat with anyone,no punctuality,no guidance and no respect at all.Very worst place to go.place is filled with equipments.People who have exercise experience can use it well without depending anyone.But newcomers who don't know anything about exercise please dont go to this gym and lost your money.Total waste of time and money.","Images":null,"When":"2 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURuczZ5UUlREAE","source":"Google","rating_scale":5,"rating_float":1,"author_url":"https://www.google.com/maps/contrib/106897014671745533958/reviews?hl=en-GB","posted_at_unix_micros":1728500686282353,"updated_at_unix_micros":1728500795196853,"language":"en","translated_lang":"","text_original":"This is not even a gym,this is a place gym master can chat with anyone,no punctuality,no guidance and no respect at all.Very worst place to go.place is filled with equipments.People who have exercise experience can use it well without depending anyone.But newcomers who don't know anything about exercise please dont go to this gym and lost your money.Total waste of time and money.","text_translated":"","published_at":"2024-10-09T19:04:46.282353Z"},{"Name":"Akshay R","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXpoM7d3_8hTZXT1Y2GVWoS6wDgkQ-MLbVUNiBqQRHthPGbWBnYvQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"Very nice trainer who pays attention to everyone. Very nice and friendly environment maintained to work out. The gym is very well \u0026 newly equiped and trainer makes us work hard. No limited or fixed timings. Price is very low compared to other gyms. Recommended.","Images":null,"When":"5 years ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUNpcDllZW1RRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109592827210043809798/reviews?hl=en-GB","posted_at_unix_micros":1605636867532355,"updated_at_unix_micros":1605636867532355,"language":"en","translated_lang":"","text_original":"Very nice trainer who pays attention to everyone. Very nice and friendly environment maintained to work out. The gym is very well \u0026 newly equiped and trainer makes us work hard. No limited or fixed timings. Price is very low compared to other gyms. Recommended.","text_translated":"","published_at":"2020-11-17T18:14:27.532355Z"},{"Name":"Ibhirim Sk","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJF0nv5uRvn16CFtx0qqSvHfSVcLx5pOnZD4rOeFnvg0FoK=s120-c-rp-mo-br100","Rating":5,"Description":"Good professional trainer , owner is friendly , nice motivation gym , worth reasonable price, am very happy to very satisfied , easily weight loss \u0026 very happy goooooood","Images":null,"When":"4 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSUNXeE1iN0pnEAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/109581885463081770199/reviews?hl=en-GB","posted_at_unix_micros":1645171430302034,"updated_at_unix_micros":1645171430302034,"language":"en","translated_lang":"","text_original":"Good professional trainer , owner is friendly , nice motivation gym , worth reasonable price, am very happy to very satisfied , easily weight loss \u0026 very happy goooooood","text_translated":"","published_at":"2022-02-18T08:03:50.302034Z"},{"Name":"sanjay kanth","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocK0FO_gCECFrUWfHPjuc2mIIENGBhBuyvVZQTnlqfdD4VEqfFg=s120-c-rp-mo-br100","Rating":5,"Description":"Very good trainer makes us work hard and help us achieve in our fitness goals. Best Gym for Reasonable price.","Images":null,"When":"5 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURpdVBHTkZREAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/114813024119859403114/reviews?hl=en-GB","posted_at_unix_micros":1606232889294316,"updated_at_unix_micros":1606232889294316,"language":"en","translated_lang":"","text_original":"Very good trainer makes us work hard and help us achieve in our fitness goals. Best Gym for Reasonable price.","text_translated":"","published_at":"2020-11-24T15:48:09.294316Z"},{"Name":"Harishankar G","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXKKAN2BfgmFWFe3IVfAzfI_rCUO1NXqGiH_SOCOtU6EMi45pXV=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"The gym has good equipments for both weight lifting and cross fit training. Zumba also available. Vino master is kind and well trainer.","Images":null,"When":"5 years ago","review_id":"ChZDSUhNMG9nS0VJQ0FnSURTODVTVUR3EAE","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/104509698944752416737/reviews?hl=en-GB","posted_at_unix_micros":1610118429104021,"updated_at_unix_micros":1610118527573740,"language":"en","translated_lang":"","text_original":"The gym has good equipments for both weight lifting and cross fit training. Zumba also available. Vino master is kind and well trainer.","text_translated":"","published_at":"2021-01-08T15:07:09.104021Z"}]</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr"/>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>(1★) vincy priya: This is not even a gym,this is a place gym master can chat with anyone,no punctuality,no guidance and no respect at all.Very worst place to go.place is filled with equipments.People who have exercise experience can use it well without depending anyone.But newcomers who don't know anything about exercise please dont go to this gym and lost your money.Total waste of time and money.</t>
+        </is>
+      </c>
+      <c r="AO95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AS95" t="n">
+        <v>919884648936</v>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
+          <t>Adambakkam</t>
+        </is>
+      </c>
+      <c r="AU95" t="n">
+        <v>600088</v>
+      </c>
+      <c r="AV95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>43</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CrossFit Gym</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Chennai, Tamil Nadu, India</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1bddc0b1-4038-4472-9efc-8686effcc817</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Planet+1+Fitness+Studio+-+Korattur/data=!4m7!3m6!1s0x3a52633c3f3112fb:0x2514d2f1af897240!8m2!3d13.1030305!4d80.1795003!16s%2Fg%2F11y3yt9cd7!19sChIJ-xIxPzxjUjoRQHKJr_HSFCU</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Planet 1 Fitness Studio - Korattur</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Railway Station Rd, Periyar Nagar, Tillai Nagar, Korattur, Chennai, Tamil Nadu 600050</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>{"Friday":["5:30 am–10 pm"],"Monday":["5:30 am–10 pm"],"Saturday":["5:30 am–10 pm"],"Sunday":["7 am–12 pm"],"Thursday":["5:30 am–10 pm"],"Tuesday":["5:30 am–10 pm"],"Wednesday":["5:30 am–10 pm"]}</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>098401 67169</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>453H+6R Chennai, Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>43</v>
+      </c>
+      <c r="O96" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>{"1":1,"2":1,"3":0,"4":2,"5":39}</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>13.10303</v>
+      </c>
+      <c r="R96" t="n">
+        <v>80.1795</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>2671992414411518528</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf3GD2vPlCnmO99eSeRoExiriLZxr7Q8AzEqY8QFdWrQ8NIieQD5TBQFIZ4APhV2rt7P8lZ1ZRNGR-KHghyjMLsneSt-WYOuhh92dIUugr-w6J1OGstQB042osdJJfuI6iuvZ_7=w408-h544-k-no</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Asia/Calcutta</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>0x3a52633c3f3112fb:0x2514d2f1af897240</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>ChIJ-xIxPzxjUjoRQHKJr_HSFCU</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>{"link":"","source":""}</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>{"id":"105960387242898327128","name":"Planet 1 Fitness Studio - Korattur (Owner)","link":"https://www.google.com/maps/contrib/105960387242898327128"}</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>{"borough":"Periyar Nagar, Tillai Nagar, Korattur","street":"Railway Station Rd","city":"Chennai","postal_code":"600050","state":"Tamil Nadu","country":"IN"}</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>[{"id":"accessibility","name":"Accessibility","options":[{"name":"Wheelchair-accessible car park","enabled":true},{"name":"Wheelchair-accessible entrance","enabled":true},{"name":"Wheelchair-accessible seating","enabled":true}]}]</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>[{"Name":"Khum ACHARYA","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjVCshp8pPiJ65WVZVqBcVcZjfHzm3lhM6y3vppiX8_sxN5oIpSbIQ=s120-c-rp-mo-ba12-br100","Rating":5,"Description":"This is Mr. Khum.\n\nMr. Akash- The coach-The best Lad.\nOwners- Great character. Additionally- If you have any issues with any machines or anything immediately they take care of those things. That's the thing I honestly love about.\n\nI can't say enough good things about Planet1 Fitness Studio! After trying several gyms in the area, I can confidently say this is hands down the best one around.\n\nFrom the moment I walked in, I knew this place was different. The equipment is top-notch and always well-maintained, the facility is impeccably clean, and the atmosphere is incredibly motivating. The staff goes above and beyond to make everyone feel welcome, whether you're a fitness newbie or a seasoned athlete.\n\nWhat really sets Planet1 apart is the sense of community here. It's not just a gym – it's a place where people genuinely support each other's fitness journeys. The trainers are knowledgeable, approachable, and truly invested in helping members reach their goals.\n\nThe variety of classes, convenient hours, and overall vibe make it so easy to stay consistent with my workouts. I actually look forward to coming here, which says everything!\n\nIf you're looking for a gym in this area, look no further. Planet1 Fitness Studio is absolutely perfect, and I couldn't be happier with my decision to join. Highly recommend to anyone serious about their fitness!","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLcAxrIIH4UBvOi2jLjh4hyPP2B23fK5JwwnC9Dr511n-2W5yhiqn5TKiLUFx_YXURX65Q5bJbThckdn5KPkNcuexoZ8W3Q9QUPaPxk6f-AVPq2Qo_OEb5Vr93n7mlu7032Bvki8pzmjsMtW=k-no"],"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT2pKa1VFazVOMVI0WkhocFZWUndXa3M1Tld0aGRIYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106618447841918082707/reviews?hl=en-GB","posted_at_unix_micros":1761722214108357,"updated_at_unix_micros":1761722214108357,"language":"en","translated_lang":"","text_original":"This is Mr. Khum.\n\nMr. Akash- The coach-The best Lad.\nOwners- Great character. Additionally- If you have any issues with any machines or anything immediately they take care of those things. That's the thing I honestly love about.\n\nI can't say enough good things about Planet1 Fitness Studio! After trying several gyms in the area, I can confidently say this is hands down the best one around.\n\nFrom the moment I walked in, I knew this place was different. The equipment is top-notch and always well-maintained, the facility is impeccably clean, and the atmosphere is incredibly motivating. The staff goes above and beyond to make everyone feel welcome, whether you're a fitness newbie or a seasoned athlete.\n\nWhat really sets Planet1 apart is the sense of community here. It's not just a gym – it's a place where people genuinely support each other's fitness journeys. The trainers are knowledgeable, approachable, and truly invested in helping members reach their goals.\n\nThe variety of classes, convenient hours, and overall vibe make it so easy to stay consistent with my workouts. I actually look forward to coming here, which says everything!\n\nIf you're looking for a gym in this area, look no further. Planet1 Fitness Studio is absolutely perfect, and I couldn't be happier with my decision to join. Highly recommend to anyone serious about their fitness!","text_translated":"","reply_text_original":"Hello Khum,\nThank you for sharing your valuable feedback. Your support means a lot to us!","reply_language":"en","reply_posted_at_unix_micros":1762870894000000,"reply_updated_at_unix_micros":1762870894000000,"published_at":"2025-10-29T07:16:54.108357Z"},{"Name":"Arun Karthik V","ProfilePicture":"https://lh3.googleusercontent.com/a/ACg8ocJofPhtQ-p8_Tt60q2M36z6YjfcQObChPtX7kASFj5J0qFLgIE=s120-c-rp-mo-br100","Rating":5,"Description":"Hi, I am Arun Karthik. Planet 1 Fitness Studio is a perfect  gym in Korattur to establish your fitness journey.  The gym me in developing and maintaining my fitness. Guided by the trainer of the gym Mr. Akash Guru, who is a perfect motivator and spokesperson of positivity. I had subscribed for personal training by Mr. Akash Guru, who would help, motivate and guide me personally, towards the goal. He's friendly and jovial to approach if you have any queries regarding workouts.\n\nThe gym conducts HIIT workouts, every Saturday to enhance core stability. These sessions are perfect to be part of social activity and meet new people , form new community. This place motivated me to add working out as a habit for me.","Images":["https://lh3.googleusercontent.com/grass-cs/AABkmLca86GrYGpPDCk8PSGbSxkG0Rw55a703Gp3pBNLCMvCY70cCR1leF3YolZ7YL_y_ELMPicH4yz75Vhc8R8Dwr0T9fdeJ1PVukv43hTZ4P9g6PRpC6y_NIPNeI-LfpMA1HuqLTei=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLfXzBpmaW8rGd6l6jzaZoPHk7aK1HxmqZOri8WUV-6b7plDJtRbH5fXNvkhmK6ZEW0_VE0x9LoowFnzpRQchlfKXr6I8bnhnM9OFp3-501fu3c8tcHVmGq5-AkGSCkU8u0JlwvT=k-no","https://lh3.googleusercontent.com/grass-cs/AABkmLf3GD2vPlCnmO99eSeRoExiriLZxr7Q8AzEqY8QFdWrQ8NIieQD5TBQFIZ4APhV2rt7P8lZ1ZRNGR-KHghyjMLsneSt-WYOuhh92dIUugr-w6J1OGstQB042osdJJfuI6iuvZ_7=k-no"],"When":"a year ago","review_id":"ChdDSUhNMG9nS0VJQ0FnSUR2d0lhT3dnRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/105528943176372245345/reviews?hl=en-GB","posted_at_unix_micros":1734355305941533,"updated_at_unix_micros":1734359800705590,"language":"en","translated_lang":"","text_original":"Hi, I am Arun Karthik. Planet 1 Fitness Studio is a perfect  gym in Korattur to establish your fitness journey.  The gym me in developing and maintaining my fitness. Guided by the trainer of the gym Mr. Akash Guru, who is a perfect motivator and spokesperson of positivity. I had subscribed for personal training by Mr. Akash Guru, who would help, motivate and guide me personally, towards the goal. He's friendly and jovial to approach if you have any queries regarding workouts.\n\nThe gym conducts HIIT workouts, every Saturday to enhance core stability. These sessions are perfect to be part of social activity and meet new people , form new community. This place motivated me to add working out as a habit for me.","text_translated":"","reply_text_original":"Thankyou so much for your valuable feedback !","reply_language":"en","reply_posted_at_unix_micros":1734770559000000,"reply_updated_at_unix_micros":1734770559000000,"published_at":"2024-12-16T13:21:45.941533Z"},{"Name":"Ramakrishnan Madhavan","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjXWIhFbNhB1YMvxFKPiDmg7c74UnQJFV5k6hqdDbqdBfpfE8g6i=s120-c-rp-mo-ba12-br100","Rating":2,"Description":"This message is for the owner of this gym -planet1, korattur branch....\n\nI currently am a customer with planet1 and we are a 3 member team who renewed our packages for the 2nd time.\n\nI would urgently want to bring to your attention that there are few equipments which have not been functioning for the last few weeks/ days and irrespective of raising the issues with the employees present in the gym (morning amd evening shift)...the only standard response I/we get is, \" the service team is busy, and we have informed them to attend the issues \"...however, till this date the issues are not addressed- should it \u003e 20 days to solve issues or is the team waiting for any emergencies to happen!!!\n\nPls note gym needs equipments which are working in good condition,  anytime. We as members pay for using the gym and this kind of equipment quality is not acceptable.\n\nAm putting this as review therefore you personally look into the problem and find a quick solution...if you might want to know what are the regular recurring issues am sure you can check out my contact info from your team.\n\nI definitely dont wish to highlight the issues here, as i like the gyms ambience. I scouted for the existing 4 gyms in the same road and joined planet1.\n\nLooking forward to hear from you soon.( i dont wish to talk to your employees becz they seem to be helpless...\n\nThanks for taking your time to read 🙏","Images":null,"When":"7 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT213NU5reEtVR3hoYW5aWVRreHFRbE5tZFZWQ2NIYxAB","source":"Google","rating_scale":5,"rating_float":2,"author_url":"https://www.google.com/maps/contrib/101832242288871985561/reviews?hl=en-GB","posted_at_unix_micros":1772008055240140,"updated_at_unix_micros":1772008055240140,"language":"en","translated_lang":"","text_original":"This message is for the owner of this gym -planet1, korattur branch....\n\nI currently am a customer with planet1 and we are a 3 member team who renewed our packages for the 2nd time.\n\nI would urgently want to bring to your attention that there are few equipments which have not been functioning for the last few weeks/ days and irrespective of raising the issues with the employees present in the gym (morning amd evening shift)...the only standard response I/we get is, \" the service team is busy, and we have informed them to attend the issues \"...however, till this date the issues are not addressed- should it \u003e 20 days to solve issues or is the team waiting for any emergencies to happen!!!\n\nPls note gym needs equipments which are working in good condition,  anytime. We as members pay for using the gym and this kind of equipment quality is not acceptable.\n\nAm putting this as review therefore you personally look into the problem and find a quick solution...if you might want to know what are the regular recurring issues am sure you can check out my contact info from your team.\n\nI definitely dont wish to highlight the issues here, as i like the gyms ambience. I scouted for the existing 4 gyms in the same road and joined planet1.\n\nLooking forward to hear from you soon.( i dont wish to talk to your employees becz they seem to be helpless...\n\nThanks for taking your time to read 🙏","text_translated":"","reply_text_original":"Hi Ramakrishnan Madhavan. Thank you for sharing your feedback. As discussed, we believe all your queries have been addressed to your satisfaction. We strive to ensure everyone has the most comfortable experience in our spaces and that we meet their expectations.","reply_language":"en","reply_posted_at_unix_micros":1772254584000000,"reply_updated_at_unix_micros":1772254584000000,"published_at":"2026-02-25T08:27:35.24014Z"},{"Name":"Bhu Vnesh","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWSPHd4xnmGd56mJFyTcm1EXCNcHqjkHYiGOKyZGp-3VIAqXuw=s120-c-rp-mo-br100","Rating":5,"Description":"Highly recommended! The gym is well-maintained with quality equipment, great ambiance, and a motivating environment. What truly sets it apart is the coach ( Akashguru and Rajesh) — knowledgeable, supportive, and genuinely invested in every member’s progress. The personalized guidance, especially on form, workouts, and nutrition, has made a huge difference in my fitness journey. If you're looking for real results with a coach who truly cares, this is the place to be!","Images":null,"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT25NdE5rdEtaRlpxVlhweFYwTTNibDlPT1dOdmJWRRAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/106751489585394803141/reviews?hl=en-GB","posted_at_unix_micros":1761670079070753,"updated_at_unix_micros":1761670079070753,"language":"en","translated_lang":"","text_original":"Highly recommended! The gym is well-maintained with quality equipment, great ambiance, and a motivating environment. What truly sets it apart is the coach ( Akashguru and Rajesh) — knowledgeable, supportive, and genuinely invested in every member’s progress. The personalized guidance, especially on form, workouts, and nutrition, has made a huge difference in my fitness journey. If you're looking for real results with a coach who truly cares, this is the place to be!","text_translated":"","reply_text_original":"Hello, Thank you for sharing your valuable feedback. We are so glad to hear you had a great experience! ","reply_language":"en","reply_posted_at_unix_micros":1762871417000000,"reply_updated_at_unix_micros":1762871417000000,"published_at":"2025-10-28T16:47:59.070753Z"},{"Name":"NARESH KUMAR","ProfilePicture":"https://lh3.googleusercontent.com/a-/ALV-UjWwvbScjF7jV4rudYbzOKtgZnsWSotNX6OlhzThhfndF8nua2zE=s120-c-rp-mo-br100","Rating":5,"Description":"I usually do not give reviews to anything online,but to this fitness centre I definitely will share my genuine reviews. The best gym in affordable price in Chennai. Brilliant ambience, supportive coaches (Brothers), high quality equipments, cleanliness , High quality music system... The best place to transform yourself... Highly recommended. Thankyou planet 1 fitness team.","Images":null,"When":"11 months ago","review_id":"Ci9DQUlRQUNvZENodHljRjlvT21aUFZqUkRXWEEzUkZCSk5YZEdWSFF6YXpReVNHYxAB","source":"Google","rating_scale":5,"rating_float":5,"author_url":"https://www.google.com/maps/contrib/110072903066357272995/reviews?hl=en-GB","posted_at_unix_micros":1762317033656136,"updated_at_unix_micros":1762317033656136,"language":"en","translated_lang":"","text_original":"I usually do not give reviews to anything online,but to this fitness centre I definitely will share my genuine reviews. The best gym in affordable price in Chennai. Brilliant ambience, supportive coaches (Brothers), high quality equipments, cleanliness , High quality music system... The best place to transform yourself... Highly recommended. Thankyou planet 1 fitness team.","text_translated":"","reply_text_original":"Hello Naresh Kumar, \nThank you so much for your valuable feedback. We’re glad to hear you had a great experience! ","reply_language":"en","reply_posted_at_unix_micros":1762871251000000,"reply_updated_at_unix_micros":1762871251000000,"published_at":"2025-11-05T04:30:33.656136Z"}]</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr"/>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>(2★) Ramakrishnan Madhavan: This message is for the owner of this gym -planet1, korattur branch.... I currently am a customer with planet1 and we are a 3 member team who renewed our packages for the 2nd time. I would urgently want to bring to your attention that there are few equipments which have not been functioning for the last few weeks/ days and irrespective of raising the issues with the employees present in the gym (morning amd evening shift)...the only standard response I/we get is, " the service team is busy, and we have informed them to attend the issues "...however, till this date the issues are not addressed- should it &gt; 20 days to solve issues or is the team waiting for any emergencies to happen!!! Pls note gym needs equipments which are working in good condition, anytime. We as members pay for using the gym and this kind of equipment quality is not acceptable. Am putting this as review therefore you personally look into the problem and find a quick solution...if you might want to know what are the regular recurring issues am sure you can check out my contact info from your team. I definitely dont wish to highlight the issues here, as i like the gyms ambience. I scouted for the existing 4 gyms in the same road and joined planet1. Looking forward to hear from you soon.( i dont wish to talk to your employees becz they seem to be helpless... Thanks for taking your time to read 🙏</t>
+        </is>
+      </c>
+      <c r="AO96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:19:30.684299+00:00</t>
+        </is>
+      </c>
+      <c r="AS96" t="n">
+        <v>919840167169</v>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
+          <t>Korattur</t>
+        </is>
+      </c>
+      <c r="AU96" t="n">
+        <v>600050</v>
+      </c>
+      <c r="AV96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR47"/>
+  <autoFilter ref="A1:AW96"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
@@ -8950,6 +17869,55 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
